--- a/ilya_feed.xlsx
+++ b/ilya_feed.xlsx
@@ -33655,6 +33655,16 @@
         <v>7945</v>
       </c>
       <c r="AH2" s="7"/>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Настройка цены целевого действия</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Настройка цены целевого действия: ручная</t>
+        </is>
+      </c>
     </row>
     <row r="3" s="6" customFormat="true" ht="45" customHeight="true">
       <c r="A3" s="6" t="s">
@@ -33741,6 +33751,16 @@
       <c r="AB3" s="6" t="s">
         <v>43</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Необязательный</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
@@ -33827,6 +33847,16 @@
       <c r="AB4" t="s">
         <v>44</v>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Одно значение из выпадающего списка в ячейке</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Подробнее о параметре</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -33925,6 +33955,99 @@
       <c r="AG5" t="s">
         <v>8061</v>
       </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
@@ -34023,6 +34146,99 @@
       <c r="AG6" t="s">
         <v>8061</v>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
@@ -34121,6 +34337,99 @@
       <c r="AG7" t="s">
         <v>8061</v>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -34222,6 +34531,99 @@
       <c r="AG8" t="s">
         <v>8061</v>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -34320,6 +34722,99 @@
       <c r="AG9" t="s">
         <v>8061</v>
       </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -34418,6 +34913,99 @@
       <c r="AG10" t="s">
         <v>8061</v>
       </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
@@ -34516,6 +35104,99 @@
       <c r="AG11" t="s">
         <v>8061</v>
       </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -34614,6 +35295,99 @@
       <c r="AG12" t="s">
         <v>8061</v>
       </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
@@ -34712,6 +35486,99 @@
       <c r="AG13" t="s">
         <v>8061</v>
       </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
@@ -34810,6 +35677,99 @@
       <c r="AG14" t="s">
         <v>8061</v>
       </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
@@ -34908,6 +35868,99 @@
       <c r="AG15" t="s">
         <v>8061</v>
       </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -35006,6 +36059,99 @@
       <c r="AG16" t="s">
         <v>8061</v>
       </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -35104,6 +36250,99 @@
       <c r="AG17" t="s">
         <v>8061</v>
       </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -35202,6 +36441,99 @@
       <c r="AG18" t="s">
         <v>8061</v>
       </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
@@ -35300,6 +36632,99 @@
       <c r="AG19" t="s">
         <v>8061</v>
       </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
@@ -35398,6 +36823,99 @@
       <c r="AG20" t="s">
         <v>8061</v>
       </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
@@ -35496,6 +37014,99 @@
       <c r="AG21" t="s">
         <v>8061</v>
       </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
@@ -35594,6 +37205,99 @@
       <c r="AG22" t="s">
         <v>8061</v>
       </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
@@ -35692,6 +37396,99 @@
       <c r="AG23" t="s">
         <v>8061</v>
       </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
@@ -35789,6 +37586,2449 @@
       </c>
       <c r="AG24" t="s">
         <v>8061</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u0917d_Rolex_Daytona_steel_panda</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/CpZJGH51/d5-Rolex-Daytona-steel-panda-0.jpg | https://i.ibb.co/8ghLBFKr/d5-Rolex-Daytona-steel-panda-1.jpg | https://i.ibb.co/RpLGgmYj/d5-Rolex-Daytona-steel-panda-2.jpg | https://i.ibb.co/gbGw7BbS/d5-Rolex-Daytona-steel-panda-3.jpg | https://i.ibb.co/zTT4GwZT/d5-Rolex-Daytona-steel-panda-4.jpg | https://i.ibb.co/gLGhr13V/d5-Rolex-Daytona-steel-panda-5.jpg</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Rolex Daytona стальной белый мужские</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolex Daytona — сталь, белый циферблат, мужские&lt;br&gt;&lt;br&gt;Белый циферблат с чёрными счётчиками и керамический безель с тахиметром — самая узнаваемая версия хронографа на стальном браслете.&lt;br&gt;&lt;br&gt;• Механизм: механический с автоподзаводом&lt;br&gt;• Корпус: сталь, 40 мм, керамический безель&lt;br&gt;• Циферблат: белый, три чёрных счётчика&lt;br&gt;• Браслет: сталь Oyster&lt;br&gt;• Функции: хронограф, водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы rolex мужские, rolex daytona, хронограф сталь, наручные часы механика&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133000</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolex</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Белый</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Серебряный</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/BrW40lo9nXr5Vg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод | Хронограф | Секундомер</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u0917d_Rolex_GMT_coke</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/v4XxGdfd/d5-Rolex-GMT-coke-0.jpg | https://i.ibb.co/B5xsytrH/d5-Rolex-GMT-coke-1.jpg | https://i.ibb.co/TxhHF15y/d5-Rolex-GMT-coke-2.jpg | https://i.ibb.co/RpQdmZrN/d5-Rolex-GMT-coke-3.jpg | https://i.ibb.co/sp4Y20VW/d5-Rolex-GMT-coke-4.jpg | https://i.ibb.co/Lmn8Xdv/d5-Rolex-GMT-coke-5.jpg</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Rolex GMT-Master II чёрный красный</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolex GMT-Master II — чёрный с красным, мужские&lt;br&gt;&lt;br&gt;Двухцветный безель «кока-кола» и браслет Jubilee: вторая часовая стрелка показывает время другого пояса, безель поворачивается для третьего.&lt;br&gt;&lt;br&gt;• Механизм: механический с автоподзаводом&lt;br&gt;• Корпус: сталь, 40 мм, керамический безель&lt;br&gt;• Циферблат: чёрный, светящиеся метки, окно даты&lt;br&gt;• Браслет: сталь Jubilee&lt;br&gt;• Функции: второй часовой пояс, дата, водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы rolex мужские, rolex gmt master, часы сталь механика, наручные часы с датой&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108000</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolex</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Серебряный</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://yadi.sk/d/E8s7jcqHTP4koA</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод | Календарь</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u0917d_Rolex_Daytona_gold</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/hxx6fwFy/d5-Rolex-Daytona-gold-0.jpg | https://i.ibb.co/r2HsLs2L/d5-Rolex-Daytona-gold-1.jpg | https://i.ibb.co/LdKqgb95/d5-Rolex-Daytona-gold-2.jpg | https://i.ibb.co/q3tGRnzy/d5-Rolex-Daytona-gold-3.jpg | https://i.ibb.co/1G80Mqk4/d5-Rolex-Daytona-gold-4.jpg | https://i.ibb.co/0ydwpmGY/d5-Rolex-Daytona-gold-5.jpg</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Rolex Daytona золото мужские механика</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolex Daytona — жёлтое золото, мужские&lt;br&gt;&lt;br&gt;Корпус и браслет цвета жёлтого золота, тёмный циферблат с золотистыми счётчиками — версия для тех, кому нужна не сталь, а вес и блеск.&lt;br&gt;&lt;br&gt;• Механизм: механический с автоподзаводом&lt;br&gt;• Корпус: цвет жёлтого золота, 40 мм&lt;br&gt;• Циферблат: тёмный, три золотистых счётчика&lt;br&gt;• Браслет: цвет жёлтого золота&lt;br&gt;• Функции: хронограф, водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы rolex мужские, rolex daytona золото, золотые часы мужские, хронограф механика&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108000</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolex</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золотой</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золотой</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/45m68ClCURDbgw</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод | Хронограф | Секундомер</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u0917d_Patek_Nautilus_moonphase</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/qL3ybtsr/d5-Patek-Nautilus-moonphase-0.jpg | https://i.ibb.co/kzJY0Wk/d5-Patek-Nautilus-moonphase-1.jpg | https://i.ibb.co/1N8WDqQ/d5-Patek-Nautilus-moonphase-2.jpg | https://i.ibb.co/B2CPVWFt/d5-Patek-Nautilus-moonphase-3.jpg | https://i.ibb.co/Z1HYPz3H/d5-Patek-Nautilus-moonphase-4.jpg | https://i.ibb.co/84Yfdhbh/d5-Patek-Nautilus-moonphase-5.jpg</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Patek Philippe Nautilus синий мужские</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patek Philippe Nautilus Moonphase — синий, мужские&lt;br&gt;&lt;br&gt;Синий циферблат с горизонтальным тиснением, окно фаз луны и годовой календарь в корпусе-иллюминаторе на интегрированном браслете.&lt;br&gt;&lt;br&gt;• Механизм: механический с автоподзаводом&lt;br&gt;• Корпус: сталь, 40 мм&lt;br&gt;• Циферблат: синий, фазы луны, счётчики календаря&lt;br&gt;• Браслет: сталь, интегрированный&lt;br&gt;• Функции: календарь, фазы луны, водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы patek philippe, patek nautilus, часы сталь механика, наручные часы с календарём&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114000</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patek Philippe</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Синий</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Серебряный</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/32ixogXfFQi8jQ</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод | Календарь</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u0917d_Patek_Cubitus_gold</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/WvZ2DqKn/d5-Patek-Cubitus-gold-0.jpg | https://i.ibb.co/Y7DWZP2b/d5-Patek-Cubitus-gold-1.jpg | https://i.ibb.co/8L7L7Lyy/d5-Patek-Cubitus-gold-2.jpg | https://i.ibb.co/Lz2kmDNf/d5-Patek-Cubitus-gold-3.jpg | https://i.ibb.co/Pz0pvwHn/d5-Patek-Cubitus-gold-4.jpg | https://i.ibb.co/8LrBhmCC/d5-Patek-Cubitus-gold-5.jpg</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Patek Philippe Cubitus золото мужские</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patek Philippe Cubitus — золото, мужские&lt;br&gt;&lt;br&gt;Квадратный корпус цвета золота с тиснёным тёмным циферблатом — новая линейка Patek, которую пока мало у кого видно на руке.&lt;br&gt;&lt;br&gt;• Механизм: механический с автоподзаводом&lt;br&gt;• Корпус: цвет золота, квадратный, 45 мм&lt;br&gt;• Циферблат: тёмный, горизонтальное тиснение, окно даты&lt;br&gt;• Браслет: цвет золота, интегрированный&lt;br&gt;• Функции: дата, водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы patek philippe, patek cubitus, золотые часы мужские, наручные часы механика&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83000</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patek Philippe</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золотой</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золотой</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/LnWIJz13dmJDHg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод | Календарь</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u0917d_Richard_Mille_blue</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/Kcykxnzf/d5-Richard-Mille-blue-0.jpg | https://i.ibb.co/gZ1G2qKS/d5-Richard-Mille-blue-1.jpg | https://i.ibb.co/4gj37dJf/d5-Richard-Mille-blue-2.jpg | https://i.ibb.co/m5dg1rG5/d5-Richard-Mille-blue-3.jpg | https://i.ibb.co/20M0C8vw/d5-Richard-Mille-blue-4.jpg | https://i.ibb.co/JjSq7xrg/d5-Richard-Mille-blue-5.jpg | https://i.ibb.co/2Y1G43bX/d5-Richard-Mille-blue-6.jpg</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Richard Mille синий скелетон мужские</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Richard Mille — синий скелетон, мужские&lt;br&gt;&lt;br&gt;Корпус-бочка из тёмного композита, полностью открытый механизм и синие акценты на мостах — часы, которые разглядывают, а не просто замечают.&lt;br&gt;&lt;br&gt;• Механизм: механический с автоподзаводом&lt;br&gt;• Корпус: композит, форма тонно&lt;br&gt;• Циферблат: скелетон, синие детали&lt;br&gt;• Ремешок: каучук&lt;br&gt;• Функции: запас хода на циферблате, водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы richard mille, richard mille скелетон, часы механика мужские, наручные часы каучук&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108000</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Richard Mille</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Синий</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Синий</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/zXHk3dtc2FECeQ</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каучуковый</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u0917d_Cartier_Santos_skeleton_blue</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/gFSKxYZg/d5-Cartier-Santos-skeleton-blue-0.jpg | https://i.ibb.co/cmX5RHD/d5-Cartier-Santos-skeleton-blue-1.jpg | https://i.ibb.co/C5h1P6SK/d5-Cartier-Santos-skeleton-blue-2.jpg | https://i.ibb.co/35Hr4ynz/d5-Cartier-Santos-skeleton-blue-3.jpg | https://i.ibb.co/4nDBN8wV/d5-Cartier-Santos-skeleton-blue-4.jpg | https://i.ibb.co/9kMnYBH4/d5-Cartier-Santos-skeleton-blue-5.jpg</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Cartier Santos скелетон синий мужские</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier Santos скелетон — синий безель, мужские&lt;br&gt;&lt;br&gt;Квадратный корпус с винтами и полностью открытый механизм, где мосты выложены римскими цифрами, синий безель по контуру.&lt;br&gt;&lt;br&gt;• Механизм: механический с автоподзаводом&lt;br&gt;• Корпус: сталь с синим безелем, квадратный&lt;br&gt;• Циферблат: скелетон, римские цифры на мостах&lt;br&gt;• Браслет: сталь&lt;br&gt;• Функции: водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы cartier мужские, cartier santos скелетон, часы сталь механика, наручные часы квадратные&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98000</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Синий</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Серебряный</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/z4T_vcUdC1puLw</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u0917d_Hublot_BigBang_chrono</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/Xrvs9zTv/d5-Hublot-Big-Bang-chrono-0.jpg | https://i.ibb.co/Gjp30NF/d5-Hublot-Big-Bang-chrono-1.jpg | https://i.ibb.co/QFnjqt8Q/d5-Hublot-Big-Bang-chrono-2.jpg | https://i.ibb.co/PZ6SwzHF/d5-Hublot-Big-Bang-chrono-3.jpg | https://i.ibb.co/BHNfNrh5/d5-Hublot-Big-Bang-chrono-4.jpg | https://i.ibb.co/cKzYbV0K/d5-Hublot-Big-Bang-chrono-5.jpg</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Hublot Big Bang серый хронограф</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot Big Bang — серый хронограф, мужские&lt;br&gt;&lt;br&gt;Крупный корпус с винтами по безелю, открытый циферблат с хронографом и каучуковый ремешок — спортивная версия для каждого дня.&lt;br&gt;&lt;br&gt;• Механизм: механический с автоподзаводом&lt;br&gt;• Корпус: серый, 44 мм, винты по безелю&lt;br&gt;• Циферблат: скелетон, счётчики хронографа&lt;br&gt;• Ремешок: каучук&lt;br&gt;• Функции: хронограф, дата, водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot big bang, хронограф механика, наручные часы каучук&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84500</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Серый</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/ucRDdChkd5dkWQ</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод | Хронограф | Секундомер</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каучуковый</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u0917d_Omega_Speedmaster_darkside</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/GvVd2vNj/d5-Omega-Speedmaster-darkside-0.jpg | https://i.ibb.co/cKv3RB7N/d5-Omega-Speedmaster-darkside-1.jpg | https://i.ibb.co/Ngc5TpDp/d5-Omega-Speedmaster-darkside-2.jpg | https://i.ibb.co/gFvzQ7Kj/d5-Omega-Speedmaster-darkside-3.jpg | https://i.ibb.co/DHKstMf7/d5-Omega-Speedmaster-darkside-4.jpg | https://i.ibb.co/DH5BMHv4/d5-Omega-Speedmaster-darkside-5.jpg | https://i.ibb.co/5tBPCBK/d5-Omega-Speedmaster-darkside-6.jpg | https://i.ibb.co/4gNvvKkV/d5-Omega-Speedmaster-darkside-7.jpg</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Omega Speedmaster чёрный керамика</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Omega Speedmaster Dark Side — чёрный, мужские&lt;br&gt;&lt;br&gt;Корпус целиком из чёрной керамики, матовый циферблат с открытым механизмом и текстильный ремешок — тот самый «лунный» хронограф в тёмной версии.&lt;br&gt;&lt;br&gt;• Механизм: механический с автоподзаводом&lt;br&gt;• Корпус: чёрная керамика, 44 мм&lt;br&gt;• Циферблат: чёрный, счётчики хронографа&lt;br&gt;• Ремешок: текстиль&lt;br&gt;• Функции: хронограф, тахиметр, водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы omega мужские, omega speedmaster, хронограф керамика, наручные часы механика&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83000</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Omega</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/L-HyUN6D0u83tg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод | Хронограф | Секундомер</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Текстиль</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u0917d_Panerai_Luminor_white</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/xK72QPhf/d5-Panerai-Luminor-white-0.jpg | https://i.ibb.co/PzgD8TsP/d5-Panerai-Luminor-white-1.jpg | https://i.ibb.co/tMFn7YF4/d5-Panerai-Luminor-white-2.jpg | https://i.ibb.co/998SfL8X/d5-Panerai-Luminor-white-3.jpg | https://i.ibb.co/h1Z4Mb29/d5-Panerai-Luminor-white-4.jpg | https://i.ibb.co/Ds47qJ6/d5-Panerai-Luminor-white-5.jpg</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Panerai Luminor Marina белый мужские</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panerai Luminor Marina — белый циферблат, мужские&lt;br&gt;&lt;br&gt;Подушкообразный корпус с фирменной скобой над заводной головкой, белый циферблат с крупными цифрами и малой секундной стрелкой.&lt;br&gt;&lt;br&gt;• Механизм: механический с автоподзаводом&lt;br&gt;• Корпус: сталь, 44 мм, защитная скоба&lt;br&gt;• Циферблат: белый, крупные цифры, окно даты&lt;br&gt;• Ремешок: кожа&lt;br&gt;• Функции: дата, малая секундная стрелка, водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы panerai мужские, panerai luminor marina, часы сталь механика, наручные часы кожа&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61500</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panerai</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Белый</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/AqbbgmVLD_ZZRw</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод | Календарь</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кожаный</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|6|100
+Алтайский край|6|100
+Амурская область|6|100
+Архангельская область|6|100
+Астраханская область|6|100
+Башкортостан|6|100
+Белгородская область|6|100
+Брянская область|6|100
+Бурятия|6|100
+Владимирская область|6|100
+Волгоградская область|6|100
+Вологодская область|6|100
+Воронежская область|6|100
+Дагестан|6|100
+другой регион|6|100
+Еврейская АО|6|100
+Забайкальский край|6|100
+Ивановская область|6|100
+Ингушетия|6|100
+Иркутская область|6|100
+Кабардино-Балкария|6|100
+Калининградская область|6|100
+Калмыкия|6|100
+Калужская область|6|100
+Камчатский край|6|100
+Карачаево-Черкесия|6|100
+Карелия|6|100
+Кемеровская область|6|100
+Кировская область|6|100
+Коми|6|100
+Костромская область|6|100
+Краснодарский край|6|100
+Красноярский край|6|100
+Крым|6|100
+Курганская область|6|100
+Курская область|6|100
+Ленинградская область|6|100
+Липецкая область|6|100
+Магаданская область|6|100
+Марий Эл|6|100
+Мордовия|6|100
+Москва|6|100
+Московская область|6|100
+Мурманская область|6|100
+Ненецкий АО|6|100
+Нижегородская область|6|100
+Новгородская область|6|100
+Новосибирская область|6|100
+Омская область|6|100
+Оренбургская область|6|100
+Орловская область|6|100
+Пензенская область|6|100
+Пермский край|6|100
+Приморский край|6|100
+Псковская область|6|100
+Республика Алтай|6|100
+Ростовская область|6|100
+Рязанская область|6|100
+Самарская область|6|100
+Санкт-Петербург|6|100
+Саратовская область|6|100
+Саха (Якутия)|6|100
+Сахалинская область|6|100
+Свердловская область|6|100
+Северная Осетия|6|100
+Смоленская область|6|100
+Ставропольский край|6|100
+Тамбовская область|6|100
+Татарстан|6|100
+Тверская область|6|100
+Томская область|6|100
+Тульская область|6|100
+Тыва|6|100
+Тюменская область|6|100
+Удмуртия|6|100
+Ульяновская область|6|100
+Хабаровский край|6|100
+Хакасия|6|100
+Ханты-Мансийский АО|6|100
+Челябинская область|6|100
+Чеченская Республика|6|100
+Чувашия|6|100
+Ямало-Ненецкий АО|6|100
+Ярославская область|6|100</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/ilya_feed.xlsx
+++ b/ilya_feed.xlsx
@@ -33655,12 +33655,12 @@
         <v>7945</v>
       </c>
       <c r="AH2" s="7"/>
-      <c r="AH2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t xml:space="preserve">Настройка цены целевого действия</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t xml:space="preserve">Настройка цены целевого действия: ручная</t>
         </is>
@@ -33750,17 +33750,17 @@
       </c>
       <c r="AB3" s="6" t="s">
         <v>43</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Необязательный</t>
-        </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t xml:space="preserve">Необязательный</t>
         </is>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
@@ -33847,12 +33847,12 @@
       <c r="AB4" t="s">
         <v>44</v>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t xml:space="preserve">Одно значение из выпадающего списка в ячейке</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t xml:space="preserve">Подробнее о параметре</t>
         </is>
@@ -33955,12 +33955,12 @@
       <c r="AG5" t="s">
         <v>8061</v>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -34146,12 +34146,12 @@
       <c r="AG6" t="s">
         <v>8061</v>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -34337,12 +34337,12 @@
       <c r="AG7" t="s">
         <v>8061</v>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -34531,12 +34531,12 @@
       <c r="AG8" t="s">
         <v>8061</v>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AJ8" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -34722,12 +34722,12 @@
       <c r="AG9" t="s">
         <v>8061</v>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AJ9" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -34913,12 +34913,12 @@
       <c r="AG10" t="s">
         <v>8061</v>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AI10" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AJ10" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -35104,12 +35104,12 @@
       <c r="AG11" t="s">
         <v>8061</v>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AI11" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AJ11" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -35295,12 +35295,12 @@
       <c r="AG12" t="s">
         <v>8061</v>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AI12" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AJ12" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -35486,12 +35486,12 @@
       <c r="AG13" t="s">
         <v>8061</v>
       </c>
-      <c r="AH13" t="inlineStr">
+      <c r="AI13" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AJ13" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -35677,12 +35677,12 @@
       <c r="AG14" t="s">
         <v>8061</v>
       </c>
-      <c r="AH14" t="inlineStr">
+      <c r="AI14" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
+      <c r="AJ14" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -35868,12 +35868,12 @@
       <c r="AG15" t="s">
         <v>8061</v>
       </c>
-      <c r="AH15" t="inlineStr">
+      <c r="AI15" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
+      <c r="AJ15" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -36059,12 +36059,12 @@
       <c r="AG16" t="s">
         <v>8061</v>
       </c>
-      <c r="AH16" t="inlineStr">
+      <c r="AI16" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
+      <c r="AJ16" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -36250,12 +36250,12 @@
       <c r="AG17" t="s">
         <v>8061</v>
       </c>
-      <c r="AH17" t="inlineStr">
+      <c r="AI17" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
+      <c r="AJ17" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -36441,12 +36441,12 @@
       <c r="AG18" t="s">
         <v>8061</v>
       </c>
-      <c r="AH18" t="inlineStr">
+      <c r="AI18" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
+      <c r="AJ18" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -36632,12 +36632,12 @@
       <c r="AG19" t="s">
         <v>8061</v>
       </c>
-      <c r="AH19" t="inlineStr">
+      <c r="AI19" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
+      <c r="AJ19" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -36823,12 +36823,12 @@
       <c r="AG20" t="s">
         <v>8061</v>
       </c>
-      <c r="AH20" t="inlineStr">
+      <c r="AI20" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
+      <c r="AJ20" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -37014,12 +37014,12 @@
       <c r="AG21" t="s">
         <v>8061</v>
       </c>
-      <c r="AH21" t="inlineStr">
+      <c r="AI21" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
+      <c r="AJ21" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -37205,12 +37205,12 @@
       <c r="AG22" t="s">
         <v>8061</v>
       </c>
-      <c r="AH22" t="inlineStr">
+      <c r="AI22" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
+      <c r="AJ22" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -37396,12 +37396,12 @@
       <c r="AG23" t="s">
         <v>8061</v>
       </c>
-      <c r="AH23" t="inlineStr">
+      <c r="AI23" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
+      <c r="AJ23" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -37587,12 +37587,12 @@
       <c r="AG24" t="s">
         <v>8061</v>
       </c>
-      <c r="AH24" t="inlineStr">
+      <c r="AI24" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
+      <c r="AJ24" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -37822,12 +37822,12 @@
           <t xml:space="preserve">ilyabalabay@mail.ru</t>
         </is>
       </c>
-      <c r="AH25" t="inlineStr">
+      <c r="AI25" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
+      <c r="AJ25" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -38057,12 +38057,12 @@
           <t xml:space="preserve">ilyabalabay@mail.ru</t>
         </is>
       </c>
-      <c r="AH26" t="inlineStr">
+      <c r="AI26" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
+      <c r="AJ26" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -38292,12 +38292,12 @@
           <t xml:space="preserve">ilyabalabay@mail.ru</t>
         </is>
       </c>
-      <c r="AH27" t="inlineStr">
+      <c r="AI27" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
+      <c r="AJ27" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -38527,12 +38527,12 @@
           <t xml:space="preserve">ilyabalabay@mail.ru</t>
         </is>
       </c>
-      <c r="AH28" t="inlineStr">
+      <c r="AI28" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr">
+      <c r="AJ28" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -38762,12 +38762,12 @@
           <t xml:space="preserve">ilyabalabay@mail.ru</t>
         </is>
       </c>
-      <c r="AH29" t="inlineStr">
+      <c r="AI29" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
+      <c r="AJ29" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -38997,12 +38997,12 @@
           <t xml:space="preserve">ilyabalabay@mail.ru</t>
         </is>
       </c>
-      <c r="AH30" t="inlineStr">
+      <c r="AI30" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
+      <c r="AJ30" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -39232,12 +39232,12 @@
           <t xml:space="preserve">ilyabalabay@mail.ru</t>
         </is>
       </c>
-      <c r="AH31" t="inlineStr">
+      <c r="AI31" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
+      <c r="AJ31" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -39467,12 +39467,12 @@
           <t xml:space="preserve">ilyabalabay@mail.ru</t>
         </is>
       </c>
-      <c r="AH32" t="inlineStr">
+      <c r="AI32" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
+      <c r="AJ32" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -39702,12 +39702,12 @@
           <t xml:space="preserve">ilyabalabay@mail.ru</t>
         </is>
       </c>
-      <c r="AH33" t="inlineStr">
+      <c r="AI33" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI33" t="inlineStr">
+      <c r="AJ33" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100
@@ -39937,12 +39937,12 @@
           <t xml:space="preserve">ilyabalabay@mail.ru</t>
         </is>
       </c>
-      <c r="AH34" t="inlineStr">
+      <c r="AI34" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
-      <c r="AI34" t="inlineStr">
+      <c r="AJ34" t="inlineStr">
         <is>
           <t xml:space="preserve">Адыгея|6|100
 Алтайский край|6|100

--- a/ilya_feed.xlsx
+++ b/ilya_feed.xlsx
@@ -31614,6 +31614,16 @@
         <v>7942</v>
       </c>
       <c r="V2" s="7"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Настройка цены целевого действия</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Настройка цены целевого действия: ручная</t>
+        </is>
+      </c>
     </row>
     <row r="3" s="6" customFormat="true" ht="45" customHeight="true">
       <c r="A3" s="6" t="s">
@@ -31664,6 +31674,16 @@
       <c r="P3" s="6" t="s">
         <v>39</v>
       </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Необязательный</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
@@ -31714,6 +31734,16 @@
       <c r="P4" t="s">
         <v>44</v>
       </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Одно значение из выпадающего списка в ячейке</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Подробнее о параметре</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -31778,6 +31808,99 @@
       </c>
       <c r="U5" t="s">
         <v>8063</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|5|100
+Алтайский край|5|100
+Амурская область|5|100
+Архангельская область|5|100
+Астраханская область|5|100
+Башкортостан|5|100
+Белгородская область|5|100
+Брянская область|5|100
+Бурятия|5|100
+Владимирская область|5|100
+Волгоградская область|5|100
+Вологодская область|5|100
+Воронежская область|5|100
+Дагестан|5|100
+другой регион|5|100
+Еврейская АО|5|100
+Забайкальский край|5|100
+Ивановская область|5|100
+Ингушетия|5|100
+Иркутская область|5|100
+Кабардино-Балкария|5|100
+Калининградская область|5|100
+Калмыкия|5|100
+Калужская область|5|100
+Камчатский край|5|100
+Карачаево-Черкесия|5|100
+Карелия|5|100
+Кемеровская область|5|100
+Кировская область|5|100
+Коми|5|100
+Костромская область|5|100
+Краснодарский край|5|100
+Красноярский край|5|100
+Крым|5|100
+Курганская область|5|100
+Курская область|5|100
+Ленинградская область|5|100
+Липецкая область|5|100
+Магаданская область|5|100
+Марий Эл|5|100
+Мордовия|5|100
+Москва|5|100
+Московская область|5|100
+Мурманская область|5|100
+Ненецкий АО|5|100
+Нижегородская область|5|100
+Новгородская область|5|100
+Новосибирская область|5|100
+Омская область|5|100
+Оренбургская область|5|100
+Орловская область|5|100
+Пензенская область|5|100
+Пермский край|5|100
+Приморский край|5|100
+Псковская область|5|100
+Республика Алтай|5|100
+Ростовская область|5|100
+Рязанская область|5|100
+Самарская область|5|100
+Санкт-Петербург|5|100
+Саратовская область|5|100
+Саха (Якутия)|5|100
+Сахалинская область|5|100
+Свердловская область|5|100
+Северная Осетия|5|100
+Смоленская область|5|100
+Ставропольский край|5|100
+Тамбовская область|5|100
+Татарстан|5|100
+Тверская область|5|100
+Томская область|5|100
+Тульская область|5|100
+Тыва|5|100
+Тюменская область|5|100
+Удмуртия|5|100
+Ульяновская область|5|100
+Хабаровский край|5|100
+Хакасия|5|100
+Ханты-Мансийский АО|5|100
+Челябинская область|5|100
+Чеченская Республика|5|100
+Чувашия|5|100
+Ямало-Ненецкий АО|5|100
+Ярославская область|5|100</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -32096,6 +32219,16 @@
         <v>7945</v>
       </c>
       <c r="V2" s="7"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Настройка цены целевого действия</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Настройка цены целевого действия: ручная</t>
+        </is>
+      </c>
     </row>
     <row r="3" s="6" customFormat="true" ht="45" customHeight="true">
       <c r="A3" s="6" t="s">
@@ -32146,6 +32279,16 @@
       <c r="P3" s="6" t="s">
         <v>39</v>
       </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Необязательный</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
@@ -32196,6 +32339,16 @@
       <c r="P4" t="s">
         <v>44</v>
       </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Одно значение из выпадающего списка в ячейке</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Подробнее о параметре</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -32261,6 +32414,99 @@
       <c r="U5" t="s">
         <v>8061</v>
       </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|2|100
+Алтайский край|2|100
+Амурская область|2|100
+Архангельская область|2|100
+Астраханская область|2|100
+Башкортостан|2|100
+Белгородская область|2|100
+Брянская область|2|100
+Бурятия|2|100
+Владимирская область|2|100
+Волгоградская область|2|100
+Вологодская область|2|100
+Воронежская область|2|100
+Дагестан|2|100
+другой регион|2|100
+Еврейская АО|2|100
+Забайкальский край|2|100
+Ивановская область|2|100
+Ингушетия|2|100
+Иркутская область|2|100
+Кабардино-Балкария|2|100
+Калининградская область|2|100
+Калмыкия|2|100
+Калужская область|2|100
+Камчатский край|2|100
+Карачаево-Черкесия|2|100
+Карелия|2|100
+Кемеровская область|2|100
+Кировская область|2|100
+Коми|2|100
+Костромская область|2|100
+Краснодарский край|2|100
+Красноярский край|2|100
+Крым|2|100
+Курганская область|2|100
+Курская область|2|100
+Ленинградская область|2|100
+Липецкая область|2|100
+Магаданская область|2|100
+Марий Эл|2|100
+Мордовия|2|100
+Москва|2|100
+Московская область|2|100
+Мурманская область|2|100
+Ненецкий АО|2|100
+Нижегородская область|2|100
+Новгородская область|2|100
+Новосибирская область|2|100
+Омская область|2|100
+Оренбургская область|2|100
+Орловская область|2|100
+Пензенская область|2|100
+Пермский край|2|100
+Приморский край|2|100
+Псковская область|2|100
+Республика Алтай|2|100
+Ростовская область|2|100
+Рязанская область|2|100
+Самарская область|2|100
+Санкт-Петербург|2|100
+Саратовская область|2|100
+Саха (Якутия)|2|100
+Сахалинская область|2|100
+Свердловская область|2|100
+Северная Осетия|2|100
+Смоленская область|2|100
+Ставропольский край|2|100
+Тамбовская область|2|100
+Татарстан|2|100
+Тверская область|2|100
+Томская область|2|100
+Тульская область|2|100
+Тыва|2|100
+Тюменская область|2|100
+Удмуртия|2|100
+Ульяновская область|2|100
+Хабаровский край|2|100
+Хакасия|2|100
+Ханты-Мансийский АО|2|100
+Челябинская область|2|100
+Чеченская Республика|2|100
+Чувашия|2|100
+Ямало-Ненецкий АО|2|100
+Ярославская область|2|100</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
@@ -32326,6 +32572,99 @@
       <c r="U6" t="s">
         <v>8061</v>
       </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|2|100
+Алтайский край|2|100
+Амурская область|2|100
+Архангельская область|2|100
+Астраханская область|2|100
+Башкортостан|2|100
+Белгородская область|2|100
+Брянская область|2|100
+Бурятия|2|100
+Владимирская область|2|100
+Волгоградская область|2|100
+Вологодская область|2|100
+Воронежская область|2|100
+Дагестан|2|100
+другой регион|2|100
+Еврейская АО|2|100
+Забайкальский край|2|100
+Ивановская область|2|100
+Ингушетия|2|100
+Иркутская область|2|100
+Кабардино-Балкария|2|100
+Калининградская область|2|100
+Калмыкия|2|100
+Калужская область|2|100
+Камчатский край|2|100
+Карачаево-Черкесия|2|100
+Карелия|2|100
+Кемеровская область|2|100
+Кировская область|2|100
+Коми|2|100
+Костромская область|2|100
+Краснодарский край|2|100
+Красноярский край|2|100
+Крым|2|100
+Курганская область|2|100
+Курская область|2|100
+Ленинградская область|2|100
+Липецкая область|2|100
+Магаданская область|2|100
+Марий Эл|2|100
+Мордовия|2|100
+Москва|2|100
+Московская область|2|100
+Мурманская область|2|100
+Ненецкий АО|2|100
+Нижегородская область|2|100
+Новгородская область|2|100
+Новосибирская область|2|100
+Омская область|2|100
+Оренбургская область|2|100
+Орловская область|2|100
+Пензенская область|2|100
+Пермский край|2|100
+Приморский край|2|100
+Псковская область|2|100
+Республика Алтай|2|100
+Ростовская область|2|100
+Рязанская область|2|100
+Самарская область|2|100
+Санкт-Петербург|2|100
+Саратовская область|2|100
+Саха (Якутия)|2|100
+Сахалинская область|2|100
+Свердловская область|2|100
+Северная Осетия|2|100
+Смоленская область|2|100
+Ставропольский край|2|100
+Тамбовская область|2|100
+Татарстан|2|100
+Тверская область|2|100
+Томская область|2|100
+Тульская область|2|100
+Тыва|2|100
+Тюменская область|2|100
+Удмуртия|2|100
+Ульяновская область|2|100
+Хабаровский край|2|100
+Хакасия|2|100
+Ханты-Мансийский АО|2|100
+Челябинская область|2|100
+Чеченская Республика|2|100
+Чувашия|2|100
+Ямало-Ненецкий АО|2|100
+Ярославская область|2|100</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
@@ -32391,6 +32730,99 @@
       <c r="U7" t="s">
         <v>8061</v>
       </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|2|100
+Алтайский край|2|100
+Амурская область|2|100
+Архангельская область|2|100
+Астраханская область|2|100
+Башкортостан|2|100
+Белгородская область|2|100
+Брянская область|2|100
+Бурятия|2|100
+Владимирская область|2|100
+Волгоградская область|2|100
+Вологодская область|2|100
+Воронежская область|2|100
+Дагестан|2|100
+другой регион|2|100
+Еврейская АО|2|100
+Забайкальский край|2|100
+Ивановская область|2|100
+Ингушетия|2|100
+Иркутская область|2|100
+Кабардино-Балкария|2|100
+Калининградская область|2|100
+Калмыкия|2|100
+Калужская область|2|100
+Камчатский край|2|100
+Карачаево-Черкесия|2|100
+Карелия|2|100
+Кемеровская область|2|100
+Кировская область|2|100
+Коми|2|100
+Костромская область|2|100
+Краснодарский край|2|100
+Красноярский край|2|100
+Крым|2|100
+Курганская область|2|100
+Курская область|2|100
+Ленинградская область|2|100
+Липецкая область|2|100
+Магаданская область|2|100
+Марий Эл|2|100
+Мордовия|2|100
+Москва|2|100
+Московская область|2|100
+Мурманская область|2|100
+Ненецкий АО|2|100
+Нижегородская область|2|100
+Новгородская область|2|100
+Новосибирская область|2|100
+Омская область|2|100
+Оренбургская область|2|100
+Орловская область|2|100
+Пензенская область|2|100
+Пермский край|2|100
+Приморский край|2|100
+Псковская область|2|100
+Республика Алтай|2|100
+Ростовская область|2|100
+Рязанская область|2|100
+Самарская область|2|100
+Санкт-Петербург|2|100
+Саратовская область|2|100
+Саха (Якутия)|2|100
+Сахалинская область|2|100
+Свердловская область|2|100
+Северная Осетия|2|100
+Смоленская область|2|100
+Ставропольский край|2|100
+Тамбовская область|2|100
+Татарстан|2|100
+Тверская область|2|100
+Томская область|2|100
+Тульская область|2|100
+Тыва|2|100
+Тюменская область|2|100
+Удмуртия|2|100
+Ульяновская область|2|100
+Хабаровский край|2|100
+Хакасия|2|100
+Ханты-Мансийский АО|2|100
+Челябинская область|2|100
+Чеченская Республика|2|100
+Чувашия|2|100
+Ямало-Ненецкий АО|2|100
+Ярославская область|2|100</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -32456,6 +32888,99 @@
       <c r="U8" t="s">
         <v>8061</v>
       </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|2|100
+Алтайский край|2|100
+Амурская область|2|100
+Архангельская область|2|100
+Астраханская область|2|100
+Башкортостан|2|100
+Белгородская область|2|100
+Брянская область|2|100
+Бурятия|2|100
+Владимирская область|2|100
+Волгоградская область|2|100
+Вологодская область|2|100
+Воронежская область|2|100
+Дагестан|2|100
+другой регион|2|100
+Еврейская АО|2|100
+Забайкальский край|2|100
+Ивановская область|2|100
+Ингушетия|2|100
+Иркутская область|2|100
+Кабардино-Балкария|2|100
+Калининградская область|2|100
+Калмыкия|2|100
+Калужская область|2|100
+Камчатский край|2|100
+Карачаево-Черкесия|2|100
+Карелия|2|100
+Кемеровская область|2|100
+Кировская область|2|100
+Коми|2|100
+Костромская область|2|100
+Краснодарский край|2|100
+Красноярский край|2|100
+Крым|2|100
+Курганская область|2|100
+Курская область|2|100
+Ленинградская область|2|100
+Липецкая область|2|100
+Магаданская область|2|100
+Марий Эл|2|100
+Мордовия|2|100
+Москва|2|100
+Московская область|2|100
+Мурманская область|2|100
+Ненецкий АО|2|100
+Нижегородская область|2|100
+Новгородская область|2|100
+Новосибирская область|2|100
+Омская область|2|100
+Оренбургская область|2|100
+Орловская область|2|100
+Пензенская область|2|100
+Пермский край|2|100
+Приморский край|2|100
+Псковская область|2|100
+Республика Алтай|2|100
+Ростовская область|2|100
+Рязанская область|2|100
+Самарская область|2|100
+Санкт-Петербург|2|100
+Саратовская область|2|100
+Саха (Якутия)|2|100
+Сахалинская область|2|100
+Свердловская область|2|100
+Северная Осетия|2|100
+Смоленская область|2|100
+Ставропольский край|2|100
+Тамбовская область|2|100
+Татарстан|2|100
+Тверская область|2|100
+Томская область|2|100
+Тульская область|2|100
+Тыва|2|100
+Тюменская область|2|100
+Удмуртия|2|100
+Ульяновская область|2|100
+Хабаровский край|2|100
+Хакасия|2|100
+Ханты-Мансийский АО|2|100
+Челябинская область|2|100
+Чеченская Республика|2|100
+Чувашия|2|100
+Ямало-Ненецкий АО|2|100
+Ярославская область|2|100</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -32521,6 +33046,99 @@
       <c r="U9" t="s">
         <v>8061</v>
       </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|2|100
+Алтайский край|2|100
+Амурская область|2|100
+Архангельская область|2|100
+Астраханская область|2|100
+Башкортостан|2|100
+Белгородская область|2|100
+Брянская область|2|100
+Бурятия|2|100
+Владимирская область|2|100
+Волгоградская область|2|100
+Вологодская область|2|100
+Воронежская область|2|100
+Дагестан|2|100
+другой регион|2|100
+Еврейская АО|2|100
+Забайкальский край|2|100
+Ивановская область|2|100
+Ингушетия|2|100
+Иркутская область|2|100
+Кабардино-Балкария|2|100
+Калининградская область|2|100
+Калмыкия|2|100
+Калужская область|2|100
+Камчатский край|2|100
+Карачаево-Черкесия|2|100
+Карелия|2|100
+Кемеровская область|2|100
+Кировская область|2|100
+Коми|2|100
+Костромская область|2|100
+Краснодарский край|2|100
+Красноярский край|2|100
+Крым|2|100
+Курганская область|2|100
+Курская область|2|100
+Ленинградская область|2|100
+Липецкая область|2|100
+Магаданская область|2|100
+Марий Эл|2|100
+Мордовия|2|100
+Москва|2|100
+Московская область|2|100
+Мурманская область|2|100
+Ненецкий АО|2|100
+Нижегородская область|2|100
+Новгородская область|2|100
+Новосибирская область|2|100
+Омская область|2|100
+Оренбургская область|2|100
+Орловская область|2|100
+Пензенская область|2|100
+Пермский край|2|100
+Приморский край|2|100
+Псковская область|2|100
+Республика Алтай|2|100
+Ростовская область|2|100
+Рязанская область|2|100
+Самарская область|2|100
+Санкт-Петербург|2|100
+Саратовская область|2|100
+Саха (Якутия)|2|100
+Сахалинская область|2|100
+Свердловская область|2|100
+Северная Осетия|2|100
+Смоленская область|2|100
+Ставропольский край|2|100
+Тамбовская область|2|100
+Татарстан|2|100
+Тверская область|2|100
+Томская область|2|100
+Тульская область|2|100
+Тыва|2|100
+Тюменская область|2|100
+Удмуртия|2|100
+Ульяновская область|2|100
+Хабаровский край|2|100
+Хакасия|2|100
+Ханты-Мансийский АО|2|100
+Челябинская область|2|100
+Чеченская Республика|2|100
+Чувашия|2|100
+Ямало-Ненецкий АО|2|100
+Ярославская область|2|100</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -32586,6 +33204,99 @@
       <c r="U10" t="s">
         <v>8061</v>
       </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|2|100
+Алтайский край|2|100
+Амурская область|2|100
+Архангельская область|2|100
+Астраханская область|2|100
+Башкортостан|2|100
+Белгородская область|2|100
+Брянская область|2|100
+Бурятия|2|100
+Владимирская область|2|100
+Волгоградская область|2|100
+Вологодская область|2|100
+Воронежская область|2|100
+Дагестан|2|100
+другой регион|2|100
+Еврейская АО|2|100
+Забайкальский край|2|100
+Ивановская область|2|100
+Ингушетия|2|100
+Иркутская область|2|100
+Кабардино-Балкария|2|100
+Калининградская область|2|100
+Калмыкия|2|100
+Калужская область|2|100
+Камчатский край|2|100
+Карачаево-Черкесия|2|100
+Карелия|2|100
+Кемеровская область|2|100
+Кировская область|2|100
+Коми|2|100
+Костромская область|2|100
+Краснодарский край|2|100
+Красноярский край|2|100
+Крым|2|100
+Курганская область|2|100
+Курская область|2|100
+Ленинградская область|2|100
+Липецкая область|2|100
+Магаданская область|2|100
+Марий Эл|2|100
+Мордовия|2|100
+Москва|2|100
+Московская область|2|100
+Мурманская область|2|100
+Ненецкий АО|2|100
+Нижегородская область|2|100
+Новгородская область|2|100
+Новосибирская область|2|100
+Омская область|2|100
+Оренбургская область|2|100
+Орловская область|2|100
+Пензенская область|2|100
+Пермский край|2|100
+Приморский край|2|100
+Псковская область|2|100
+Республика Алтай|2|100
+Ростовская область|2|100
+Рязанская область|2|100
+Самарская область|2|100
+Санкт-Петербург|2|100
+Саратовская область|2|100
+Саха (Якутия)|2|100
+Сахалинская область|2|100
+Свердловская область|2|100
+Северная Осетия|2|100
+Смоленская область|2|100
+Ставропольский край|2|100
+Тамбовская область|2|100
+Татарстан|2|100
+Тверская область|2|100
+Томская область|2|100
+Тульская область|2|100
+Тыва|2|100
+Тюменская область|2|100
+Удмуртия|2|100
+Ульяновская область|2|100
+Хабаровский край|2|100
+Хакасия|2|100
+Ханты-Мансийский АО|2|100
+Челябинская область|2|100
+Чеченская Республика|2|100
+Чувашия|2|100
+Ямало-Ненецкий АО|2|100
+Ярославская область|2|100</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
@@ -32651,6 +33362,99 @@
       <c r="U11" t="s">
         <v>8061</v>
       </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|5|100
+Алтайский край|5|100
+Амурская область|5|100
+Архангельская область|5|100
+Астраханская область|5|100
+Башкортостан|5|100
+Белгородская область|5|100
+Брянская область|5|100
+Бурятия|5|100
+Владимирская область|5|100
+Волгоградская область|5|100
+Вологодская область|5|100
+Воронежская область|5|100
+Дагестан|5|100
+другой регион|5|100
+Еврейская АО|5|100
+Забайкальский край|5|100
+Ивановская область|5|100
+Ингушетия|5|100
+Иркутская область|5|100
+Кабардино-Балкария|5|100
+Калининградская область|5|100
+Калмыкия|5|100
+Калужская область|5|100
+Камчатский край|5|100
+Карачаево-Черкесия|5|100
+Карелия|5|100
+Кемеровская область|5|100
+Кировская область|5|100
+Коми|5|100
+Костромская область|5|100
+Краснодарский край|5|100
+Красноярский край|5|100
+Крым|5|100
+Курганская область|5|100
+Курская область|5|100
+Ленинградская область|5|100
+Липецкая область|5|100
+Магаданская область|5|100
+Марий Эл|5|100
+Мордовия|5|100
+Москва|5|100
+Московская область|5|100
+Мурманская область|5|100
+Ненецкий АО|5|100
+Нижегородская область|5|100
+Новгородская область|5|100
+Новосибирская область|5|100
+Омская область|5|100
+Оренбургская область|5|100
+Орловская область|5|100
+Пензенская область|5|100
+Пермский край|5|100
+Приморский край|5|100
+Псковская область|5|100
+Республика Алтай|5|100
+Ростовская область|5|100
+Рязанская область|5|100
+Самарская область|5|100
+Санкт-Петербург|5|100
+Саратовская область|5|100
+Саха (Якутия)|5|100
+Сахалинская область|5|100
+Свердловская область|5|100
+Северная Осетия|5|100
+Смоленская область|5|100
+Ставропольский край|5|100
+Тамбовская область|5|100
+Татарстан|5|100
+Тверская область|5|100
+Томская область|5|100
+Тульская область|5|100
+Тыва|5|100
+Тюменская область|5|100
+Удмуртия|5|100
+Ульяновская область|5|100
+Хабаровский край|5|100
+Хакасия|5|100
+Ханты-Мансийский АО|5|100
+Челябинская область|5|100
+Чеченская Республика|5|100
+Чувашия|5|100
+Ямало-Ненецкий АО|5|100
+Ярославская область|5|100</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -32716,6 +33520,99 @@
       <c r="U12" t="s">
         <v>8061</v>
       </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|2|100
+Алтайский край|2|100
+Амурская область|2|100
+Архангельская область|2|100
+Астраханская область|2|100
+Башкортостан|2|100
+Белгородская область|2|100
+Брянская область|2|100
+Бурятия|2|100
+Владимирская область|2|100
+Волгоградская область|2|100
+Вологодская область|2|100
+Воронежская область|2|100
+Дагестан|2|100
+другой регион|2|100
+Еврейская АО|2|100
+Забайкальский край|2|100
+Ивановская область|2|100
+Ингушетия|2|100
+Иркутская область|2|100
+Кабардино-Балкария|2|100
+Калининградская область|2|100
+Калмыкия|2|100
+Калужская область|2|100
+Камчатский край|2|100
+Карачаево-Черкесия|2|100
+Карелия|2|100
+Кемеровская область|2|100
+Кировская область|2|100
+Коми|2|100
+Костромская область|2|100
+Краснодарский край|2|100
+Красноярский край|2|100
+Крым|2|100
+Курганская область|2|100
+Курская область|2|100
+Ленинградская область|2|100
+Липецкая область|2|100
+Магаданская область|2|100
+Марий Эл|2|100
+Мордовия|2|100
+Москва|2|100
+Московская область|2|100
+Мурманская область|2|100
+Ненецкий АО|2|100
+Нижегородская область|2|100
+Новгородская область|2|100
+Новосибирская область|2|100
+Омская область|2|100
+Оренбургская область|2|100
+Орловская область|2|100
+Пензенская область|2|100
+Пермский край|2|100
+Приморский край|2|100
+Псковская область|2|100
+Республика Алтай|2|100
+Ростовская область|2|100
+Рязанская область|2|100
+Самарская область|2|100
+Санкт-Петербург|2|100
+Саратовская область|2|100
+Саха (Якутия)|2|100
+Сахалинская область|2|100
+Свердловская область|2|100
+Северная Осетия|2|100
+Смоленская область|2|100
+Ставропольский край|2|100
+Тамбовская область|2|100
+Татарстан|2|100
+Тверская область|2|100
+Томская область|2|100
+Тульская область|2|100
+Тыва|2|100
+Тюменская область|2|100
+Удмуртия|2|100
+Ульяновская область|2|100
+Хабаровский край|2|100
+Хакасия|2|100
+Ханты-Мансийский АО|2|100
+Челябинская область|2|100
+Чеченская Республика|2|100
+Чувашия|2|100
+Ямало-Ненецкий АО|2|100
+Ярославская область|2|100</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
@@ -32781,6 +33678,99 @@
       <c r="U13" t="s">
         <v>8061</v>
       </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|2|100
+Алтайский край|2|100
+Амурская область|2|100
+Архангельская область|2|100
+Астраханская область|2|100
+Башкортостан|2|100
+Белгородская область|2|100
+Брянская область|2|100
+Бурятия|2|100
+Владимирская область|2|100
+Волгоградская область|2|100
+Вологодская область|2|100
+Воронежская область|2|100
+Дагестан|2|100
+другой регион|2|100
+Еврейская АО|2|100
+Забайкальский край|2|100
+Ивановская область|2|100
+Ингушетия|2|100
+Иркутская область|2|100
+Кабардино-Балкария|2|100
+Калининградская область|2|100
+Калмыкия|2|100
+Калужская область|2|100
+Камчатский край|2|100
+Карачаево-Черкесия|2|100
+Карелия|2|100
+Кемеровская область|2|100
+Кировская область|2|100
+Коми|2|100
+Костромская область|2|100
+Краснодарский край|2|100
+Красноярский край|2|100
+Крым|2|100
+Курганская область|2|100
+Курская область|2|100
+Ленинградская область|2|100
+Липецкая область|2|100
+Магаданская область|2|100
+Марий Эл|2|100
+Мордовия|2|100
+Москва|2|100
+Московская область|2|100
+Мурманская область|2|100
+Ненецкий АО|2|100
+Нижегородская область|2|100
+Новгородская область|2|100
+Новосибирская область|2|100
+Омская область|2|100
+Оренбургская область|2|100
+Орловская область|2|100
+Пензенская область|2|100
+Пермский край|2|100
+Приморский край|2|100
+Псковская область|2|100
+Республика Алтай|2|100
+Ростовская область|2|100
+Рязанская область|2|100
+Самарская область|2|100
+Санкт-Петербург|2|100
+Саратовская область|2|100
+Саха (Якутия)|2|100
+Сахалинская область|2|100
+Свердловская область|2|100
+Северная Осетия|2|100
+Смоленская область|2|100
+Ставропольский край|2|100
+Тамбовская область|2|100
+Татарстан|2|100
+Тверская область|2|100
+Томская область|2|100
+Тульская область|2|100
+Тыва|2|100
+Тюменская область|2|100
+Удмуртия|2|100
+Ульяновская область|2|100
+Хабаровский край|2|100
+Хакасия|2|100
+Ханты-Мансийский АО|2|100
+Челябинская область|2|100
+Чеченская Республика|2|100
+Чувашия|2|100
+Ямало-Ненецкий АО|2|100
+Ярославская область|2|100</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
@@ -32846,6 +33836,99 @@
       <c r="U14" t="s">
         <v>8061</v>
       </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|2|100
+Алтайский край|2|100
+Амурская область|2|100
+Архангельская область|2|100
+Астраханская область|2|100
+Башкортостан|2|100
+Белгородская область|2|100
+Брянская область|2|100
+Бурятия|2|100
+Владимирская область|2|100
+Волгоградская область|2|100
+Вологодская область|2|100
+Воронежская область|2|100
+Дагестан|2|100
+другой регион|2|100
+Еврейская АО|2|100
+Забайкальский край|2|100
+Ивановская область|2|100
+Ингушетия|2|100
+Иркутская область|2|100
+Кабардино-Балкария|2|100
+Калининградская область|2|100
+Калмыкия|2|100
+Калужская область|2|100
+Камчатский край|2|100
+Карачаево-Черкесия|2|100
+Карелия|2|100
+Кемеровская область|2|100
+Кировская область|2|100
+Коми|2|100
+Костромская область|2|100
+Краснодарский край|2|100
+Красноярский край|2|100
+Крым|2|100
+Курганская область|2|100
+Курская область|2|100
+Ленинградская область|2|100
+Липецкая область|2|100
+Магаданская область|2|100
+Марий Эл|2|100
+Мордовия|2|100
+Москва|2|100
+Московская область|2|100
+Мурманская область|2|100
+Ненецкий АО|2|100
+Нижегородская область|2|100
+Новгородская область|2|100
+Новосибирская область|2|100
+Омская область|2|100
+Оренбургская область|2|100
+Орловская область|2|100
+Пензенская область|2|100
+Пермский край|2|100
+Приморский край|2|100
+Псковская область|2|100
+Республика Алтай|2|100
+Ростовская область|2|100
+Рязанская область|2|100
+Самарская область|2|100
+Санкт-Петербург|2|100
+Саратовская область|2|100
+Саха (Якутия)|2|100
+Сахалинская область|2|100
+Свердловская область|2|100
+Северная Осетия|2|100
+Смоленская область|2|100
+Ставропольский край|2|100
+Тамбовская область|2|100
+Татарстан|2|100
+Тверская область|2|100
+Томская область|2|100
+Тульская область|2|100
+Тыва|2|100
+Тюменская область|2|100
+Удмуртия|2|100
+Ульяновская область|2|100
+Хабаровский край|2|100
+Хакасия|2|100
+Ханты-Мансийский АО|2|100
+Челябинская область|2|100
+Чеченская Республика|2|100
+Чувашия|2|100
+Ямало-Ненецкий АО|2|100
+Ярославская область|2|100</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
@@ -32911,6 +33994,99 @@
       <c r="U15" t="s">
         <v>8061</v>
       </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|2|100
+Алтайский край|2|100
+Амурская область|2|100
+Архангельская область|2|100
+Астраханская область|2|100
+Башкортостан|2|100
+Белгородская область|2|100
+Брянская область|2|100
+Бурятия|2|100
+Владимирская область|2|100
+Волгоградская область|2|100
+Вологодская область|2|100
+Воронежская область|2|100
+Дагестан|2|100
+другой регион|2|100
+Еврейская АО|2|100
+Забайкальский край|2|100
+Ивановская область|2|100
+Ингушетия|2|100
+Иркутская область|2|100
+Кабардино-Балкария|2|100
+Калининградская область|2|100
+Калмыкия|2|100
+Калужская область|2|100
+Камчатский край|2|100
+Карачаево-Черкесия|2|100
+Карелия|2|100
+Кемеровская область|2|100
+Кировская область|2|100
+Коми|2|100
+Костромская область|2|100
+Краснодарский край|2|100
+Красноярский край|2|100
+Крым|2|100
+Курганская область|2|100
+Курская область|2|100
+Ленинградская область|2|100
+Липецкая область|2|100
+Магаданская область|2|100
+Марий Эл|2|100
+Мордовия|2|100
+Москва|2|100
+Московская область|2|100
+Мурманская область|2|100
+Ненецкий АО|2|100
+Нижегородская область|2|100
+Новгородская область|2|100
+Новосибирская область|2|100
+Омская область|2|100
+Оренбургская область|2|100
+Орловская область|2|100
+Пензенская область|2|100
+Пермский край|2|100
+Приморский край|2|100
+Псковская область|2|100
+Республика Алтай|2|100
+Ростовская область|2|100
+Рязанская область|2|100
+Самарская область|2|100
+Санкт-Петербург|2|100
+Саратовская область|2|100
+Саха (Якутия)|2|100
+Сахалинская область|2|100
+Свердловская область|2|100
+Северная Осетия|2|100
+Смоленская область|2|100
+Ставропольский край|2|100
+Тамбовская область|2|100
+Татарстан|2|100
+Тверская область|2|100
+Томская область|2|100
+Тульская область|2|100
+Тыва|2|100
+Тюменская область|2|100
+Удмуртия|2|100
+Ульяновская область|2|100
+Хабаровский край|2|100
+Хакасия|2|100
+Ханты-Мансийский АО|2|100
+Челябинская область|2|100
+Чеченская Республика|2|100
+Чувашия|2|100
+Ямало-Ненецкий АО|2|100
+Ярославская область|2|100</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -32976,6 +34152,99 @@
       <c r="U16" t="s">
         <v>8061</v>
       </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|2|100
+Алтайский край|2|100
+Амурская область|2|100
+Архангельская область|2|100
+Астраханская область|2|100
+Башкортостан|2|100
+Белгородская область|2|100
+Брянская область|2|100
+Бурятия|2|100
+Владимирская область|2|100
+Волгоградская область|2|100
+Вологодская область|2|100
+Воронежская область|2|100
+Дагестан|2|100
+другой регион|2|100
+Еврейская АО|2|100
+Забайкальский край|2|100
+Ивановская область|2|100
+Ингушетия|2|100
+Иркутская область|2|100
+Кабардино-Балкария|2|100
+Калининградская область|2|100
+Калмыкия|2|100
+Калужская область|2|100
+Камчатский край|2|100
+Карачаево-Черкесия|2|100
+Карелия|2|100
+Кемеровская область|2|100
+Кировская область|2|100
+Коми|2|100
+Костромская область|2|100
+Краснодарский край|2|100
+Красноярский край|2|100
+Крым|2|100
+Курганская область|2|100
+Курская область|2|100
+Ленинградская область|2|100
+Липецкая область|2|100
+Магаданская область|2|100
+Марий Эл|2|100
+Мордовия|2|100
+Москва|2|100
+Московская область|2|100
+Мурманская область|2|100
+Ненецкий АО|2|100
+Нижегородская область|2|100
+Новгородская область|2|100
+Новосибирская область|2|100
+Омская область|2|100
+Оренбургская область|2|100
+Орловская область|2|100
+Пензенская область|2|100
+Пермский край|2|100
+Приморский край|2|100
+Псковская область|2|100
+Республика Алтай|2|100
+Ростовская область|2|100
+Рязанская область|2|100
+Самарская область|2|100
+Санкт-Петербург|2|100
+Саратовская область|2|100
+Саха (Якутия)|2|100
+Сахалинская область|2|100
+Свердловская область|2|100
+Северная Осетия|2|100
+Смоленская область|2|100
+Ставропольский край|2|100
+Тамбовская область|2|100
+Татарстан|2|100
+Тверская область|2|100
+Томская область|2|100
+Тульская область|2|100
+Тыва|2|100
+Тюменская область|2|100
+Удмуртия|2|100
+Ульяновская область|2|100
+Хабаровский край|2|100
+Хакасия|2|100
+Ханты-Мансийский АО|2|100
+Челябинская область|2|100
+Чеченская Республика|2|100
+Чувашия|2|100
+Ямало-Ненецкий АО|2|100
+Ярославская область|2|100</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -33041,6 +34310,99 @@
       <c r="U17" t="s">
         <v>8061</v>
       </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|2|100
+Алтайский край|2|100
+Амурская область|2|100
+Архангельская область|2|100
+Астраханская область|2|100
+Башкортостан|2|100
+Белгородская область|2|100
+Брянская область|2|100
+Бурятия|2|100
+Владимирская область|2|100
+Волгоградская область|2|100
+Вологодская область|2|100
+Воронежская область|2|100
+Дагестан|2|100
+другой регион|2|100
+Еврейская АО|2|100
+Забайкальский край|2|100
+Ивановская область|2|100
+Ингушетия|2|100
+Иркутская область|2|100
+Кабардино-Балкария|2|100
+Калининградская область|2|100
+Калмыкия|2|100
+Калужская область|2|100
+Камчатский край|2|100
+Карачаево-Черкесия|2|100
+Карелия|2|100
+Кемеровская область|2|100
+Кировская область|2|100
+Коми|2|100
+Костромская область|2|100
+Краснодарский край|2|100
+Красноярский край|2|100
+Крым|2|100
+Курганская область|2|100
+Курская область|2|100
+Ленинградская область|2|100
+Липецкая область|2|100
+Магаданская область|2|100
+Марий Эл|2|100
+Мордовия|2|100
+Москва|2|100
+Московская область|2|100
+Мурманская область|2|100
+Ненецкий АО|2|100
+Нижегородская область|2|100
+Новгородская область|2|100
+Новосибирская область|2|100
+Омская область|2|100
+Оренбургская область|2|100
+Орловская область|2|100
+Пензенская область|2|100
+Пермский край|2|100
+Приморский край|2|100
+Псковская область|2|100
+Республика Алтай|2|100
+Ростовская область|2|100
+Рязанская область|2|100
+Самарская область|2|100
+Санкт-Петербург|2|100
+Саратовская область|2|100
+Саха (Якутия)|2|100
+Сахалинская область|2|100
+Свердловская область|2|100
+Северная Осетия|2|100
+Смоленская область|2|100
+Ставропольский край|2|100
+Тамбовская область|2|100
+Татарстан|2|100
+Тверская область|2|100
+Томская область|2|100
+Тульская область|2|100
+Тыва|2|100
+Тюменская область|2|100
+Удмуртия|2|100
+Ульяновская область|2|100
+Хабаровский край|2|100
+Хакасия|2|100
+Ханты-Мансийский АО|2|100
+Челябинская область|2|100
+Чеченская Республика|2|100
+Чувашия|2|100
+Ямало-Ненецкий АО|2|100
+Ярославская область|2|100</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -33106,6 +34468,99 @@
       <c r="U18" t="s">
         <v>8061</v>
       </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|2|100
+Алтайский край|2|100
+Амурская область|2|100
+Архангельская область|2|100
+Астраханская область|2|100
+Башкортостан|2|100
+Белгородская область|2|100
+Брянская область|2|100
+Бурятия|2|100
+Владимирская область|2|100
+Волгоградская область|2|100
+Вологодская область|2|100
+Воронежская область|2|100
+Дагестан|2|100
+другой регион|2|100
+Еврейская АО|2|100
+Забайкальский край|2|100
+Ивановская область|2|100
+Ингушетия|2|100
+Иркутская область|2|100
+Кабардино-Балкария|2|100
+Калининградская область|2|100
+Калмыкия|2|100
+Калужская область|2|100
+Камчатский край|2|100
+Карачаево-Черкесия|2|100
+Карелия|2|100
+Кемеровская область|2|100
+Кировская область|2|100
+Коми|2|100
+Костромская область|2|100
+Краснодарский край|2|100
+Красноярский край|2|100
+Крым|2|100
+Курганская область|2|100
+Курская область|2|100
+Ленинградская область|2|100
+Липецкая область|2|100
+Магаданская область|2|100
+Марий Эл|2|100
+Мордовия|2|100
+Москва|2|100
+Московская область|2|100
+Мурманская область|2|100
+Ненецкий АО|2|100
+Нижегородская область|2|100
+Новгородская область|2|100
+Новосибирская область|2|100
+Омская область|2|100
+Оренбургская область|2|100
+Орловская область|2|100
+Пензенская область|2|100
+Пермский край|2|100
+Приморский край|2|100
+Псковская область|2|100
+Республика Алтай|2|100
+Ростовская область|2|100
+Рязанская область|2|100
+Самарская область|2|100
+Санкт-Петербург|2|100
+Саратовская область|2|100
+Саха (Якутия)|2|100
+Сахалинская область|2|100
+Свердловская область|2|100
+Северная Осетия|2|100
+Смоленская область|2|100
+Ставропольский край|2|100
+Тамбовская область|2|100
+Татарстан|2|100
+Тверская область|2|100
+Томская область|2|100
+Тульская область|2|100
+Тыва|2|100
+Тюменская область|2|100
+Удмуртия|2|100
+Ульяновская область|2|100
+Хабаровский край|2|100
+Хакасия|2|100
+Ханты-Мансийский АО|2|100
+Челябинская область|2|100
+Чеченская Республика|2|100
+Чувашия|2|100
+Ямало-Ненецкий АО|2|100
+Ярославская область|2|100</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
@@ -33171,6 +34626,99 @@
       <c r="U19" t="s">
         <v>8061</v>
       </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|2|100
+Алтайский край|2|100
+Амурская область|2|100
+Архангельская область|2|100
+Астраханская область|2|100
+Башкортостан|2|100
+Белгородская область|2|100
+Брянская область|2|100
+Бурятия|2|100
+Владимирская область|2|100
+Волгоградская область|2|100
+Вологодская область|2|100
+Воронежская область|2|100
+Дагестан|2|100
+другой регион|2|100
+Еврейская АО|2|100
+Забайкальский край|2|100
+Ивановская область|2|100
+Ингушетия|2|100
+Иркутская область|2|100
+Кабардино-Балкария|2|100
+Калининградская область|2|100
+Калмыкия|2|100
+Калужская область|2|100
+Камчатский край|2|100
+Карачаево-Черкесия|2|100
+Карелия|2|100
+Кемеровская область|2|100
+Кировская область|2|100
+Коми|2|100
+Костромская область|2|100
+Краснодарский край|2|100
+Красноярский край|2|100
+Крым|2|100
+Курганская область|2|100
+Курская область|2|100
+Ленинградская область|2|100
+Липецкая область|2|100
+Магаданская область|2|100
+Марий Эл|2|100
+Мордовия|2|100
+Москва|2|100
+Московская область|2|100
+Мурманская область|2|100
+Ненецкий АО|2|100
+Нижегородская область|2|100
+Новгородская область|2|100
+Новосибирская область|2|100
+Омская область|2|100
+Оренбургская область|2|100
+Орловская область|2|100
+Пензенская область|2|100
+Пермский край|2|100
+Приморский край|2|100
+Псковская область|2|100
+Республика Алтай|2|100
+Ростовская область|2|100
+Рязанская область|2|100
+Самарская область|2|100
+Санкт-Петербург|2|100
+Саратовская область|2|100
+Саха (Якутия)|2|100
+Сахалинская область|2|100
+Свердловская область|2|100
+Северная Осетия|2|100
+Смоленская область|2|100
+Ставропольский край|2|100
+Тамбовская область|2|100
+Татарстан|2|100
+Тверская область|2|100
+Томская область|2|100
+Тульская область|2|100
+Тыва|2|100
+Тюменская область|2|100
+Удмуртия|2|100
+Ульяновская область|2|100
+Хабаровский край|2|100
+Хакасия|2|100
+Ханты-Мансийский АО|2|100
+Челябинская область|2|100
+Чеченская Республика|2|100
+Чувашия|2|100
+Ямало-Ненецкий АО|2|100
+Ярославская область|2|100</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
@@ -33236,6 +34784,99 @@
       <c r="U20" t="s">
         <v>8061</v>
       </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|5|100
+Алтайский край|5|100
+Амурская область|5|100
+Архангельская область|5|100
+Астраханская область|5|100
+Башкортостан|5|100
+Белгородская область|5|100
+Брянская область|5|100
+Бурятия|5|100
+Владимирская область|5|100
+Волгоградская область|5|100
+Вологодская область|5|100
+Воронежская область|5|100
+Дагестан|5|100
+другой регион|5|100
+Еврейская АО|5|100
+Забайкальский край|5|100
+Ивановская область|5|100
+Ингушетия|5|100
+Иркутская область|5|100
+Кабардино-Балкария|5|100
+Калининградская область|5|100
+Калмыкия|5|100
+Калужская область|5|100
+Камчатский край|5|100
+Карачаево-Черкесия|5|100
+Карелия|5|100
+Кемеровская область|5|100
+Кировская область|5|100
+Коми|5|100
+Костромская область|5|100
+Краснодарский край|5|100
+Красноярский край|5|100
+Крым|5|100
+Курганская область|5|100
+Курская область|5|100
+Ленинградская область|5|100
+Липецкая область|5|100
+Магаданская область|5|100
+Марий Эл|5|100
+Мордовия|5|100
+Москва|5|100
+Московская область|5|100
+Мурманская область|5|100
+Ненецкий АО|5|100
+Нижегородская область|5|100
+Новгородская область|5|100
+Новосибирская область|5|100
+Омская область|5|100
+Оренбургская область|5|100
+Орловская область|5|100
+Пензенская область|5|100
+Пермский край|5|100
+Приморский край|5|100
+Псковская область|5|100
+Республика Алтай|5|100
+Ростовская область|5|100
+Рязанская область|5|100
+Самарская область|5|100
+Санкт-Петербург|5|100
+Саратовская область|5|100
+Саха (Якутия)|5|100
+Сахалинская область|5|100
+Свердловская область|5|100
+Северная Осетия|5|100
+Смоленская область|5|100
+Ставропольский край|5|100
+Тамбовская область|5|100
+Татарстан|5|100
+Тверская область|5|100
+Томская область|5|100
+Тульская область|5|100
+Тыва|5|100
+Тюменская область|5|100
+Удмуртия|5|100
+Ульяновская область|5|100
+Хабаровский край|5|100
+Хакасия|5|100
+Ханты-Мансийский АО|5|100
+Челябинская область|5|100
+Чеченская Республика|5|100
+Чувашия|5|100
+Ямало-Ненецкий АО|5|100
+Ярославская область|5|100</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
@@ -33300,6 +34941,99 @@
       </c>
       <c r="U21" t="s">
         <v>8061</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|2|100
+Алтайский край|2|100
+Амурская область|2|100
+Архангельская область|2|100
+Астраханская область|2|100
+Башкортостан|2|100
+Белгородская область|2|100
+Брянская область|2|100
+Бурятия|2|100
+Владимирская область|2|100
+Волгоградская область|2|100
+Вологодская область|2|100
+Воронежская область|2|100
+Дагестан|2|100
+другой регион|2|100
+Еврейская АО|2|100
+Забайкальский край|2|100
+Ивановская область|2|100
+Ингушетия|2|100
+Иркутская область|2|100
+Кабардино-Балкария|2|100
+Калининградская область|2|100
+Калмыкия|2|100
+Калужская область|2|100
+Камчатский край|2|100
+Карачаево-Черкесия|2|100
+Карелия|2|100
+Кемеровская область|2|100
+Кировская область|2|100
+Коми|2|100
+Костромская область|2|100
+Краснодарский край|2|100
+Красноярский край|2|100
+Крым|2|100
+Курганская область|2|100
+Курская область|2|100
+Ленинградская область|2|100
+Липецкая область|2|100
+Магаданская область|2|100
+Марий Эл|2|100
+Мордовия|2|100
+Москва|2|100
+Московская область|2|100
+Мурманская область|2|100
+Ненецкий АО|2|100
+Нижегородская область|2|100
+Новгородская область|2|100
+Новосибирская область|2|100
+Омская область|2|100
+Оренбургская область|2|100
+Орловская область|2|100
+Пензенская область|2|100
+Пермский край|2|100
+Приморский край|2|100
+Псковская область|2|100
+Республика Алтай|2|100
+Ростовская область|2|100
+Рязанская область|2|100
+Самарская область|2|100
+Санкт-Петербург|2|100
+Саратовская область|2|100
+Саха (Якутия)|2|100
+Сахалинская область|2|100
+Свердловская область|2|100
+Северная Осетия|2|100
+Смоленская область|2|100
+Ставропольский край|2|100
+Тамбовская область|2|100
+Татарстан|2|100
+Тверская область|2|100
+Томская область|2|100
+Тульская область|2|100
+Тыва|2|100
+Тюменская область|2|100
+Удмуртия|2|100
+Ульяновская область|2|100
+Хабаровский край|2|100
+Хакасия|2|100
+Ханты-Мансийский АО|2|100
+Челябинская область|2|100
+Чеченская Республика|2|100
+Чувашия|2|100
+Ямало-Ненецкий АО|2|100
+Ярославская область|2|100</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -34048,6 +35782,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|5|100
+Алтайский край|5|100
+Амурская область|5|100
+Архангельская область|5|100
+Астраханская область|5|100
+Башкортостан|5|100
+Белгородская область|5|100
+Брянская область|5|100
+Бурятия|5|100
+Владимирская область|5|100
+Волгоградская область|5|100
+Вологодская область|5|100
+Воронежская область|5|100
+Дагестан|5|100
+другой регион|5|100
+Еврейская АО|5|100
+Забайкальский край|5|100
+Ивановская область|5|100
+Ингушетия|5|100
+Иркутская область|5|100
+Кабардино-Балкария|5|100
+Калининградская область|5|100
+Калмыкия|5|100
+Калужская область|5|100
+Камчатский край|5|100
+Карачаево-Черкесия|5|100
+Карелия|5|100
+Кемеровская область|5|100
+Кировская область|5|100
+Коми|5|100
+Костромская область|5|100
+Краснодарский край|5|100
+Красноярский край|5|100
+Крым|5|100
+Курганская область|5|100
+Курская область|5|100
+Ленинградская область|5|100
+Липецкая область|5|100
+Магаданская область|5|100
+Марий Эл|5|100
+Мордовия|5|100
+Москва|5|100
+Московская область|5|100
+Мурманская область|5|100
+Ненецкий АО|5|100
+Нижегородская область|5|100
+Новгородская область|5|100
+Новосибирская область|5|100
+Омская область|5|100
+Оренбургская область|5|100
+Орловская область|5|100
+Пензенская область|5|100
+Пермский край|5|100
+Приморский край|5|100
+Псковская область|5|100
+Республика Алтай|5|100
+Ростовская область|5|100
+Рязанская область|5|100
+Самарская область|5|100
+Санкт-Петербург|5|100
+Саратовская область|5|100
+Саха (Якутия)|5|100
+Сахалинская область|5|100
+Свердловская область|5|100
+Северная Осетия|5|100
+Смоленская область|5|100
+Ставропольский край|5|100
+Тамбовская область|5|100
+Татарстан|5|100
+Тверская область|5|100
+Томская область|5|100
+Тульская область|5|100
+Тыва|5|100
+Тюменская область|5|100
+Удмуртия|5|100
+Ульяновская область|5|100
+Хабаровский край|5|100
+Хакасия|5|100
+Ханты-Мансийский АО|5|100
+Челябинская область|5|100
+Чеченская Республика|5|100
+Чувашия|5|100
+Ямало-Ненецкий АО|5|100
+Ярославская область|5|100</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
@@ -34239,6 +36066,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|5|100
+Алтайский край|5|100
+Амурская область|5|100
+Архангельская область|5|100
+Астраханская область|5|100
+Башкортостан|5|100
+Белгородская область|5|100
+Брянская область|5|100
+Бурятия|5|100
+Владимирская область|5|100
+Волгоградская область|5|100
+Вологодская область|5|100
+Воронежская область|5|100
+Дагестан|5|100
+другой регион|5|100
+Еврейская АО|5|100
+Забайкальский край|5|100
+Ивановская область|5|100
+Ингушетия|5|100
+Иркутская область|5|100
+Кабардино-Балкария|5|100
+Калининградская область|5|100
+Калмыкия|5|100
+Калужская область|5|100
+Камчатский край|5|100
+Карачаево-Черкесия|5|100
+Карелия|5|100
+Кемеровская область|5|100
+Кировская область|5|100
+Коми|5|100
+Костромская область|5|100
+Краснодарский край|5|100
+Красноярский край|5|100
+Крым|5|100
+Курганская область|5|100
+Курская область|5|100
+Ленинградская область|5|100
+Липецкая область|5|100
+Магаданская область|5|100
+Марий Эл|5|100
+Мордовия|5|100
+Москва|5|100
+Московская область|5|100
+Мурманская область|5|100
+Ненецкий АО|5|100
+Нижегородская область|5|100
+Новгородская область|5|100
+Новосибирская область|5|100
+Омская область|5|100
+Оренбургская область|5|100
+Орловская область|5|100
+Пензенская область|5|100
+Пермский край|5|100
+Приморский край|5|100
+Псковская область|5|100
+Республика Алтай|5|100
+Ростовская область|5|100
+Рязанская область|5|100
+Самарская область|5|100
+Санкт-Петербург|5|100
+Саратовская область|5|100
+Саха (Якутия)|5|100
+Сахалинская область|5|100
+Свердловская область|5|100
+Северная Осетия|5|100
+Смоленская область|5|100
+Ставропольский край|5|100
+Тамбовская область|5|100
+Татарстан|5|100
+Тверская область|5|100
+Томская область|5|100
+Тульская область|5|100
+Тыва|5|100
+Тюменская область|5|100
+Удмуртия|5|100
+Ульяновская область|5|100
+Хабаровский край|5|100
+Хакасия|5|100
+Ханты-Мансийский АО|5|100
+Челябинская область|5|100
+Чеченская Республика|5|100
+Чувашия|5|100
+Ямало-Ненецкий АО|5|100
+Ярославская область|5|100</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
@@ -34430,6 +36350,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|5|100
+Алтайский край|5|100
+Амурская область|5|100
+Архангельская область|5|100
+Астраханская область|5|100
+Башкортостан|5|100
+Белгородская область|5|100
+Брянская область|5|100
+Бурятия|5|100
+Владимирская область|5|100
+Волгоградская область|5|100
+Вологодская область|5|100
+Воронежская область|5|100
+Дагестан|5|100
+другой регион|5|100
+Еврейская АО|5|100
+Забайкальский край|5|100
+Ивановская область|5|100
+Ингушетия|5|100
+Иркутская область|5|100
+Кабардино-Балкария|5|100
+Калининградская область|5|100
+Калмыкия|5|100
+Калужская область|5|100
+Камчатский край|5|100
+Карачаево-Черкесия|5|100
+Карелия|5|100
+Кемеровская область|5|100
+Кировская область|5|100
+Коми|5|100
+Костромская область|5|100
+Краснодарский край|5|100
+Красноярский край|5|100
+Крым|5|100
+Курганская область|5|100
+Курская область|5|100
+Ленинградская область|5|100
+Липецкая область|5|100
+Магаданская область|5|100
+Марий Эл|5|100
+Мордовия|5|100
+Москва|5|100
+Московская область|5|100
+Мурманская область|5|100
+Ненецкий АО|5|100
+Нижегородская область|5|100
+Новгородская область|5|100
+Новосибирская область|5|100
+Омская область|5|100
+Оренбургская область|5|100
+Орловская область|5|100
+Пензенская область|5|100
+Пермский край|5|100
+Приморский край|5|100
+Псковская область|5|100
+Республика Алтай|5|100
+Ростовская область|5|100
+Рязанская область|5|100
+Самарская область|5|100
+Санкт-Петербург|5|100
+Саратовская область|5|100
+Саха (Якутия)|5|100
+Сахалинская область|5|100
+Свердловская область|5|100
+Северная Осетия|5|100
+Смоленская область|5|100
+Ставропольский край|5|100
+Тамбовская область|5|100
+Татарстан|5|100
+Тверская область|5|100
+Томская область|5|100
+Тульская область|5|100
+Тыва|5|100
+Тюменская область|5|100
+Удмуртия|5|100
+Ульяновская область|5|100
+Хабаровский край|5|100
+Хакасия|5|100
+Ханты-Мансийский АО|5|100
+Челябинская область|5|100
+Чеченская Республика|5|100
+Чувашия|5|100
+Ямало-Ненецкий АО|5|100
+Ярославская область|5|100</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -34624,6 +36637,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|5|100
+Алтайский край|5|100
+Амурская область|5|100
+Архангельская область|5|100
+Астраханская область|5|100
+Башкортостан|5|100
+Белгородская область|5|100
+Брянская область|5|100
+Бурятия|5|100
+Владимирская область|5|100
+Волгоградская область|5|100
+Вологодская область|5|100
+Воронежская область|5|100
+Дагестан|5|100
+другой регион|5|100
+Еврейская АО|5|100
+Забайкальский край|5|100
+Ивановская область|5|100
+Ингушетия|5|100
+Иркутская область|5|100
+Кабардино-Балкария|5|100
+Калининградская область|5|100
+Калмыкия|5|100
+Калужская область|5|100
+Камчатский край|5|100
+Карачаево-Черкесия|5|100
+Карелия|5|100
+Кемеровская область|5|100
+Кировская область|5|100
+Коми|5|100
+Костромская область|5|100
+Краснодарский край|5|100
+Красноярский край|5|100
+Крым|5|100
+Курганская область|5|100
+Курская область|5|100
+Ленинградская область|5|100
+Липецкая область|5|100
+Магаданская область|5|100
+Марий Эл|5|100
+Мордовия|5|100
+Москва|5|100
+Московская область|5|100
+Мурманская область|5|100
+Ненецкий АО|5|100
+Нижегородская область|5|100
+Новгородская область|5|100
+Новосибирская область|5|100
+Омская область|5|100
+Оренбургская область|5|100
+Орловская область|5|100
+Пензенская область|5|100
+Пермский край|5|100
+Приморский край|5|100
+Псковская область|5|100
+Республика Алтай|5|100
+Ростовская область|5|100
+Рязанская область|5|100
+Самарская область|5|100
+Санкт-Петербург|5|100
+Саратовская область|5|100
+Саха (Якутия)|5|100
+Сахалинская область|5|100
+Свердловская область|5|100
+Северная Осетия|5|100
+Смоленская область|5|100
+Ставропольский край|5|100
+Тамбовская область|5|100
+Татарстан|5|100
+Тверская область|5|100
+Томская область|5|100
+Тульская область|5|100
+Тыва|5|100
+Тюменская область|5|100
+Удмуртия|5|100
+Ульяновская область|5|100
+Хабаровский край|5|100
+Хакасия|5|100
+Ханты-Мансийский АО|5|100
+Челябинская область|5|100
+Чеченская Республика|5|100
+Чувашия|5|100
+Ямало-Ненецкий АО|5|100
+Ярославская область|5|100</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -34815,6 +36921,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|5|100
+Алтайский край|5|100
+Амурская область|5|100
+Архангельская область|5|100
+Астраханская область|5|100
+Башкортостан|5|100
+Белгородская область|5|100
+Брянская область|5|100
+Бурятия|5|100
+Владимирская область|5|100
+Волгоградская область|5|100
+Вологодская область|5|100
+Воронежская область|5|100
+Дагестан|5|100
+другой регион|5|100
+Еврейская АО|5|100
+Забайкальский край|5|100
+Ивановская область|5|100
+Ингушетия|5|100
+Иркутская область|5|100
+Кабардино-Балкария|5|100
+Калининградская область|5|100
+Калмыкия|5|100
+Калужская область|5|100
+Камчатский край|5|100
+Карачаево-Черкесия|5|100
+Карелия|5|100
+Кемеровская область|5|100
+Кировская область|5|100
+Коми|5|100
+Костромская область|5|100
+Краснодарский край|5|100
+Красноярский край|5|100
+Крым|5|100
+Курганская область|5|100
+Курская область|5|100
+Ленинградская область|5|100
+Липецкая область|5|100
+Магаданская область|5|100
+Марий Эл|5|100
+Мордовия|5|100
+Москва|5|100
+Московская область|5|100
+Мурманская область|5|100
+Ненецкий АО|5|100
+Нижегородская область|5|100
+Новгородская область|5|100
+Новосибирская область|5|100
+Омская область|5|100
+Оренбургская область|5|100
+Орловская область|5|100
+Пензенская область|5|100
+Пермский край|5|100
+Приморский край|5|100
+Псковская область|5|100
+Республика Алтай|5|100
+Ростовская область|5|100
+Рязанская область|5|100
+Самарская область|5|100
+Санкт-Петербург|5|100
+Саратовская область|5|100
+Саха (Якутия)|5|100
+Сахалинская область|5|100
+Свердловская область|5|100
+Северная Осетия|5|100
+Смоленская область|5|100
+Ставропольский край|5|100
+Тамбовская область|5|100
+Татарстан|5|100
+Тверская область|5|100
+Томская область|5|100
+Тульская область|5|100
+Тыва|5|100
+Тюменская область|5|100
+Удмуртия|5|100
+Ульяновская область|5|100
+Хабаровский край|5|100
+Хакасия|5|100
+Ханты-Мансийский АО|5|100
+Челябинская область|5|100
+Чеченская Республика|5|100
+Чувашия|5|100
+Ямало-Ненецкий АО|5|100
+Ярославская область|5|100</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -35006,6 +37205,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|5|100
+Алтайский край|5|100
+Амурская область|5|100
+Архангельская область|5|100
+Астраханская область|5|100
+Башкортостан|5|100
+Белгородская область|5|100
+Брянская область|5|100
+Бурятия|5|100
+Владимирская область|5|100
+Волгоградская область|5|100
+Вологодская область|5|100
+Воронежская область|5|100
+Дагестан|5|100
+другой регион|5|100
+Еврейская АО|5|100
+Забайкальский край|5|100
+Ивановская область|5|100
+Ингушетия|5|100
+Иркутская область|5|100
+Кабардино-Балкария|5|100
+Калининградская область|5|100
+Калмыкия|5|100
+Калужская область|5|100
+Камчатский край|5|100
+Карачаево-Черкесия|5|100
+Карелия|5|100
+Кемеровская область|5|100
+Кировская область|5|100
+Коми|5|100
+Костромская область|5|100
+Краснодарский край|5|100
+Красноярский край|5|100
+Крым|5|100
+Курганская область|5|100
+Курская область|5|100
+Ленинградская область|5|100
+Липецкая область|5|100
+Магаданская область|5|100
+Марий Эл|5|100
+Мордовия|5|100
+Москва|5|100
+Московская область|5|100
+Мурманская область|5|100
+Ненецкий АО|5|100
+Нижегородская область|5|100
+Новгородская область|5|100
+Новосибирская область|5|100
+Омская область|5|100
+Оренбургская область|5|100
+Орловская область|5|100
+Пензенская область|5|100
+Пермский край|5|100
+Приморский край|5|100
+Псковская область|5|100
+Республика Алтай|5|100
+Ростовская область|5|100
+Рязанская область|5|100
+Самарская область|5|100
+Санкт-Петербург|5|100
+Саратовская область|5|100
+Саха (Якутия)|5|100
+Сахалинская область|5|100
+Свердловская область|5|100
+Северная Осетия|5|100
+Смоленская область|5|100
+Ставропольский край|5|100
+Тамбовская область|5|100
+Татарстан|5|100
+Тверская область|5|100
+Томская область|5|100
+Тульская область|5|100
+Тыва|5|100
+Тюменская область|5|100
+Удмуртия|5|100
+Ульяновская область|5|100
+Хабаровский край|5|100
+Хакасия|5|100
+Ханты-Мансийский АО|5|100
+Челябинская область|5|100
+Чеченская Республика|5|100
+Чувашия|5|100
+Ямало-Ненецкий АО|5|100
+Ярославская область|5|100</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
@@ -35197,6 +37489,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|4|100
+Алтайский край|4|100
+Амурская область|4|100
+Архангельская область|4|100
+Астраханская область|4|100
+Башкортостан|4|100
+Белгородская область|4|100
+Брянская область|4|100
+Бурятия|4|100
+Владимирская область|4|100
+Волгоградская область|4|100
+Вологодская область|4|100
+Воронежская область|4|100
+Дагестан|4|100
+другой регион|4|100
+Еврейская АО|4|100
+Забайкальский край|4|100
+Ивановская область|4|100
+Ингушетия|4|100
+Иркутская область|4|100
+Кабардино-Балкария|4|100
+Калининградская область|4|100
+Калмыкия|4|100
+Калужская область|4|100
+Камчатский край|4|100
+Карачаево-Черкесия|4|100
+Карелия|4|100
+Кемеровская область|4|100
+Кировская область|4|100
+Коми|4|100
+Костромская область|4|100
+Краснодарский край|4|100
+Красноярский край|4|100
+Крым|4|100
+Курганская область|4|100
+Курская область|4|100
+Ленинградская область|4|100
+Липецкая область|4|100
+Магаданская область|4|100
+Марий Эл|4|100
+Мордовия|4|100
+Москва|4|100
+Московская область|4|100
+Мурманская область|4|100
+Ненецкий АО|4|100
+Нижегородская область|4|100
+Новгородская область|4|100
+Новосибирская область|4|100
+Омская область|4|100
+Оренбургская область|4|100
+Орловская область|4|100
+Пензенская область|4|100
+Пермский край|4|100
+Приморский край|4|100
+Псковская область|4|100
+Республика Алтай|4|100
+Ростовская область|4|100
+Рязанская область|4|100
+Самарская область|4|100
+Санкт-Петербург|4|100
+Саратовская область|4|100
+Саха (Якутия)|4|100
+Сахалинская область|4|100
+Свердловская область|4|100
+Северная Осетия|4|100
+Смоленская область|4|100
+Ставропольский край|4|100
+Тамбовская область|4|100
+Татарстан|4|100
+Тверская область|4|100
+Томская область|4|100
+Тульская область|4|100
+Тыва|4|100
+Тюменская область|4|100
+Удмуртия|4|100
+Ульяновская область|4|100
+Хабаровский край|4|100
+Хакасия|4|100
+Ханты-Мансийский АО|4|100
+Челябинская область|4|100
+Чеченская Республика|4|100
+Чувашия|4|100
+Ямало-Ненецкий АО|4|100
+Ярославская область|4|100</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -35388,6 +37773,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|4|100
+Алтайский край|4|100
+Амурская область|4|100
+Архангельская область|4|100
+Астраханская область|4|100
+Башкортостан|4|100
+Белгородская область|4|100
+Брянская область|4|100
+Бурятия|4|100
+Владимирская область|4|100
+Волгоградская область|4|100
+Вологодская область|4|100
+Воронежская область|4|100
+Дагестан|4|100
+другой регион|4|100
+Еврейская АО|4|100
+Забайкальский край|4|100
+Ивановская область|4|100
+Ингушетия|4|100
+Иркутская область|4|100
+Кабардино-Балкария|4|100
+Калининградская область|4|100
+Калмыкия|4|100
+Калужская область|4|100
+Камчатский край|4|100
+Карачаево-Черкесия|4|100
+Карелия|4|100
+Кемеровская область|4|100
+Кировская область|4|100
+Коми|4|100
+Костромская область|4|100
+Краснодарский край|4|100
+Красноярский край|4|100
+Крым|4|100
+Курганская область|4|100
+Курская область|4|100
+Ленинградская область|4|100
+Липецкая область|4|100
+Магаданская область|4|100
+Марий Эл|4|100
+Мордовия|4|100
+Москва|4|100
+Московская область|4|100
+Мурманская область|4|100
+Ненецкий АО|4|100
+Нижегородская область|4|100
+Новгородская область|4|100
+Новосибирская область|4|100
+Омская область|4|100
+Оренбургская область|4|100
+Орловская область|4|100
+Пензенская область|4|100
+Пермский край|4|100
+Приморский край|4|100
+Псковская область|4|100
+Республика Алтай|4|100
+Ростовская область|4|100
+Рязанская область|4|100
+Самарская область|4|100
+Санкт-Петербург|4|100
+Саратовская область|4|100
+Саха (Якутия)|4|100
+Сахалинская область|4|100
+Свердловская область|4|100
+Северная Осетия|4|100
+Смоленская область|4|100
+Ставропольский край|4|100
+Тамбовская область|4|100
+Татарстан|4|100
+Тверская область|4|100
+Томская область|4|100
+Тульская область|4|100
+Тыва|4|100
+Тюменская область|4|100
+Удмуртия|4|100
+Ульяновская область|4|100
+Хабаровский край|4|100
+Хакасия|4|100
+Ханты-Мансийский АО|4|100
+Челябинская область|4|100
+Чеченская Республика|4|100
+Чувашия|4|100
+Ямало-Ненецкий АО|4|100
+Ярославская область|4|100</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
@@ -35579,6 +38057,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|4|100
+Алтайский край|4|100
+Амурская область|4|100
+Архангельская область|4|100
+Астраханская область|4|100
+Башкортостан|4|100
+Белгородская область|4|100
+Брянская область|4|100
+Бурятия|4|100
+Владимирская область|4|100
+Волгоградская область|4|100
+Вологодская область|4|100
+Воронежская область|4|100
+Дагестан|4|100
+другой регион|4|100
+Еврейская АО|4|100
+Забайкальский край|4|100
+Ивановская область|4|100
+Ингушетия|4|100
+Иркутская область|4|100
+Кабардино-Балкария|4|100
+Калининградская область|4|100
+Калмыкия|4|100
+Калужская область|4|100
+Камчатский край|4|100
+Карачаево-Черкесия|4|100
+Карелия|4|100
+Кемеровская область|4|100
+Кировская область|4|100
+Коми|4|100
+Костромская область|4|100
+Краснодарский край|4|100
+Красноярский край|4|100
+Крым|4|100
+Курганская область|4|100
+Курская область|4|100
+Ленинградская область|4|100
+Липецкая область|4|100
+Магаданская область|4|100
+Марий Эл|4|100
+Мордовия|4|100
+Москва|4|100
+Московская область|4|100
+Мурманская область|4|100
+Ненецкий АО|4|100
+Нижегородская область|4|100
+Новгородская область|4|100
+Новосибирская область|4|100
+Омская область|4|100
+Оренбургская область|4|100
+Орловская область|4|100
+Пензенская область|4|100
+Пермский край|4|100
+Приморский край|4|100
+Псковская область|4|100
+Республика Алтай|4|100
+Ростовская область|4|100
+Рязанская область|4|100
+Самарская область|4|100
+Санкт-Петербург|4|100
+Саратовская область|4|100
+Саха (Якутия)|4|100
+Сахалинская область|4|100
+Свердловская область|4|100
+Северная Осетия|4|100
+Смоленская область|4|100
+Ставропольский край|4|100
+Тамбовская область|4|100
+Татарстан|4|100
+Тверская область|4|100
+Томская область|4|100
+Тульская область|4|100
+Тыва|4|100
+Тюменская область|4|100
+Удмуртия|4|100
+Ульяновская область|4|100
+Хабаровский край|4|100
+Хакасия|4|100
+Ханты-Мансийский АО|4|100
+Челябинская область|4|100
+Чеченская Республика|4|100
+Чувашия|4|100
+Ямало-Ненецкий АО|4|100
+Ярославская область|4|100</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
@@ -35770,6 +38341,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|5|100
+Алтайский край|5|100
+Амурская область|5|100
+Архангельская область|5|100
+Астраханская область|5|100
+Башкортостан|5|100
+Белгородская область|5|100
+Брянская область|5|100
+Бурятия|5|100
+Владимирская область|5|100
+Волгоградская область|5|100
+Вологодская область|5|100
+Воронежская область|5|100
+Дагестан|5|100
+другой регион|5|100
+Еврейская АО|5|100
+Забайкальский край|5|100
+Ивановская область|5|100
+Ингушетия|5|100
+Иркутская область|5|100
+Кабардино-Балкария|5|100
+Калининградская область|5|100
+Калмыкия|5|100
+Калужская область|5|100
+Камчатский край|5|100
+Карачаево-Черкесия|5|100
+Карелия|5|100
+Кемеровская область|5|100
+Кировская область|5|100
+Коми|5|100
+Костромская область|5|100
+Краснодарский край|5|100
+Красноярский край|5|100
+Крым|5|100
+Курганская область|5|100
+Курская область|5|100
+Ленинградская область|5|100
+Липецкая область|5|100
+Магаданская область|5|100
+Марий Эл|5|100
+Мордовия|5|100
+Москва|5|100
+Московская область|5|100
+Мурманская область|5|100
+Ненецкий АО|5|100
+Нижегородская область|5|100
+Новгородская область|5|100
+Новосибирская область|5|100
+Омская область|5|100
+Оренбургская область|5|100
+Орловская область|5|100
+Пензенская область|5|100
+Пермский край|5|100
+Приморский край|5|100
+Псковская область|5|100
+Республика Алтай|5|100
+Ростовская область|5|100
+Рязанская область|5|100
+Самарская область|5|100
+Санкт-Петербург|5|100
+Саратовская область|5|100
+Саха (Якутия)|5|100
+Сахалинская область|5|100
+Свердловская область|5|100
+Северная Осетия|5|100
+Смоленская область|5|100
+Ставропольский край|5|100
+Тамбовская область|5|100
+Татарстан|5|100
+Тверская область|5|100
+Томская область|5|100
+Тульская область|5|100
+Тыва|5|100
+Тюменская область|5|100
+Удмуртия|5|100
+Ульяновская область|5|100
+Хабаровский край|5|100
+Хакасия|5|100
+Ханты-Мансийский АО|5|100
+Челябинская область|5|100
+Чеченская Республика|5|100
+Чувашия|5|100
+Ямало-Ненецкий АО|5|100
+Ярославская область|5|100</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
@@ -35961,6 +38625,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|4|100
+Алтайский край|4|100
+Амурская область|4|100
+Архангельская область|4|100
+Астраханская область|4|100
+Башкортостан|4|100
+Белгородская область|4|100
+Брянская область|4|100
+Бурятия|4|100
+Владимирская область|4|100
+Волгоградская область|4|100
+Вологодская область|4|100
+Воронежская область|4|100
+Дагестан|4|100
+другой регион|4|100
+Еврейская АО|4|100
+Забайкальский край|4|100
+Ивановская область|4|100
+Ингушетия|4|100
+Иркутская область|4|100
+Кабардино-Балкария|4|100
+Калининградская область|4|100
+Калмыкия|4|100
+Калужская область|4|100
+Камчатский край|4|100
+Карачаево-Черкесия|4|100
+Карелия|4|100
+Кемеровская область|4|100
+Кировская область|4|100
+Коми|4|100
+Костромская область|4|100
+Краснодарский край|4|100
+Красноярский край|4|100
+Крым|4|100
+Курганская область|4|100
+Курская область|4|100
+Ленинградская область|4|100
+Липецкая область|4|100
+Магаданская область|4|100
+Марий Эл|4|100
+Мордовия|4|100
+Москва|4|100
+Московская область|4|100
+Мурманская область|4|100
+Ненецкий АО|4|100
+Нижегородская область|4|100
+Новгородская область|4|100
+Новосибирская область|4|100
+Омская область|4|100
+Оренбургская область|4|100
+Орловская область|4|100
+Пензенская область|4|100
+Пермский край|4|100
+Приморский край|4|100
+Псковская область|4|100
+Республика Алтай|4|100
+Ростовская область|4|100
+Рязанская область|4|100
+Самарская область|4|100
+Санкт-Петербург|4|100
+Саратовская область|4|100
+Саха (Якутия)|4|100
+Сахалинская область|4|100
+Свердловская область|4|100
+Северная Осетия|4|100
+Смоленская область|4|100
+Ставропольский край|4|100
+Тамбовская область|4|100
+Татарстан|4|100
+Тверская область|4|100
+Томская область|4|100
+Тульская область|4|100
+Тыва|4|100
+Тюменская область|4|100
+Удмуртия|4|100
+Ульяновская область|4|100
+Хабаровский край|4|100
+Хакасия|4|100
+Ханты-Мансийский АО|4|100
+Челябинская область|4|100
+Чеченская Республика|4|100
+Чувашия|4|100
+Ямало-Ненецкий АО|4|100
+Ярославская область|4|100</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -36152,6 +38909,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|4|100
+Алтайский край|4|100
+Амурская область|4|100
+Архангельская область|4|100
+Астраханская область|4|100
+Башкортостан|4|100
+Белгородская область|4|100
+Брянская область|4|100
+Бурятия|4|100
+Владимирская область|4|100
+Волгоградская область|4|100
+Вологодская область|4|100
+Воронежская область|4|100
+Дагестан|4|100
+другой регион|4|100
+Еврейская АО|4|100
+Забайкальский край|4|100
+Ивановская область|4|100
+Ингушетия|4|100
+Иркутская область|4|100
+Кабардино-Балкария|4|100
+Калининградская область|4|100
+Калмыкия|4|100
+Калужская область|4|100
+Камчатский край|4|100
+Карачаево-Черкесия|4|100
+Карелия|4|100
+Кемеровская область|4|100
+Кировская область|4|100
+Коми|4|100
+Костромская область|4|100
+Краснодарский край|4|100
+Красноярский край|4|100
+Крым|4|100
+Курганская область|4|100
+Курская область|4|100
+Ленинградская область|4|100
+Липецкая область|4|100
+Магаданская область|4|100
+Марий Эл|4|100
+Мордовия|4|100
+Москва|4|100
+Московская область|4|100
+Мурманская область|4|100
+Ненецкий АО|4|100
+Нижегородская область|4|100
+Новгородская область|4|100
+Новосибирская область|4|100
+Омская область|4|100
+Оренбургская область|4|100
+Орловская область|4|100
+Пензенская область|4|100
+Пермский край|4|100
+Приморский край|4|100
+Псковская область|4|100
+Республика Алтай|4|100
+Ростовская область|4|100
+Рязанская область|4|100
+Самарская область|4|100
+Санкт-Петербург|4|100
+Саратовская область|4|100
+Саха (Якутия)|4|100
+Сахалинская область|4|100
+Свердловская область|4|100
+Северная Осетия|4|100
+Смоленская область|4|100
+Ставропольский край|4|100
+Тамбовская область|4|100
+Татарстан|4|100
+Тверская область|4|100
+Томская область|4|100
+Тульская область|4|100
+Тыва|4|100
+Тюменская область|4|100
+Удмуртия|4|100
+Ульяновская область|4|100
+Хабаровский край|4|100
+Хакасия|4|100
+Ханты-Мансийский АО|4|100
+Челябинская область|4|100
+Чеченская Республика|4|100
+Чувашия|4|100
+Ямало-Ненецкий АО|4|100
+Ярославская область|4|100</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -36343,6 +39193,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|4|100
+Алтайский край|4|100
+Амурская область|4|100
+Архангельская область|4|100
+Астраханская область|4|100
+Башкортостан|4|100
+Белгородская область|4|100
+Брянская область|4|100
+Бурятия|4|100
+Владимирская область|4|100
+Волгоградская область|4|100
+Вологодская область|4|100
+Воронежская область|4|100
+Дагестан|4|100
+другой регион|4|100
+Еврейская АО|4|100
+Забайкальский край|4|100
+Ивановская область|4|100
+Ингушетия|4|100
+Иркутская область|4|100
+Кабардино-Балкария|4|100
+Калининградская область|4|100
+Калмыкия|4|100
+Калужская область|4|100
+Камчатский край|4|100
+Карачаево-Черкесия|4|100
+Карелия|4|100
+Кемеровская область|4|100
+Кировская область|4|100
+Коми|4|100
+Костромская область|4|100
+Краснодарский край|4|100
+Красноярский край|4|100
+Крым|4|100
+Курганская область|4|100
+Курская область|4|100
+Ленинградская область|4|100
+Липецкая область|4|100
+Магаданская область|4|100
+Марий Эл|4|100
+Мордовия|4|100
+Москва|4|100
+Московская область|4|100
+Мурманская область|4|100
+Ненецкий АО|4|100
+Нижегородская область|4|100
+Новгородская область|4|100
+Новосибирская область|4|100
+Омская область|4|100
+Оренбургская область|4|100
+Орловская область|4|100
+Пензенская область|4|100
+Пермский край|4|100
+Приморский край|4|100
+Псковская область|4|100
+Республика Алтай|4|100
+Ростовская область|4|100
+Рязанская область|4|100
+Самарская область|4|100
+Санкт-Петербург|4|100
+Саратовская область|4|100
+Саха (Якутия)|4|100
+Сахалинская область|4|100
+Свердловская область|4|100
+Северная Осетия|4|100
+Смоленская область|4|100
+Ставропольский край|4|100
+Тамбовская область|4|100
+Татарстан|4|100
+Тверская область|4|100
+Томская область|4|100
+Тульская область|4|100
+Тыва|4|100
+Тюменская область|4|100
+Удмуртия|4|100
+Ульяновская область|4|100
+Хабаровский край|4|100
+Хакасия|4|100
+Ханты-Мансийский АО|4|100
+Челябинская область|4|100
+Чеченская Республика|4|100
+Чувашия|4|100
+Ямало-Ненецкий АО|4|100
+Ярославская область|4|100</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -36534,6 +39477,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|5|100
+Алтайский край|5|100
+Амурская область|5|100
+Архангельская область|5|100
+Астраханская область|5|100
+Башкортостан|5|100
+Белгородская область|5|100
+Брянская область|5|100
+Бурятия|5|100
+Владимирская область|5|100
+Волгоградская область|5|100
+Вологодская область|5|100
+Воронежская область|5|100
+Дагестан|5|100
+другой регион|5|100
+Еврейская АО|5|100
+Забайкальский край|5|100
+Ивановская область|5|100
+Ингушетия|5|100
+Иркутская область|5|100
+Кабардино-Балкария|5|100
+Калининградская область|5|100
+Калмыкия|5|100
+Калужская область|5|100
+Камчатский край|5|100
+Карачаево-Черкесия|5|100
+Карелия|5|100
+Кемеровская область|5|100
+Кировская область|5|100
+Коми|5|100
+Костромская область|5|100
+Краснодарский край|5|100
+Красноярский край|5|100
+Крым|5|100
+Курганская область|5|100
+Курская область|5|100
+Ленинградская область|5|100
+Липецкая область|5|100
+Магаданская область|5|100
+Марий Эл|5|100
+Мордовия|5|100
+Москва|5|100
+Московская область|5|100
+Мурманская область|5|100
+Ненецкий АО|5|100
+Нижегородская область|5|100
+Новгородская область|5|100
+Новосибирская область|5|100
+Омская область|5|100
+Оренбургская область|5|100
+Орловская область|5|100
+Пензенская область|5|100
+Пермский край|5|100
+Приморский край|5|100
+Псковская область|5|100
+Республика Алтай|5|100
+Ростовская область|5|100
+Рязанская область|5|100
+Самарская область|5|100
+Санкт-Петербург|5|100
+Саратовская область|5|100
+Саха (Якутия)|5|100
+Сахалинская область|5|100
+Свердловская область|5|100
+Северная Осетия|5|100
+Смоленская область|5|100
+Ставропольский край|5|100
+Тамбовская область|5|100
+Татарстан|5|100
+Тверская область|5|100
+Томская область|5|100
+Тульская область|5|100
+Тыва|5|100
+Тюменская область|5|100
+Удмуртия|5|100
+Ульяновская область|5|100
+Хабаровский край|5|100
+Хакасия|5|100
+Ханты-Мансийский АО|5|100
+Челябинская область|5|100
+Чеченская Республика|5|100
+Чувашия|5|100
+Ямало-Ненецкий АО|5|100
+Ярославская область|5|100</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
@@ -36725,6 +39761,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|5|100
+Алтайский край|5|100
+Амурская область|5|100
+Архангельская область|5|100
+Астраханская область|5|100
+Башкортостан|5|100
+Белгородская область|5|100
+Брянская область|5|100
+Бурятия|5|100
+Владимирская область|5|100
+Волгоградская область|5|100
+Вологодская область|5|100
+Воронежская область|5|100
+Дагестан|5|100
+другой регион|5|100
+Еврейская АО|5|100
+Забайкальский край|5|100
+Ивановская область|5|100
+Ингушетия|5|100
+Иркутская область|5|100
+Кабардино-Балкария|5|100
+Калининградская область|5|100
+Калмыкия|5|100
+Калужская область|5|100
+Камчатский край|5|100
+Карачаево-Черкесия|5|100
+Карелия|5|100
+Кемеровская область|5|100
+Кировская область|5|100
+Коми|5|100
+Костромская область|5|100
+Краснодарский край|5|100
+Красноярский край|5|100
+Крым|5|100
+Курганская область|5|100
+Курская область|5|100
+Ленинградская область|5|100
+Липецкая область|5|100
+Магаданская область|5|100
+Марий Эл|5|100
+Мордовия|5|100
+Москва|5|100
+Московская область|5|100
+Мурманская область|5|100
+Ненецкий АО|5|100
+Нижегородская область|5|100
+Новгородская область|5|100
+Новосибирская область|5|100
+Омская область|5|100
+Оренбургская область|5|100
+Орловская область|5|100
+Пензенская область|5|100
+Пермский край|5|100
+Приморский край|5|100
+Псковская область|5|100
+Республика Алтай|5|100
+Ростовская область|5|100
+Рязанская область|5|100
+Самарская область|5|100
+Санкт-Петербург|5|100
+Саратовская область|5|100
+Саха (Якутия)|5|100
+Сахалинская область|5|100
+Свердловская область|5|100
+Северная Осетия|5|100
+Смоленская область|5|100
+Ставропольский край|5|100
+Тамбовская область|5|100
+Татарстан|5|100
+Тверская область|5|100
+Томская область|5|100
+Тульская область|5|100
+Тыва|5|100
+Тюменская область|5|100
+Удмуртия|5|100
+Ульяновская область|5|100
+Хабаровский край|5|100
+Хакасия|5|100
+Ханты-Мансийский АО|5|100
+Челябинская область|5|100
+Чеченская Республика|5|100
+Чувашия|5|100
+Ямало-Ненецкий АО|5|100
+Ярославская область|5|100</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
@@ -36916,6 +40045,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|4|100
+Алтайский край|4|100
+Амурская область|4|100
+Архангельская область|4|100
+Астраханская область|4|100
+Башкортостан|4|100
+Белгородская область|4|100
+Брянская область|4|100
+Бурятия|4|100
+Владимирская область|4|100
+Волгоградская область|4|100
+Вологодская область|4|100
+Воронежская область|4|100
+Дагестан|4|100
+другой регион|4|100
+Еврейская АО|4|100
+Забайкальский край|4|100
+Ивановская область|4|100
+Ингушетия|4|100
+Иркутская область|4|100
+Кабардино-Балкария|4|100
+Калининградская область|4|100
+Калмыкия|4|100
+Калужская область|4|100
+Камчатский край|4|100
+Карачаево-Черкесия|4|100
+Карелия|4|100
+Кемеровская область|4|100
+Кировская область|4|100
+Коми|4|100
+Костромская область|4|100
+Краснодарский край|4|100
+Красноярский край|4|100
+Крым|4|100
+Курганская область|4|100
+Курская область|4|100
+Ленинградская область|4|100
+Липецкая область|4|100
+Магаданская область|4|100
+Марий Эл|4|100
+Мордовия|4|100
+Москва|4|100
+Московская область|4|100
+Мурманская область|4|100
+Ненецкий АО|4|100
+Нижегородская область|4|100
+Новгородская область|4|100
+Новосибирская область|4|100
+Омская область|4|100
+Оренбургская область|4|100
+Орловская область|4|100
+Пензенская область|4|100
+Пермский край|4|100
+Приморский край|4|100
+Псковская область|4|100
+Республика Алтай|4|100
+Ростовская область|4|100
+Рязанская область|4|100
+Самарская область|4|100
+Санкт-Петербург|4|100
+Саратовская область|4|100
+Саха (Якутия)|4|100
+Сахалинская область|4|100
+Свердловская область|4|100
+Северная Осетия|4|100
+Смоленская область|4|100
+Ставропольский край|4|100
+Тамбовская область|4|100
+Татарстан|4|100
+Тверская область|4|100
+Томская область|4|100
+Тульская область|4|100
+Тыва|4|100
+Тюменская область|4|100
+Удмуртия|4|100
+Ульяновская область|4|100
+Хабаровский край|4|100
+Хакасия|4|100
+Ханты-Мансийский АО|4|100
+Челябинская область|4|100
+Чеченская Республика|4|100
+Чувашия|4|100
+Ямало-Ненецкий АО|4|100
+Ярославская область|4|100</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
@@ -37107,6 +40329,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|5|100
+Алтайский край|5|100
+Амурская область|5|100
+Архангельская область|5|100
+Астраханская область|5|100
+Башкортостан|5|100
+Белгородская область|5|100
+Брянская область|5|100
+Бурятия|5|100
+Владимирская область|5|100
+Волгоградская область|5|100
+Вологодская область|5|100
+Воронежская область|5|100
+Дагестан|5|100
+другой регион|5|100
+Еврейская АО|5|100
+Забайкальский край|5|100
+Ивановская область|5|100
+Ингушетия|5|100
+Иркутская область|5|100
+Кабардино-Балкария|5|100
+Калининградская область|5|100
+Калмыкия|5|100
+Калужская область|5|100
+Камчатский край|5|100
+Карачаево-Черкесия|5|100
+Карелия|5|100
+Кемеровская область|5|100
+Кировская область|5|100
+Коми|5|100
+Костромская область|5|100
+Краснодарский край|5|100
+Красноярский край|5|100
+Крым|5|100
+Курганская область|5|100
+Курская область|5|100
+Ленинградская область|5|100
+Липецкая область|5|100
+Магаданская область|5|100
+Марий Эл|5|100
+Мордовия|5|100
+Москва|5|100
+Московская область|5|100
+Мурманская область|5|100
+Ненецкий АО|5|100
+Нижегородская область|5|100
+Новгородская область|5|100
+Новосибирская область|5|100
+Омская область|5|100
+Оренбургская область|5|100
+Орловская область|5|100
+Пензенская область|5|100
+Пермский край|5|100
+Приморский край|5|100
+Псковская область|5|100
+Республика Алтай|5|100
+Ростовская область|5|100
+Рязанская область|5|100
+Самарская область|5|100
+Санкт-Петербург|5|100
+Саратовская область|5|100
+Саха (Якутия)|5|100
+Сахалинская область|5|100
+Свердловская область|5|100
+Северная Осетия|5|100
+Смоленская область|5|100
+Ставропольский край|5|100
+Тамбовская область|5|100
+Татарстан|5|100
+Тверская область|5|100
+Томская область|5|100
+Тульская область|5|100
+Тыва|5|100
+Тюменская область|5|100
+Удмуртия|5|100
+Ульяновская область|5|100
+Хабаровский край|5|100
+Хакасия|5|100
+Ханты-Мансийский АО|5|100
+Челябинская область|5|100
+Чеченская Республика|5|100
+Чувашия|5|100
+Ямало-Ненецкий АО|5|100
+Ярославская область|5|100</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
@@ -37298,6 +40613,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|4|100
+Алтайский край|4|100
+Амурская область|4|100
+Архангельская область|4|100
+Астраханская область|4|100
+Башкортостан|4|100
+Белгородская область|4|100
+Брянская область|4|100
+Бурятия|4|100
+Владимирская область|4|100
+Волгоградская область|4|100
+Вологодская область|4|100
+Воронежская область|4|100
+Дагестан|4|100
+другой регион|4|100
+Еврейская АО|4|100
+Забайкальский край|4|100
+Ивановская область|4|100
+Ингушетия|4|100
+Иркутская область|4|100
+Кабардино-Балкария|4|100
+Калининградская область|4|100
+Калмыкия|4|100
+Калужская область|4|100
+Камчатский край|4|100
+Карачаево-Черкесия|4|100
+Карелия|4|100
+Кемеровская область|4|100
+Кировская область|4|100
+Коми|4|100
+Костромская область|4|100
+Краснодарский край|4|100
+Красноярский край|4|100
+Крым|4|100
+Курганская область|4|100
+Курская область|4|100
+Ленинградская область|4|100
+Липецкая область|4|100
+Магаданская область|4|100
+Марий Эл|4|100
+Мордовия|4|100
+Москва|4|100
+Московская область|4|100
+Мурманская область|4|100
+Ненецкий АО|4|100
+Нижегородская область|4|100
+Новгородская область|4|100
+Новосибирская область|4|100
+Омская область|4|100
+Оренбургская область|4|100
+Орловская область|4|100
+Пензенская область|4|100
+Пермский край|4|100
+Приморский край|4|100
+Псковская область|4|100
+Республика Алтай|4|100
+Ростовская область|4|100
+Рязанская область|4|100
+Самарская область|4|100
+Санкт-Петербург|4|100
+Саратовская область|4|100
+Саха (Якутия)|4|100
+Сахалинская область|4|100
+Свердловская область|4|100
+Северная Осетия|4|100
+Смоленская область|4|100
+Ставропольский край|4|100
+Тамбовская область|4|100
+Татарстан|4|100
+Тверская область|4|100
+Томская область|4|100
+Тульская область|4|100
+Тыва|4|100
+Тюменская область|4|100
+Удмуртия|4|100
+Ульяновская область|4|100
+Хабаровский край|4|100
+Хакасия|4|100
+Ханты-Мансийский АО|4|100
+Челябинская область|4|100
+Чеченская Республика|4|100
+Чувашия|4|100
+Ямало-Ненецкий АО|4|100
+Ярославская область|4|100</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
@@ -37489,6 +40897,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|4|100
+Алтайский край|4|100
+Амурская область|4|100
+Архангельская область|4|100
+Астраханская область|4|100
+Башкортостан|4|100
+Белгородская область|4|100
+Брянская область|4|100
+Бурятия|4|100
+Владимирская область|4|100
+Волгоградская область|4|100
+Вологодская область|4|100
+Воронежская область|4|100
+Дагестан|4|100
+другой регион|4|100
+Еврейская АО|4|100
+Забайкальский край|4|100
+Ивановская область|4|100
+Ингушетия|4|100
+Иркутская область|4|100
+Кабардино-Балкария|4|100
+Калининградская область|4|100
+Калмыкия|4|100
+Калужская область|4|100
+Камчатский край|4|100
+Карачаево-Черкесия|4|100
+Карелия|4|100
+Кемеровская область|4|100
+Кировская область|4|100
+Коми|4|100
+Костромская область|4|100
+Краснодарский край|4|100
+Красноярский край|4|100
+Крым|4|100
+Курганская область|4|100
+Курская область|4|100
+Ленинградская область|4|100
+Липецкая область|4|100
+Магаданская область|4|100
+Марий Эл|4|100
+Мордовия|4|100
+Москва|4|100
+Московская область|4|100
+Мурманская область|4|100
+Ненецкий АО|4|100
+Нижегородская область|4|100
+Новгородская область|4|100
+Новосибирская область|4|100
+Омская область|4|100
+Оренбургская область|4|100
+Орловская область|4|100
+Пензенская область|4|100
+Пермский край|4|100
+Приморский край|4|100
+Псковская область|4|100
+Республика Алтай|4|100
+Ростовская область|4|100
+Рязанская область|4|100
+Самарская область|4|100
+Санкт-Петербург|4|100
+Саратовская область|4|100
+Саха (Якутия)|4|100
+Сахалинская область|4|100
+Свердловская область|4|100
+Северная Осетия|4|100
+Смоленская область|4|100
+Ставропольский край|4|100
+Тамбовская область|4|100
+Татарстан|4|100
+Тверская область|4|100
+Томская область|4|100
+Тульская область|4|100
+Тыва|4|100
+Тюменская область|4|100
+Удмуртия|4|100
+Ульяновская область|4|100
+Хабаровский край|4|100
+Хакасия|4|100
+Ханты-Мансийский АО|4|100
+Челябинская область|4|100
+Чеченская Республика|4|100
+Чувашия|4|100
+Ямало-Ненецкий АО|4|100
+Ярославская область|4|100</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
@@ -37680,6 +41181,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|4|100
+Алтайский край|4|100
+Амурская область|4|100
+Архангельская область|4|100
+Астраханская область|4|100
+Башкортостан|4|100
+Белгородская область|4|100
+Брянская область|4|100
+Бурятия|4|100
+Владимирская область|4|100
+Волгоградская область|4|100
+Вологодская область|4|100
+Воронежская область|4|100
+Дагестан|4|100
+другой регион|4|100
+Еврейская АО|4|100
+Забайкальский край|4|100
+Ивановская область|4|100
+Ингушетия|4|100
+Иркутская область|4|100
+Кабардино-Балкария|4|100
+Калининградская область|4|100
+Калмыкия|4|100
+Калужская область|4|100
+Камчатский край|4|100
+Карачаево-Черкесия|4|100
+Карелия|4|100
+Кемеровская область|4|100
+Кировская область|4|100
+Коми|4|100
+Костромская область|4|100
+Краснодарский край|4|100
+Красноярский край|4|100
+Крым|4|100
+Курганская область|4|100
+Курская область|4|100
+Ленинградская область|4|100
+Липецкая область|4|100
+Магаданская область|4|100
+Марий Эл|4|100
+Мордовия|4|100
+Москва|4|100
+Московская область|4|100
+Мурманская область|4|100
+Ненецкий АО|4|100
+Нижегородская область|4|100
+Новгородская область|4|100
+Новосибирская область|4|100
+Омская область|4|100
+Оренбургская область|4|100
+Орловская область|4|100
+Пензенская область|4|100
+Пермский край|4|100
+Приморский край|4|100
+Псковская область|4|100
+Республика Алтай|4|100
+Ростовская область|4|100
+Рязанская область|4|100
+Самарская область|4|100
+Санкт-Петербург|4|100
+Саратовская область|4|100
+Саха (Якутия)|4|100
+Сахалинская область|4|100
+Свердловская область|4|100
+Северная Осетия|4|100
+Смоленская область|4|100
+Ставропольский край|4|100
+Тамбовская область|4|100
+Татарстан|4|100
+Тверская область|4|100
+Томская область|4|100
+Тульская область|4|100
+Тыва|4|100
+Тюменская область|4|100
+Удмуртия|4|100
+Ульяновская область|4|100
+Хабаровский край|4|100
+Хакасия|4|100
+Ханты-Мансийский АО|4|100
+Челябинская область|4|100
+Чеченская Республика|4|100
+Чувашия|4|100
+Ямало-Ненецкий АО|4|100
+Ярославская область|4|100</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -37915,6 +41509,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|4|100
+Алтайский край|4|100
+Амурская область|4|100
+Архангельская область|4|100
+Астраханская область|4|100
+Башкортостан|4|100
+Белгородская область|4|100
+Брянская область|4|100
+Бурятия|4|100
+Владимирская область|4|100
+Волгоградская область|4|100
+Вологодская область|4|100
+Воронежская область|4|100
+Дагестан|4|100
+другой регион|4|100
+Еврейская АО|4|100
+Забайкальский край|4|100
+Ивановская область|4|100
+Ингушетия|4|100
+Иркутская область|4|100
+Кабардино-Балкария|4|100
+Калининградская область|4|100
+Калмыкия|4|100
+Калужская область|4|100
+Камчатский край|4|100
+Карачаево-Черкесия|4|100
+Карелия|4|100
+Кемеровская область|4|100
+Кировская область|4|100
+Коми|4|100
+Костромская область|4|100
+Краснодарский край|4|100
+Красноярский край|4|100
+Крым|4|100
+Курганская область|4|100
+Курская область|4|100
+Ленинградская область|4|100
+Липецкая область|4|100
+Магаданская область|4|100
+Марий Эл|4|100
+Мордовия|4|100
+Москва|4|100
+Московская область|4|100
+Мурманская область|4|100
+Ненецкий АО|4|100
+Нижегородская область|4|100
+Новгородская область|4|100
+Новосибирская область|4|100
+Омская область|4|100
+Оренбургская область|4|100
+Орловская область|4|100
+Пензенская область|4|100
+Пермский край|4|100
+Приморский край|4|100
+Псковская область|4|100
+Республика Алтай|4|100
+Ростовская область|4|100
+Рязанская область|4|100
+Самарская область|4|100
+Санкт-Петербург|4|100
+Саратовская область|4|100
+Саха (Якутия)|4|100
+Сахалинская область|4|100
+Свердловская область|4|100
+Северная Осетия|4|100
+Смоленская область|4|100
+Ставропольский край|4|100
+Тамбовская область|4|100
+Татарстан|4|100
+Тверская область|4|100
+Томская область|4|100
+Тульская область|4|100
+Тыва|4|100
+Тюменская область|4|100
+Удмуртия|4|100
+Ульяновская область|4|100
+Хабаровский край|4|100
+Хакасия|4|100
+Ханты-Мансийский АО|4|100
+Челябинская область|4|100
+Чеченская Республика|4|100
+Чувашия|4|100
+Ямало-Ненецкий АО|4|100
+Ярославская область|4|100</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -38150,6 +41837,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|4|100
+Алтайский край|4|100
+Амурская область|4|100
+Архангельская область|4|100
+Астраханская область|4|100
+Башкортостан|4|100
+Белгородская область|4|100
+Брянская область|4|100
+Бурятия|4|100
+Владимирская область|4|100
+Волгоградская область|4|100
+Вологодская область|4|100
+Воронежская область|4|100
+Дагестан|4|100
+другой регион|4|100
+Еврейская АО|4|100
+Забайкальский край|4|100
+Ивановская область|4|100
+Ингушетия|4|100
+Иркутская область|4|100
+Кабардино-Балкария|4|100
+Калининградская область|4|100
+Калмыкия|4|100
+Калужская область|4|100
+Камчатский край|4|100
+Карачаево-Черкесия|4|100
+Карелия|4|100
+Кемеровская область|4|100
+Кировская область|4|100
+Коми|4|100
+Костромская область|4|100
+Краснодарский край|4|100
+Красноярский край|4|100
+Крым|4|100
+Курганская область|4|100
+Курская область|4|100
+Ленинградская область|4|100
+Липецкая область|4|100
+Магаданская область|4|100
+Марий Эл|4|100
+Мордовия|4|100
+Москва|4|100
+Московская область|4|100
+Мурманская область|4|100
+Ненецкий АО|4|100
+Нижегородская область|4|100
+Новгородская область|4|100
+Новосибирская область|4|100
+Омская область|4|100
+Оренбургская область|4|100
+Орловская область|4|100
+Пензенская область|4|100
+Пермский край|4|100
+Приморский край|4|100
+Псковская область|4|100
+Республика Алтай|4|100
+Ростовская область|4|100
+Рязанская область|4|100
+Самарская область|4|100
+Санкт-Петербург|4|100
+Саратовская область|4|100
+Саха (Якутия)|4|100
+Сахалинская область|4|100
+Свердловская область|4|100
+Северная Осетия|4|100
+Смоленская область|4|100
+Ставропольский край|4|100
+Тамбовская область|4|100
+Татарстан|4|100
+Тверская область|4|100
+Томская область|4|100
+Тульская область|4|100
+Тыва|4|100
+Тюменская область|4|100
+Удмуртия|4|100
+Ульяновская область|4|100
+Хабаровский край|4|100
+Хакасия|4|100
+Ханты-Мансийский АО|4|100
+Челябинская область|4|100
+Чеченская Республика|4|100
+Чувашия|4|100
+Ямало-Ненецкий АО|4|100
+Ярославская область|4|100</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -38385,6 +42165,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|4|100
+Алтайский край|4|100
+Амурская область|4|100
+Архангельская область|4|100
+Астраханская область|4|100
+Башкортостан|4|100
+Белгородская область|4|100
+Брянская область|4|100
+Бурятия|4|100
+Владимирская область|4|100
+Волгоградская область|4|100
+Вологодская область|4|100
+Воронежская область|4|100
+Дагестан|4|100
+другой регион|4|100
+Еврейская АО|4|100
+Забайкальский край|4|100
+Ивановская область|4|100
+Ингушетия|4|100
+Иркутская область|4|100
+Кабардино-Балкария|4|100
+Калининградская область|4|100
+Калмыкия|4|100
+Калужская область|4|100
+Камчатский край|4|100
+Карачаево-Черкесия|4|100
+Карелия|4|100
+Кемеровская область|4|100
+Кировская область|4|100
+Коми|4|100
+Костромская область|4|100
+Краснодарский край|4|100
+Красноярский край|4|100
+Крым|4|100
+Курганская область|4|100
+Курская область|4|100
+Ленинградская область|4|100
+Липецкая область|4|100
+Магаданская область|4|100
+Марий Эл|4|100
+Мордовия|4|100
+Москва|4|100
+Московская область|4|100
+Мурманская область|4|100
+Ненецкий АО|4|100
+Нижегородская область|4|100
+Новгородская область|4|100
+Новосибирская область|4|100
+Омская область|4|100
+Оренбургская область|4|100
+Орловская область|4|100
+Пензенская область|4|100
+Пермский край|4|100
+Приморский край|4|100
+Псковская область|4|100
+Республика Алтай|4|100
+Ростовская область|4|100
+Рязанская область|4|100
+Самарская область|4|100
+Санкт-Петербург|4|100
+Саратовская область|4|100
+Саха (Якутия)|4|100
+Сахалинская область|4|100
+Свердловская область|4|100
+Северная Осетия|4|100
+Смоленская область|4|100
+Ставропольский край|4|100
+Тамбовская область|4|100
+Татарстан|4|100
+Тверская область|4|100
+Томская область|4|100
+Тульская область|4|100
+Тыва|4|100
+Тюменская область|4|100
+Удмуртия|4|100
+Ульяновская область|4|100
+Хабаровский край|4|100
+Хакасия|4|100
+Ханты-Мансийский АО|4|100
+Челябинская область|4|100
+Чеченская Республика|4|100
+Чувашия|4|100
+Ямало-Ненецкий АО|4|100
+Ярославская область|4|100</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -38620,6 +42493,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|4|100
+Алтайский край|4|100
+Амурская область|4|100
+Архангельская область|4|100
+Астраханская область|4|100
+Башкортостан|4|100
+Белгородская область|4|100
+Брянская область|4|100
+Бурятия|4|100
+Владимирская область|4|100
+Волгоградская область|4|100
+Вологодская область|4|100
+Воронежская область|4|100
+Дагестан|4|100
+другой регион|4|100
+Еврейская АО|4|100
+Забайкальский край|4|100
+Ивановская область|4|100
+Ингушетия|4|100
+Иркутская область|4|100
+Кабардино-Балкария|4|100
+Калининградская область|4|100
+Калмыкия|4|100
+Калужская область|4|100
+Камчатский край|4|100
+Карачаево-Черкесия|4|100
+Карелия|4|100
+Кемеровская область|4|100
+Кировская область|4|100
+Коми|4|100
+Костромская область|4|100
+Краснодарский край|4|100
+Красноярский край|4|100
+Крым|4|100
+Курганская область|4|100
+Курская область|4|100
+Ленинградская область|4|100
+Липецкая область|4|100
+Магаданская область|4|100
+Марий Эл|4|100
+Мордовия|4|100
+Москва|4|100
+Московская область|4|100
+Мурманская область|4|100
+Ненецкий АО|4|100
+Нижегородская область|4|100
+Новгородская область|4|100
+Новосибирская область|4|100
+Омская область|4|100
+Оренбургская область|4|100
+Орловская область|4|100
+Пензенская область|4|100
+Пермский край|4|100
+Приморский край|4|100
+Псковская область|4|100
+Республика Алтай|4|100
+Ростовская область|4|100
+Рязанская область|4|100
+Самарская область|4|100
+Санкт-Петербург|4|100
+Саратовская область|4|100
+Саха (Якутия)|4|100
+Сахалинская область|4|100
+Свердловская область|4|100
+Северная Осетия|4|100
+Смоленская область|4|100
+Ставропольский край|4|100
+Тамбовская область|4|100
+Татарстан|4|100
+Тверская область|4|100
+Томская область|4|100
+Тульская область|4|100
+Тыва|4|100
+Тюменская область|4|100
+Удмуртия|4|100
+Ульяновская область|4|100
+Хабаровский край|4|100
+Хакасия|4|100
+Ханты-Мансийский АО|4|100
+Челябинская область|4|100
+Чеченская Республика|4|100
+Чувашия|4|100
+Ямало-Ненецкий АО|4|100
+Ярославская область|4|100</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -38855,6 +42821,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|4|100
+Алтайский край|4|100
+Амурская область|4|100
+Архангельская область|4|100
+Астраханская область|4|100
+Башкортостан|4|100
+Белгородская область|4|100
+Брянская область|4|100
+Бурятия|4|100
+Владимирская область|4|100
+Волгоградская область|4|100
+Вологодская область|4|100
+Воронежская область|4|100
+Дагестан|4|100
+другой регион|4|100
+Еврейская АО|4|100
+Забайкальский край|4|100
+Ивановская область|4|100
+Ингушетия|4|100
+Иркутская область|4|100
+Кабардино-Балкария|4|100
+Калининградская область|4|100
+Калмыкия|4|100
+Калужская область|4|100
+Камчатский край|4|100
+Карачаево-Черкесия|4|100
+Карелия|4|100
+Кемеровская область|4|100
+Кировская область|4|100
+Коми|4|100
+Костромская область|4|100
+Краснодарский край|4|100
+Красноярский край|4|100
+Крым|4|100
+Курганская область|4|100
+Курская область|4|100
+Ленинградская область|4|100
+Липецкая область|4|100
+Магаданская область|4|100
+Марий Эл|4|100
+Мордовия|4|100
+Москва|4|100
+Московская область|4|100
+Мурманская область|4|100
+Ненецкий АО|4|100
+Нижегородская область|4|100
+Новгородская область|4|100
+Новосибирская область|4|100
+Омская область|4|100
+Оренбургская область|4|100
+Орловская область|4|100
+Пензенская область|4|100
+Пермский край|4|100
+Приморский край|4|100
+Псковская область|4|100
+Республика Алтай|4|100
+Ростовская область|4|100
+Рязанская область|4|100
+Самарская область|4|100
+Санкт-Петербург|4|100
+Саратовская область|4|100
+Саха (Якутия)|4|100
+Сахалинская область|4|100
+Свердловская область|4|100
+Северная Осетия|4|100
+Смоленская область|4|100
+Ставропольский край|4|100
+Тамбовская область|4|100
+Татарстан|4|100
+Тверская область|4|100
+Томская область|4|100
+Тульская область|4|100
+Тыва|4|100
+Тюменская область|4|100
+Удмуртия|4|100
+Ульяновская область|4|100
+Хабаровский край|4|100
+Хакасия|4|100
+Ханты-Мансийский АО|4|100
+Челябинская область|4|100
+Чеченская Республика|4|100
+Чувашия|4|100
+Ямало-Ненецкий АО|4|100
+Ярославская область|4|100</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -39090,6 +43149,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|4|100
+Алтайский край|4|100
+Амурская область|4|100
+Архангельская область|4|100
+Астраханская область|4|100
+Башкортостан|4|100
+Белгородская область|4|100
+Брянская область|4|100
+Бурятия|4|100
+Владимирская область|4|100
+Волгоградская область|4|100
+Вологодская область|4|100
+Воронежская область|4|100
+Дагестан|4|100
+другой регион|4|100
+Еврейская АО|4|100
+Забайкальский край|4|100
+Ивановская область|4|100
+Ингушетия|4|100
+Иркутская область|4|100
+Кабардино-Балкария|4|100
+Калининградская область|4|100
+Калмыкия|4|100
+Калужская область|4|100
+Камчатский край|4|100
+Карачаево-Черкесия|4|100
+Карелия|4|100
+Кемеровская область|4|100
+Кировская область|4|100
+Коми|4|100
+Костромская область|4|100
+Краснодарский край|4|100
+Красноярский край|4|100
+Крым|4|100
+Курганская область|4|100
+Курская область|4|100
+Ленинградская область|4|100
+Липецкая область|4|100
+Магаданская область|4|100
+Марий Эл|4|100
+Мордовия|4|100
+Москва|4|100
+Московская область|4|100
+Мурманская область|4|100
+Ненецкий АО|4|100
+Нижегородская область|4|100
+Новгородская область|4|100
+Новосибирская область|4|100
+Омская область|4|100
+Оренбургская область|4|100
+Орловская область|4|100
+Пензенская область|4|100
+Пермский край|4|100
+Приморский край|4|100
+Псковская область|4|100
+Республика Алтай|4|100
+Ростовская область|4|100
+Рязанская область|4|100
+Самарская область|4|100
+Санкт-Петербург|4|100
+Саратовская область|4|100
+Саха (Якутия)|4|100
+Сахалинская область|4|100
+Свердловская область|4|100
+Северная Осетия|4|100
+Смоленская область|4|100
+Ставропольский край|4|100
+Тамбовская область|4|100
+Татарстан|4|100
+Тверская область|4|100
+Томская область|4|100
+Тульская область|4|100
+Тыва|4|100
+Тюменская область|4|100
+Удмуртия|4|100
+Ульяновская область|4|100
+Хабаровский край|4|100
+Хакасия|4|100
+Ханты-Мансийский АО|4|100
+Челябинская область|4|100
+Чеченская Республика|4|100
+Чувашия|4|100
+Ямало-Ненецкий АО|4|100
+Ярославская область|4|100</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -39325,6 +43477,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|4|100
+Алтайский край|4|100
+Амурская область|4|100
+Архангельская область|4|100
+Астраханская область|4|100
+Башкортостан|4|100
+Белгородская область|4|100
+Брянская область|4|100
+Бурятия|4|100
+Владимирская область|4|100
+Волгоградская область|4|100
+Вологодская область|4|100
+Воронежская область|4|100
+Дагестан|4|100
+другой регион|4|100
+Еврейская АО|4|100
+Забайкальский край|4|100
+Ивановская область|4|100
+Ингушетия|4|100
+Иркутская область|4|100
+Кабардино-Балкария|4|100
+Калининградская область|4|100
+Калмыкия|4|100
+Калужская область|4|100
+Камчатский край|4|100
+Карачаево-Черкесия|4|100
+Карелия|4|100
+Кемеровская область|4|100
+Кировская область|4|100
+Коми|4|100
+Костромская область|4|100
+Краснодарский край|4|100
+Красноярский край|4|100
+Крым|4|100
+Курганская область|4|100
+Курская область|4|100
+Ленинградская область|4|100
+Липецкая область|4|100
+Магаданская область|4|100
+Марий Эл|4|100
+Мордовия|4|100
+Москва|4|100
+Московская область|4|100
+Мурманская область|4|100
+Ненецкий АО|4|100
+Нижегородская область|4|100
+Новгородская область|4|100
+Новосибирская область|4|100
+Омская область|4|100
+Оренбургская область|4|100
+Орловская область|4|100
+Пензенская область|4|100
+Пермский край|4|100
+Приморский край|4|100
+Псковская область|4|100
+Республика Алтай|4|100
+Ростовская область|4|100
+Рязанская область|4|100
+Самарская область|4|100
+Санкт-Петербург|4|100
+Саратовская область|4|100
+Саха (Якутия)|4|100
+Сахалинская область|4|100
+Свердловская область|4|100
+Северная Осетия|4|100
+Смоленская область|4|100
+Ставропольский край|4|100
+Тамбовская область|4|100
+Татарстан|4|100
+Тверская область|4|100
+Томская область|4|100
+Тульская область|4|100
+Тыва|4|100
+Тюменская область|4|100
+Удмуртия|4|100
+Ульяновская область|4|100
+Хабаровский край|4|100
+Хакасия|4|100
+Ханты-Мансийский АО|4|100
+Челябинская область|4|100
+Чеченская Республика|4|100
+Чувашия|4|100
+Ямало-Ненецкий АО|4|100
+Ярославская область|4|100</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -39560,6 +43805,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|4|100
+Алтайский край|4|100
+Амурская область|4|100
+Архангельская область|4|100
+Астраханская область|4|100
+Башкортостан|4|100
+Белгородская область|4|100
+Брянская область|4|100
+Бурятия|4|100
+Владимирская область|4|100
+Волгоградская область|4|100
+Вологодская область|4|100
+Воронежская область|4|100
+Дагестан|4|100
+другой регион|4|100
+Еврейская АО|4|100
+Забайкальский край|4|100
+Ивановская область|4|100
+Ингушетия|4|100
+Иркутская область|4|100
+Кабардино-Балкария|4|100
+Калининградская область|4|100
+Калмыкия|4|100
+Калужская область|4|100
+Камчатский край|4|100
+Карачаево-Черкесия|4|100
+Карелия|4|100
+Кемеровская область|4|100
+Кировская область|4|100
+Коми|4|100
+Костромская область|4|100
+Краснодарский край|4|100
+Красноярский край|4|100
+Крым|4|100
+Курганская область|4|100
+Курская область|4|100
+Ленинградская область|4|100
+Липецкая область|4|100
+Магаданская область|4|100
+Марий Эл|4|100
+Мордовия|4|100
+Москва|4|100
+Московская область|4|100
+Мурманская область|4|100
+Ненецкий АО|4|100
+Нижегородская область|4|100
+Новгородская область|4|100
+Новосибирская область|4|100
+Омская область|4|100
+Оренбургская область|4|100
+Орловская область|4|100
+Пензенская область|4|100
+Пермский край|4|100
+Приморский край|4|100
+Псковская область|4|100
+Республика Алтай|4|100
+Ростовская область|4|100
+Рязанская область|4|100
+Самарская область|4|100
+Санкт-Петербург|4|100
+Саратовская область|4|100
+Саха (Якутия)|4|100
+Сахалинская область|4|100
+Свердловская область|4|100
+Северная Осетия|4|100
+Смоленская область|4|100
+Ставропольский край|4|100
+Тамбовская область|4|100
+Татарстан|4|100
+Тверская область|4|100
+Томская область|4|100
+Тульская область|4|100
+Тыва|4|100
+Тюменская область|4|100
+Удмуртия|4|100
+Ульяновская область|4|100
+Хабаровский край|4|100
+Хакасия|4|100
+Ханты-Мансийский АО|4|100
+Челябинская область|4|100
+Чеченская Республика|4|100
+Чувашия|4|100
+Ямало-Ненецкий АО|4|100
+Ярославская область|4|100</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -39795,6 +44133,99 @@
 Ярославская область|6|100</t>
         </is>
       </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|4|100
+Алтайский край|4|100
+Амурская область|4|100
+Архангельская область|4|100
+Астраханская область|4|100
+Башкортостан|4|100
+Белгородская область|4|100
+Брянская область|4|100
+Бурятия|4|100
+Владимирская область|4|100
+Волгоградская область|4|100
+Вологодская область|4|100
+Воронежская область|4|100
+Дагестан|4|100
+другой регион|4|100
+Еврейская АО|4|100
+Забайкальский край|4|100
+Ивановская область|4|100
+Ингушетия|4|100
+Иркутская область|4|100
+Кабардино-Балкария|4|100
+Калининградская область|4|100
+Калмыкия|4|100
+Калужская область|4|100
+Камчатский край|4|100
+Карачаево-Черкесия|4|100
+Карелия|4|100
+Кемеровская область|4|100
+Кировская область|4|100
+Коми|4|100
+Костромская область|4|100
+Краснодарский край|4|100
+Красноярский край|4|100
+Крым|4|100
+Курганская область|4|100
+Курская область|4|100
+Ленинградская область|4|100
+Липецкая область|4|100
+Магаданская область|4|100
+Марий Эл|4|100
+Мордовия|4|100
+Москва|4|100
+Московская область|4|100
+Мурманская область|4|100
+Ненецкий АО|4|100
+Нижегородская область|4|100
+Новгородская область|4|100
+Новосибирская область|4|100
+Омская область|4|100
+Оренбургская область|4|100
+Орловская область|4|100
+Пензенская область|4|100
+Пермский край|4|100
+Приморский край|4|100
+Псковская область|4|100
+Республика Алтай|4|100
+Ростовская область|4|100
+Рязанская область|4|100
+Самарская область|4|100
+Санкт-Петербург|4|100
+Саратовская область|4|100
+Саха (Якутия)|4|100
+Сахалинская область|4|100
+Свердловская область|4|100
+Северная Осетия|4|100
+Смоленская область|4|100
+Ставропольский край|4|100
+Тамбовская область|4|100
+Татарстан|4|100
+Тверская область|4|100
+Томская область|4|100
+Тульская область|4|100
+Тыва|4|100
+Тюменская область|4|100
+Удмуртия|4|100
+Ульяновская область|4|100
+Хабаровский край|4|100
+Хакасия|4|100
+Ханты-Мансийский АО|4|100
+Челябинская область|4|100
+Чеченская Республика|4|100
+Чувашия|4|100
+Ямало-Ненецкий АО|4|100
+Ярославская область|4|100</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -40028,6 +44459,99 @@
 Чувашия|6|100
 Ямало-Ненецкий АО|6|100
 Ярославская область|6|100</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|4|100
+Алтайский край|4|100
+Амурская область|4|100
+Архангельская область|4|100
+Астраханская область|4|100
+Башкортостан|4|100
+Белгородская область|4|100
+Брянская область|4|100
+Бурятия|4|100
+Владимирская область|4|100
+Волгоградская область|4|100
+Вологодская область|4|100
+Воронежская область|4|100
+Дагестан|4|100
+другой регион|4|100
+Еврейская АО|4|100
+Забайкальский край|4|100
+Ивановская область|4|100
+Ингушетия|4|100
+Иркутская область|4|100
+Кабардино-Балкария|4|100
+Калининградская область|4|100
+Калмыкия|4|100
+Калужская область|4|100
+Камчатский край|4|100
+Карачаево-Черкесия|4|100
+Карелия|4|100
+Кемеровская область|4|100
+Кировская область|4|100
+Коми|4|100
+Костромская область|4|100
+Краснодарский край|4|100
+Красноярский край|4|100
+Крым|4|100
+Курганская область|4|100
+Курская область|4|100
+Ленинградская область|4|100
+Липецкая область|4|100
+Магаданская область|4|100
+Марий Эл|4|100
+Мордовия|4|100
+Москва|4|100
+Московская область|4|100
+Мурманская область|4|100
+Ненецкий АО|4|100
+Нижегородская область|4|100
+Новгородская область|4|100
+Новосибирская область|4|100
+Омская область|4|100
+Оренбургская область|4|100
+Орловская область|4|100
+Пензенская область|4|100
+Пермский край|4|100
+Приморский край|4|100
+Псковская область|4|100
+Республика Алтай|4|100
+Ростовская область|4|100
+Рязанская область|4|100
+Самарская область|4|100
+Санкт-Петербург|4|100
+Саратовская область|4|100
+Саха (Якутия)|4|100
+Сахалинская область|4|100
+Свердловская область|4|100
+Северная Осетия|4|100
+Смоленская область|4|100
+Ставропольский край|4|100
+Тамбовская область|4|100
+Татарстан|4|100
+Тверская область|4|100
+Томская область|4|100
+Тульская область|4|100
+Тыва|4|100
+Тюменская область|4|100
+Удмуртия|4|100
+Ульяновская область|4|100
+Хабаровский край|4|100
+Хакасия|4|100
+Ханты-Мансийский АО|4|100
+Челябинская область|4|100
+Чеченская Республика|4|100
+Чувашия|4|100
+Ямало-Ненецкий АО|4|100
+Ярославская область|4|100</t>
         </is>
       </c>
     </row>
@@ -79394,6 +83918,16 @@
         <v>7942</v>
       </c>
       <c r="Y2" s="7"/>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Настройка цены целевого действия</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Настройка цены целевого действия: ручная</t>
+        </is>
+      </c>
     </row>
     <row r="3" s="6" customFormat="true" ht="45" customHeight="true">
       <c r="A3" s="6" t="s">
@@ -79450,6 +83984,16 @@
       <c r="R3" s="6" t="s">
         <v>43</v>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Необязательный</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
@@ -79506,6 +84050,16 @@
       <c r="R4" t="s">
         <v>44</v>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Одно значение из выпадающего списка в ячейке</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Подробнее о параметре</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -79576,6 +84130,99 @@
       </c>
       <c r="X5" t="s">
         <v>8078</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|5|100
+Алтайский край|5|100
+Амурская область|5|100
+Архангельская область|5|100
+Астраханская область|5|100
+Башкортостан|5|100
+Белгородская область|5|100
+Брянская область|5|100
+Бурятия|5|100
+Владимирская область|5|100
+Волгоградская область|5|100
+Вологодская область|5|100
+Воронежская область|5|100
+Дагестан|5|100
+другой регион|5|100
+Еврейская АО|5|100
+Забайкальский край|5|100
+Ивановская область|5|100
+Ингушетия|5|100
+Иркутская область|5|100
+Кабардино-Балкария|5|100
+Калининградская область|5|100
+Калмыкия|5|100
+Калужская область|5|100
+Камчатский край|5|100
+Карачаево-Черкесия|5|100
+Карелия|5|100
+Кемеровская область|5|100
+Кировская область|5|100
+Коми|5|100
+Костромская область|5|100
+Краснодарский край|5|100
+Красноярский край|5|100
+Крым|5|100
+Курганская область|5|100
+Курская область|5|100
+Ленинградская область|5|100
+Липецкая область|5|100
+Магаданская область|5|100
+Марий Эл|5|100
+Мордовия|5|100
+Москва|5|100
+Московская область|5|100
+Мурманская область|5|100
+Ненецкий АО|5|100
+Нижегородская область|5|100
+Новгородская область|5|100
+Новосибирская область|5|100
+Омская область|5|100
+Оренбургская область|5|100
+Орловская область|5|100
+Пензенская область|5|100
+Пермский край|5|100
+Приморский край|5|100
+Псковская область|5|100
+Республика Алтай|5|100
+Ростовская область|5|100
+Рязанская область|5|100
+Самарская область|5|100
+Санкт-Петербург|5|100
+Саратовская область|5|100
+Саха (Якутия)|5|100
+Сахалинская область|5|100
+Свердловская область|5|100
+Северная Осетия|5|100
+Смоленская область|5|100
+Ставропольский край|5|100
+Тамбовская область|5|100
+Татарстан|5|100
+Тверская область|5|100
+Томская область|5|100
+Тульская область|5|100
+Тыва|5|100
+Тюменская область|5|100
+Удмуртия|5|100
+Ульяновская область|5|100
+Хабаровский край|5|100
+Хакасия|5|100
+Ханты-Мансийский АО|5|100
+Челябинская область|5|100
+Чеченская Республика|5|100
+Чувашия|5|100
+Ямало-Ненецкий АО|5|100
+Ярославская область|5|100</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -79891,6 +84538,16 @@
         <v>7944</v>
       </c>
       <c r="V2" s="7"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Настройка цены целевого действия</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Настройка цены целевого действия: ручная</t>
+        </is>
+      </c>
     </row>
     <row r="3" s="6" customFormat="true" ht="45" customHeight="true">
       <c r="A3" s="6" t="s">
@@ -79941,6 +84598,16 @@
       <c r="P3" s="6" t="s">
         <v>39</v>
       </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Необязательный</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
@@ -79991,6 +84658,16 @@
       <c r="P4" t="s">
         <v>44</v>
       </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Одно значение из выпадающего списка в ячейке</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Подробнее о параметре</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -80055,6 +84732,99 @@
       </c>
       <c r="U5" t="s">
         <v>8060</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|5|100
+Алтайский край|5|100
+Амурская область|5|100
+Архангельская область|5|100
+Астраханская область|5|100
+Башкортостан|5|100
+Белгородская область|5|100
+Брянская область|5|100
+Бурятия|5|100
+Владимирская область|5|100
+Волгоградская область|5|100
+Вологодская область|5|100
+Воронежская область|5|100
+Дагестан|5|100
+другой регион|5|100
+Еврейская АО|5|100
+Забайкальский край|5|100
+Ивановская область|5|100
+Ингушетия|5|100
+Иркутская область|5|100
+Кабардино-Балкария|5|100
+Калининградская область|5|100
+Калмыкия|5|100
+Калужская область|5|100
+Камчатский край|5|100
+Карачаево-Черкесия|5|100
+Карелия|5|100
+Кемеровская область|5|100
+Кировская область|5|100
+Коми|5|100
+Костромская область|5|100
+Краснодарский край|5|100
+Красноярский край|5|100
+Крым|5|100
+Курганская область|5|100
+Курская область|5|100
+Ленинградская область|5|100
+Липецкая область|5|100
+Магаданская область|5|100
+Марий Эл|5|100
+Мордовия|5|100
+Москва|5|100
+Московская область|5|100
+Мурманская область|5|100
+Ненецкий АО|5|100
+Нижегородская область|5|100
+Новгородская область|5|100
+Новосибирская область|5|100
+Омская область|5|100
+Оренбургская область|5|100
+Орловская область|5|100
+Пензенская область|5|100
+Пермский край|5|100
+Приморский край|5|100
+Псковская область|5|100
+Республика Алтай|5|100
+Ростовская область|5|100
+Рязанская область|5|100
+Самарская область|5|100
+Санкт-Петербург|5|100
+Саратовская область|5|100
+Саха (Якутия)|5|100
+Сахалинская область|5|100
+Свердловская область|5|100
+Северная Осетия|5|100
+Смоленская область|5|100
+Ставропольский край|5|100
+Тамбовская область|5|100
+Татарстан|5|100
+Тверская область|5|100
+Томская область|5|100
+Тульская область|5|100
+Тыва|5|100
+Тюменская область|5|100
+Удмуртия|5|100
+Ульяновская область|5|100
+Хабаровский край|5|100
+Хакасия|5|100
+Ханты-Мансийский АО|5|100
+Челябинская область|5|100
+Чеченская Республика|5|100
+Чувашия|5|100
+Ямало-Ненецкий АО|5|100
+Ярославская область|5|100</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -80293,6 +85063,16 @@
         <v>7944</v>
       </c>
       <c r="V2" s="7"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Настройка цены целевого действия</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Настройка цены целевого действия: ручная</t>
+        </is>
+      </c>
     </row>
     <row r="3" s="6" customFormat="true" ht="45" customHeight="true">
       <c r="A3" s="6" t="s">
@@ -80343,6 +85123,16 @@
       <c r="P3" s="6" t="s">
         <v>43</v>
       </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Необязательный</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
@@ -80393,6 +85183,16 @@
       <c r="P4" s="5" t="s">
         <v>41</v>
       </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Одно значение из выпадающего списка в ячейке</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Подробнее о параметре</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -80455,6 +85255,99 @@
       <c r="U5" t="s">
         <v>8060</v>
       </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|2|100
+Алтайский край|2|100
+Амурская область|2|100
+Архангельская область|2|100
+Астраханская область|2|100
+Башкортостан|2|100
+Белгородская область|2|100
+Брянская область|2|100
+Бурятия|2|100
+Владимирская область|2|100
+Волгоградская область|2|100
+Вологодская область|2|100
+Воронежская область|2|100
+Дагестан|2|100
+другой регион|2|100
+Еврейская АО|2|100
+Забайкальский край|2|100
+Ивановская область|2|100
+Ингушетия|2|100
+Иркутская область|2|100
+Кабардино-Балкария|2|100
+Калининградская область|2|100
+Калмыкия|2|100
+Калужская область|2|100
+Камчатский край|2|100
+Карачаево-Черкесия|2|100
+Карелия|2|100
+Кемеровская область|2|100
+Кировская область|2|100
+Коми|2|100
+Костромская область|2|100
+Краснодарский край|2|100
+Красноярский край|2|100
+Крым|2|100
+Курганская область|2|100
+Курская область|2|100
+Ленинградская область|2|100
+Липецкая область|2|100
+Магаданская область|2|100
+Марий Эл|2|100
+Мордовия|2|100
+Москва|2|100
+Московская область|2|100
+Мурманская область|2|100
+Ненецкий АО|2|100
+Нижегородская область|2|100
+Новгородская область|2|100
+Новосибирская область|2|100
+Омская область|2|100
+Оренбургская область|2|100
+Орловская область|2|100
+Пензенская область|2|100
+Пермский край|2|100
+Приморский край|2|100
+Псковская область|2|100
+Республика Алтай|2|100
+Ростовская область|2|100
+Рязанская область|2|100
+Самарская область|2|100
+Санкт-Петербург|2|100
+Саратовская область|2|100
+Саха (Якутия)|2|100
+Сахалинская область|2|100
+Свердловская область|2|100
+Северная Осетия|2|100
+Смоленская область|2|100
+Ставропольский край|2|100
+Тамбовская область|2|100
+Татарстан|2|100
+Тверская область|2|100
+Томская область|2|100
+Тульская область|2|100
+Тыва|2|100
+Тюменская область|2|100
+Удмуртия|2|100
+Ульяновская область|2|100
+Хабаровский край|2|100
+Хакасия|2|100
+Ханты-Мансийский АО|2|100
+Челябинская область|2|100
+Чеченская Республика|2|100
+Чувашия|2|100
+Ямало-Ненецкий АО|2|100
+Ярославская область|2|100</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
@@ -80517,6 +85410,99 @@
       <c r="U6" t="s">
         <v>8060</v>
       </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|2|100
+Алтайский край|2|100
+Амурская область|2|100
+Архангельская область|2|100
+Астраханская область|2|100
+Башкортостан|2|100
+Белгородская область|2|100
+Брянская область|2|100
+Бурятия|2|100
+Владимирская область|2|100
+Волгоградская область|2|100
+Вологодская область|2|100
+Воронежская область|2|100
+Дагестан|2|100
+другой регион|2|100
+Еврейская АО|2|100
+Забайкальский край|2|100
+Ивановская область|2|100
+Ингушетия|2|100
+Иркутская область|2|100
+Кабардино-Балкария|2|100
+Калининградская область|2|100
+Калмыкия|2|100
+Калужская область|2|100
+Камчатский край|2|100
+Карачаево-Черкесия|2|100
+Карелия|2|100
+Кемеровская область|2|100
+Кировская область|2|100
+Коми|2|100
+Костромская область|2|100
+Краснодарский край|2|100
+Красноярский край|2|100
+Крым|2|100
+Курганская область|2|100
+Курская область|2|100
+Ленинградская область|2|100
+Липецкая область|2|100
+Магаданская область|2|100
+Марий Эл|2|100
+Мордовия|2|100
+Москва|2|100
+Московская область|2|100
+Мурманская область|2|100
+Ненецкий АО|2|100
+Нижегородская область|2|100
+Новгородская область|2|100
+Новосибирская область|2|100
+Омская область|2|100
+Оренбургская область|2|100
+Орловская область|2|100
+Пензенская область|2|100
+Пермский край|2|100
+Приморский край|2|100
+Псковская область|2|100
+Республика Алтай|2|100
+Ростовская область|2|100
+Рязанская область|2|100
+Самарская область|2|100
+Санкт-Петербург|2|100
+Саратовская область|2|100
+Саха (Якутия)|2|100
+Сахалинская область|2|100
+Свердловская область|2|100
+Северная Осетия|2|100
+Смоленская область|2|100
+Ставропольский край|2|100
+Тамбовская область|2|100
+Татарстан|2|100
+Тверская область|2|100
+Томская область|2|100
+Тульская область|2|100
+Тыва|2|100
+Тюменская область|2|100
+Удмуртия|2|100
+Ульяновская область|2|100
+Хабаровский край|2|100
+Хакасия|2|100
+Ханты-Мансийский АО|2|100
+Челябинская область|2|100
+Чеченская Республика|2|100
+Чувашия|2|100
+Ямало-Ненецкий АО|2|100
+Ярославская область|2|100</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
@@ -80579,6 +85565,99 @@
       <c r="U7" t="s">
         <v>8060</v>
       </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|2|100
+Алтайский край|2|100
+Амурская область|2|100
+Архангельская область|2|100
+Астраханская область|2|100
+Башкортостан|2|100
+Белгородская область|2|100
+Брянская область|2|100
+Бурятия|2|100
+Владимирская область|2|100
+Волгоградская область|2|100
+Вологодская область|2|100
+Воронежская область|2|100
+Дагестан|2|100
+другой регион|2|100
+Еврейская АО|2|100
+Забайкальский край|2|100
+Ивановская область|2|100
+Ингушетия|2|100
+Иркутская область|2|100
+Кабардино-Балкария|2|100
+Калининградская область|2|100
+Калмыкия|2|100
+Калужская область|2|100
+Камчатский край|2|100
+Карачаево-Черкесия|2|100
+Карелия|2|100
+Кемеровская область|2|100
+Кировская область|2|100
+Коми|2|100
+Костромская область|2|100
+Краснодарский край|2|100
+Красноярский край|2|100
+Крым|2|100
+Курганская область|2|100
+Курская область|2|100
+Ленинградская область|2|100
+Липецкая область|2|100
+Магаданская область|2|100
+Марий Эл|2|100
+Мордовия|2|100
+Москва|2|100
+Московская область|2|100
+Мурманская область|2|100
+Ненецкий АО|2|100
+Нижегородская область|2|100
+Новгородская область|2|100
+Новосибирская область|2|100
+Омская область|2|100
+Оренбургская область|2|100
+Орловская область|2|100
+Пензенская область|2|100
+Пермский край|2|100
+Приморский край|2|100
+Псковская область|2|100
+Республика Алтай|2|100
+Ростовская область|2|100
+Рязанская область|2|100
+Самарская область|2|100
+Санкт-Петербург|2|100
+Саратовская область|2|100
+Саха (Якутия)|2|100
+Сахалинская область|2|100
+Свердловская область|2|100
+Северная Осетия|2|100
+Смоленская область|2|100
+Ставропольский край|2|100
+Тамбовская область|2|100
+Татарстан|2|100
+Тверская область|2|100
+Томская область|2|100
+Тульская область|2|100
+Тыва|2|100
+Тюменская область|2|100
+Удмуртия|2|100
+Ульяновская область|2|100
+Хабаровский край|2|100
+Хакасия|2|100
+Ханты-Мансийский АО|2|100
+Челябинская область|2|100
+Чеченская Республика|2|100
+Чувашия|2|100
+Ямало-Ненецкий АО|2|100
+Ярославская область|2|100</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -80640,6 +85719,99 @@
       </c>
       <c r="U8" t="s">
         <v>8060</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Адыгея|5|100
+Алтайский край|5|100
+Амурская область|5|100
+Архангельская область|5|100
+Астраханская область|5|100
+Башкортостан|5|100
+Белгородская область|5|100
+Брянская область|5|100
+Бурятия|5|100
+Владимирская область|5|100
+Волгоградская область|5|100
+Вологодская область|5|100
+Воронежская область|5|100
+Дагестан|5|100
+другой регион|5|100
+Еврейская АО|5|100
+Забайкальский край|5|100
+Ивановская область|5|100
+Ингушетия|5|100
+Иркутская область|5|100
+Кабардино-Балкария|5|100
+Калининградская область|5|100
+Калмыкия|5|100
+Калужская область|5|100
+Камчатский край|5|100
+Карачаево-Черкесия|5|100
+Карелия|5|100
+Кемеровская область|5|100
+Кировская область|5|100
+Коми|5|100
+Костромская область|5|100
+Краснодарский край|5|100
+Красноярский край|5|100
+Крым|5|100
+Курганская область|5|100
+Курская область|5|100
+Ленинградская область|5|100
+Липецкая область|5|100
+Магаданская область|5|100
+Марий Эл|5|100
+Мордовия|5|100
+Москва|5|100
+Московская область|5|100
+Мурманская область|5|100
+Ненецкий АО|5|100
+Нижегородская область|5|100
+Новгородская область|5|100
+Новосибирская область|5|100
+Омская область|5|100
+Оренбургская область|5|100
+Орловская область|5|100
+Пензенская область|5|100
+Пермский край|5|100
+Приморский край|5|100
+Псковская область|5|100
+Республика Алтай|5|100
+Ростовская область|5|100
+Рязанская область|5|100
+Самарская область|5|100
+Санкт-Петербург|5|100
+Саратовская область|5|100
+Саха (Якутия)|5|100
+Сахалинская область|5|100
+Свердловская область|5|100
+Северная Осетия|5|100
+Смоленская область|5|100
+Ставропольский край|5|100
+Тамбовская область|5|100
+Татарстан|5|100
+Тверская область|5|100
+Томская область|5|100
+Тульская область|5|100
+Тыва|5|100
+Тюменская область|5|100
+Удмуртия|5|100
+Ульяновская область|5|100
+Хабаровский край|5|100
+Хакасия|5|100
+Ханты-Мансийский АО|5|100
+Челябинская область|5|100
+Чеченская Республика|5|100
+Чувашия|5|100
+Ямало-Ненецкий АО|5|100
+Ярославская область|5|100</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/ilya_feed.xlsx
+++ b/ilya_feed.xlsx
@@ -31614,16 +31614,6 @@
         <v>7942</v>
       </c>
       <c r="V2" s="7"/>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Настройка цены целевого действия</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Настройка цены целевого действия: ручная</t>
-        </is>
-      </c>
     </row>
     <row r="3" s="6" customFormat="true" ht="45" customHeight="true">
       <c r="A3" s="6" t="s">
@@ -31674,16 +31664,6 @@
       <c r="P3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Необязательный</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Необязательный</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
@@ -31734,16 +31714,6 @@
       <c r="P4" t="s">
         <v>44</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Одно значение из выпадающего списка в ячейке</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Подробнее о параметре</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -31808,99 +31778,6 @@
       </c>
       <c r="U5" t="s">
         <v>8063</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|5|100
-Алтайский край|5|100
-Амурская область|5|100
-Архангельская область|5|100
-Астраханская область|5|100
-Башкортостан|5|100
-Белгородская область|5|100
-Брянская область|5|100
-Бурятия|5|100
-Владимирская область|5|100
-Волгоградская область|5|100
-Вологодская область|5|100
-Воронежская область|5|100
-Дагестан|5|100
-другой регион|5|100
-Еврейская АО|5|100
-Забайкальский край|5|100
-Ивановская область|5|100
-Ингушетия|5|100
-Иркутская область|5|100
-Кабардино-Балкария|5|100
-Калининградская область|5|100
-Калмыкия|5|100
-Калужская область|5|100
-Камчатский край|5|100
-Карачаево-Черкесия|5|100
-Карелия|5|100
-Кемеровская область|5|100
-Кировская область|5|100
-Коми|5|100
-Костромская область|5|100
-Краснодарский край|5|100
-Красноярский край|5|100
-Крым|5|100
-Курганская область|5|100
-Курская область|5|100
-Ленинградская область|5|100
-Липецкая область|5|100
-Магаданская область|5|100
-Марий Эл|5|100
-Мордовия|5|100
-Москва|5|100
-Московская область|5|100
-Мурманская область|5|100
-Ненецкий АО|5|100
-Нижегородская область|5|100
-Новгородская область|5|100
-Новосибирская область|5|100
-Омская область|5|100
-Оренбургская область|5|100
-Орловская область|5|100
-Пензенская область|5|100
-Пермский край|5|100
-Приморский край|5|100
-Псковская область|5|100
-Республика Алтай|5|100
-Ростовская область|5|100
-Рязанская область|5|100
-Самарская область|5|100
-Санкт-Петербург|5|100
-Саратовская область|5|100
-Саха (Якутия)|5|100
-Сахалинская область|5|100
-Свердловская область|5|100
-Северная Осетия|5|100
-Смоленская область|5|100
-Ставропольский край|5|100
-Тамбовская область|5|100
-Татарстан|5|100
-Тверская область|5|100
-Томская область|5|100
-Тульская область|5|100
-Тыва|5|100
-Тюменская область|5|100
-Удмуртия|5|100
-Ульяновская область|5|100
-Хабаровский край|5|100
-Хакасия|5|100
-Ханты-Мансийский АО|5|100
-Челябинская область|5|100
-Чеченская Республика|5|100
-Чувашия|5|100
-Ямало-Ненецкий АО|5|100
-Ярославская область|5|100</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -32219,16 +32096,6 @@
         <v>7945</v>
       </c>
       <c r="V2" s="7"/>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Настройка цены целевого действия</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Настройка цены целевого действия: ручная</t>
-        </is>
-      </c>
     </row>
     <row r="3" s="6" customFormat="true" ht="45" customHeight="true">
       <c r="A3" s="6" t="s">
@@ -32279,16 +32146,6 @@
       <c r="P3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Необязательный</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Необязательный</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
@@ -32339,16 +32196,6 @@
       <c r="P4" t="s">
         <v>44</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Одно значение из выпадающего списка в ячейке</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Подробнее о параметре</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -32414,99 +32261,6 @@
       <c r="U5" t="s">
         <v>8061</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|2|100
-Алтайский край|2|100
-Амурская область|2|100
-Архангельская область|2|100
-Астраханская область|2|100
-Башкортостан|2|100
-Белгородская область|2|100
-Брянская область|2|100
-Бурятия|2|100
-Владимирская область|2|100
-Волгоградская область|2|100
-Вологодская область|2|100
-Воронежская область|2|100
-Дагестан|2|100
-другой регион|2|100
-Еврейская АО|2|100
-Забайкальский край|2|100
-Ивановская область|2|100
-Ингушетия|2|100
-Иркутская область|2|100
-Кабардино-Балкария|2|100
-Калининградская область|2|100
-Калмыкия|2|100
-Калужская область|2|100
-Камчатский край|2|100
-Карачаево-Черкесия|2|100
-Карелия|2|100
-Кемеровская область|2|100
-Кировская область|2|100
-Коми|2|100
-Костромская область|2|100
-Краснодарский край|2|100
-Красноярский край|2|100
-Крым|2|100
-Курганская область|2|100
-Курская область|2|100
-Ленинградская область|2|100
-Липецкая область|2|100
-Магаданская область|2|100
-Марий Эл|2|100
-Мордовия|2|100
-Москва|2|100
-Московская область|2|100
-Мурманская область|2|100
-Ненецкий АО|2|100
-Нижегородская область|2|100
-Новгородская область|2|100
-Новосибирская область|2|100
-Омская область|2|100
-Оренбургская область|2|100
-Орловская область|2|100
-Пензенская область|2|100
-Пермский край|2|100
-Приморский край|2|100
-Псковская область|2|100
-Республика Алтай|2|100
-Ростовская область|2|100
-Рязанская область|2|100
-Самарская область|2|100
-Санкт-Петербург|2|100
-Саратовская область|2|100
-Саха (Якутия)|2|100
-Сахалинская область|2|100
-Свердловская область|2|100
-Северная Осетия|2|100
-Смоленская область|2|100
-Ставропольский край|2|100
-Тамбовская область|2|100
-Татарстан|2|100
-Тверская область|2|100
-Томская область|2|100
-Тульская область|2|100
-Тыва|2|100
-Тюменская область|2|100
-Удмуртия|2|100
-Ульяновская область|2|100
-Хабаровский край|2|100
-Хакасия|2|100
-Ханты-Мансийский АО|2|100
-Челябинская область|2|100
-Чеченская Республика|2|100
-Чувашия|2|100
-Ямало-Ненецкий АО|2|100
-Ярославская область|2|100</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
@@ -32572,99 +32326,6 @@
       <c r="U6" t="s">
         <v>8061</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|2|100
-Алтайский край|2|100
-Амурская область|2|100
-Архангельская область|2|100
-Астраханская область|2|100
-Башкортостан|2|100
-Белгородская область|2|100
-Брянская область|2|100
-Бурятия|2|100
-Владимирская область|2|100
-Волгоградская область|2|100
-Вологодская область|2|100
-Воронежская область|2|100
-Дагестан|2|100
-другой регион|2|100
-Еврейская АО|2|100
-Забайкальский край|2|100
-Ивановская область|2|100
-Ингушетия|2|100
-Иркутская область|2|100
-Кабардино-Балкария|2|100
-Калининградская область|2|100
-Калмыкия|2|100
-Калужская область|2|100
-Камчатский край|2|100
-Карачаево-Черкесия|2|100
-Карелия|2|100
-Кемеровская область|2|100
-Кировская область|2|100
-Коми|2|100
-Костромская область|2|100
-Краснодарский край|2|100
-Красноярский край|2|100
-Крым|2|100
-Курганская область|2|100
-Курская область|2|100
-Ленинградская область|2|100
-Липецкая область|2|100
-Магаданская область|2|100
-Марий Эл|2|100
-Мордовия|2|100
-Москва|2|100
-Московская область|2|100
-Мурманская область|2|100
-Ненецкий АО|2|100
-Нижегородская область|2|100
-Новгородская область|2|100
-Новосибирская область|2|100
-Омская область|2|100
-Оренбургская область|2|100
-Орловская область|2|100
-Пензенская область|2|100
-Пермский край|2|100
-Приморский край|2|100
-Псковская область|2|100
-Республика Алтай|2|100
-Ростовская область|2|100
-Рязанская область|2|100
-Самарская область|2|100
-Санкт-Петербург|2|100
-Саратовская область|2|100
-Саха (Якутия)|2|100
-Сахалинская область|2|100
-Свердловская область|2|100
-Северная Осетия|2|100
-Смоленская область|2|100
-Ставропольский край|2|100
-Тамбовская область|2|100
-Татарстан|2|100
-Тверская область|2|100
-Томская область|2|100
-Тульская область|2|100
-Тыва|2|100
-Тюменская область|2|100
-Удмуртия|2|100
-Ульяновская область|2|100
-Хабаровский край|2|100
-Хакасия|2|100
-Ханты-Мансийский АО|2|100
-Челябинская область|2|100
-Чеченская Республика|2|100
-Чувашия|2|100
-Ямало-Ненецкий АО|2|100
-Ярославская область|2|100</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
@@ -32730,99 +32391,6 @@
       <c r="U7" t="s">
         <v>8061</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|2|100
-Алтайский край|2|100
-Амурская область|2|100
-Архангельская область|2|100
-Астраханская область|2|100
-Башкортостан|2|100
-Белгородская область|2|100
-Брянская область|2|100
-Бурятия|2|100
-Владимирская область|2|100
-Волгоградская область|2|100
-Вологодская область|2|100
-Воронежская область|2|100
-Дагестан|2|100
-другой регион|2|100
-Еврейская АО|2|100
-Забайкальский край|2|100
-Ивановская область|2|100
-Ингушетия|2|100
-Иркутская область|2|100
-Кабардино-Балкария|2|100
-Калининградская область|2|100
-Калмыкия|2|100
-Калужская область|2|100
-Камчатский край|2|100
-Карачаево-Черкесия|2|100
-Карелия|2|100
-Кемеровская область|2|100
-Кировская область|2|100
-Коми|2|100
-Костромская область|2|100
-Краснодарский край|2|100
-Красноярский край|2|100
-Крым|2|100
-Курганская область|2|100
-Курская область|2|100
-Ленинградская область|2|100
-Липецкая область|2|100
-Магаданская область|2|100
-Марий Эл|2|100
-Мордовия|2|100
-Москва|2|100
-Московская область|2|100
-Мурманская область|2|100
-Ненецкий АО|2|100
-Нижегородская область|2|100
-Новгородская область|2|100
-Новосибирская область|2|100
-Омская область|2|100
-Оренбургская область|2|100
-Орловская область|2|100
-Пензенская область|2|100
-Пермский край|2|100
-Приморский край|2|100
-Псковская область|2|100
-Республика Алтай|2|100
-Ростовская область|2|100
-Рязанская область|2|100
-Самарская область|2|100
-Санкт-Петербург|2|100
-Саратовская область|2|100
-Саха (Якутия)|2|100
-Сахалинская область|2|100
-Свердловская область|2|100
-Северная Осетия|2|100
-Смоленская область|2|100
-Ставропольский край|2|100
-Тамбовская область|2|100
-Татарстан|2|100
-Тверская область|2|100
-Томская область|2|100
-Тульская область|2|100
-Тыва|2|100
-Тюменская область|2|100
-Удмуртия|2|100
-Ульяновская область|2|100
-Хабаровский край|2|100
-Хакасия|2|100
-Ханты-Мансийский АО|2|100
-Челябинская область|2|100
-Чеченская Республика|2|100
-Чувашия|2|100
-Ямало-Ненецкий АО|2|100
-Ярославская область|2|100</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -32888,99 +32456,6 @@
       <c r="U8" t="s">
         <v>8061</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|2|100
-Алтайский край|2|100
-Амурская область|2|100
-Архангельская область|2|100
-Астраханская область|2|100
-Башкортостан|2|100
-Белгородская область|2|100
-Брянская область|2|100
-Бурятия|2|100
-Владимирская область|2|100
-Волгоградская область|2|100
-Вологодская область|2|100
-Воронежская область|2|100
-Дагестан|2|100
-другой регион|2|100
-Еврейская АО|2|100
-Забайкальский край|2|100
-Ивановская область|2|100
-Ингушетия|2|100
-Иркутская область|2|100
-Кабардино-Балкария|2|100
-Калининградская область|2|100
-Калмыкия|2|100
-Калужская область|2|100
-Камчатский край|2|100
-Карачаево-Черкесия|2|100
-Карелия|2|100
-Кемеровская область|2|100
-Кировская область|2|100
-Коми|2|100
-Костромская область|2|100
-Краснодарский край|2|100
-Красноярский край|2|100
-Крым|2|100
-Курганская область|2|100
-Курская область|2|100
-Ленинградская область|2|100
-Липецкая область|2|100
-Магаданская область|2|100
-Марий Эл|2|100
-Мордовия|2|100
-Москва|2|100
-Московская область|2|100
-Мурманская область|2|100
-Ненецкий АО|2|100
-Нижегородская область|2|100
-Новгородская область|2|100
-Новосибирская область|2|100
-Омская область|2|100
-Оренбургская область|2|100
-Орловская область|2|100
-Пензенская область|2|100
-Пермский край|2|100
-Приморский край|2|100
-Псковская область|2|100
-Республика Алтай|2|100
-Ростовская область|2|100
-Рязанская область|2|100
-Самарская область|2|100
-Санкт-Петербург|2|100
-Саратовская область|2|100
-Саха (Якутия)|2|100
-Сахалинская область|2|100
-Свердловская область|2|100
-Северная Осетия|2|100
-Смоленская область|2|100
-Ставропольский край|2|100
-Тамбовская область|2|100
-Татарстан|2|100
-Тверская область|2|100
-Томская область|2|100
-Тульская область|2|100
-Тыва|2|100
-Тюменская область|2|100
-Удмуртия|2|100
-Ульяновская область|2|100
-Хабаровский край|2|100
-Хакасия|2|100
-Ханты-Мансийский АО|2|100
-Челябинская область|2|100
-Чеченская Республика|2|100
-Чувашия|2|100
-Ямало-Ненецкий АО|2|100
-Ярославская область|2|100</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -33046,99 +32521,6 @@
       <c r="U9" t="s">
         <v>8061</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|2|100
-Алтайский край|2|100
-Амурская область|2|100
-Архангельская область|2|100
-Астраханская область|2|100
-Башкортостан|2|100
-Белгородская область|2|100
-Брянская область|2|100
-Бурятия|2|100
-Владимирская область|2|100
-Волгоградская область|2|100
-Вологодская область|2|100
-Воронежская область|2|100
-Дагестан|2|100
-другой регион|2|100
-Еврейская АО|2|100
-Забайкальский край|2|100
-Ивановская область|2|100
-Ингушетия|2|100
-Иркутская область|2|100
-Кабардино-Балкария|2|100
-Калининградская область|2|100
-Калмыкия|2|100
-Калужская область|2|100
-Камчатский край|2|100
-Карачаево-Черкесия|2|100
-Карелия|2|100
-Кемеровская область|2|100
-Кировская область|2|100
-Коми|2|100
-Костромская область|2|100
-Краснодарский край|2|100
-Красноярский край|2|100
-Крым|2|100
-Курганская область|2|100
-Курская область|2|100
-Ленинградская область|2|100
-Липецкая область|2|100
-Магаданская область|2|100
-Марий Эл|2|100
-Мордовия|2|100
-Москва|2|100
-Московская область|2|100
-Мурманская область|2|100
-Ненецкий АО|2|100
-Нижегородская область|2|100
-Новгородская область|2|100
-Новосибирская область|2|100
-Омская область|2|100
-Оренбургская область|2|100
-Орловская область|2|100
-Пензенская область|2|100
-Пермский край|2|100
-Приморский край|2|100
-Псковская область|2|100
-Республика Алтай|2|100
-Ростовская область|2|100
-Рязанская область|2|100
-Самарская область|2|100
-Санкт-Петербург|2|100
-Саратовская область|2|100
-Саха (Якутия)|2|100
-Сахалинская область|2|100
-Свердловская область|2|100
-Северная Осетия|2|100
-Смоленская область|2|100
-Ставропольский край|2|100
-Тамбовская область|2|100
-Татарстан|2|100
-Тверская область|2|100
-Томская область|2|100
-Тульская область|2|100
-Тыва|2|100
-Тюменская область|2|100
-Удмуртия|2|100
-Ульяновская область|2|100
-Хабаровский край|2|100
-Хакасия|2|100
-Ханты-Мансийский АО|2|100
-Челябинская область|2|100
-Чеченская Республика|2|100
-Чувашия|2|100
-Ямало-Ненецкий АО|2|100
-Ярославская область|2|100</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -33204,99 +32586,6 @@
       <c r="U10" t="s">
         <v>8061</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|2|100
-Алтайский край|2|100
-Амурская область|2|100
-Архангельская область|2|100
-Астраханская область|2|100
-Башкортостан|2|100
-Белгородская область|2|100
-Брянская область|2|100
-Бурятия|2|100
-Владимирская область|2|100
-Волгоградская область|2|100
-Вологодская область|2|100
-Воронежская область|2|100
-Дагестан|2|100
-другой регион|2|100
-Еврейская АО|2|100
-Забайкальский край|2|100
-Ивановская область|2|100
-Ингушетия|2|100
-Иркутская область|2|100
-Кабардино-Балкария|2|100
-Калининградская область|2|100
-Калмыкия|2|100
-Калужская область|2|100
-Камчатский край|2|100
-Карачаево-Черкесия|2|100
-Карелия|2|100
-Кемеровская область|2|100
-Кировская область|2|100
-Коми|2|100
-Костромская область|2|100
-Краснодарский край|2|100
-Красноярский край|2|100
-Крым|2|100
-Курганская область|2|100
-Курская область|2|100
-Ленинградская область|2|100
-Липецкая область|2|100
-Магаданская область|2|100
-Марий Эл|2|100
-Мордовия|2|100
-Москва|2|100
-Московская область|2|100
-Мурманская область|2|100
-Ненецкий АО|2|100
-Нижегородская область|2|100
-Новгородская область|2|100
-Новосибирская область|2|100
-Омская область|2|100
-Оренбургская область|2|100
-Орловская область|2|100
-Пензенская область|2|100
-Пермский край|2|100
-Приморский край|2|100
-Псковская область|2|100
-Республика Алтай|2|100
-Ростовская область|2|100
-Рязанская область|2|100
-Самарская область|2|100
-Санкт-Петербург|2|100
-Саратовская область|2|100
-Саха (Якутия)|2|100
-Сахалинская область|2|100
-Свердловская область|2|100
-Северная Осетия|2|100
-Смоленская область|2|100
-Ставропольский край|2|100
-Тамбовская область|2|100
-Татарстан|2|100
-Тверская область|2|100
-Томская область|2|100
-Тульская область|2|100
-Тыва|2|100
-Тюменская область|2|100
-Удмуртия|2|100
-Ульяновская область|2|100
-Хабаровский край|2|100
-Хакасия|2|100
-Ханты-Мансийский АО|2|100
-Челябинская область|2|100
-Чеченская Республика|2|100
-Чувашия|2|100
-Ямало-Ненецкий АО|2|100
-Ярославская область|2|100</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
@@ -33362,99 +32651,6 @@
       <c r="U11" t="s">
         <v>8061</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|5|100
-Алтайский край|5|100
-Амурская область|5|100
-Архангельская область|5|100
-Астраханская область|5|100
-Башкортостан|5|100
-Белгородская область|5|100
-Брянская область|5|100
-Бурятия|5|100
-Владимирская область|5|100
-Волгоградская область|5|100
-Вологодская область|5|100
-Воронежская область|5|100
-Дагестан|5|100
-другой регион|5|100
-Еврейская АО|5|100
-Забайкальский край|5|100
-Ивановская область|5|100
-Ингушетия|5|100
-Иркутская область|5|100
-Кабардино-Балкария|5|100
-Калининградская область|5|100
-Калмыкия|5|100
-Калужская область|5|100
-Камчатский край|5|100
-Карачаево-Черкесия|5|100
-Карелия|5|100
-Кемеровская область|5|100
-Кировская область|5|100
-Коми|5|100
-Костромская область|5|100
-Краснодарский край|5|100
-Красноярский край|5|100
-Крым|5|100
-Курганская область|5|100
-Курская область|5|100
-Ленинградская область|5|100
-Липецкая область|5|100
-Магаданская область|5|100
-Марий Эл|5|100
-Мордовия|5|100
-Москва|5|100
-Московская область|5|100
-Мурманская область|5|100
-Ненецкий АО|5|100
-Нижегородская область|5|100
-Новгородская область|5|100
-Новосибирская область|5|100
-Омская область|5|100
-Оренбургская область|5|100
-Орловская область|5|100
-Пензенская область|5|100
-Пермский край|5|100
-Приморский край|5|100
-Псковская область|5|100
-Республика Алтай|5|100
-Ростовская область|5|100
-Рязанская область|5|100
-Самарская область|5|100
-Санкт-Петербург|5|100
-Саратовская область|5|100
-Саха (Якутия)|5|100
-Сахалинская область|5|100
-Свердловская область|5|100
-Северная Осетия|5|100
-Смоленская область|5|100
-Ставропольский край|5|100
-Тамбовская область|5|100
-Татарстан|5|100
-Тверская область|5|100
-Томская область|5|100
-Тульская область|5|100
-Тыва|5|100
-Тюменская область|5|100
-Удмуртия|5|100
-Ульяновская область|5|100
-Хабаровский край|5|100
-Хакасия|5|100
-Ханты-Мансийский АО|5|100
-Челябинская область|5|100
-Чеченская Республика|5|100
-Чувашия|5|100
-Ямало-Ненецкий АО|5|100
-Ярославская область|5|100</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -33520,99 +32716,6 @@
       <c r="U12" t="s">
         <v>8061</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|2|100
-Алтайский край|2|100
-Амурская область|2|100
-Архангельская область|2|100
-Астраханская область|2|100
-Башкортостан|2|100
-Белгородская область|2|100
-Брянская область|2|100
-Бурятия|2|100
-Владимирская область|2|100
-Волгоградская область|2|100
-Вологодская область|2|100
-Воронежская область|2|100
-Дагестан|2|100
-другой регион|2|100
-Еврейская АО|2|100
-Забайкальский край|2|100
-Ивановская область|2|100
-Ингушетия|2|100
-Иркутская область|2|100
-Кабардино-Балкария|2|100
-Калининградская область|2|100
-Калмыкия|2|100
-Калужская область|2|100
-Камчатский край|2|100
-Карачаево-Черкесия|2|100
-Карелия|2|100
-Кемеровская область|2|100
-Кировская область|2|100
-Коми|2|100
-Костромская область|2|100
-Краснодарский край|2|100
-Красноярский край|2|100
-Крым|2|100
-Курганская область|2|100
-Курская область|2|100
-Ленинградская область|2|100
-Липецкая область|2|100
-Магаданская область|2|100
-Марий Эл|2|100
-Мордовия|2|100
-Москва|2|100
-Московская область|2|100
-Мурманская область|2|100
-Ненецкий АО|2|100
-Нижегородская область|2|100
-Новгородская область|2|100
-Новосибирская область|2|100
-Омская область|2|100
-Оренбургская область|2|100
-Орловская область|2|100
-Пензенская область|2|100
-Пермский край|2|100
-Приморский край|2|100
-Псковская область|2|100
-Республика Алтай|2|100
-Ростовская область|2|100
-Рязанская область|2|100
-Самарская область|2|100
-Санкт-Петербург|2|100
-Саратовская область|2|100
-Саха (Якутия)|2|100
-Сахалинская область|2|100
-Свердловская область|2|100
-Северная Осетия|2|100
-Смоленская область|2|100
-Ставропольский край|2|100
-Тамбовская область|2|100
-Татарстан|2|100
-Тверская область|2|100
-Томская область|2|100
-Тульская область|2|100
-Тыва|2|100
-Тюменская область|2|100
-Удмуртия|2|100
-Ульяновская область|2|100
-Хабаровский край|2|100
-Хакасия|2|100
-Ханты-Мансийский АО|2|100
-Челябинская область|2|100
-Чеченская Республика|2|100
-Чувашия|2|100
-Ямало-Ненецкий АО|2|100
-Ярославская область|2|100</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
@@ -33678,99 +32781,6 @@
       <c r="U13" t="s">
         <v>8061</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|2|100
-Алтайский край|2|100
-Амурская область|2|100
-Архангельская область|2|100
-Астраханская область|2|100
-Башкортостан|2|100
-Белгородская область|2|100
-Брянская область|2|100
-Бурятия|2|100
-Владимирская область|2|100
-Волгоградская область|2|100
-Вологодская область|2|100
-Воронежская область|2|100
-Дагестан|2|100
-другой регион|2|100
-Еврейская АО|2|100
-Забайкальский край|2|100
-Ивановская область|2|100
-Ингушетия|2|100
-Иркутская область|2|100
-Кабардино-Балкария|2|100
-Калининградская область|2|100
-Калмыкия|2|100
-Калужская область|2|100
-Камчатский край|2|100
-Карачаево-Черкесия|2|100
-Карелия|2|100
-Кемеровская область|2|100
-Кировская область|2|100
-Коми|2|100
-Костромская область|2|100
-Краснодарский край|2|100
-Красноярский край|2|100
-Крым|2|100
-Курганская область|2|100
-Курская область|2|100
-Ленинградская область|2|100
-Липецкая область|2|100
-Магаданская область|2|100
-Марий Эл|2|100
-Мордовия|2|100
-Москва|2|100
-Московская область|2|100
-Мурманская область|2|100
-Ненецкий АО|2|100
-Нижегородская область|2|100
-Новгородская область|2|100
-Новосибирская область|2|100
-Омская область|2|100
-Оренбургская область|2|100
-Орловская область|2|100
-Пензенская область|2|100
-Пермский край|2|100
-Приморский край|2|100
-Псковская область|2|100
-Республика Алтай|2|100
-Ростовская область|2|100
-Рязанская область|2|100
-Самарская область|2|100
-Санкт-Петербург|2|100
-Саратовская область|2|100
-Саха (Якутия)|2|100
-Сахалинская область|2|100
-Свердловская область|2|100
-Северная Осетия|2|100
-Смоленская область|2|100
-Ставропольский край|2|100
-Тамбовская область|2|100
-Татарстан|2|100
-Тверская область|2|100
-Томская область|2|100
-Тульская область|2|100
-Тыва|2|100
-Тюменская область|2|100
-Удмуртия|2|100
-Ульяновская область|2|100
-Хабаровский край|2|100
-Хакасия|2|100
-Ханты-Мансийский АО|2|100
-Челябинская область|2|100
-Чеченская Республика|2|100
-Чувашия|2|100
-Ямало-Ненецкий АО|2|100
-Ярославская область|2|100</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
@@ -33836,99 +32846,6 @@
       <c r="U14" t="s">
         <v>8061</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|2|100
-Алтайский край|2|100
-Амурская область|2|100
-Архангельская область|2|100
-Астраханская область|2|100
-Башкортостан|2|100
-Белгородская область|2|100
-Брянская область|2|100
-Бурятия|2|100
-Владимирская область|2|100
-Волгоградская область|2|100
-Вологодская область|2|100
-Воронежская область|2|100
-Дагестан|2|100
-другой регион|2|100
-Еврейская АО|2|100
-Забайкальский край|2|100
-Ивановская область|2|100
-Ингушетия|2|100
-Иркутская область|2|100
-Кабардино-Балкария|2|100
-Калининградская область|2|100
-Калмыкия|2|100
-Калужская область|2|100
-Камчатский край|2|100
-Карачаево-Черкесия|2|100
-Карелия|2|100
-Кемеровская область|2|100
-Кировская область|2|100
-Коми|2|100
-Костромская область|2|100
-Краснодарский край|2|100
-Красноярский край|2|100
-Крым|2|100
-Курганская область|2|100
-Курская область|2|100
-Ленинградская область|2|100
-Липецкая область|2|100
-Магаданская область|2|100
-Марий Эл|2|100
-Мордовия|2|100
-Москва|2|100
-Московская область|2|100
-Мурманская область|2|100
-Ненецкий АО|2|100
-Нижегородская область|2|100
-Новгородская область|2|100
-Новосибирская область|2|100
-Омская область|2|100
-Оренбургская область|2|100
-Орловская область|2|100
-Пензенская область|2|100
-Пермский край|2|100
-Приморский край|2|100
-Псковская область|2|100
-Республика Алтай|2|100
-Ростовская область|2|100
-Рязанская область|2|100
-Самарская область|2|100
-Санкт-Петербург|2|100
-Саратовская область|2|100
-Саха (Якутия)|2|100
-Сахалинская область|2|100
-Свердловская область|2|100
-Северная Осетия|2|100
-Смоленская область|2|100
-Ставропольский край|2|100
-Тамбовская область|2|100
-Татарстан|2|100
-Тверская область|2|100
-Томская область|2|100
-Тульская область|2|100
-Тыва|2|100
-Тюменская область|2|100
-Удмуртия|2|100
-Ульяновская область|2|100
-Хабаровский край|2|100
-Хакасия|2|100
-Ханты-Мансийский АО|2|100
-Челябинская область|2|100
-Чеченская Республика|2|100
-Чувашия|2|100
-Ямало-Ненецкий АО|2|100
-Ярославская область|2|100</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
@@ -33994,99 +32911,6 @@
       <c r="U15" t="s">
         <v>8061</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|2|100
-Алтайский край|2|100
-Амурская область|2|100
-Архангельская область|2|100
-Астраханская область|2|100
-Башкортостан|2|100
-Белгородская область|2|100
-Брянская область|2|100
-Бурятия|2|100
-Владимирская область|2|100
-Волгоградская область|2|100
-Вологодская область|2|100
-Воронежская область|2|100
-Дагестан|2|100
-другой регион|2|100
-Еврейская АО|2|100
-Забайкальский край|2|100
-Ивановская область|2|100
-Ингушетия|2|100
-Иркутская область|2|100
-Кабардино-Балкария|2|100
-Калининградская область|2|100
-Калмыкия|2|100
-Калужская область|2|100
-Камчатский край|2|100
-Карачаево-Черкесия|2|100
-Карелия|2|100
-Кемеровская область|2|100
-Кировская область|2|100
-Коми|2|100
-Костромская область|2|100
-Краснодарский край|2|100
-Красноярский край|2|100
-Крым|2|100
-Курганская область|2|100
-Курская область|2|100
-Ленинградская область|2|100
-Липецкая область|2|100
-Магаданская область|2|100
-Марий Эл|2|100
-Мордовия|2|100
-Москва|2|100
-Московская область|2|100
-Мурманская область|2|100
-Ненецкий АО|2|100
-Нижегородская область|2|100
-Новгородская область|2|100
-Новосибирская область|2|100
-Омская область|2|100
-Оренбургская область|2|100
-Орловская область|2|100
-Пензенская область|2|100
-Пермский край|2|100
-Приморский край|2|100
-Псковская область|2|100
-Республика Алтай|2|100
-Ростовская область|2|100
-Рязанская область|2|100
-Самарская область|2|100
-Санкт-Петербург|2|100
-Саратовская область|2|100
-Саха (Якутия)|2|100
-Сахалинская область|2|100
-Свердловская область|2|100
-Северная Осетия|2|100
-Смоленская область|2|100
-Ставропольский край|2|100
-Тамбовская область|2|100
-Татарстан|2|100
-Тверская область|2|100
-Томская область|2|100
-Тульская область|2|100
-Тыва|2|100
-Тюменская область|2|100
-Удмуртия|2|100
-Ульяновская область|2|100
-Хабаровский край|2|100
-Хакасия|2|100
-Ханты-Мансийский АО|2|100
-Челябинская область|2|100
-Чеченская Республика|2|100
-Чувашия|2|100
-Ямало-Ненецкий АО|2|100
-Ярославская область|2|100</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -34152,99 +32976,6 @@
       <c r="U16" t="s">
         <v>8061</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|2|100
-Алтайский край|2|100
-Амурская область|2|100
-Архангельская область|2|100
-Астраханская область|2|100
-Башкортостан|2|100
-Белгородская область|2|100
-Брянская область|2|100
-Бурятия|2|100
-Владимирская область|2|100
-Волгоградская область|2|100
-Вологодская область|2|100
-Воронежская область|2|100
-Дагестан|2|100
-другой регион|2|100
-Еврейская АО|2|100
-Забайкальский край|2|100
-Ивановская область|2|100
-Ингушетия|2|100
-Иркутская область|2|100
-Кабардино-Балкария|2|100
-Калининградская область|2|100
-Калмыкия|2|100
-Калужская область|2|100
-Камчатский край|2|100
-Карачаево-Черкесия|2|100
-Карелия|2|100
-Кемеровская область|2|100
-Кировская область|2|100
-Коми|2|100
-Костромская область|2|100
-Краснодарский край|2|100
-Красноярский край|2|100
-Крым|2|100
-Курганская область|2|100
-Курская область|2|100
-Ленинградская область|2|100
-Липецкая область|2|100
-Магаданская область|2|100
-Марий Эл|2|100
-Мордовия|2|100
-Москва|2|100
-Московская область|2|100
-Мурманская область|2|100
-Ненецкий АО|2|100
-Нижегородская область|2|100
-Новгородская область|2|100
-Новосибирская область|2|100
-Омская область|2|100
-Оренбургская область|2|100
-Орловская область|2|100
-Пензенская область|2|100
-Пермский край|2|100
-Приморский край|2|100
-Псковская область|2|100
-Республика Алтай|2|100
-Ростовская область|2|100
-Рязанская область|2|100
-Самарская область|2|100
-Санкт-Петербург|2|100
-Саратовская область|2|100
-Саха (Якутия)|2|100
-Сахалинская область|2|100
-Свердловская область|2|100
-Северная Осетия|2|100
-Смоленская область|2|100
-Ставропольский край|2|100
-Тамбовская область|2|100
-Татарстан|2|100
-Тверская область|2|100
-Томская область|2|100
-Тульская область|2|100
-Тыва|2|100
-Тюменская область|2|100
-Удмуртия|2|100
-Ульяновская область|2|100
-Хабаровский край|2|100
-Хакасия|2|100
-Ханты-Мансийский АО|2|100
-Челябинская область|2|100
-Чеченская Республика|2|100
-Чувашия|2|100
-Ямало-Ненецкий АО|2|100
-Ярославская область|2|100</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -34310,99 +33041,6 @@
       <c r="U17" t="s">
         <v>8061</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|2|100
-Алтайский край|2|100
-Амурская область|2|100
-Архангельская область|2|100
-Астраханская область|2|100
-Башкортостан|2|100
-Белгородская область|2|100
-Брянская область|2|100
-Бурятия|2|100
-Владимирская область|2|100
-Волгоградская область|2|100
-Вологодская область|2|100
-Воронежская область|2|100
-Дагестан|2|100
-другой регион|2|100
-Еврейская АО|2|100
-Забайкальский край|2|100
-Ивановская область|2|100
-Ингушетия|2|100
-Иркутская область|2|100
-Кабардино-Балкария|2|100
-Калининградская область|2|100
-Калмыкия|2|100
-Калужская область|2|100
-Камчатский край|2|100
-Карачаево-Черкесия|2|100
-Карелия|2|100
-Кемеровская область|2|100
-Кировская область|2|100
-Коми|2|100
-Костромская область|2|100
-Краснодарский край|2|100
-Красноярский край|2|100
-Крым|2|100
-Курганская область|2|100
-Курская область|2|100
-Ленинградская область|2|100
-Липецкая область|2|100
-Магаданская область|2|100
-Марий Эл|2|100
-Мордовия|2|100
-Москва|2|100
-Московская область|2|100
-Мурманская область|2|100
-Ненецкий АО|2|100
-Нижегородская область|2|100
-Новгородская область|2|100
-Новосибирская область|2|100
-Омская область|2|100
-Оренбургская область|2|100
-Орловская область|2|100
-Пензенская область|2|100
-Пермский край|2|100
-Приморский край|2|100
-Псковская область|2|100
-Республика Алтай|2|100
-Ростовская область|2|100
-Рязанская область|2|100
-Самарская область|2|100
-Санкт-Петербург|2|100
-Саратовская область|2|100
-Саха (Якутия)|2|100
-Сахалинская область|2|100
-Свердловская область|2|100
-Северная Осетия|2|100
-Смоленская область|2|100
-Ставропольский край|2|100
-Тамбовская область|2|100
-Татарстан|2|100
-Тверская область|2|100
-Томская область|2|100
-Тульская область|2|100
-Тыва|2|100
-Тюменская область|2|100
-Удмуртия|2|100
-Ульяновская область|2|100
-Хабаровский край|2|100
-Хакасия|2|100
-Ханты-Мансийский АО|2|100
-Челябинская область|2|100
-Чеченская Республика|2|100
-Чувашия|2|100
-Ямало-Ненецкий АО|2|100
-Ярославская область|2|100</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -34468,99 +33106,6 @@
       <c r="U18" t="s">
         <v>8061</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|2|100
-Алтайский край|2|100
-Амурская область|2|100
-Архангельская область|2|100
-Астраханская область|2|100
-Башкортостан|2|100
-Белгородская область|2|100
-Брянская область|2|100
-Бурятия|2|100
-Владимирская область|2|100
-Волгоградская область|2|100
-Вологодская область|2|100
-Воронежская область|2|100
-Дагестан|2|100
-другой регион|2|100
-Еврейская АО|2|100
-Забайкальский край|2|100
-Ивановская область|2|100
-Ингушетия|2|100
-Иркутская область|2|100
-Кабардино-Балкария|2|100
-Калининградская область|2|100
-Калмыкия|2|100
-Калужская область|2|100
-Камчатский край|2|100
-Карачаево-Черкесия|2|100
-Карелия|2|100
-Кемеровская область|2|100
-Кировская область|2|100
-Коми|2|100
-Костромская область|2|100
-Краснодарский край|2|100
-Красноярский край|2|100
-Крым|2|100
-Курганская область|2|100
-Курская область|2|100
-Ленинградская область|2|100
-Липецкая область|2|100
-Магаданская область|2|100
-Марий Эл|2|100
-Мордовия|2|100
-Москва|2|100
-Московская область|2|100
-Мурманская область|2|100
-Ненецкий АО|2|100
-Нижегородская область|2|100
-Новгородская область|2|100
-Новосибирская область|2|100
-Омская область|2|100
-Оренбургская область|2|100
-Орловская область|2|100
-Пензенская область|2|100
-Пермский край|2|100
-Приморский край|2|100
-Псковская область|2|100
-Республика Алтай|2|100
-Ростовская область|2|100
-Рязанская область|2|100
-Самарская область|2|100
-Санкт-Петербург|2|100
-Саратовская область|2|100
-Саха (Якутия)|2|100
-Сахалинская область|2|100
-Свердловская область|2|100
-Северная Осетия|2|100
-Смоленская область|2|100
-Ставропольский край|2|100
-Тамбовская область|2|100
-Татарстан|2|100
-Тверская область|2|100
-Томская область|2|100
-Тульская область|2|100
-Тыва|2|100
-Тюменская область|2|100
-Удмуртия|2|100
-Ульяновская область|2|100
-Хабаровский край|2|100
-Хакасия|2|100
-Ханты-Мансийский АО|2|100
-Челябинская область|2|100
-Чеченская Республика|2|100
-Чувашия|2|100
-Ямало-Ненецкий АО|2|100
-Ярославская область|2|100</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
@@ -34626,99 +33171,6 @@
       <c r="U19" t="s">
         <v>8061</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|2|100
-Алтайский край|2|100
-Амурская область|2|100
-Архангельская область|2|100
-Астраханская область|2|100
-Башкортостан|2|100
-Белгородская область|2|100
-Брянская область|2|100
-Бурятия|2|100
-Владимирская область|2|100
-Волгоградская область|2|100
-Вологодская область|2|100
-Воронежская область|2|100
-Дагестан|2|100
-другой регион|2|100
-Еврейская АО|2|100
-Забайкальский край|2|100
-Ивановская область|2|100
-Ингушетия|2|100
-Иркутская область|2|100
-Кабардино-Балкария|2|100
-Калининградская область|2|100
-Калмыкия|2|100
-Калужская область|2|100
-Камчатский край|2|100
-Карачаево-Черкесия|2|100
-Карелия|2|100
-Кемеровская область|2|100
-Кировская область|2|100
-Коми|2|100
-Костромская область|2|100
-Краснодарский край|2|100
-Красноярский край|2|100
-Крым|2|100
-Курганская область|2|100
-Курская область|2|100
-Ленинградская область|2|100
-Липецкая область|2|100
-Магаданская область|2|100
-Марий Эл|2|100
-Мордовия|2|100
-Москва|2|100
-Московская область|2|100
-Мурманская область|2|100
-Ненецкий АО|2|100
-Нижегородская область|2|100
-Новгородская область|2|100
-Новосибирская область|2|100
-Омская область|2|100
-Оренбургская область|2|100
-Орловская область|2|100
-Пензенская область|2|100
-Пермский край|2|100
-Приморский край|2|100
-Псковская область|2|100
-Республика Алтай|2|100
-Ростовская область|2|100
-Рязанская область|2|100
-Самарская область|2|100
-Санкт-Петербург|2|100
-Саратовская область|2|100
-Саха (Якутия)|2|100
-Сахалинская область|2|100
-Свердловская область|2|100
-Северная Осетия|2|100
-Смоленская область|2|100
-Ставропольский край|2|100
-Тамбовская область|2|100
-Татарстан|2|100
-Тверская область|2|100
-Томская область|2|100
-Тульская область|2|100
-Тыва|2|100
-Тюменская область|2|100
-Удмуртия|2|100
-Ульяновская область|2|100
-Хабаровский край|2|100
-Хакасия|2|100
-Ханты-Мансийский АО|2|100
-Челябинская область|2|100
-Чеченская Республика|2|100
-Чувашия|2|100
-Ямало-Ненецкий АО|2|100
-Ярославская область|2|100</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
@@ -34784,99 +33236,6 @@
       <c r="U20" t="s">
         <v>8061</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|5|100
-Алтайский край|5|100
-Амурская область|5|100
-Архангельская область|5|100
-Астраханская область|5|100
-Башкортостан|5|100
-Белгородская область|5|100
-Брянская область|5|100
-Бурятия|5|100
-Владимирская область|5|100
-Волгоградская область|5|100
-Вологодская область|5|100
-Воронежская область|5|100
-Дагестан|5|100
-другой регион|5|100
-Еврейская АО|5|100
-Забайкальский край|5|100
-Ивановская область|5|100
-Ингушетия|5|100
-Иркутская область|5|100
-Кабардино-Балкария|5|100
-Калининградская область|5|100
-Калмыкия|5|100
-Калужская область|5|100
-Камчатский край|5|100
-Карачаево-Черкесия|5|100
-Карелия|5|100
-Кемеровская область|5|100
-Кировская область|5|100
-Коми|5|100
-Костромская область|5|100
-Краснодарский край|5|100
-Красноярский край|5|100
-Крым|5|100
-Курганская область|5|100
-Курская область|5|100
-Ленинградская область|5|100
-Липецкая область|5|100
-Магаданская область|5|100
-Марий Эл|5|100
-Мордовия|5|100
-Москва|5|100
-Московская область|5|100
-Мурманская область|5|100
-Ненецкий АО|5|100
-Нижегородская область|5|100
-Новгородская область|5|100
-Новосибирская область|5|100
-Омская область|5|100
-Оренбургская область|5|100
-Орловская область|5|100
-Пензенская область|5|100
-Пермский край|5|100
-Приморский край|5|100
-Псковская область|5|100
-Республика Алтай|5|100
-Ростовская область|5|100
-Рязанская область|5|100
-Самарская область|5|100
-Санкт-Петербург|5|100
-Саратовская область|5|100
-Саха (Якутия)|5|100
-Сахалинская область|5|100
-Свердловская область|5|100
-Северная Осетия|5|100
-Смоленская область|5|100
-Ставропольский край|5|100
-Тамбовская область|5|100
-Татарстан|5|100
-Тверская область|5|100
-Томская область|5|100
-Тульская область|5|100
-Тыва|5|100
-Тюменская область|5|100
-Удмуртия|5|100
-Ульяновская область|5|100
-Хабаровский край|5|100
-Хакасия|5|100
-Ханты-Мансийский АО|5|100
-Челябинская область|5|100
-Чеченская Республика|5|100
-Чувашия|5|100
-Ямало-Ненецкий АО|5|100
-Ярославская область|5|100</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
@@ -34941,99 +33300,6 @@
       </c>
       <c r="U21" t="s">
         <v>8061</v>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|2|100
-Алтайский край|2|100
-Амурская область|2|100
-Архангельская область|2|100
-Астраханская область|2|100
-Башкортостан|2|100
-Белгородская область|2|100
-Брянская область|2|100
-Бурятия|2|100
-Владимирская область|2|100
-Волгоградская область|2|100
-Вологодская область|2|100
-Воронежская область|2|100
-Дагестан|2|100
-другой регион|2|100
-Еврейская АО|2|100
-Забайкальский край|2|100
-Ивановская область|2|100
-Ингушетия|2|100
-Иркутская область|2|100
-Кабардино-Балкария|2|100
-Калининградская область|2|100
-Калмыкия|2|100
-Калужская область|2|100
-Камчатский край|2|100
-Карачаево-Черкесия|2|100
-Карелия|2|100
-Кемеровская область|2|100
-Кировская область|2|100
-Коми|2|100
-Костромская область|2|100
-Краснодарский край|2|100
-Красноярский край|2|100
-Крым|2|100
-Курганская область|2|100
-Курская область|2|100
-Ленинградская область|2|100
-Липецкая область|2|100
-Магаданская область|2|100
-Марий Эл|2|100
-Мордовия|2|100
-Москва|2|100
-Московская область|2|100
-Мурманская область|2|100
-Ненецкий АО|2|100
-Нижегородская область|2|100
-Новгородская область|2|100
-Новосибирская область|2|100
-Омская область|2|100
-Оренбургская область|2|100
-Орловская область|2|100
-Пензенская область|2|100
-Пермский край|2|100
-Приморский край|2|100
-Псковская область|2|100
-Республика Алтай|2|100
-Ростовская область|2|100
-Рязанская область|2|100
-Самарская область|2|100
-Санкт-Петербург|2|100
-Саратовская область|2|100
-Саха (Якутия)|2|100
-Сахалинская область|2|100
-Свердловская область|2|100
-Северная Осетия|2|100
-Смоленская область|2|100
-Ставропольский край|2|100
-Тамбовская область|2|100
-Татарстан|2|100
-Тверская область|2|100
-Томская область|2|100
-Тульская область|2|100
-Тыва|2|100
-Тюменская область|2|100
-Удмуртия|2|100
-Ульяновская область|2|100
-Хабаровский край|2|100
-Хакасия|2|100
-Ханты-Мансийский АО|2|100
-Челябинская область|2|100
-Чеченская Республика|2|100
-Чувашия|2|100
-Ямало-Ненецкий АО|2|100
-Ярославская область|2|100</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -35389,16 +33655,6 @@
         <v>7945</v>
       </c>
       <c r="AH2" s="7"/>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Настройка цены целевого действия</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Настройка цены целевого действия: ручная</t>
-        </is>
-      </c>
     </row>
     <row r="3" s="6" customFormat="true" ht="45" customHeight="true">
       <c r="A3" s="6" t="s">
@@ -35485,16 +33741,6 @@
       <c r="AB3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Необязательный</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Необязательный</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
@@ -35581,16 +33827,6 @@
       <c r="AB4" t="s">
         <v>44</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Одно значение из выпадающего списка в ячейке</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Подробнее о параметре</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -35689,192 +33925,6 @@
       <c r="AG5" t="s">
         <v>8061</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|5|100
-Алтайский край|5|100
-Амурская область|5|100
-Архангельская область|5|100
-Астраханская область|5|100
-Башкортостан|5|100
-Белгородская область|5|100
-Брянская область|5|100
-Бурятия|5|100
-Владимирская область|5|100
-Волгоградская область|5|100
-Вологодская область|5|100
-Воронежская область|5|100
-Дагестан|5|100
-другой регион|5|100
-Еврейская АО|5|100
-Забайкальский край|5|100
-Ивановская область|5|100
-Ингушетия|5|100
-Иркутская область|5|100
-Кабардино-Балкария|5|100
-Калининградская область|5|100
-Калмыкия|5|100
-Калужская область|5|100
-Камчатский край|5|100
-Карачаево-Черкесия|5|100
-Карелия|5|100
-Кемеровская область|5|100
-Кировская область|5|100
-Коми|5|100
-Костромская область|5|100
-Краснодарский край|5|100
-Красноярский край|5|100
-Крым|5|100
-Курганская область|5|100
-Курская область|5|100
-Ленинградская область|5|100
-Липецкая область|5|100
-Магаданская область|5|100
-Марий Эл|5|100
-Мордовия|5|100
-Москва|5|100
-Московская область|5|100
-Мурманская область|5|100
-Ненецкий АО|5|100
-Нижегородская область|5|100
-Новгородская область|5|100
-Новосибирская область|5|100
-Омская область|5|100
-Оренбургская область|5|100
-Орловская область|5|100
-Пензенская область|5|100
-Пермский край|5|100
-Приморский край|5|100
-Псковская область|5|100
-Республика Алтай|5|100
-Ростовская область|5|100
-Рязанская область|5|100
-Самарская область|5|100
-Санкт-Петербург|5|100
-Саратовская область|5|100
-Саха (Якутия)|5|100
-Сахалинская область|5|100
-Свердловская область|5|100
-Северная Осетия|5|100
-Смоленская область|5|100
-Ставропольский край|5|100
-Тамбовская область|5|100
-Татарстан|5|100
-Тверская область|5|100
-Томская область|5|100
-Тульская область|5|100
-Тыва|5|100
-Тюменская область|5|100
-Удмуртия|5|100
-Ульяновская область|5|100
-Хабаровский край|5|100
-Хакасия|5|100
-Ханты-Мансийский АО|5|100
-Челябинская область|5|100
-Чеченская Республика|5|100
-Чувашия|5|100
-Ямало-Ненецкий АО|5|100
-Ярославская область|5|100</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
@@ -35973,192 +34023,6 @@
       <c r="AG6" t="s">
         <v>8061</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|5|100
-Алтайский край|5|100
-Амурская область|5|100
-Архангельская область|5|100
-Астраханская область|5|100
-Башкортостан|5|100
-Белгородская область|5|100
-Брянская область|5|100
-Бурятия|5|100
-Владимирская область|5|100
-Волгоградская область|5|100
-Вологодская область|5|100
-Воронежская область|5|100
-Дагестан|5|100
-другой регион|5|100
-Еврейская АО|5|100
-Забайкальский край|5|100
-Ивановская область|5|100
-Ингушетия|5|100
-Иркутская область|5|100
-Кабардино-Балкария|5|100
-Калининградская область|5|100
-Калмыкия|5|100
-Калужская область|5|100
-Камчатский край|5|100
-Карачаево-Черкесия|5|100
-Карелия|5|100
-Кемеровская область|5|100
-Кировская область|5|100
-Коми|5|100
-Костромская область|5|100
-Краснодарский край|5|100
-Красноярский край|5|100
-Крым|5|100
-Курганская область|5|100
-Курская область|5|100
-Ленинградская область|5|100
-Липецкая область|5|100
-Магаданская область|5|100
-Марий Эл|5|100
-Мордовия|5|100
-Москва|5|100
-Московская область|5|100
-Мурманская область|5|100
-Ненецкий АО|5|100
-Нижегородская область|5|100
-Новгородская область|5|100
-Новосибирская область|5|100
-Омская область|5|100
-Оренбургская область|5|100
-Орловская область|5|100
-Пензенская область|5|100
-Пермский край|5|100
-Приморский край|5|100
-Псковская область|5|100
-Республика Алтай|5|100
-Ростовская область|5|100
-Рязанская область|5|100
-Самарская область|5|100
-Санкт-Петербург|5|100
-Саратовская область|5|100
-Саха (Якутия)|5|100
-Сахалинская область|5|100
-Свердловская область|5|100
-Северная Осетия|5|100
-Смоленская область|5|100
-Ставропольский край|5|100
-Тамбовская область|5|100
-Татарстан|5|100
-Тверская область|5|100
-Томская область|5|100
-Тульская область|5|100
-Тыва|5|100
-Тюменская область|5|100
-Удмуртия|5|100
-Ульяновская область|5|100
-Хабаровский край|5|100
-Хакасия|5|100
-Ханты-Мансийский АО|5|100
-Челябинская область|5|100
-Чеченская Республика|5|100
-Чувашия|5|100
-Ямало-Ненецкий АО|5|100
-Ярославская область|5|100</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
@@ -36257,192 +34121,6 @@
       <c r="AG7" t="s">
         <v>8061</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|5|100
-Алтайский край|5|100
-Амурская область|5|100
-Архангельская область|5|100
-Астраханская область|5|100
-Башкортостан|5|100
-Белгородская область|5|100
-Брянская область|5|100
-Бурятия|5|100
-Владимирская область|5|100
-Волгоградская область|5|100
-Вологодская область|5|100
-Воронежская область|5|100
-Дагестан|5|100
-другой регион|5|100
-Еврейская АО|5|100
-Забайкальский край|5|100
-Ивановская область|5|100
-Ингушетия|5|100
-Иркутская область|5|100
-Кабардино-Балкария|5|100
-Калининградская область|5|100
-Калмыкия|5|100
-Калужская область|5|100
-Камчатский край|5|100
-Карачаево-Черкесия|5|100
-Карелия|5|100
-Кемеровская область|5|100
-Кировская область|5|100
-Коми|5|100
-Костромская область|5|100
-Краснодарский край|5|100
-Красноярский край|5|100
-Крым|5|100
-Курганская область|5|100
-Курская область|5|100
-Ленинградская область|5|100
-Липецкая область|5|100
-Магаданская область|5|100
-Марий Эл|5|100
-Мордовия|5|100
-Москва|5|100
-Московская область|5|100
-Мурманская область|5|100
-Ненецкий АО|5|100
-Нижегородская область|5|100
-Новгородская область|5|100
-Новосибирская область|5|100
-Омская область|5|100
-Оренбургская область|5|100
-Орловская область|5|100
-Пензенская область|5|100
-Пермский край|5|100
-Приморский край|5|100
-Псковская область|5|100
-Республика Алтай|5|100
-Ростовская область|5|100
-Рязанская область|5|100
-Самарская область|5|100
-Санкт-Петербург|5|100
-Саратовская область|5|100
-Саха (Якутия)|5|100
-Сахалинская область|5|100
-Свердловская область|5|100
-Северная Осетия|5|100
-Смоленская область|5|100
-Ставропольский край|5|100
-Тамбовская область|5|100
-Татарстан|5|100
-Тверская область|5|100
-Томская область|5|100
-Тульская область|5|100
-Тыва|5|100
-Тюменская область|5|100
-Удмуртия|5|100
-Ульяновская область|5|100
-Хабаровский край|5|100
-Хакасия|5|100
-Ханты-Мансийский АО|5|100
-Челябинская область|5|100
-Чеченская Республика|5|100
-Чувашия|5|100
-Ямало-Ненецкий АО|5|100
-Ярославская область|5|100</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -36544,192 +34222,6 @@
       <c r="AG8" t="s">
         <v>8061</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|5|100
-Алтайский край|5|100
-Амурская область|5|100
-Архангельская область|5|100
-Астраханская область|5|100
-Башкортостан|5|100
-Белгородская область|5|100
-Брянская область|5|100
-Бурятия|5|100
-Владимирская область|5|100
-Волгоградская область|5|100
-Вологодская область|5|100
-Воронежская область|5|100
-Дагестан|5|100
-другой регион|5|100
-Еврейская АО|5|100
-Забайкальский край|5|100
-Ивановская область|5|100
-Ингушетия|5|100
-Иркутская область|5|100
-Кабардино-Балкария|5|100
-Калининградская область|5|100
-Калмыкия|5|100
-Калужская область|5|100
-Камчатский край|5|100
-Карачаево-Черкесия|5|100
-Карелия|5|100
-Кемеровская область|5|100
-Кировская область|5|100
-Коми|5|100
-Костромская область|5|100
-Краснодарский край|5|100
-Красноярский край|5|100
-Крым|5|100
-Курганская область|5|100
-Курская область|5|100
-Ленинградская область|5|100
-Липецкая область|5|100
-Магаданская область|5|100
-Марий Эл|5|100
-Мордовия|5|100
-Москва|5|100
-Московская область|5|100
-Мурманская область|5|100
-Ненецкий АО|5|100
-Нижегородская область|5|100
-Новгородская область|5|100
-Новосибирская область|5|100
-Омская область|5|100
-Оренбургская область|5|100
-Орловская область|5|100
-Пензенская область|5|100
-Пермский край|5|100
-Приморский край|5|100
-Псковская область|5|100
-Республика Алтай|5|100
-Ростовская область|5|100
-Рязанская область|5|100
-Самарская область|5|100
-Санкт-Петербург|5|100
-Саратовская область|5|100
-Саха (Якутия)|5|100
-Сахалинская область|5|100
-Свердловская область|5|100
-Северная Осетия|5|100
-Смоленская область|5|100
-Ставропольский край|5|100
-Тамбовская область|5|100
-Татарстан|5|100
-Тверская область|5|100
-Томская область|5|100
-Тульская область|5|100
-Тыва|5|100
-Тюменская область|5|100
-Удмуртия|5|100
-Ульяновская область|5|100
-Хабаровский край|5|100
-Хакасия|5|100
-Ханты-Мансийский АО|5|100
-Челябинская область|5|100
-Чеченская Республика|5|100
-Чувашия|5|100
-Ямало-Ненецкий АО|5|100
-Ярославская область|5|100</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -36828,192 +34320,6 @@
       <c r="AG9" t="s">
         <v>8061</v>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|5|100
-Алтайский край|5|100
-Амурская область|5|100
-Архангельская область|5|100
-Астраханская область|5|100
-Башкортостан|5|100
-Белгородская область|5|100
-Брянская область|5|100
-Бурятия|5|100
-Владимирская область|5|100
-Волгоградская область|5|100
-Вологодская область|5|100
-Воронежская область|5|100
-Дагестан|5|100
-другой регион|5|100
-Еврейская АО|5|100
-Забайкальский край|5|100
-Ивановская область|5|100
-Ингушетия|5|100
-Иркутская область|5|100
-Кабардино-Балкария|5|100
-Калининградская область|5|100
-Калмыкия|5|100
-Калужская область|5|100
-Камчатский край|5|100
-Карачаево-Черкесия|5|100
-Карелия|5|100
-Кемеровская область|5|100
-Кировская область|5|100
-Коми|5|100
-Костромская область|5|100
-Краснодарский край|5|100
-Красноярский край|5|100
-Крым|5|100
-Курганская область|5|100
-Курская область|5|100
-Ленинградская область|5|100
-Липецкая область|5|100
-Магаданская область|5|100
-Марий Эл|5|100
-Мордовия|5|100
-Москва|5|100
-Московская область|5|100
-Мурманская область|5|100
-Ненецкий АО|5|100
-Нижегородская область|5|100
-Новгородская область|5|100
-Новосибирская область|5|100
-Омская область|5|100
-Оренбургская область|5|100
-Орловская область|5|100
-Пензенская область|5|100
-Пермский край|5|100
-Приморский край|5|100
-Псковская область|5|100
-Республика Алтай|5|100
-Ростовская область|5|100
-Рязанская область|5|100
-Самарская область|5|100
-Санкт-Петербург|5|100
-Саратовская область|5|100
-Саха (Якутия)|5|100
-Сахалинская область|5|100
-Свердловская область|5|100
-Северная Осетия|5|100
-Смоленская область|5|100
-Ставропольский край|5|100
-Тамбовская область|5|100
-Татарстан|5|100
-Тверская область|5|100
-Томская область|5|100
-Тульская область|5|100
-Тыва|5|100
-Тюменская область|5|100
-Удмуртия|5|100
-Ульяновская область|5|100
-Хабаровский край|5|100
-Хакасия|5|100
-Ханты-Мансийский АО|5|100
-Челябинская область|5|100
-Чеченская Республика|5|100
-Чувашия|5|100
-Ямало-Ненецкий АО|5|100
-Ярославская область|5|100</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -37112,192 +34418,6 @@
       <c r="AG10" t="s">
         <v>8061</v>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|5|100
-Алтайский край|5|100
-Амурская область|5|100
-Архангельская область|5|100
-Астраханская область|5|100
-Башкортостан|5|100
-Белгородская область|5|100
-Брянская область|5|100
-Бурятия|5|100
-Владимирская область|5|100
-Волгоградская область|5|100
-Вологодская область|5|100
-Воронежская область|5|100
-Дагестан|5|100
-другой регион|5|100
-Еврейская АО|5|100
-Забайкальский край|5|100
-Ивановская область|5|100
-Ингушетия|5|100
-Иркутская область|5|100
-Кабардино-Балкария|5|100
-Калининградская область|5|100
-Калмыкия|5|100
-Калужская область|5|100
-Камчатский край|5|100
-Карачаево-Черкесия|5|100
-Карелия|5|100
-Кемеровская область|5|100
-Кировская область|5|100
-Коми|5|100
-Костромская область|5|100
-Краснодарский край|5|100
-Красноярский край|5|100
-Крым|5|100
-Курганская область|5|100
-Курская область|5|100
-Ленинградская область|5|100
-Липецкая область|5|100
-Магаданская область|5|100
-Марий Эл|5|100
-Мордовия|5|100
-Москва|5|100
-Московская область|5|100
-Мурманская область|5|100
-Ненецкий АО|5|100
-Нижегородская область|5|100
-Новгородская область|5|100
-Новосибирская область|5|100
-Омская область|5|100
-Оренбургская область|5|100
-Орловская область|5|100
-Пензенская область|5|100
-Пермский край|5|100
-Приморский край|5|100
-Псковская область|5|100
-Республика Алтай|5|100
-Ростовская область|5|100
-Рязанская область|5|100
-Самарская область|5|100
-Санкт-Петербург|5|100
-Саратовская область|5|100
-Саха (Якутия)|5|100
-Сахалинская область|5|100
-Свердловская область|5|100
-Северная Осетия|5|100
-Смоленская область|5|100
-Ставропольский край|5|100
-Тамбовская область|5|100
-Татарстан|5|100
-Тверская область|5|100
-Томская область|5|100
-Тульская область|5|100
-Тыва|5|100
-Тюменская область|5|100
-Удмуртия|5|100
-Ульяновская область|5|100
-Хабаровский край|5|100
-Хакасия|5|100
-Ханты-Мансийский АО|5|100
-Челябинская область|5|100
-Чеченская Республика|5|100
-Чувашия|5|100
-Ямало-Ненецкий АО|5|100
-Ярославская область|5|100</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
@@ -37396,192 +34516,6 @@
       <c r="AG11" t="s">
         <v>8061</v>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|4|100
-Алтайский край|4|100
-Амурская область|4|100
-Архангельская область|4|100
-Астраханская область|4|100
-Башкортостан|4|100
-Белгородская область|4|100
-Брянская область|4|100
-Бурятия|4|100
-Владимирская область|4|100
-Волгоградская область|4|100
-Вологодская область|4|100
-Воронежская область|4|100
-Дагестан|4|100
-другой регион|4|100
-Еврейская АО|4|100
-Забайкальский край|4|100
-Ивановская область|4|100
-Ингушетия|4|100
-Иркутская область|4|100
-Кабардино-Балкария|4|100
-Калининградская область|4|100
-Калмыкия|4|100
-Калужская область|4|100
-Камчатский край|4|100
-Карачаево-Черкесия|4|100
-Карелия|4|100
-Кемеровская область|4|100
-Кировская область|4|100
-Коми|4|100
-Костромская область|4|100
-Краснодарский край|4|100
-Красноярский край|4|100
-Крым|4|100
-Курганская область|4|100
-Курская область|4|100
-Ленинградская область|4|100
-Липецкая область|4|100
-Магаданская область|4|100
-Марий Эл|4|100
-Мордовия|4|100
-Москва|4|100
-Московская область|4|100
-Мурманская область|4|100
-Ненецкий АО|4|100
-Нижегородская область|4|100
-Новгородская область|4|100
-Новосибирская область|4|100
-Омская область|4|100
-Оренбургская область|4|100
-Орловская область|4|100
-Пензенская область|4|100
-Пермский край|4|100
-Приморский край|4|100
-Псковская область|4|100
-Республика Алтай|4|100
-Ростовская область|4|100
-Рязанская область|4|100
-Самарская область|4|100
-Санкт-Петербург|4|100
-Саратовская область|4|100
-Саха (Якутия)|4|100
-Сахалинская область|4|100
-Свердловская область|4|100
-Северная Осетия|4|100
-Смоленская область|4|100
-Ставропольский край|4|100
-Тамбовская область|4|100
-Татарстан|4|100
-Тверская область|4|100
-Томская область|4|100
-Тульская область|4|100
-Тыва|4|100
-Тюменская область|4|100
-Удмуртия|4|100
-Ульяновская область|4|100
-Хабаровский край|4|100
-Хакасия|4|100
-Ханты-Мансийский АО|4|100
-Челябинская область|4|100
-Чеченская Республика|4|100
-Чувашия|4|100
-Ямало-Ненецкий АО|4|100
-Ярославская область|4|100</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -37680,192 +34614,6 @@
       <c r="AG12" t="s">
         <v>8061</v>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|4|100
-Алтайский край|4|100
-Амурская область|4|100
-Архангельская область|4|100
-Астраханская область|4|100
-Башкортостан|4|100
-Белгородская область|4|100
-Брянская область|4|100
-Бурятия|4|100
-Владимирская область|4|100
-Волгоградская область|4|100
-Вологодская область|4|100
-Воронежская область|4|100
-Дагестан|4|100
-другой регион|4|100
-Еврейская АО|4|100
-Забайкальский край|4|100
-Ивановская область|4|100
-Ингушетия|4|100
-Иркутская область|4|100
-Кабардино-Балкария|4|100
-Калининградская область|4|100
-Калмыкия|4|100
-Калужская область|4|100
-Камчатский край|4|100
-Карачаево-Черкесия|4|100
-Карелия|4|100
-Кемеровская область|4|100
-Кировская область|4|100
-Коми|4|100
-Костромская область|4|100
-Краснодарский край|4|100
-Красноярский край|4|100
-Крым|4|100
-Курганская область|4|100
-Курская область|4|100
-Ленинградская область|4|100
-Липецкая область|4|100
-Магаданская область|4|100
-Марий Эл|4|100
-Мордовия|4|100
-Москва|4|100
-Московская область|4|100
-Мурманская область|4|100
-Ненецкий АО|4|100
-Нижегородская область|4|100
-Новгородская область|4|100
-Новосибирская область|4|100
-Омская область|4|100
-Оренбургская область|4|100
-Орловская область|4|100
-Пензенская область|4|100
-Пермский край|4|100
-Приморский край|4|100
-Псковская область|4|100
-Республика Алтай|4|100
-Ростовская область|4|100
-Рязанская область|4|100
-Самарская область|4|100
-Санкт-Петербург|4|100
-Саратовская область|4|100
-Саха (Якутия)|4|100
-Сахалинская область|4|100
-Свердловская область|4|100
-Северная Осетия|4|100
-Смоленская область|4|100
-Ставропольский край|4|100
-Тамбовская область|4|100
-Татарстан|4|100
-Тверская область|4|100
-Томская область|4|100
-Тульская область|4|100
-Тыва|4|100
-Тюменская область|4|100
-Удмуртия|4|100
-Ульяновская область|4|100
-Хабаровский край|4|100
-Хакасия|4|100
-Ханты-Мансийский АО|4|100
-Челябинская область|4|100
-Чеченская Республика|4|100
-Чувашия|4|100
-Ямало-Ненецкий АО|4|100
-Ярославская область|4|100</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
@@ -37964,192 +34712,6 @@
       <c r="AG13" t="s">
         <v>8061</v>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|4|100
-Алтайский край|4|100
-Амурская область|4|100
-Архангельская область|4|100
-Астраханская область|4|100
-Башкортостан|4|100
-Белгородская область|4|100
-Брянская область|4|100
-Бурятия|4|100
-Владимирская область|4|100
-Волгоградская область|4|100
-Вологодская область|4|100
-Воронежская область|4|100
-Дагестан|4|100
-другой регион|4|100
-Еврейская АО|4|100
-Забайкальский край|4|100
-Ивановская область|4|100
-Ингушетия|4|100
-Иркутская область|4|100
-Кабардино-Балкария|4|100
-Калининградская область|4|100
-Калмыкия|4|100
-Калужская область|4|100
-Камчатский край|4|100
-Карачаево-Черкесия|4|100
-Карелия|4|100
-Кемеровская область|4|100
-Кировская область|4|100
-Коми|4|100
-Костромская область|4|100
-Краснодарский край|4|100
-Красноярский край|4|100
-Крым|4|100
-Курганская область|4|100
-Курская область|4|100
-Ленинградская область|4|100
-Липецкая область|4|100
-Магаданская область|4|100
-Марий Эл|4|100
-Мордовия|4|100
-Москва|4|100
-Московская область|4|100
-Мурманская область|4|100
-Ненецкий АО|4|100
-Нижегородская область|4|100
-Новгородская область|4|100
-Новосибирская область|4|100
-Омская область|4|100
-Оренбургская область|4|100
-Орловская область|4|100
-Пензенская область|4|100
-Пермский край|4|100
-Приморский край|4|100
-Псковская область|4|100
-Республика Алтай|4|100
-Ростовская область|4|100
-Рязанская область|4|100
-Самарская область|4|100
-Санкт-Петербург|4|100
-Саратовская область|4|100
-Саха (Якутия)|4|100
-Сахалинская область|4|100
-Свердловская область|4|100
-Северная Осетия|4|100
-Смоленская область|4|100
-Ставропольский край|4|100
-Тамбовская область|4|100
-Татарстан|4|100
-Тверская область|4|100
-Томская область|4|100
-Тульская область|4|100
-Тыва|4|100
-Тюменская область|4|100
-Удмуртия|4|100
-Ульяновская область|4|100
-Хабаровский край|4|100
-Хакасия|4|100
-Ханты-Мансийский АО|4|100
-Челябинская область|4|100
-Чеченская Республика|4|100
-Чувашия|4|100
-Ямало-Ненецкий АО|4|100
-Ярославская область|4|100</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
@@ -38248,192 +34810,6 @@
       <c r="AG14" t="s">
         <v>8061</v>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|5|100
-Алтайский край|5|100
-Амурская область|5|100
-Архангельская область|5|100
-Астраханская область|5|100
-Башкортостан|5|100
-Белгородская область|5|100
-Брянская область|5|100
-Бурятия|5|100
-Владимирская область|5|100
-Волгоградская область|5|100
-Вологодская область|5|100
-Воронежская область|5|100
-Дагестан|5|100
-другой регион|5|100
-Еврейская АО|5|100
-Забайкальский край|5|100
-Ивановская область|5|100
-Ингушетия|5|100
-Иркутская область|5|100
-Кабардино-Балкария|5|100
-Калининградская область|5|100
-Калмыкия|5|100
-Калужская область|5|100
-Камчатский край|5|100
-Карачаево-Черкесия|5|100
-Карелия|5|100
-Кемеровская область|5|100
-Кировская область|5|100
-Коми|5|100
-Костромская область|5|100
-Краснодарский край|5|100
-Красноярский край|5|100
-Крым|5|100
-Курганская область|5|100
-Курская область|5|100
-Ленинградская область|5|100
-Липецкая область|5|100
-Магаданская область|5|100
-Марий Эл|5|100
-Мордовия|5|100
-Москва|5|100
-Московская область|5|100
-Мурманская область|5|100
-Ненецкий АО|5|100
-Нижегородская область|5|100
-Новгородская область|5|100
-Новосибирская область|5|100
-Омская область|5|100
-Оренбургская область|5|100
-Орловская область|5|100
-Пензенская область|5|100
-Пермский край|5|100
-Приморский край|5|100
-Псковская область|5|100
-Республика Алтай|5|100
-Ростовская область|5|100
-Рязанская область|5|100
-Самарская область|5|100
-Санкт-Петербург|5|100
-Саратовская область|5|100
-Саха (Якутия)|5|100
-Сахалинская область|5|100
-Свердловская область|5|100
-Северная Осетия|5|100
-Смоленская область|5|100
-Ставропольский край|5|100
-Тамбовская область|5|100
-Татарстан|5|100
-Тверская область|5|100
-Томская область|5|100
-Тульская область|5|100
-Тыва|5|100
-Тюменская область|5|100
-Удмуртия|5|100
-Ульяновская область|5|100
-Хабаровский край|5|100
-Хакасия|5|100
-Ханты-Мансийский АО|5|100
-Челябинская область|5|100
-Чеченская Республика|5|100
-Чувашия|5|100
-Ямало-Ненецкий АО|5|100
-Ярославская область|5|100</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
@@ -38532,192 +34908,6 @@
       <c r="AG15" t="s">
         <v>8061</v>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|4|100
-Алтайский край|4|100
-Амурская область|4|100
-Архангельская область|4|100
-Астраханская область|4|100
-Башкортостан|4|100
-Белгородская область|4|100
-Брянская область|4|100
-Бурятия|4|100
-Владимирская область|4|100
-Волгоградская область|4|100
-Вологодская область|4|100
-Воронежская область|4|100
-Дагестан|4|100
-другой регион|4|100
-Еврейская АО|4|100
-Забайкальский край|4|100
-Ивановская область|4|100
-Ингушетия|4|100
-Иркутская область|4|100
-Кабардино-Балкария|4|100
-Калининградская область|4|100
-Калмыкия|4|100
-Калужская область|4|100
-Камчатский край|4|100
-Карачаево-Черкесия|4|100
-Карелия|4|100
-Кемеровская область|4|100
-Кировская область|4|100
-Коми|4|100
-Костромская область|4|100
-Краснодарский край|4|100
-Красноярский край|4|100
-Крым|4|100
-Курганская область|4|100
-Курская область|4|100
-Ленинградская область|4|100
-Липецкая область|4|100
-Магаданская область|4|100
-Марий Эл|4|100
-Мордовия|4|100
-Москва|4|100
-Московская область|4|100
-Мурманская область|4|100
-Ненецкий АО|4|100
-Нижегородская область|4|100
-Новгородская область|4|100
-Новосибирская область|4|100
-Омская область|4|100
-Оренбургская область|4|100
-Орловская область|4|100
-Пензенская область|4|100
-Пермский край|4|100
-Приморский край|4|100
-Псковская область|4|100
-Республика Алтай|4|100
-Ростовская область|4|100
-Рязанская область|4|100
-Самарская область|4|100
-Санкт-Петербург|4|100
-Саратовская область|4|100
-Саха (Якутия)|4|100
-Сахалинская область|4|100
-Свердловская область|4|100
-Северная Осетия|4|100
-Смоленская область|4|100
-Ставропольский край|4|100
-Тамбовская область|4|100
-Татарстан|4|100
-Тверская область|4|100
-Томская область|4|100
-Тульская область|4|100
-Тыва|4|100
-Тюменская область|4|100
-Удмуртия|4|100
-Ульяновская область|4|100
-Хабаровский край|4|100
-Хакасия|4|100
-Ханты-Мансийский АО|4|100
-Челябинская область|4|100
-Чеченская Республика|4|100
-Чувашия|4|100
-Ямало-Ненецкий АО|4|100
-Ярославская область|4|100</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -38816,192 +35006,6 @@
       <c r="AG16" t="s">
         <v>8061</v>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|4|100
-Алтайский край|4|100
-Амурская область|4|100
-Архангельская область|4|100
-Астраханская область|4|100
-Башкортостан|4|100
-Белгородская область|4|100
-Брянская область|4|100
-Бурятия|4|100
-Владимирская область|4|100
-Волгоградская область|4|100
-Вологодская область|4|100
-Воронежская область|4|100
-Дагестан|4|100
-другой регион|4|100
-Еврейская АО|4|100
-Забайкальский край|4|100
-Ивановская область|4|100
-Ингушетия|4|100
-Иркутская область|4|100
-Кабардино-Балкария|4|100
-Калининградская область|4|100
-Калмыкия|4|100
-Калужская область|4|100
-Камчатский край|4|100
-Карачаево-Черкесия|4|100
-Карелия|4|100
-Кемеровская область|4|100
-Кировская область|4|100
-Коми|4|100
-Костромская область|4|100
-Краснодарский край|4|100
-Красноярский край|4|100
-Крым|4|100
-Курганская область|4|100
-Курская область|4|100
-Ленинградская область|4|100
-Липецкая область|4|100
-Магаданская область|4|100
-Марий Эл|4|100
-Мордовия|4|100
-Москва|4|100
-Московская область|4|100
-Мурманская область|4|100
-Ненецкий АО|4|100
-Нижегородская область|4|100
-Новгородская область|4|100
-Новосибирская область|4|100
-Омская область|4|100
-Оренбургская область|4|100
-Орловская область|4|100
-Пензенская область|4|100
-Пермский край|4|100
-Приморский край|4|100
-Псковская область|4|100
-Республика Алтай|4|100
-Ростовская область|4|100
-Рязанская область|4|100
-Самарская область|4|100
-Санкт-Петербург|4|100
-Саратовская область|4|100
-Саха (Якутия)|4|100
-Сахалинская область|4|100
-Свердловская область|4|100
-Северная Осетия|4|100
-Смоленская область|4|100
-Ставропольский край|4|100
-Тамбовская область|4|100
-Татарстан|4|100
-Тверская область|4|100
-Томская область|4|100
-Тульская область|4|100
-Тыва|4|100
-Тюменская область|4|100
-Удмуртия|4|100
-Ульяновская область|4|100
-Хабаровский край|4|100
-Хакасия|4|100
-Ханты-Мансийский АО|4|100
-Челябинская область|4|100
-Чеченская Республика|4|100
-Чувашия|4|100
-Ямало-Ненецкий АО|4|100
-Ярославская область|4|100</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -39100,192 +35104,6 @@
       <c r="AG17" t="s">
         <v>8061</v>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|4|100
-Алтайский край|4|100
-Амурская область|4|100
-Архангельская область|4|100
-Астраханская область|4|100
-Башкортостан|4|100
-Белгородская область|4|100
-Брянская область|4|100
-Бурятия|4|100
-Владимирская область|4|100
-Волгоградская область|4|100
-Вологодская область|4|100
-Воронежская область|4|100
-Дагестан|4|100
-другой регион|4|100
-Еврейская АО|4|100
-Забайкальский край|4|100
-Ивановская область|4|100
-Ингушетия|4|100
-Иркутская область|4|100
-Кабардино-Балкария|4|100
-Калининградская область|4|100
-Калмыкия|4|100
-Калужская область|4|100
-Камчатский край|4|100
-Карачаево-Черкесия|4|100
-Карелия|4|100
-Кемеровская область|4|100
-Кировская область|4|100
-Коми|4|100
-Костромская область|4|100
-Краснодарский край|4|100
-Красноярский край|4|100
-Крым|4|100
-Курганская область|4|100
-Курская область|4|100
-Ленинградская область|4|100
-Липецкая область|4|100
-Магаданская область|4|100
-Марий Эл|4|100
-Мордовия|4|100
-Москва|4|100
-Московская область|4|100
-Мурманская область|4|100
-Ненецкий АО|4|100
-Нижегородская область|4|100
-Новгородская область|4|100
-Новосибирская область|4|100
-Омская область|4|100
-Оренбургская область|4|100
-Орловская область|4|100
-Пензенская область|4|100
-Пермский край|4|100
-Приморский край|4|100
-Псковская область|4|100
-Республика Алтай|4|100
-Ростовская область|4|100
-Рязанская область|4|100
-Самарская область|4|100
-Санкт-Петербург|4|100
-Саратовская область|4|100
-Саха (Якутия)|4|100
-Сахалинская область|4|100
-Свердловская область|4|100
-Северная Осетия|4|100
-Смоленская область|4|100
-Ставропольский край|4|100
-Тамбовская область|4|100
-Татарстан|4|100
-Тверская область|4|100
-Томская область|4|100
-Тульская область|4|100
-Тыва|4|100
-Тюменская область|4|100
-Удмуртия|4|100
-Ульяновская область|4|100
-Хабаровский край|4|100
-Хакасия|4|100
-Ханты-Мансийский АО|4|100
-Челябинская область|4|100
-Чеченская Республика|4|100
-Чувашия|4|100
-Ямало-Ненецкий АО|4|100
-Ярославская область|4|100</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -39384,192 +35202,6 @@
       <c r="AG18" t="s">
         <v>8061</v>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|5|100
-Алтайский край|5|100
-Амурская область|5|100
-Архангельская область|5|100
-Астраханская область|5|100
-Башкортостан|5|100
-Белгородская область|5|100
-Брянская область|5|100
-Бурятия|5|100
-Владимирская область|5|100
-Волгоградская область|5|100
-Вологодская область|5|100
-Воронежская область|5|100
-Дагестан|5|100
-другой регион|5|100
-Еврейская АО|5|100
-Забайкальский край|5|100
-Ивановская область|5|100
-Ингушетия|5|100
-Иркутская область|5|100
-Кабардино-Балкария|5|100
-Калининградская область|5|100
-Калмыкия|5|100
-Калужская область|5|100
-Камчатский край|5|100
-Карачаево-Черкесия|5|100
-Карелия|5|100
-Кемеровская область|5|100
-Кировская область|5|100
-Коми|5|100
-Костромская область|5|100
-Краснодарский край|5|100
-Красноярский край|5|100
-Крым|5|100
-Курганская область|5|100
-Курская область|5|100
-Ленинградская область|5|100
-Липецкая область|5|100
-Магаданская область|5|100
-Марий Эл|5|100
-Мордовия|5|100
-Москва|5|100
-Московская область|5|100
-Мурманская область|5|100
-Ненецкий АО|5|100
-Нижегородская область|5|100
-Новгородская область|5|100
-Новосибирская область|5|100
-Омская область|5|100
-Оренбургская область|5|100
-Орловская область|5|100
-Пензенская область|5|100
-Пермский край|5|100
-Приморский край|5|100
-Псковская область|5|100
-Республика Алтай|5|100
-Ростовская область|5|100
-Рязанская область|5|100
-Самарская область|5|100
-Санкт-Петербург|5|100
-Саратовская область|5|100
-Саха (Якутия)|5|100
-Сахалинская область|5|100
-Свердловская область|5|100
-Северная Осетия|5|100
-Смоленская область|5|100
-Ставропольский край|5|100
-Тамбовская область|5|100
-Татарстан|5|100
-Тверская область|5|100
-Томская область|5|100
-Тульская область|5|100
-Тыва|5|100
-Тюменская область|5|100
-Удмуртия|5|100
-Ульяновская область|5|100
-Хабаровский край|5|100
-Хакасия|5|100
-Ханты-Мансийский АО|5|100
-Челябинская область|5|100
-Чеченская Республика|5|100
-Чувашия|5|100
-Ямало-Ненецкий АО|5|100
-Ярославская область|5|100</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
@@ -39668,192 +35300,6 @@
       <c r="AG19" t="s">
         <v>8061</v>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|5|100
-Алтайский край|5|100
-Амурская область|5|100
-Архангельская область|5|100
-Астраханская область|5|100
-Башкортостан|5|100
-Белгородская область|5|100
-Брянская область|5|100
-Бурятия|5|100
-Владимирская область|5|100
-Волгоградская область|5|100
-Вологодская область|5|100
-Воронежская область|5|100
-Дагестан|5|100
-другой регион|5|100
-Еврейская АО|5|100
-Забайкальский край|5|100
-Ивановская область|5|100
-Ингушетия|5|100
-Иркутская область|5|100
-Кабардино-Балкария|5|100
-Калининградская область|5|100
-Калмыкия|5|100
-Калужская область|5|100
-Камчатский край|5|100
-Карачаево-Черкесия|5|100
-Карелия|5|100
-Кемеровская область|5|100
-Кировская область|5|100
-Коми|5|100
-Костромская область|5|100
-Краснодарский край|5|100
-Красноярский край|5|100
-Крым|5|100
-Курганская область|5|100
-Курская область|5|100
-Ленинградская область|5|100
-Липецкая область|5|100
-Магаданская область|5|100
-Марий Эл|5|100
-Мордовия|5|100
-Москва|5|100
-Московская область|5|100
-Мурманская область|5|100
-Ненецкий АО|5|100
-Нижегородская область|5|100
-Новгородская область|5|100
-Новосибирская область|5|100
-Омская область|5|100
-Оренбургская область|5|100
-Орловская область|5|100
-Пензенская область|5|100
-Пермский край|5|100
-Приморский край|5|100
-Псковская область|5|100
-Республика Алтай|5|100
-Ростовская область|5|100
-Рязанская область|5|100
-Самарская область|5|100
-Санкт-Петербург|5|100
-Саратовская область|5|100
-Саха (Якутия)|5|100
-Сахалинская область|5|100
-Свердловская область|5|100
-Северная Осетия|5|100
-Смоленская область|5|100
-Ставропольский край|5|100
-Тамбовская область|5|100
-Татарстан|5|100
-Тверская область|5|100
-Томская область|5|100
-Тульская область|5|100
-Тыва|5|100
-Тюменская область|5|100
-Удмуртия|5|100
-Ульяновская область|5|100
-Хабаровский край|5|100
-Хакасия|5|100
-Ханты-Мансийский АО|5|100
-Челябинская область|5|100
-Чеченская Республика|5|100
-Чувашия|5|100
-Ямало-Ненецкий АО|5|100
-Ярославская область|5|100</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
@@ -39952,192 +35398,6 @@
       <c r="AG20" t="s">
         <v>8061</v>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|4|100
-Алтайский край|4|100
-Амурская область|4|100
-Архангельская область|4|100
-Астраханская область|4|100
-Башкортостан|4|100
-Белгородская область|4|100
-Брянская область|4|100
-Бурятия|4|100
-Владимирская область|4|100
-Волгоградская область|4|100
-Вологодская область|4|100
-Воронежская область|4|100
-Дагестан|4|100
-другой регион|4|100
-Еврейская АО|4|100
-Забайкальский край|4|100
-Ивановская область|4|100
-Ингушетия|4|100
-Иркутская область|4|100
-Кабардино-Балкария|4|100
-Калининградская область|4|100
-Калмыкия|4|100
-Калужская область|4|100
-Камчатский край|4|100
-Карачаево-Черкесия|4|100
-Карелия|4|100
-Кемеровская область|4|100
-Кировская область|4|100
-Коми|4|100
-Костромская область|4|100
-Краснодарский край|4|100
-Красноярский край|4|100
-Крым|4|100
-Курганская область|4|100
-Курская область|4|100
-Ленинградская область|4|100
-Липецкая область|4|100
-Магаданская область|4|100
-Марий Эл|4|100
-Мордовия|4|100
-Москва|4|100
-Московская область|4|100
-Мурманская область|4|100
-Ненецкий АО|4|100
-Нижегородская область|4|100
-Новгородская область|4|100
-Новосибирская область|4|100
-Омская область|4|100
-Оренбургская область|4|100
-Орловская область|4|100
-Пензенская область|4|100
-Пермский край|4|100
-Приморский край|4|100
-Псковская область|4|100
-Республика Алтай|4|100
-Ростовская область|4|100
-Рязанская область|4|100
-Самарская область|4|100
-Санкт-Петербург|4|100
-Саратовская область|4|100
-Саха (Якутия)|4|100
-Сахалинская область|4|100
-Свердловская область|4|100
-Северная Осетия|4|100
-Смоленская область|4|100
-Ставропольский край|4|100
-Тамбовская область|4|100
-Татарстан|4|100
-Тверская область|4|100
-Томская область|4|100
-Тульская область|4|100
-Тыва|4|100
-Тюменская область|4|100
-Удмуртия|4|100
-Ульяновская область|4|100
-Хабаровский край|4|100
-Хакасия|4|100
-Ханты-Мансийский АО|4|100
-Челябинская область|4|100
-Чеченская Республика|4|100
-Чувашия|4|100
-Ямало-Ненецкий АО|4|100
-Ярославская область|4|100</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
@@ -40236,192 +35496,6 @@
       <c r="AG21" t="s">
         <v>8061</v>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|5|100
-Алтайский край|5|100
-Амурская область|5|100
-Архангельская область|5|100
-Астраханская область|5|100
-Башкортостан|5|100
-Белгородская область|5|100
-Брянская область|5|100
-Бурятия|5|100
-Владимирская область|5|100
-Волгоградская область|5|100
-Вологодская область|5|100
-Воронежская область|5|100
-Дагестан|5|100
-другой регион|5|100
-Еврейская АО|5|100
-Забайкальский край|5|100
-Ивановская область|5|100
-Ингушетия|5|100
-Иркутская область|5|100
-Кабардино-Балкария|5|100
-Калининградская область|5|100
-Калмыкия|5|100
-Калужская область|5|100
-Камчатский край|5|100
-Карачаево-Черкесия|5|100
-Карелия|5|100
-Кемеровская область|5|100
-Кировская область|5|100
-Коми|5|100
-Костромская область|5|100
-Краснодарский край|5|100
-Красноярский край|5|100
-Крым|5|100
-Курганская область|5|100
-Курская область|5|100
-Ленинградская область|5|100
-Липецкая область|5|100
-Магаданская область|5|100
-Марий Эл|5|100
-Мордовия|5|100
-Москва|5|100
-Московская область|5|100
-Мурманская область|5|100
-Ненецкий АО|5|100
-Нижегородская область|5|100
-Новгородская область|5|100
-Новосибирская область|5|100
-Омская область|5|100
-Оренбургская область|5|100
-Орловская область|5|100
-Пензенская область|5|100
-Пермский край|5|100
-Приморский край|5|100
-Псковская область|5|100
-Республика Алтай|5|100
-Ростовская область|5|100
-Рязанская область|5|100
-Самарская область|5|100
-Санкт-Петербург|5|100
-Саратовская область|5|100
-Саха (Якутия)|5|100
-Сахалинская область|5|100
-Свердловская область|5|100
-Северная Осетия|5|100
-Смоленская область|5|100
-Ставропольский край|5|100
-Тамбовская область|5|100
-Татарстан|5|100
-Тверская область|5|100
-Томская область|5|100
-Тульская область|5|100
-Тыва|5|100
-Тюменская область|5|100
-Удмуртия|5|100
-Ульяновская область|5|100
-Хабаровский край|5|100
-Хакасия|5|100
-Ханты-Мансийский АО|5|100
-Челябинская область|5|100
-Чеченская Республика|5|100
-Чувашия|5|100
-Ямало-Ненецкий АО|5|100
-Ярославская область|5|100</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
@@ -40520,192 +35594,6 @@
       <c r="AG22" t="s">
         <v>8061</v>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|4|100
-Алтайский край|4|100
-Амурская область|4|100
-Архангельская область|4|100
-Астраханская область|4|100
-Башкортостан|4|100
-Белгородская область|4|100
-Брянская область|4|100
-Бурятия|4|100
-Владимирская область|4|100
-Волгоградская область|4|100
-Вологодская область|4|100
-Воронежская область|4|100
-Дагестан|4|100
-другой регион|4|100
-Еврейская АО|4|100
-Забайкальский край|4|100
-Ивановская область|4|100
-Ингушетия|4|100
-Иркутская область|4|100
-Кабардино-Балкария|4|100
-Калининградская область|4|100
-Калмыкия|4|100
-Калужская область|4|100
-Камчатский край|4|100
-Карачаево-Черкесия|4|100
-Карелия|4|100
-Кемеровская область|4|100
-Кировская область|4|100
-Коми|4|100
-Костромская область|4|100
-Краснодарский край|4|100
-Красноярский край|4|100
-Крым|4|100
-Курганская область|4|100
-Курская область|4|100
-Ленинградская область|4|100
-Липецкая область|4|100
-Магаданская область|4|100
-Марий Эл|4|100
-Мордовия|4|100
-Москва|4|100
-Московская область|4|100
-Мурманская область|4|100
-Ненецкий АО|4|100
-Нижегородская область|4|100
-Новгородская область|4|100
-Новосибирская область|4|100
-Омская область|4|100
-Оренбургская область|4|100
-Орловская область|4|100
-Пензенская область|4|100
-Пермский край|4|100
-Приморский край|4|100
-Псковская область|4|100
-Республика Алтай|4|100
-Ростовская область|4|100
-Рязанская область|4|100
-Самарская область|4|100
-Санкт-Петербург|4|100
-Саратовская область|4|100
-Саха (Якутия)|4|100
-Сахалинская область|4|100
-Свердловская область|4|100
-Северная Осетия|4|100
-Смоленская область|4|100
-Ставропольский край|4|100
-Тамбовская область|4|100
-Татарстан|4|100
-Тверская область|4|100
-Томская область|4|100
-Тульская область|4|100
-Тыва|4|100
-Тюменская область|4|100
-Удмуртия|4|100
-Ульяновская область|4|100
-Хабаровский край|4|100
-Хакасия|4|100
-Ханты-Мансийский АО|4|100
-Челябинская область|4|100
-Чеченская Республика|4|100
-Чувашия|4|100
-Ямало-Ненецкий АО|4|100
-Ярославская область|4|100</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
@@ -40804,192 +35692,6 @@
       <c r="AG23" t="s">
         <v>8061</v>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|4|100
-Алтайский край|4|100
-Амурская область|4|100
-Архангельская область|4|100
-Астраханская область|4|100
-Башкортостан|4|100
-Белгородская область|4|100
-Брянская область|4|100
-Бурятия|4|100
-Владимирская область|4|100
-Волгоградская область|4|100
-Вологодская область|4|100
-Воронежская область|4|100
-Дагестан|4|100
-другой регион|4|100
-Еврейская АО|4|100
-Забайкальский край|4|100
-Ивановская область|4|100
-Ингушетия|4|100
-Иркутская область|4|100
-Кабардино-Балкария|4|100
-Калининградская область|4|100
-Калмыкия|4|100
-Калужская область|4|100
-Камчатский край|4|100
-Карачаево-Черкесия|4|100
-Карелия|4|100
-Кемеровская область|4|100
-Кировская область|4|100
-Коми|4|100
-Костромская область|4|100
-Краснодарский край|4|100
-Красноярский край|4|100
-Крым|4|100
-Курганская область|4|100
-Курская область|4|100
-Ленинградская область|4|100
-Липецкая область|4|100
-Магаданская область|4|100
-Марий Эл|4|100
-Мордовия|4|100
-Москва|4|100
-Московская область|4|100
-Мурманская область|4|100
-Ненецкий АО|4|100
-Нижегородская область|4|100
-Новгородская область|4|100
-Новосибирская область|4|100
-Омская область|4|100
-Оренбургская область|4|100
-Орловская область|4|100
-Пензенская область|4|100
-Пермский край|4|100
-Приморский край|4|100
-Псковская область|4|100
-Республика Алтай|4|100
-Ростовская область|4|100
-Рязанская область|4|100
-Самарская область|4|100
-Санкт-Петербург|4|100
-Саратовская область|4|100
-Саха (Якутия)|4|100
-Сахалинская область|4|100
-Свердловская область|4|100
-Северная Осетия|4|100
-Смоленская область|4|100
-Ставропольский край|4|100
-Тамбовская область|4|100
-Татарстан|4|100
-Тверская область|4|100
-Томская область|4|100
-Тульская область|4|100
-Тыва|4|100
-Тюменская область|4|100
-Удмуртия|4|100
-Ульяновская область|4|100
-Хабаровский край|4|100
-Хакасия|4|100
-Ханты-Мансийский АО|4|100
-Челябинская область|4|100
-Чеченская Республика|4|100
-Чувашия|4|100
-Ямало-Ненецкий АО|4|100
-Ярославская область|4|100</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
@@ -41087,192 +35789,6 @@
       </c>
       <c r="AG24" t="s">
         <v>8061</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|4|100
-Алтайский край|4|100
-Амурская область|4|100
-Архангельская область|4|100
-Астраханская область|4|100
-Башкортостан|4|100
-Белгородская область|4|100
-Брянская область|4|100
-Бурятия|4|100
-Владимирская область|4|100
-Волгоградская область|4|100
-Вологодская область|4|100
-Воронежская область|4|100
-Дагестан|4|100
-другой регион|4|100
-Еврейская АО|4|100
-Забайкальский край|4|100
-Ивановская область|4|100
-Ингушетия|4|100
-Иркутская область|4|100
-Кабардино-Балкария|4|100
-Калининградская область|4|100
-Калмыкия|4|100
-Калужская область|4|100
-Камчатский край|4|100
-Карачаево-Черкесия|4|100
-Карелия|4|100
-Кемеровская область|4|100
-Кировская область|4|100
-Коми|4|100
-Костромская область|4|100
-Краснодарский край|4|100
-Красноярский край|4|100
-Крым|4|100
-Курганская область|4|100
-Курская область|4|100
-Ленинградская область|4|100
-Липецкая область|4|100
-Магаданская область|4|100
-Марий Эл|4|100
-Мордовия|4|100
-Москва|4|100
-Московская область|4|100
-Мурманская область|4|100
-Ненецкий АО|4|100
-Нижегородская область|4|100
-Новгородская область|4|100
-Новосибирская область|4|100
-Омская область|4|100
-Оренбургская область|4|100
-Орловская область|4|100
-Пензенская область|4|100
-Пермский край|4|100
-Приморский край|4|100
-Псковская область|4|100
-Республика Алтай|4|100
-Ростовская область|4|100
-Рязанская область|4|100
-Самарская область|4|100
-Санкт-Петербург|4|100
-Саратовская область|4|100
-Саха (Якутия)|4|100
-Сахалинская область|4|100
-Свердловская область|4|100
-Северная Осетия|4|100
-Смоленская область|4|100
-Ставропольский край|4|100
-Тамбовская область|4|100
-Татарстан|4|100
-Тверская область|4|100
-Томская область|4|100
-Тульская область|4|100
-Тыва|4|100
-Тюменская область|4|100
-Удмуртия|4|100
-Ульяновская область|4|100
-Хабаровский край|4|100
-Хакасия|4|100
-Ханты-Мансийский АО|4|100
-Челябинская область|4|100
-Чеченская Республика|4|100
-Чувашия|4|100
-Ямало-Ненецкий АО|4|100
-Ярославская область|4|100</t>
-        </is>
       </c>
     </row>
     <row r="25">
@@ -41416,192 +35932,6 @@
           <t xml:space="preserve">ilyabalabay@mail.ru</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|4|100
-Алтайский край|4|100
-Амурская область|4|100
-Архангельская область|4|100
-Астраханская область|4|100
-Башкортостан|4|100
-Белгородская область|4|100
-Брянская область|4|100
-Бурятия|4|100
-Владимирская область|4|100
-Волгоградская область|4|100
-Вологодская область|4|100
-Воронежская область|4|100
-Дагестан|4|100
-другой регион|4|100
-Еврейская АО|4|100
-Забайкальский край|4|100
-Ивановская область|4|100
-Ингушетия|4|100
-Иркутская область|4|100
-Кабардино-Балкария|4|100
-Калининградская область|4|100
-Калмыкия|4|100
-Калужская область|4|100
-Камчатский край|4|100
-Карачаево-Черкесия|4|100
-Карелия|4|100
-Кемеровская область|4|100
-Кировская область|4|100
-Коми|4|100
-Костромская область|4|100
-Краснодарский край|4|100
-Красноярский край|4|100
-Крым|4|100
-Курганская область|4|100
-Курская область|4|100
-Ленинградская область|4|100
-Липецкая область|4|100
-Магаданская область|4|100
-Марий Эл|4|100
-Мордовия|4|100
-Москва|4|100
-Московская область|4|100
-Мурманская область|4|100
-Ненецкий АО|4|100
-Нижегородская область|4|100
-Новгородская область|4|100
-Новосибирская область|4|100
-Омская область|4|100
-Оренбургская область|4|100
-Орловская область|4|100
-Пензенская область|4|100
-Пермский край|4|100
-Приморский край|4|100
-Псковская область|4|100
-Республика Алтай|4|100
-Ростовская область|4|100
-Рязанская область|4|100
-Самарская область|4|100
-Санкт-Петербург|4|100
-Саратовская область|4|100
-Саха (Якутия)|4|100
-Сахалинская область|4|100
-Свердловская область|4|100
-Северная Осетия|4|100
-Смоленская область|4|100
-Ставропольский край|4|100
-Тамбовская область|4|100
-Татарстан|4|100
-Тверская область|4|100
-Томская область|4|100
-Тульская область|4|100
-Тыва|4|100
-Тюменская область|4|100
-Удмуртия|4|100
-Ульяновская область|4|100
-Хабаровский край|4|100
-Хакасия|4|100
-Ханты-Мансийский АО|4|100
-Челябинская область|4|100
-Чеченская Республика|4|100
-Чувашия|4|100
-Ямало-Ненецкий АО|4|100
-Ярославская область|4|100</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -41744,192 +36074,6 @@
           <t xml:space="preserve">ilyabalabay@mail.ru</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|4|100
-Алтайский край|4|100
-Амурская область|4|100
-Архангельская область|4|100
-Астраханская область|4|100
-Башкортостан|4|100
-Белгородская область|4|100
-Брянская область|4|100
-Бурятия|4|100
-Владимирская область|4|100
-Волгоградская область|4|100
-Вологодская область|4|100
-Воронежская область|4|100
-Дагестан|4|100
-другой регион|4|100
-Еврейская АО|4|100
-Забайкальский край|4|100
-Ивановская область|4|100
-Ингушетия|4|100
-Иркутская область|4|100
-Кабардино-Балкария|4|100
-Калининградская область|4|100
-Калмыкия|4|100
-Калужская область|4|100
-Камчатский край|4|100
-Карачаево-Черкесия|4|100
-Карелия|4|100
-Кемеровская область|4|100
-Кировская область|4|100
-Коми|4|100
-Костромская область|4|100
-Краснодарский край|4|100
-Красноярский край|4|100
-Крым|4|100
-Курганская область|4|100
-Курская область|4|100
-Ленинградская область|4|100
-Липецкая область|4|100
-Магаданская область|4|100
-Марий Эл|4|100
-Мордовия|4|100
-Москва|4|100
-Московская область|4|100
-Мурманская область|4|100
-Ненецкий АО|4|100
-Нижегородская область|4|100
-Новгородская область|4|100
-Новосибирская область|4|100
-Омская область|4|100
-Оренбургская область|4|100
-Орловская область|4|100
-Пензенская область|4|100
-Пермский край|4|100
-Приморский край|4|100
-Псковская область|4|100
-Республика Алтай|4|100
-Ростовская область|4|100
-Рязанская область|4|100
-Самарская область|4|100
-Санкт-Петербург|4|100
-Саратовская область|4|100
-Саха (Якутия)|4|100
-Сахалинская область|4|100
-Свердловская область|4|100
-Северная Осетия|4|100
-Смоленская область|4|100
-Ставропольский край|4|100
-Тамбовская область|4|100
-Татарстан|4|100
-Тверская область|4|100
-Томская область|4|100
-Тульская область|4|100
-Тыва|4|100
-Тюменская область|4|100
-Удмуртия|4|100
-Ульяновская область|4|100
-Хабаровский край|4|100
-Хакасия|4|100
-Ханты-Мансийский АО|4|100
-Челябинская область|4|100
-Чеченская Республика|4|100
-Чувашия|4|100
-Ямало-Ненецкий АО|4|100
-Ярославская область|4|100</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -42072,192 +36216,6 @@
           <t xml:space="preserve">ilyabalabay@mail.ru</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|4|100
-Алтайский край|4|100
-Амурская область|4|100
-Архангельская область|4|100
-Астраханская область|4|100
-Башкортостан|4|100
-Белгородская область|4|100
-Брянская область|4|100
-Бурятия|4|100
-Владимирская область|4|100
-Волгоградская область|4|100
-Вологодская область|4|100
-Воронежская область|4|100
-Дагестан|4|100
-другой регион|4|100
-Еврейская АО|4|100
-Забайкальский край|4|100
-Ивановская область|4|100
-Ингушетия|4|100
-Иркутская область|4|100
-Кабардино-Балкария|4|100
-Калининградская область|4|100
-Калмыкия|4|100
-Калужская область|4|100
-Камчатский край|4|100
-Карачаево-Черкесия|4|100
-Карелия|4|100
-Кемеровская область|4|100
-Кировская область|4|100
-Коми|4|100
-Костромская область|4|100
-Краснодарский край|4|100
-Красноярский край|4|100
-Крым|4|100
-Курганская область|4|100
-Курская область|4|100
-Ленинградская область|4|100
-Липецкая область|4|100
-Магаданская область|4|100
-Марий Эл|4|100
-Мордовия|4|100
-Москва|4|100
-Московская область|4|100
-Мурманская область|4|100
-Ненецкий АО|4|100
-Нижегородская область|4|100
-Новгородская область|4|100
-Новосибирская область|4|100
-Омская область|4|100
-Оренбургская область|4|100
-Орловская область|4|100
-Пензенская область|4|100
-Пермский край|4|100
-Приморский край|4|100
-Псковская область|4|100
-Республика Алтай|4|100
-Ростовская область|4|100
-Рязанская область|4|100
-Самарская область|4|100
-Санкт-Петербург|4|100
-Саратовская область|4|100
-Саха (Якутия)|4|100
-Сахалинская область|4|100
-Свердловская область|4|100
-Северная Осетия|4|100
-Смоленская область|4|100
-Ставропольский край|4|100
-Тамбовская область|4|100
-Татарстан|4|100
-Тверская область|4|100
-Томская область|4|100
-Тульская область|4|100
-Тыва|4|100
-Тюменская область|4|100
-Удмуртия|4|100
-Ульяновская область|4|100
-Хабаровский край|4|100
-Хакасия|4|100
-Ханты-Мансийский АО|4|100
-Челябинская область|4|100
-Чеченская Республика|4|100
-Чувашия|4|100
-Ямало-Ненецкий АО|4|100
-Ярославская область|4|100</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -42400,192 +36358,6 @@
           <t xml:space="preserve">ilyabalabay@mail.ru</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|4|100
-Алтайский край|4|100
-Амурская область|4|100
-Архангельская область|4|100
-Астраханская область|4|100
-Башкортостан|4|100
-Белгородская область|4|100
-Брянская область|4|100
-Бурятия|4|100
-Владимирская область|4|100
-Волгоградская область|4|100
-Вологодская область|4|100
-Воронежская область|4|100
-Дагестан|4|100
-другой регион|4|100
-Еврейская АО|4|100
-Забайкальский край|4|100
-Ивановская область|4|100
-Ингушетия|4|100
-Иркутская область|4|100
-Кабардино-Балкария|4|100
-Калининградская область|4|100
-Калмыкия|4|100
-Калужская область|4|100
-Камчатский край|4|100
-Карачаево-Черкесия|4|100
-Карелия|4|100
-Кемеровская область|4|100
-Кировская область|4|100
-Коми|4|100
-Костромская область|4|100
-Краснодарский край|4|100
-Красноярский край|4|100
-Крым|4|100
-Курганская область|4|100
-Курская область|4|100
-Ленинградская область|4|100
-Липецкая область|4|100
-Магаданская область|4|100
-Марий Эл|4|100
-Мордовия|4|100
-Москва|4|100
-Московская область|4|100
-Мурманская область|4|100
-Ненецкий АО|4|100
-Нижегородская область|4|100
-Новгородская область|4|100
-Новосибирская область|4|100
-Омская область|4|100
-Оренбургская область|4|100
-Орловская область|4|100
-Пензенская область|4|100
-Пермский край|4|100
-Приморский край|4|100
-Псковская область|4|100
-Республика Алтай|4|100
-Ростовская область|4|100
-Рязанская область|4|100
-Самарская область|4|100
-Санкт-Петербург|4|100
-Саратовская область|4|100
-Саха (Якутия)|4|100
-Сахалинская область|4|100
-Свердловская область|4|100
-Северная Осетия|4|100
-Смоленская область|4|100
-Ставропольский край|4|100
-Тамбовская область|4|100
-Татарстан|4|100
-Тверская область|4|100
-Томская область|4|100
-Тульская область|4|100
-Тыва|4|100
-Тюменская область|4|100
-Удмуртия|4|100
-Ульяновская область|4|100
-Хабаровский край|4|100
-Хакасия|4|100
-Ханты-Мансийский АО|4|100
-Челябинская область|4|100
-Чеченская Республика|4|100
-Чувашия|4|100
-Ямало-Ненецкий АО|4|100
-Ярославская область|4|100</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -42728,192 +36500,6 @@
           <t xml:space="preserve">ilyabalabay@mail.ru</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|4|100
-Алтайский край|4|100
-Амурская область|4|100
-Архангельская область|4|100
-Астраханская область|4|100
-Башкортостан|4|100
-Белгородская область|4|100
-Брянская область|4|100
-Бурятия|4|100
-Владимирская область|4|100
-Волгоградская область|4|100
-Вологодская область|4|100
-Воронежская область|4|100
-Дагестан|4|100
-другой регион|4|100
-Еврейская АО|4|100
-Забайкальский край|4|100
-Ивановская область|4|100
-Ингушетия|4|100
-Иркутская область|4|100
-Кабардино-Балкария|4|100
-Калининградская область|4|100
-Калмыкия|4|100
-Калужская область|4|100
-Камчатский край|4|100
-Карачаево-Черкесия|4|100
-Карелия|4|100
-Кемеровская область|4|100
-Кировская область|4|100
-Коми|4|100
-Костромская область|4|100
-Краснодарский край|4|100
-Красноярский край|4|100
-Крым|4|100
-Курганская область|4|100
-Курская область|4|100
-Ленинградская область|4|100
-Липецкая область|4|100
-Магаданская область|4|100
-Марий Эл|4|100
-Мордовия|4|100
-Москва|4|100
-Московская область|4|100
-Мурманская область|4|100
-Ненецкий АО|4|100
-Нижегородская область|4|100
-Новгородская область|4|100
-Новосибирская область|4|100
-Омская область|4|100
-Оренбургская область|4|100
-Орловская область|4|100
-Пензенская область|4|100
-Пермский край|4|100
-Приморский край|4|100
-Псковская область|4|100
-Республика Алтай|4|100
-Ростовская область|4|100
-Рязанская область|4|100
-Самарская область|4|100
-Санкт-Петербург|4|100
-Саратовская область|4|100
-Саха (Якутия)|4|100
-Сахалинская область|4|100
-Свердловская область|4|100
-Северная Осетия|4|100
-Смоленская область|4|100
-Ставропольский край|4|100
-Тамбовская область|4|100
-Татарстан|4|100
-Тверская область|4|100
-Томская область|4|100
-Тульская область|4|100
-Тыва|4|100
-Тюменская область|4|100
-Удмуртия|4|100
-Ульяновская область|4|100
-Хабаровский край|4|100
-Хакасия|4|100
-Ханты-Мансийский АО|4|100
-Челябинская область|4|100
-Чеченская Республика|4|100
-Чувашия|4|100
-Ямало-Ненецкий АО|4|100
-Ярославская область|4|100</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -43056,192 +36642,6 @@
           <t xml:space="preserve">ilyabalabay@mail.ru</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|4|100
-Алтайский край|4|100
-Амурская область|4|100
-Архангельская область|4|100
-Астраханская область|4|100
-Башкортостан|4|100
-Белгородская область|4|100
-Брянская область|4|100
-Бурятия|4|100
-Владимирская область|4|100
-Волгоградская область|4|100
-Вологодская область|4|100
-Воронежская область|4|100
-Дагестан|4|100
-другой регион|4|100
-Еврейская АО|4|100
-Забайкальский край|4|100
-Ивановская область|4|100
-Ингушетия|4|100
-Иркутская область|4|100
-Кабардино-Балкария|4|100
-Калининградская область|4|100
-Калмыкия|4|100
-Калужская область|4|100
-Камчатский край|4|100
-Карачаево-Черкесия|4|100
-Карелия|4|100
-Кемеровская область|4|100
-Кировская область|4|100
-Коми|4|100
-Костромская область|4|100
-Краснодарский край|4|100
-Красноярский край|4|100
-Крым|4|100
-Курганская область|4|100
-Курская область|4|100
-Ленинградская область|4|100
-Липецкая область|4|100
-Магаданская область|4|100
-Марий Эл|4|100
-Мордовия|4|100
-Москва|4|100
-Московская область|4|100
-Мурманская область|4|100
-Ненецкий АО|4|100
-Нижегородская область|4|100
-Новгородская область|4|100
-Новосибирская область|4|100
-Омская область|4|100
-Оренбургская область|4|100
-Орловская область|4|100
-Пензенская область|4|100
-Пермский край|4|100
-Приморский край|4|100
-Псковская область|4|100
-Республика Алтай|4|100
-Ростовская область|4|100
-Рязанская область|4|100
-Самарская область|4|100
-Санкт-Петербург|4|100
-Саратовская область|4|100
-Саха (Якутия)|4|100
-Сахалинская область|4|100
-Свердловская область|4|100
-Северная Осетия|4|100
-Смоленская область|4|100
-Ставропольский край|4|100
-Тамбовская область|4|100
-Татарстан|4|100
-Тверская область|4|100
-Томская область|4|100
-Тульская область|4|100
-Тыва|4|100
-Тюменская область|4|100
-Удмуртия|4|100
-Ульяновская область|4|100
-Хабаровский край|4|100
-Хакасия|4|100
-Ханты-Мансийский АО|4|100
-Челябинская область|4|100
-Чеченская Республика|4|100
-Чувашия|4|100
-Ямало-Ненецкий АО|4|100
-Ярославская область|4|100</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -43384,192 +36784,6 @@
           <t xml:space="preserve">ilyabalabay@mail.ru</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|4|100
-Алтайский край|4|100
-Амурская область|4|100
-Архангельская область|4|100
-Астраханская область|4|100
-Башкортостан|4|100
-Белгородская область|4|100
-Брянская область|4|100
-Бурятия|4|100
-Владимирская область|4|100
-Волгоградская область|4|100
-Вологодская область|4|100
-Воронежская область|4|100
-Дагестан|4|100
-другой регион|4|100
-Еврейская АО|4|100
-Забайкальский край|4|100
-Ивановская область|4|100
-Ингушетия|4|100
-Иркутская область|4|100
-Кабардино-Балкария|4|100
-Калининградская область|4|100
-Калмыкия|4|100
-Калужская область|4|100
-Камчатский край|4|100
-Карачаево-Черкесия|4|100
-Карелия|4|100
-Кемеровская область|4|100
-Кировская область|4|100
-Коми|4|100
-Костромская область|4|100
-Краснодарский край|4|100
-Красноярский край|4|100
-Крым|4|100
-Курганская область|4|100
-Курская область|4|100
-Ленинградская область|4|100
-Липецкая область|4|100
-Магаданская область|4|100
-Марий Эл|4|100
-Мордовия|4|100
-Москва|4|100
-Московская область|4|100
-Мурманская область|4|100
-Ненецкий АО|4|100
-Нижегородская область|4|100
-Новгородская область|4|100
-Новосибирская область|4|100
-Омская область|4|100
-Оренбургская область|4|100
-Орловская область|4|100
-Пензенская область|4|100
-Пермский край|4|100
-Приморский край|4|100
-Псковская область|4|100
-Республика Алтай|4|100
-Ростовская область|4|100
-Рязанская область|4|100
-Самарская область|4|100
-Санкт-Петербург|4|100
-Саратовская область|4|100
-Саха (Якутия)|4|100
-Сахалинская область|4|100
-Свердловская область|4|100
-Северная Осетия|4|100
-Смоленская область|4|100
-Ставропольский край|4|100
-Тамбовская область|4|100
-Татарстан|4|100
-Тверская область|4|100
-Томская область|4|100
-Тульская область|4|100
-Тыва|4|100
-Тюменская область|4|100
-Удмуртия|4|100
-Ульяновская область|4|100
-Хабаровский край|4|100
-Хакасия|4|100
-Ханты-Мансийский АО|4|100
-Челябинская область|4|100
-Чеченская Республика|4|100
-Чувашия|4|100
-Ямало-Ненецкий АО|4|100
-Ярославская область|4|100</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -43712,192 +36926,6 @@
           <t xml:space="preserve">ilyabalabay@mail.ru</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|4|100
-Алтайский край|4|100
-Амурская область|4|100
-Архангельская область|4|100
-Астраханская область|4|100
-Башкортостан|4|100
-Белгородская область|4|100
-Брянская область|4|100
-Бурятия|4|100
-Владимирская область|4|100
-Волгоградская область|4|100
-Вологодская область|4|100
-Воронежская область|4|100
-Дагестан|4|100
-другой регион|4|100
-Еврейская АО|4|100
-Забайкальский край|4|100
-Ивановская область|4|100
-Ингушетия|4|100
-Иркутская область|4|100
-Кабардино-Балкария|4|100
-Калининградская область|4|100
-Калмыкия|4|100
-Калужская область|4|100
-Камчатский край|4|100
-Карачаево-Черкесия|4|100
-Карелия|4|100
-Кемеровская область|4|100
-Кировская область|4|100
-Коми|4|100
-Костромская область|4|100
-Краснодарский край|4|100
-Красноярский край|4|100
-Крым|4|100
-Курганская область|4|100
-Курская область|4|100
-Ленинградская область|4|100
-Липецкая область|4|100
-Магаданская область|4|100
-Марий Эл|4|100
-Мордовия|4|100
-Москва|4|100
-Московская область|4|100
-Мурманская область|4|100
-Ненецкий АО|4|100
-Нижегородская область|4|100
-Новгородская область|4|100
-Новосибирская область|4|100
-Омская область|4|100
-Оренбургская область|4|100
-Орловская область|4|100
-Пензенская область|4|100
-Пермский край|4|100
-Приморский край|4|100
-Псковская область|4|100
-Республика Алтай|4|100
-Ростовская область|4|100
-Рязанская область|4|100
-Самарская область|4|100
-Санкт-Петербург|4|100
-Саратовская область|4|100
-Саха (Якутия)|4|100
-Сахалинская область|4|100
-Свердловская область|4|100
-Северная Осетия|4|100
-Смоленская область|4|100
-Ставропольский край|4|100
-Тамбовская область|4|100
-Татарстан|4|100
-Тверская область|4|100
-Томская область|4|100
-Тульская область|4|100
-Тыва|4|100
-Тюменская область|4|100
-Удмуртия|4|100
-Ульяновская область|4|100
-Хабаровский край|4|100
-Хакасия|4|100
-Ханты-Мансийский АО|4|100
-Челябинская область|4|100
-Чеченская Республика|4|100
-Чувашия|4|100
-Ямало-Ненецкий АО|4|100
-Ярославская область|4|100</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -44040,192 +37068,6 @@
           <t xml:space="preserve">ilyabalabay@mail.ru</t>
         </is>
       </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|4|100
-Алтайский край|4|100
-Амурская область|4|100
-Архангельская область|4|100
-Астраханская область|4|100
-Башкортостан|4|100
-Белгородская область|4|100
-Брянская область|4|100
-Бурятия|4|100
-Владимирская область|4|100
-Волгоградская область|4|100
-Вологодская область|4|100
-Воронежская область|4|100
-Дагестан|4|100
-другой регион|4|100
-Еврейская АО|4|100
-Забайкальский край|4|100
-Ивановская область|4|100
-Ингушетия|4|100
-Иркутская область|4|100
-Кабардино-Балкария|4|100
-Калининградская область|4|100
-Калмыкия|4|100
-Калужская область|4|100
-Камчатский край|4|100
-Карачаево-Черкесия|4|100
-Карелия|4|100
-Кемеровская область|4|100
-Кировская область|4|100
-Коми|4|100
-Костромская область|4|100
-Краснодарский край|4|100
-Красноярский край|4|100
-Крым|4|100
-Курганская область|4|100
-Курская область|4|100
-Ленинградская область|4|100
-Липецкая область|4|100
-Магаданская область|4|100
-Марий Эл|4|100
-Мордовия|4|100
-Москва|4|100
-Московская область|4|100
-Мурманская область|4|100
-Ненецкий АО|4|100
-Нижегородская область|4|100
-Новгородская область|4|100
-Новосибирская область|4|100
-Омская область|4|100
-Оренбургская область|4|100
-Орловская область|4|100
-Пензенская область|4|100
-Пермский край|4|100
-Приморский край|4|100
-Псковская область|4|100
-Республика Алтай|4|100
-Ростовская область|4|100
-Рязанская область|4|100
-Самарская область|4|100
-Санкт-Петербург|4|100
-Саратовская область|4|100
-Саха (Якутия)|4|100
-Сахалинская область|4|100
-Свердловская область|4|100
-Северная Осетия|4|100
-Смоленская область|4|100
-Ставропольский край|4|100
-Тамбовская область|4|100
-Татарстан|4|100
-Тверская область|4|100
-Томская область|4|100
-Тульская область|4|100
-Тыва|4|100
-Тюменская область|4|100
-Удмуртия|4|100
-Ульяновская область|4|100
-Хабаровский край|4|100
-Хакасия|4|100
-Ханты-Мансийский АО|4|100
-Челябинская область|4|100
-Чеченская Республика|4|100
-Чувашия|4|100
-Ямало-Ненецкий АО|4|100
-Ярославская область|4|100</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -44366,192 +37208,6 @@
       <c r="AF34" t="inlineStr">
         <is>
           <t xml:space="preserve">ilyabalabay@mail.ru</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|6|100
-Алтайский край|6|100
-Амурская область|6|100
-Архангельская область|6|100
-Астраханская область|6|100
-Башкортостан|6|100
-Белгородская область|6|100
-Брянская область|6|100
-Бурятия|6|100
-Владимирская область|6|100
-Волгоградская область|6|100
-Вологодская область|6|100
-Воронежская область|6|100
-Дагестан|6|100
-другой регион|6|100
-Еврейская АО|6|100
-Забайкальский край|6|100
-Ивановская область|6|100
-Ингушетия|6|100
-Иркутская область|6|100
-Кабардино-Балкария|6|100
-Калининградская область|6|100
-Калмыкия|6|100
-Калужская область|6|100
-Камчатский край|6|100
-Карачаево-Черкесия|6|100
-Карелия|6|100
-Кемеровская область|6|100
-Кировская область|6|100
-Коми|6|100
-Костромская область|6|100
-Краснодарский край|6|100
-Красноярский край|6|100
-Крым|6|100
-Курганская область|6|100
-Курская область|6|100
-Ленинградская область|6|100
-Липецкая область|6|100
-Магаданская область|6|100
-Марий Эл|6|100
-Мордовия|6|100
-Москва|6|100
-Московская область|6|100
-Мурманская область|6|100
-Ненецкий АО|6|100
-Нижегородская область|6|100
-Новгородская область|6|100
-Новосибирская область|6|100
-Омская область|6|100
-Оренбургская область|6|100
-Орловская область|6|100
-Пензенская область|6|100
-Пермский край|6|100
-Приморский край|6|100
-Псковская область|6|100
-Республика Алтай|6|100
-Ростовская область|6|100
-Рязанская область|6|100
-Самарская область|6|100
-Санкт-Петербург|6|100
-Саратовская область|6|100
-Саха (Якутия)|6|100
-Сахалинская область|6|100
-Свердловская область|6|100
-Северная Осетия|6|100
-Смоленская область|6|100
-Ставропольский край|6|100
-Тамбовская область|6|100
-Татарстан|6|100
-Тверская область|6|100
-Томская область|6|100
-Тульская область|6|100
-Тыва|6|100
-Тюменская область|6|100
-Удмуртия|6|100
-Ульяновская область|6|100
-Хабаровский край|6|100
-Хакасия|6|100
-Ханты-Мансийский АО|6|100
-Челябинская область|6|100
-Чеченская Республика|6|100
-Чувашия|6|100
-Ямало-Ненецкий АО|6|100
-Ярославская область|6|100</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|4|100
-Алтайский край|4|100
-Амурская область|4|100
-Архангельская область|4|100
-Астраханская область|4|100
-Башкортостан|4|100
-Белгородская область|4|100
-Брянская область|4|100
-Бурятия|4|100
-Владимирская область|4|100
-Волгоградская область|4|100
-Вологодская область|4|100
-Воронежская область|4|100
-Дагестан|4|100
-другой регион|4|100
-Еврейская АО|4|100
-Забайкальский край|4|100
-Ивановская область|4|100
-Ингушетия|4|100
-Иркутская область|4|100
-Кабардино-Балкария|4|100
-Калининградская область|4|100
-Калмыкия|4|100
-Калужская область|4|100
-Камчатский край|4|100
-Карачаево-Черкесия|4|100
-Карелия|4|100
-Кемеровская область|4|100
-Кировская область|4|100
-Коми|4|100
-Костромская область|4|100
-Краснодарский край|4|100
-Красноярский край|4|100
-Крым|4|100
-Курганская область|4|100
-Курская область|4|100
-Ленинградская область|4|100
-Липецкая область|4|100
-Магаданская область|4|100
-Марий Эл|4|100
-Мордовия|4|100
-Москва|4|100
-Московская область|4|100
-Мурманская область|4|100
-Ненецкий АО|4|100
-Нижегородская область|4|100
-Новгородская область|4|100
-Новосибирская область|4|100
-Омская область|4|100
-Оренбургская область|4|100
-Орловская область|4|100
-Пензенская область|4|100
-Пермский край|4|100
-Приморский край|4|100
-Псковская область|4|100
-Республика Алтай|4|100
-Ростовская область|4|100
-Рязанская область|4|100
-Самарская область|4|100
-Санкт-Петербург|4|100
-Саратовская область|4|100
-Саха (Якутия)|4|100
-Сахалинская область|4|100
-Свердловская область|4|100
-Северная Осетия|4|100
-Смоленская область|4|100
-Ставропольский край|4|100
-Тамбовская область|4|100
-Татарстан|4|100
-Тверская область|4|100
-Томская область|4|100
-Тульская область|4|100
-Тыва|4|100
-Тюменская область|4|100
-Удмуртия|4|100
-Ульяновская область|4|100
-Хабаровский край|4|100
-Хакасия|4|100
-Ханты-Мансийский АО|4|100
-Челябинская область|4|100
-Чеченская Республика|4|100
-Чувашия|4|100
-Ямало-Ненецкий АО|4|100
-Ярославская область|4|100</t>
         </is>
       </c>
     </row>
@@ -83918,16 +76574,6 @@
         <v>7942</v>
       </c>
       <c r="Y2" s="7"/>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Настройка цены целевого действия</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Настройка цены целевого действия: ручная</t>
-        </is>
-      </c>
     </row>
     <row r="3" s="6" customFormat="true" ht="45" customHeight="true">
       <c r="A3" s="6" t="s">
@@ -83984,16 +76630,6 @@
       <c r="R3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Необязательный</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Необязательный</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
@@ -84050,16 +76686,6 @@
       <c r="R4" t="s">
         <v>44</v>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Одно значение из выпадающего списка в ячейке</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Подробнее о параметре</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -84130,99 +76756,6 @@
       </c>
       <c r="X5" t="s">
         <v>8078</v>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|5|100
-Алтайский край|5|100
-Амурская область|5|100
-Архангельская область|5|100
-Астраханская область|5|100
-Башкортостан|5|100
-Белгородская область|5|100
-Брянская область|5|100
-Бурятия|5|100
-Владимирская область|5|100
-Волгоградская область|5|100
-Вологодская область|5|100
-Воронежская область|5|100
-Дагестан|5|100
-другой регион|5|100
-Еврейская АО|5|100
-Забайкальский край|5|100
-Ивановская область|5|100
-Ингушетия|5|100
-Иркутская область|5|100
-Кабардино-Балкария|5|100
-Калининградская область|5|100
-Калмыкия|5|100
-Калужская область|5|100
-Камчатский край|5|100
-Карачаево-Черкесия|5|100
-Карелия|5|100
-Кемеровская область|5|100
-Кировская область|5|100
-Коми|5|100
-Костромская область|5|100
-Краснодарский край|5|100
-Красноярский край|5|100
-Крым|5|100
-Курганская область|5|100
-Курская область|5|100
-Ленинградская область|5|100
-Липецкая область|5|100
-Магаданская область|5|100
-Марий Эл|5|100
-Мордовия|5|100
-Москва|5|100
-Московская область|5|100
-Мурманская область|5|100
-Ненецкий АО|5|100
-Нижегородская область|5|100
-Новгородская область|5|100
-Новосибирская область|5|100
-Омская область|5|100
-Оренбургская область|5|100
-Орловская область|5|100
-Пензенская область|5|100
-Пермский край|5|100
-Приморский край|5|100
-Псковская область|5|100
-Республика Алтай|5|100
-Ростовская область|5|100
-Рязанская область|5|100
-Самарская область|5|100
-Санкт-Петербург|5|100
-Саратовская область|5|100
-Саха (Якутия)|5|100
-Сахалинская область|5|100
-Свердловская область|5|100
-Северная Осетия|5|100
-Смоленская область|5|100
-Ставропольский край|5|100
-Тамбовская область|5|100
-Татарстан|5|100
-Тверская область|5|100
-Томская область|5|100
-Тульская область|5|100
-Тыва|5|100
-Тюменская область|5|100
-Удмуртия|5|100
-Ульяновская область|5|100
-Хабаровский край|5|100
-Хакасия|5|100
-Ханты-Мансийский АО|5|100
-Челябинская область|5|100
-Чеченская Республика|5|100
-Чувашия|5|100
-Ямало-Ненецкий АО|5|100
-Ярославская область|5|100</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -84538,16 +77071,6 @@
         <v>7944</v>
       </c>
       <c r="V2" s="7"/>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Настройка цены целевого действия</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Настройка цены целевого действия: ручная</t>
-        </is>
-      </c>
     </row>
     <row r="3" s="6" customFormat="true" ht="45" customHeight="true">
       <c r="A3" s="6" t="s">
@@ -84598,16 +77121,6 @@
       <c r="P3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Необязательный</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Необязательный</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
@@ -84658,16 +77171,6 @@
       <c r="P4" t="s">
         <v>44</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Одно значение из выпадающего списка в ячейке</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Подробнее о параметре</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -84732,99 +77235,6 @@
       </c>
       <c r="U5" t="s">
         <v>8060</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|5|100
-Алтайский край|5|100
-Амурская область|5|100
-Архангельская область|5|100
-Астраханская область|5|100
-Башкортостан|5|100
-Белгородская область|5|100
-Брянская область|5|100
-Бурятия|5|100
-Владимирская область|5|100
-Волгоградская область|5|100
-Вологодская область|5|100
-Воронежская область|5|100
-Дагестан|5|100
-другой регион|5|100
-Еврейская АО|5|100
-Забайкальский край|5|100
-Ивановская область|5|100
-Ингушетия|5|100
-Иркутская область|5|100
-Кабардино-Балкария|5|100
-Калининградская область|5|100
-Калмыкия|5|100
-Калужская область|5|100
-Камчатский край|5|100
-Карачаево-Черкесия|5|100
-Карелия|5|100
-Кемеровская область|5|100
-Кировская область|5|100
-Коми|5|100
-Костромская область|5|100
-Краснодарский край|5|100
-Красноярский край|5|100
-Крым|5|100
-Курганская область|5|100
-Курская область|5|100
-Ленинградская область|5|100
-Липецкая область|5|100
-Магаданская область|5|100
-Марий Эл|5|100
-Мордовия|5|100
-Москва|5|100
-Московская область|5|100
-Мурманская область|5|100
-Ненецкий АО|5|100
-Нижегородская область|5|100
-Новгородская область|5|100
-Новосибирская область|5|100
-Омская область|5|100
-Оренбургская область|5|100
-Орловская область|5|100
-Пензенская область|5|100
-Пермский край|5|100
-Приморский край|5|100
-Псковская область|5|100
-Республика Алтай|5|100
-Ростовская область|5|100
-Рязанская область|5|100
-Самарская область|5|100
-Санкт-Петербург|5|100
-Саратовская область|5|100
-Саха (Якутия)|5|100
-Сахалинская область|5|100
-Свердловская область|5|100
-Северная Осетия|5|100
-Смоленская область|5|100
-Ставропольский край|5|100
-Тамбовская область|5|100
-Татарстан|5|100
-Тверская область|5|100
-Томская область|5|100
-Тульская область|5|100
-Тыва|5|100
-Тюменская область|5|100
-Удмуртия|5|100
-Ульяновская область|5|100
-Хабаровский край|5|100
-Хакасия|5|100
-Ханты-Мансийский АО|5|100
-Челябинская область|5|100
-Чеченская Республика|5|100
-Чувашия|5|100
-Ямало-Ненецкий АО|5|100
-Ярославская область|5|100</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -85063,16 +77473,6 @@
         <v>7944</v>
       </c>
       <c r="V2" s="7"/>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Настройка цены целевого действия</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Настройка цены целевого действия: ручная</t>
-        </is>
-      </c>
     </row>
     <row r="3" s="6" customFormat="true" ht="45" customHeight="true">
       <c r="A3" s="6" t="s">
@@ -85123,16 +77523,6 @@
       <c r="P3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Необязательный</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Необязательный</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
@@ -85183,16 +77573,6 @@
       <c r="P4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Одно значение из выпадающего списка в ячейке</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Подробнее о параметре</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -85255,99 +77635,6 @@
       <c r="U5" t="s">
         <v>8060</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|2|100
-Алтайский край|2|100
-Амурская область|2|100
-Архангельская область|2|100
-Астраханская область|2|100
-Башкортостан|2|100
-Белгородская область|2|100
-Брянская область|2|100
-Бурятия|2|100
-Владимирская область|2|100
-Волгоградская область|2|100
-Вологодская область|2|100
-Воронежская область|2|100
-Дагестан|2|100
-другой регион|2|100
-Еврейская АО|2|100
-Забайкальский край|2|100
-Ивановская область|2|100
-Ингушетия|2|100
-Иркутская область|2|100
-Кабардино-Балкария|2|100
-Калининградская область|2|100
-Калмыкия|2|100
-Калужская область|2|100
-Камчатский край|2|100
-Карачаево-Черкесия|2|100
-Карелия|2|100
-Кемеровская область|2|100
-Кировская область|2|100
-Коми|2|100
-Костромская область|2|100
-Краснодарский край|2|100
-Красноярский край|2|100
-Крым|2|100
-Курганская область|2|100
-Курская область|2|100
-Ленинградская область|2|100
-Липецкая область|2|100
-Магаданская область|2|100
-Марий Эл|2|100
-Мордовия|2|100
-Москва|2|100
-Московская область|2|100
-Мурманская область|2|100
-Ненецкий АО|2|100
-Нижегородская область|2|100
-Новгородская область|2|100
-Новосибирская область|2|100
-Омская область|2|100
-Оренбургская область|2|100
-Орловская область|2|100
-Пензенская область|2|100
-Пермский край|2|100
-Приморский край|2|100
-Псковская область|2|100
-Республика Алтай|2|100
-Ростовская область|2|100
-Рязанская область|2|100
-Самарская область|2|100
-Санкт-Петербург|2|100
-Саратовская область|2|100
-Саха (Якутия)|2|100
-Сахалинская область|2|100
-Свердловская область|2|100
-Северная Осетия|2|100
-Смоленская область|2|100
-Ставропольский край|2|100
-Тамбовская область|2|100
-Татарстан|2|100
-Тверская область|2|100
-Томская область|2|100
-Тульская область|2|100
-Тыва|2|100
-Тюменская область|2|100
-Удмуртия|2|100
-Ульяновская область|2|100
-Хабаровский край|2|100
-Хакасия|2|100
-Ханты-Мансийский АО|2|100
-Челябинская область|2|100
-Чеченская Республика|2|100
-Чувашия|2|100
-Ямало-Ненецкий АО|2|100
-Ярославская область|2|100</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
@@ -85410,99 +77697,6 @@
       <c r="U6" t="s">
         <v>8060</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|2|100
-Алтайский край|2|100
-Амурская область|2|100
-Архангельская область|2|100
-Астраханская область|2|100
-Башкортостан|2|100
-Белгородская область|2|100
-Брянская область|2|100
-Бурятия|2|100
-Владимирская область|2|100
-Волгоградская область|2|100
-Вологодская область|2|100
-Воронежская область|2|100
-Дагестан|2|100
-другой регион|2|100
-Еврейская АО|2|100
-Забайкальский край|2|100
-Ивановская область|2|100
-Ингушетия|2|100
-Иркутская область|2|100
-Кабардино-Балкария|2|100
-Калининградская область|2|100
-Калмыкия|2|100
-Калужская область|2|100
-Камчатский край|2|100
-Карачаево-Черкесия|2|100
-Карелия|2|100
-Кемеровская область|2|100
-Кировская область|2|100
-Коми|2|100
-Костромская область|2|100
-Краснодарский край|2|100
-Красноярский край|2|100
-Крым|2|100
-Курганская область|2|100
-Курская область|2|100
-Ленинградская область|2|100
-Липецкая область|2|100
-Магаданская область|2|100
-Марий Эл|2|100
-Мордовия|2|100
-Москва|2|100
-Московская область|2|100
-Мурманская область|2|100
-Ненецкий АО|2|100
-Нижегородская область|2|100
-Новгородская область|2|100
-Новосибирская область|2|100
-Омская область|2|100
-Оренбургская область|2|100
-Орловская область|2|100
-Пензенская область|2|100
-Пермский край|2|100
-Приморский край|2|100
-Псковская область|2|100
-Республика Алтай|2|100
-Ростовская область|2|100
-Рязанская область|2|100
-Самарская область|2|100
-Санкт-Петербург|2|100
-Саратовская область|2|100
-Саха (Якутия)|2|100
-Сахалинская область|2|100
-Свердловская область|2|100
-Северная Осетия|2|100
-Смоленская область|2|100
-Ставропольский край|2|100
-Тамбовская область|2|100
-Татарстан|2|100
-Тверская область|2|100
-Томская область|2|100
-Тульская область|2|100
-Тыва|2|100
-Тюменская область|2|100
-Удмуртия|2|100
-Ульяновская область|2|100
-Хабаровский край|2|100
-Хакасия|2|100
-Ханты-Мансийский АО|2|100
-Челябинская область|2|100
-Чеченская Республика|2|100
-Чувашия|2|100
-Ямало-Ненецкий АО|2|100
-Ярославская область|2|100</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
@@ -85565,99 +77759,6 @@
       <c r="U7" t="s">
         <v>8060</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|2|100
-Алтайский край|2|100
-Амурская область|2|100
-Архангельская область|2|100
-Астраханская область|2|100
-Башкортостан|2|100
-Белгородская область|2|100
-Брянская область|2|100
-Бурятия|2|100
-Владимирская область|2|100
-Волгоградская область|2|100
-Вологодская область|2|100
-Воронежская область|2|100
-Дагестан|2|100
-другой регион|2|100
-Еврейская АО|2|100
-Забайкальский край|2|100
-Ивановская область|2|100
-Ингушетия|2|100
-Иркутская область|2|100
-Кабардино-Балкария|2|100
-Калининградская область|2|100
-Калмыкия|2|100
-Калужская область|2|100
-Камчатский край|2|100
-Карачаево-Черкесия|2|100
-Карелия|2|100
-Кемеровская область|2|100
-Кировская область|2|100
-Коми|2|100
-Костромская область|2|100
-Краснодарский край|2|100
-Красноярский край|2|100
-Крым|2|100
-Курганская область|2|100
-Курская область|2|100
-Ленинградская область|2|100
-Липецкая область|2|100
-Магаданская область|2|100
-Марий Эл|2|100
-Мордовия|2|100
-Москва|2|100
-Московская область|2|100
-Мурманская область|2|100
-Ненецкий АО|2|100
-Нижегородская область|2|100
-Новгородская область|2|100
-Новосибирская область|2|100
-Омская область|2|100
-Оренбургская область|2|100
-Орловская область|2|100
-Пензенская область|2|100
-Пермский край|2|100
-Приморский край|2|100
-Псковская область|2|100
-Республика Алтай|2|100
-Ростовская область|2|100
-Рязанская область|2|100
-Самарская область|2|100
-Санкт-Петербург|2|100
-Саратовская область|2|100
-Саха (Якутия)|2|100
-Сахалинская область|2|100
-Свердловская область|2|100
-Северная Осетия|2|100
-Смоленская область|2|100
-Ставропольский край|2|100
-Тамбовская область|2|100
-Татарстан|2|100
-Тверская область|2|100
-Томская область|2|100
-Тульская область|2|100
-Тыва|2|100
-Тюменская область|2|100
-Удмуртия|2|100
-Ульяновская область|2|100
-Хабаровский край|2|100
-Хакасия|2|100
-Ханты-Мансийский АО|2|100
-Челябинская область|2|100
-Чеченская Республика|2|100
-Чувашия|2|100
-Ямало-Ненецкий АО|2|100
-Ярославская область|2|100</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -85719,99 +77820,6 @@
       </c>
       <c r="U8" t="s">
         <v>8060</v>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Адыгея|5|100
-Алтайский край|5|100
-Амурская область|5|100
-Архангельская область|5|100
-Астраханская область|5|100
-Башкортостан|5|100
-Белгородская область|5|100
-Брянская область|5|100
-Бурятия|5|100
-Владимирская область|5|100
-Волгоградская область|5|100
-Вологодская область|5|100
-Воронежская область|5|100
-Дагестан|5|100
-другой регион|5|100
-Еврейская АО|5|100
-Забайкальский край|5|100
-Ивановская область|5|100
-Ингушетия|5|100
-Иркутская область|5|100
-Кабардино-Балкария|5|100
-Калининградская область|5|100
-Калмыкия|5|100
-Калужская область|5|100
-Камчатский край|5|100
-Карачаево-Черкесия|5|100
-Карелия|5|100
-Кемеровская область|5|100
-Кировская область|5|100
-Коми|5|100
-Костромская область|5|100
-Краснодарский край|5|100
-Красноярский край|5|100
-Крым|5|100
-Курганская область|5|100
-Курская область|5|100
-Ленинградская область|5|100
-Липецкая область|5|100
-Магаданская область|5|100
-Марий Эл|5|100
-Мордовия|5|100
-Москва|5|100
-Московская область|5|100
-Мурманская область|5|100
-Ненецкий АО|5|100
-Нижегородская область|5|100
-Новгородская область|5|100
-Новосибирская область|5|100
-Омская область|5|100
-Оренбургская область|5|100
-Орловская область|5|100
-Пензенская область|5|100
-Пермский край|5|100
-Приморский край|5|100
-Псковская область|5|100
-Республика Алтай|5|100
-Ростовская область|5|100
-Рязанская область|5|100
-Самарская область|5|100
-Санкт-Петербург|5|100
-Саратовская область|5|100
-Саха (Якутия)|5|100
-Сахалинская область|5|100
-Свердловская область|5|100
-Северная Осетия|5|100
-Смоленская область|5|100
-Ставропольский край|5|100
-Тамбовская область|5|100
-Татарстан|5|100
-Тверская область|5|100
-Томская область|5|100
-Тульская область|5|100
-Тыва|5|100
-Тюменская область|5|100
-Удмуртия|5|100
-Ульяновская область|5|100
-Хабаровский край|5|100
-Хакасия|5|100
-Ханты-Мансийский АО|5|100
-Челябинская область|5|100
-Чеченская Республика|5|100
-Чувашия|5|100
-Ямало-Ненецкий АО|5|100
-Ярославская область|5|100</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/ilya_feed.xlsx
+++ b/ilya_feed.xlsx
@@ -31535,14 +31535,6 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1"/>
-  <cols>
-    <col customWidth="true" max="1" min="1" width="28.33"/>
-    <col customWidth="true" max="2" min="2" width="17"/>
-    <col customWidth="true" max="3" min="3" width="25"/>
-    <col customWidth="true" max="5" min="4" width="16"/>
-    <col customWidth="true" max="7" min="6" width="19"/>
-    <col customWidth="true" max="17" min="8" width="16"/>
-  </cols>
   <sheetData>
     <row r="1" ht="50" customHeight="true">
       <c r="A1" s="4" t="s">
@@ -31598,22 +31590,27 @@
       <c r="P2" s="7" t="s">
         <v>8027</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="R2" s="7" t="s">
         <v>7943</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="S2" s="7" t="s">
         <v>7944</v>
       </c>
-      <c r="S2" s="7" t="s">
+      <c r="T2" s="7" t="s">
         <v>7945</v>
       </c>
-      <c r="T2" s="7" t="s">
+      <c r="U2" s="7" t="s">
         <v>7941</v>
       </c>
-      <c r="U2" s="7" t="s">
+      <c r="V2" s="7" t="s">
         <v>7942</v>
       </c>
-      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Способ доставки</t>
+        </is>
+      </c>
     </row>
     <row r="3" s="6" customFormat="true" ht="45" customHeight="true">
       <c r="A3" s="6" t="s">
@@ -31664,6 +31661,11 @@
       <c r="P3" s="6" t="s">
         <v>39</v>
       </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
@@ -31764,20 +31766,25 @@
       <c r="P5" t="s">
         <v>8033</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>8059</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>8060</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>8061</v>
       </c>
-      <c r="T5" t="s">
+      <c r="U5" t="s">
         <v>8062</v>
       </c>
-      <c r="U5" t="s">
+      <c r="V5" t="s">
         <v>8063</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -32016,15 +32023,6 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1"/>
-  <cols>
-    <col customWidth="true" max="1" min="1" width="28.33"/>
-    <col customWidth="true" max="2" min="2" width="17"/>
-    <col customWidth="true" max="3" min="3" width="25"/>
-    <col customWidth="true" max="5" min="4" width="16"/>
-    <col customWidth="true" max="7" min="6" width="19"/>
-    <col customWidth="true" max="15" min="8" width="16"/>
-    <col customWidth="true" max="17" min="16" width="28.33"/>
-  </cols>
   <sheetData>
     <row r="1" ht="50" customHeight="true">
       <c r="A1" s="4" t="s">
@@ -32083,19 +32081,24 @@
       <c r="Q2" s="7" t="s">
         <v>7944</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="S2" s="7" t="s">
         <v>7943</v>
       </c>
-      <c r="S2" s="7" t="s">
+      <c r="T2" s="7" t="s">
         <v>7942</v>
       </c>
-      <c r="T2" s="7" t="s">
+      <c r="U2" s="7" t="s">
         <v>7941</v>
       </c>
-      <c r="U2" s="7" t="s">
+      <c r="V2" s="7" t="s">
         <v>7945</v>
       </c>
-      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Способ доставки</t>
+        </is>
+      </c>
     </row>
     <row r="3" s="6" customFormat="true" ht="45" customHeight="true">
       <c r="A3" s="6" t="s">
@@ -32146,6 +32149,11 @@
       <c r="P3" s="6" t="s">
         <v>39</v>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
@@ -32249,17 +32257,22 @@
       <c r="Q5" t="s">
         <v>8060</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>8059</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>8237</v>
       </c>
-      <c r="T5" t="s">
+      <c r="U5" t="s">
         <v>8062</v>
       </c>
-      <c r="U5" t="s">
+      <c r="V5" t="s">
         <v>8061</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -32314,17 +32327,22 @@
       <c r="Q6" t="s">
         <v>8060</v>
       </c>
-      <c r="R6" t="s">
+      <c r="S6" t="s">
         <v>8059</v>
       </c>
-      <c r="S6" t="s">
+      <c r="T6" t="s">
         <v>8244</v>
       </c>
-      <c r="T6" t="s">
+      <c r="U6" t="s">
         <v>8062</v>
       </c>
-      <c r="U6" t="s">
+      <c r="V6" t="s">
         <v>8061</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -32379,17 +32397,22 @@
       <c r="Q7" t="s">
         <v>8060</v>
       </c>
-      <c r="R7" t="s">
+      <c r="S7" t="s">
         <v>8059</v>
       </c>
-      <c r="S7" t="s">
+      <c r="T7" t="s">
         <v>8251</v>
       </c>
-      <c r="T7" t="s">
+      <c r="U7" t="s">
         <v>8062</v>
       </c>
-      <c r="U7" t="s">
+      <c r="V7" t="s">
         <v>8061</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -32444,17 +32467,22 @@
       <c r="Q8" t="s">
         <v>8060</v>
       </c>
-      <c r="R8" t="s">
+      <c r="S8" t="s">
         <v>8059</v>
       </c>
-      <c r="S8" t="s">
+      <c r="T8" t="s">
         <v>8258</v>
       </c>
-      <c r="T8" t="s">
+      <c r="U8" t="s">
         <v>8062</v>
       </c>
-      <c r="U8" t="s">
+      <c r="V8" t="s">
         <v>8061</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -32509,17 +32537,22 @@
       <c r="Q9" t="s">
         <v>8060</v>
       </c>
-      <c r="R9" t="s">
+      <c r="S9" t="s">
         <v>8059</v>
       </c>
-      <c r="S9" t="s">
+      <c r="T9" t="s">
         <v>8265</v>
       </c>
-      <c r="T9" t="s">
+      <c r="U9" t="s">
         <v>8062</v>
       </c>
-      <c r="U9" t="s">
+      <c r="V9" t="s">
         <v>8061</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -32574,17 +32607,22 @@
       <c r="Q10" t="s">
         <v>8060</v>
       </c>
-      <c r="R10" t="s">
+      <c r="S10" t="s">
         <v>8059</v>
       </c>
-      <c r="S10" t="s">
+      <c r="T10" t="s">
         <v>8272</v>
       </c>
-      <c r="T10" t="s">
+      <c r="U10" t="s">
         <v>8062</v>
       </c>
-      <c r="U10" t="s">
+      <c r="V10" t="s">
         <v>8061</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -32639,17 +32677,22 @@
       <c r="Q11" t="s">
         <v>8060</v>
       </c>
-      <c r="R11" t="s">
+      <c r="S11" t="s">
         <v>8059</v>
       </c>
-      <c r="S11" t="s">
+      <c r="T11" t="s">
         <v>8278</v>
       </c>
-      <c r="T11" t="s">
+      <c r="U11" t="s">
         <v>8062</v>
       </c>
-      <c r="U11" t="s">
+      <c r="V11" t="s">
         <v>8061</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -32704,17 +32747,22 @@
       <c r="Q12" t="s">
         <v>8060</v>
       </c>
-      <c r="R12" t="s">
+      <c r="S12" t="s">
         <v>8059</v>
       </c>
-      <c r="S12" t="s">
+      <c r="T12" t="s">
         <v>8285</v>
       </c>
-      <c r="T12" t="s">
+      <c r="U12" t="s">
         <v>8062</v>
       </c>
-      <c r="U12" t="s">
+      <c r="V12" t="s">
         <v>8061</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -32769,17 +32817,22 @@
       <c r="Q13" t="s">
         <v>8060</v>
       </c>
-      <c r="R13" t="s">
+      <c r="S13" t="s">
         <v>8059</v>
       </c>
-      <c r="S13" t="s">
+      <c r="T13" t="s">
         <v>8292</v>
       </c>
-      <c r="T13" t="s">
+      <c r="U13" t="s">
         <v>8062</v>
       </c>
-      <c r="U13" t="s">
+      <c r="V13" t="s">
         <v>8061</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -32834,17 +32887,22 @@
       <c r="Q14" t="s">
         <v>8060</v>
       </c>
-      <c r="R14" t="s">
+      <c r="S14" t="s">
         <v>8059</v>
       </c>
-      <c r="S14" t="s">
+      <c r="T14" t="s">
         <v>8299</v>
       </c>
-      <c r="T14" t="s">
+      <c r="U14" t="s">
         <v>8062</v>
       </c>
-      <c r="U14" t="s">
+      <c r="V14" t="s">
         <v>8061</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -32899,17 +32957,22 @@
       <c r="Q15" t="s">
         <v>8060</v>
       </c>
-      <c r="R15" t="s">
+      <c r="S15" t="s">
         <v>8059</v>
       </c>
-      <c r="S15" t="s">
+      <c r="T15" t="s">
         <v>8306</v>
       </c>
-      <c r="T15" t="s">
+      <c r="U15" t="s">
         <v>8062</v>
       </c>
-      <c r="U15" t="s">
+      <c r="V15" t="s">
         <v>8061</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -32964,17 +33027,22 @@
       <c r="Q16" t="s">
         <v>8060</v>
       </c>
-      <c r="R16" t="s">
+      <c r="S16" t="s">
         <v>8059</v>
       </c>
-      <c r="S16" t="s">
+      <c r="T16" t="s">
         <v>8313</v>
       </c>
-      <c r="T16" t="s">
+      <c r="U16" t="s">
         <v>8062</v>
       </c>
-      <c r="U16" t="s">
+      <c r="V16" t="s">
         <v>8061</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -33029,17 +33097,22 @@
       <c r="Q17" t="s">
         <v>8060</v>
       </c>
-      <c r="R17" t="s">
+      <c r="S17" t="s">
         <v>8059</v>
       </c>
-      <c r="S17" t="s">
+      <c r="T17" t="s">
         <v>8320</v>
       </c>
-      <c r="T17" t="s">
+      <c r="U17" t="s">
         <v>8062</v>
       </c>
-      <c r="U17" t="s">
+      <c r="V17" t="s">
         <v>8061</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -33094,17 +33167,22 @@
       <c r="Q18" t="s">
         <v>8060</v>
       </c>
-      <c r="R18" t="s">
+      <c r="S18" t="s">
         <v>8059</v>
       </c>
-      <c r="S18" t="s">
+      <c r="T18" t="s">
         <v>8327</v>
       </c>
-      <c r="T18" t="s">
+      <c r="U18" t="s">
         <v>8062</v>
       </c>
-      <c r="U18" t="s">
+      <c r="V18" t="s">
         <v>8061</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -33159,17 +33237,22 @@
       <c r="Q19" t="s">
         <v>8060</v>
       </c>
-      <c r="R19" t="s">
+      <c r="S19" t="s">
         <v>8059</v>
       </c>
-      <c r="S19" t="s">
+      <c r="T19" t="s">
         <v>8333</v>
       </c>
-      <c r="T19" t="s">
+      <c r="U19" t="s">
         <v>8062</v>
       </c>
-      <c r="U19" t="s">
+      <c r="V19" t="s">
         <v>8061</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -33224,17 +33307,22 @@
       <c r="Q20" t="s">
         <v>8060</v>
       </c>
-      <c r="R20" t="s">
+      <c r="S20" t="s">
         <v>8059</v>
       </c>
-      <c r="S20" t="s">
+      <c r="T20" t="s">
         <v>8340</v>
       </c>
-      <c r="T20" t="s">
+      <c r="U20" t="s">
         <v>8062</v>
       </c>
-      <c r="U20" t="s">
+      <c r="V20" t="s">
         <v>8061</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -33289,17 +33377,22 @@
       <c r="Q21" t="s">
         <v>8060</v>
       </c>
-      <c r="R21" t="s">
+      <c r="S21" t="s">
         <v>8059</v>
       </c>
-      <c r="S21" t="s">
+      <c r="T21" t="s">
         <v>8347</v>
       </c>
-      <c r="T21" t="s">
+      <c r="U21" t="s">
         <v>8062</v>
       </c>
-      <c r="U21" t="s">
+      <c r="V21" t="s">
         <v>8061</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -76484,16 +76577,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1"/>
-  <cols>
-    <col customWidth="true" max="1" min="1" width="28.33"/>
-    <col customWidth="true" max="2" min="2" width="17"/>
-    <col customWidth="true" max="3" min="3" width="25"/>
-    <col customWidth="true" max="7" min="4" width="16"/>
-    <col customWidth="true" max="8" min="8" width="19"/>
-    <col customWidth="true" max="9" min="9" width="16"/>
-    <col customWidth="true" max="10" min="10" width="19"/>
-    <col customWidth="true" max="19" min="11" width="16"/>
-  </cols>
   <sheetData>
     <row r="1" ht="50" customHeight="true">
       <c r="A1" s="4" t="s">
@@ -76561,19 +76644,24 @@
       <c r="T2" s="7" t="s">
         <v>7944</v>
       </c>
-      <c r="U2" s="7" t="s">
+      <c r="V2" s="7" t="s">
         <v>7945</v>
       </c>
-      <c r="V2" s="7" t="s">
+      <c r="W2" s="7" t="s">
         <v>7981</v>
       </c>
-      <c r="W2" s="7" t="s">
+      <c r="X2" s="7" t="s">
         <v>7943</v>
       </c>
-      <c r="X2" s="7" t="s">
+      <c r="Y2" s="7" t="s">
         <v>7942</v>
       </c>
-      <c r="Y2" s="7"/>
+      <c r="Z2" s="7"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Способ доставки</t>
+        </is>
+      </c>
     </row>
     <row r="3" s="6" customFormat="true" ht="45" customHeight="true">
       <c r="A3" s="6" t="s">
@@ -76630,6 +76718,11 @@
       <c r="R3" s="6" t="s">
         <v>43</v>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
@@ -76745,17 +76838,22 @@
       <c r="T5" t="s">
         <v>8060</v>
       </c>
-      <c r="U5" t="s">
+      <c r="V5" t="s">
         <v>8061</v>
       </c>
-      <c r="V5" t="s">
+      <c r="W5" t="s">
         <v>8077</v>
       </c>
-      <c r="W5" t="s">
+      <c r="X5" t="s">
         <v>8059</v>
       </c>
-      <c r="X5" t="s">
+      <c r="Y5" t="s">
         <v>8078</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -76991,15 +77089,6 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1"/>
-  <cols>
-    <col customWidth="true" max="1" min="1" width="28.33"/>
-    <col customWidth="true" max="2" min="2" width="17"/>
-    <col customWidth="true" max="3" min="3" width="25"/>
-    <col customWidth="true" max="5" min="4" width="16"/>
-    <col customWidth="true" max="7" min="6" width="19"/>
-    <col customWidth="true" max="15" min="8" width="16"/>
-    <col customWidth="true" max="17" min="16" width="17"/>
-  </cols>
   <sheetData>
     <row r="1" ht="50" customHeight="true">
       <c r="A1" s="4" t="s">
@@ -77058,19 +77147,24 @@
       <c r="Q2" s="7" t="s">
         <v>7941</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="S2" s="7" t="s">
         <v>7943</v>
       </c>
-      <c r="S2" s="7" t="s">
+      <c r="T2" s="7" t="s">
         <v>7942</v>
       </c>
-      <c r="T2" s="7" t="s">
+      <c r="U2" s="7" t="s">
         <v>7945</v>
       </c>
-      <c r="U2" s="7" t="s">
+      <c r="V2" s="7" t="s">
         <v>7944</v>
       </c>
-      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Способ доставки</t>
+        </is>
+      </c>
     </row>
     <row r="3" s="6" customFormat="true" ht="45" customHeight="true">
       <c r="A3" s="6" t="s">
@@ -77121,6 +77215,11 @@
       <c r="P3" s="6" t="s">
         <v>39</v>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
@@ -77224,17 +77323,22 @@
       <c r="Q5" t="s">
         <v>8062</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>8059</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>8070</v>
       </c>
-      <c r="T5" t="s">
+      <c r="U5" t="s">
         <v>8061</v>
       </c>
-      <c r="U5" t="s">
+      <c r="V5" t="s">
         <v>8060</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -77394,14 +77498,6 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1"/>
-  <cols>
-    <col customWidth="true" max="1" min="1" width="28.33"/>
-    <col customWidth="true" max="2" min="2" width="17"/>
-    <col customWidth="true" max="3" min="3" width="25"/>
-    <col customWidth="true" max="5" min="4" width="16"/>
-    <col customWidth="true" max="7" min="6" width="19"/>
-    <col customWidth="true" max="17" min="8" width="16"/>
-  </cols>
   <sheetData>
     <row r="1" ht="50" customHeight="true">
       <c r="A1" s="4" t="s">
@@ -77457,22 +77553,27 @@
       <c r="P2" s="7" t="s">
         <v>7846</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="R2" s="7" t="s">
         <v>7943</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="S2" s="7" t="s">
         <v>7945</v>
       </c>
-      <c r="S2" s="7" t="s">
+      <c r="T2" s="7" t="s">
         <v>7941</v>
       </c>
-      <c r="T2" s="7" t="s">
+      <c r="U2" s="7" t="s">
         <v>7942</v>
       </c>
-      <c r="U2" s="7" t="s">
+      <c r="V2" s="7" t="s">
         <v>7944</v>
       </c>
-      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Способ доставки</t>
+        </is>
+      </c>
     </row>
     <row r="3" s="6" customFormat="true" ht="45" customHeight="true">
       <c r="A3" s="6" t="s">
@@ -77523,6 +77624,11 @@
       <c r="P3" s="6" t="s">
         <v>43</v>
       </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
@@ -77620,20 +77726,25 @@
       <c r="P5" t="s">
         <v>8353</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>8059</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>8061</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>8062</v>
       </c>
-      <c r="T5" t="s">
+      <c r="U5" t="s">
         <v>8354</v>
       </c>
-      <c r="U5" t="s">
+      <c r="V5" t="s">
         <v>8060</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -77682,20 +77793,25 @@
       <c r="P6" t="s">
         <v>8360</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>8059</v>
       </c>
-      <c r="R6" t="s">
+      <c r="S6" t="s">
         <v>8061</v>
       </c>
-      <c r="S6" t="s">
+      <c r="T6" t="s">
         <v>8062</v>
       </c>
-      <c r="T6" t="s">
+      <c r="U6" t="s">
         <v>8361</v>
       </c>
-      <c r="U6" t="s">
+      <c r="V6" t="s">
         <v>8060</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -77744,20 +77860,25 @@
       <c r="P7" t="s">
         <v>8366</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
         <v>8059</v>
       </c>
-      <c r="R7" t="s">
+      <c r="S7" t="s">
         <v>8061</v>
       </c>
-      <c r="S7" t="s">
+      <c r="T7" t="s">
         <v>8062</v>
       </c>
-      <c r="T7" t="s">
+      <c r="U7" t="s">
         <v>8367</v>
       </c>
-      <c r="U7" t="s">
+      <c r="V7" t="s">
         <v>8060</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -77806,20 +77927,25 @@
       <c r="P8" t="s">
         <v>8372</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>8059</v>
       </c>
-      <c r="R8" t="s">
+      <c r="S8" t="s">
         <v>8061</v>
       </c>
-      <c r="S8" t="s">
+      <c r="T8" t="s">
         <v>8062</v>
       </c>
-      <c r="T8" t="s">
+      <c r="U8" t="s">
         <v>8373</v>
       </c>
-      <c r="U8" t="s">
+      <c r="V8" t="s">
         <v>8060</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/ilya_feed.xlsx
+++ b/ilya_feed.xlsx
@@ -37304,6 +37304,1426 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u0918d_Richard_Mille_carbon_blue</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/sp8KMfy8/d5-Richard-Mille-carbon-blue-0.jpg | https://i.ibb.co/27TTnLLc/d5-Richard-Mille-carbon-blue-1.jpg | https://i.ibb.co/VYfjn4Px/d5-Richard-Mille-carbon-blue-2.jpg | https://i.ibb.co/WpsrSdvm/d5-Richard-Mille-carbon-blue-3.jpg | https://i.ibb.co/YFBPp5D5/d5-Richard-Mille-carbon-blue-4.jpg | https://i.ibb.co/JWCSy984/d5-Richard-Mille-carbon-blue-5.jpg</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Richard Mille синий карбон мужские</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Richard Mille — синий карбон, мужские&lt;br&gt;&lt;br&gt;Корпус-бочка из тёмного композита с синей рамкой и полностью открытый механизм: видно, как работают мосты и балансир.&lt;br&gt;&lt;br&gt;• Механизм: механический с автоподзаводом&lt;br&gt;• Корпус: карбон с синей вставкой, форма тонно&lt;br&gt;• Циферблат: скелетон&lt;br&gt;• Ремешок: белый каучук&lt;br&gt;• Функции: водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы richard mille, richard mille карбон, часы скелетон мужские, наручные часы каучук&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93500</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Richard Mille</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Синий</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Белый</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/zH-g09oev7NF-Q</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каучуковый</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u0918d_Panerai_Luminor_blue</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/sdjtPQ38/d5-Panerai-Luminor-blue-0.jpg | https://i.ibb.co/s9y1yTW0/d5-Panerai-Luminor-blue-1.jpg | https://i.ibb.co/CsDMD8Pb/d5-Panerai-Luminor-blue-2.jpg | https://i.ibb.co/Y7T4HfYZ/d5-Panerai-Luminor-blue-3.jpg | https://i.ibb.co/Q240snh/d5-Panerai-Luminor-blue-4.jpg | https://i.ibb.co/5WtsH0Qz/d5-Panerai-Luminor-blue-5.jpg</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Panerai Luminor Marina синий мужские</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panerai Luminor Marina — синий циферблат, мужские&lt;br&gt;&lt;br&gt;Подушкообразный корпус с фирменной скобой над головкой, глубокий синий циферблат с крупными цифрами и малой секундной стрелкой.&lt;br&gt;&lt;br&gt;• Механизм: механический с автоподзаводом&lt;br&gt;• Корпус: сталь, 44 мм, защитная скоба&lt;br&gt;• Циферблат: синий, крупные цифры, окно даты&lt;br&gt;• Ремешок: синяя кожа&lt;br&gt;• Функции: дата, водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы panerai мужские, panerai luminor marina, часы синие мужские, наручные часы кожа&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64500</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panerai</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Синий</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Синий</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/2LeA-oy5BqQUNA</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод | Календарь</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кожаный</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u0918d_Cartier_oval_diamonds</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/6702LLfQ/d5-Cartier-oval-diamonds-0.jpg | https://i.ibb.co/tT41yDjc/d5-Cartier-oval-diamonds-1.jpg | https://i.ibb.co/fb9zZsd/d5-Cartier-oval-diamonds-2.jpg | https://i.ibb.co/ycncjSBF/d5-Cartier-oval-diamonds-3.jpg | https://i.ibb.co/vCKGJbYQ/d5-Cartier-oval-diamonds-4.jpg | https://i.ibb.co/7ws6HM3/d5-Cartier-oval-diamonds-5.jpg | https://i.ibb.co/zT00L4G4/d5-Cartier-oval-diamonds-6.jpg</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Cartier овальные с камнями женские</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier — овальный корпус с камнями, женские&lt;br&gt;&lt;br&gt;Небольшой овальный корпус, полностью обрамлённый камнями, светлый циферблат с римскими цифрами и тонкий кожаный ремешок.&lt;br&gt;&lt;br&gt;• Механизм: кварцевый&lt;br&gt;• Корпус: овальный, камни по рамке&lt;br&gt;• Циферблат: светлый, римские цифры&lt;br&gt;• Ремешок: чёрная кожа&lt;br&gt;• Функции: водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы cartier женские, cartier овальные, часы с камнями женские, наручные часы кварц&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67500</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Серебряный</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/-syX074TGPcJDw</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Женские</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кожаный</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u0918d_Cartier_Santos_steel_gold</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/cSDKSYGN/d5-Cartier-Santos-steel-gold-0.jpg | https://i.ibb.co/gLtP8Qnm/d5-Cartier-Santos-steel-gold-1.jpg | https://i.ibb.co/yFzPYH32/d5-Cartier-Santos-steel-gold-2.jpg | https://i.ibb.co/bgvv8GN1/d5-Cartier-Santos-steel-gold-3.jpg | https://i.ibb.co/mFHWzKvT/d5-Cartier-Santos-steel-gold-4.jpg | https://i.ibb.co/G3sYxLJc/d5-Cartier-Santos-steel-gold-5.jpg | https://i.ibb.co/X1Wsg4Q/d5-Cartier-Santos-steel-gold-6.jpg</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Cartier Santos сталь золото мужские</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier Santos — сталь и золото, мужские&lt;br&gt;&lt;br&gt;Квадратный корпус с винтами по безелю и двухцветный браслет: золотистые винты и звенья на стальной базе, белый циферблат с римскими цифрами.&lt;br&gt;&lt;br&gt;• Механизм: механический с автоподзаводом&lt;br&gt;• Корпус: сталь с золотистым безелем, квадратный&lt;br&gt;• Циферблат: белый, римские цифры, окно даты&lt;br&gt;• Браслет: сталь с золотистыми звеньями&lt;br&gt;• Функции: дата, водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы cartier мужские, cartier santos, часы сталь золото, наручные часы механика&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69000</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Белый</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золотой</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://yadi.sk/d/A8ZAswZ3hu6p0g</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод | Календарь</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u0918d_Cartier_Santos_white_gold</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/Mkgjrdp1/d5-Cartier-Santos-white-gold-0.jpg | https://i.ibb.co/0pd5pf7Z/d5-Cartier-Santos-white-gold-1.jpg | https://i.ibb.co/S4vQB3kc/d5-Cartier-Santos-white-gold-2.jpg | https://i.ibb.co/LzSbJMm4/d5-Cartier-Santos-white-gold-3.jpg | https://i.ibb.co/35DG7QZR/d5-Cartier-Santos-white-gold-4.jpg | https://i.ibb.co/zW7s39h4/d5-Cartier-Santos-white-gold-5.jpg | https://i.ibb.co/6RJXwDQr/d5-Cartier-Santos-white-gold-6.jpg</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Cartier Santos белый сталь золото</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier Santos — белый циферблат, сталь и золото&lt;br&gt;&lt;br&gt;Тот же квадратный корпус с винтами, но браслет с более широкими золотистыми звеньями — вариант заметнее и теплее по тону.&lt;br&gt;&lt;br&gt;• Механизм: механический с автоподзаводом&lt;br&gt;• Корпус: сталь и цвет золота, квадратный&lt;br&gt;• Циферблат: белый, римские цифры, окно даты&lt;br&gt;• Браслет: сталь и цвет золота&lt;br&gt;• Функции: дата, водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы cartier мужские, cartier santos золото, часы квадратные мужские, наручные часы механика&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74000</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Белый</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золотой</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/Gu4qpVZtJ3kGMQ</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод | Календарь</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u0918d_Roger_Dubuis_skeleton</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/nqzJtGYN/d5-Roger-Dubuis-skeleton-0.jpg | https://i.ibb.co/XP8P8ST/d5-Roger-Dubuis-skeleton-1.jpg | https://i.ibb.co/BJXWcJV/d5-Roger-Dubuis-skeleton-2.jpg | https://i.ibb.co/ynGWb9f2/d5-Roger-Dubuis-skeleton-3.jpg | https://i.ibb.co/cKcVQLFd/d5-Roger-Dubuis-skeleton-4.jpg | https://i.ibb.co/0jX2Sd0C/d5-Roger-Dubuis-skeleton-5.jpg</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Roger Dubuis скелетон чёрный мужские</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roger Dubuis Excalibur — скелетон, мужские&lt;br&gt;&lt;br&gt;Полностью открытый механизм со звездой мостов в центре, тёмный корпус и рифлёный безель с цифрами.&lt;br&gt;&lt;br&gt;• Механизм: механический с автоподзаводом&lt;br&gt;• Корпус: тёмный, 45 мм&lt;br&gt;• Циферблат: скелетон, звезда мостов&lt;br&gt;• Ремешок: чёрный каучук&lt;br&gt;• Функции: водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы roger dubuis, roger dubuis excalibur, часы скелетон мужские, наручные часы каучук&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roger Dubuis</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/jSPiRfFWYQxwZA</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каучуковый</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u0918d_Omega_Speedmaster_red</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/JRN5g9Gq/d5-Omega-Speedmaster-red-0.jpg | https://i.ibb.co/fY4m8M5S/d5-Omega-Speedmaster-red-1.jpg | https://i.ibb.co/vCgCrSTJ/d5-Omega-Speedmaster-red-2.jpg | https://i.ibb.co/yHjFTBv/d5-Omega-Speedmaster-red-3.jpg | https://i.ibb.co/MyfJfgK6/d5-Omega-Speedmaster-red-4.jpg | https://i.ibb.co/JW2QfLnV/d5-Omega-Speedmaster-red-5.jpg | https://i.ibb.co/vx8KM5MW/d5-Omega-Speedmaster-red-6.jpg | https://i.ibb.co/234XDspJ/d5-Omega-Speedmaster-red-7.jpg</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Omega Speedmaster чёрный красный</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Omega Speedmaster Dark Side — чёрный с красным, мужские&lt;br&gt;&lt;br&gt;Чёрная керамика по всему корпусу, открытый циферблат хронографа и красная секундная стрелка с красной строчкой на ремешке.&lt;br&gt;&lt;br&gt;• Механизм: механический с автоподзаводом&lt;br&gt;• Корпус: чёрная керамика, 44 мм&lt;br&gt;• Циферблат: чёрный, счётчики хронографа, красные детали&lt;br&gt;• Ремешок: кожа с перфорацией&lt;br&gt;• Функции: хронограф, тахиметр, водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы omega мужские, omega speedmaster, хронограф керамика, наручные часы механика&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83000</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Omega</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/8T0Snr466Fy9tw</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод | Хронограф | Секундомер</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кожаный</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u0918d_Patek_Cubitus_green</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/CKGgQz6r/d5-Patek-Cubitus-green-0.jpg | https://i.ibb.co/Q3Dq92LD/d5-Patek-Cubitus-green-1.jpg | https://i.ibb.co/zhmKmGCQ/d5-Patek-Cubitus-green-2.jpg | https://i.ibb.co/9mwGJtGR/d5-Patek-Cubitus-green-3.jpg | https://i.ibb.co/JjR7BBMG/d5-Patek-Cubitus-green-4.jpg | https://i.ibb.co/kstF8LNN/d5-Patek-Cubitus-green-5.jpg</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Patek Philippe Cubitus зелёный мужские</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patek Philippe Cubitus — зелёный, мужские&lt;br&gt;&lt;br&gt;Квадратный стальной корпус и зелёный циферблат с горизонтальным тиснением на интегрированном браслете — новая линейка, которой пока мало у кого есть.&lt;br&gt;&lt;br&gt;• Механизм: механический с автоподзаводом&lt;br&gt;• Корпус: сталь, квадратный, 45 мм&lt;br&gt;• Циферблат: зелёный, горизонтальное тиснение, окно даты&lt;br&gt;• Браслет: сталь, интегрированный&lt;br&gt;• Функции: дата, водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы patek philippe, patek cubitus, часы зелёные мужские, наручные часы механика&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83000</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patek Philippe</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Серебряный</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/TSiX-8LvvIenNg</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод | Календарь</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u0918d_Breguet_classic</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/rG0xLVDM/d5-Breguet-classic-0.jpg | https://i.ibb.co/B51jhfnR/d5-Breguet-classic-1.jpg | https://i.ibb.co/rKw9yJ7C/d5-Breguet-classic-2.jpg | https://i.ibb.co/v6zP1gxt/d5-Breguet-classic-3.jpg | https://i.ibb.co/ymyS9mpX/d5-Breguet-classic-4.jpg</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Breguet чёрный циферблат мужские</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Breguet — чёрный циферблат, мужские&lt;br&gt;&lt;br&gt;Классический круглый корпус с рифлёным ободом, чёрный циферблат с гильошированием и тонкие стрелки «яблоко Бреге» на кожаном ремешке.&lt;br&gt;&lt;br&gt;• Механизм: механический с автоподзаводом&lt;br&gt;• Корпус: сталь, рифлёный обод&lt;br&gt;• Циферблат: чёрный, гильоше, малые счётчики&lt;br&gt;• Ремешок: чёрная кожа&lt;br&gt;• Функции: дата, водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы breguet мужские, breguet классика, часы чёрные мужские, наручные часы кожа&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67500</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Breguet</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/ew_7EGQkLEvf3g</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод | Календарь</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кожаный</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u0918d_Hublot_BigBang_green</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/7tNtQMBP/d5-Hublot-Big-Bang-green-0.jpg | https://i.ibb.co/PGkwZGnh/d5-Hublot-Big-Bang-green-1.jpg | https://i.ibb.co/jvZvmmLT/d5-Hublot-Big-Bang-green-2.jpg | https://i.ibb.co/tVgnQb1/d5-Hublot-Big-Bang-green-3.jpg | https://i.ibb.co/ns3rZ9pJ/d5-Hublot-Big-Bang-green-4.jpg | https://i.ibb.co/jpQLfjV/d5-Hublot-Big-Bang-green-5.jpg</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Hublot Big Bang зелёный мужские</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot Big Bang — зелёный, мужские&lt;br&gt;&lt;br&gt;Крупный корпус болотно-зелёного оттенка с винтами по безелю, открытый циферблат с хронографом и каучуковый ремешок в тон.&lt;br&gt;&lt;br&gt;• Механизм: механический с автоподзаводом&lt;br&gt;• Корпус: зелёный, 44 мм, винты по безелю&lt;br&gt;• Циферблат: скелетон, счётчики хронографа&lt;br&gt;• Ремешок: зелёный каучук&lt;br&gt;• Функции: хронограф, дата, водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot big bang, часы зелёные мужские, наручные часы каучук&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74000</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/hbJncGSM824VDQ</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод | Хронограф | Секундомер</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каучуковый</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="M5:M1048576">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/ilya_feed.xlsx
+++ b/ilya_feed.xlsx
@@ -38724,6 +38724,1426 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d5_Richard_Mille_skeleton_dark</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/C3cyVmSQ/d5-Richard-Mille-skeleton-dark-0.jpg | https://i.ibb.co/tw2MK6Ym/d5-Richard-Mille-skeleton-dark-1.jpg | https://i.ibb.co/fzmm0qG3/d5-Richard-Mille-skeleton-dark-2.jpg | https://i.ibb.co/Qv2m62g9/d5-Richard-Mille-skeleton-dark-3.jpg | https://i.ibb.co/6J0k9knC/d5-Richard-Mille-skeleton-dark-4.jpg | https://i.ibb.co/mCGd4pgh/d5-Richard-Mille-skeleton-dark-5.jpg | https://i.ibb.co/nNgVMcLG/d5-Richard-Mille-skeleton-dark-6.jpg</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Richard Mille скелетон чёрный мужские</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Richard Mille — чёрный корпус, скелетон, мужские&lt;br&gt;&lt;br&gt;Корпус-бочка в матовом чёрном исполнении и полностью открытый механизм: мосты, балансир и колёса видны с лицевой стороны, как через стекло.&lt;br&gt;&lt;br&gt;• Механизм: механический с автоподзаводом&lt;br&gt;• Корпус: матовый чёрный, форма тонно&lt;br&gt;• Циферблат: скелетон&lt;br&gt;• Ремешок: чёрный каучук&lt;br&gt;• Функции: водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы richard mille, richard mille чёрные, часы скелетон мужские, наручные часы каучук&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93500</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Richard Mille</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/B4f_lH7BdPbhug</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каучуковый</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d5_Cartier_Santos_skeleton_steel</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/WNZ7qn34/d5-Cartier-Santos-skeleton-steel-0.jpg | https://i.ibb.co/s9QvCjD4/d5-Cartier-Santos-skeleton-steel-1.jpg | https://i.ibb.co/Vc7LhkzL/d5-Cartier-Santos-skeleton-steel-2.jpg | https://i.ibb.co/TDpR7HHL/d5-Cartier-Santos-skeleton-steel-3.jpg | https://i.ibb.co/HffRZVBn/d5-Cartier-Santos-skeleton-steel-4.jpg | https://i.ibb.co/rfdcLv8c/d5-Cartier-Santos-skeleton-steel-5.jpg</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Cartier Santos скелетон сталь мужские</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier Santos — скелетон, сталь, мужские&lt;br&gt;&lt;br&gt;Квадратный стальной корпус с винтами по безелю и вырезанным циферблатом: римские цифры остаются контуром, а сквозь них виден механизм. Синие стрелки-мечи на стальном браслете.&lt;br&gt;&lt;br&gt;• Механизм: механический с автоподзаводом&lt;br&gt;• Корпус: сталь, квадратный, винты по безелю&lt;br&gt;• Циферблат: скелетон, римские цифры&lt;br&gt;• Браслет: сталь&lt;br&gt;• Функции: водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы cartier мужские, cartier santos скелетон, часы сталь мужские, наручные часы механика&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Серебряный</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Серебряный</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/EaYvOGmOdxuiFQ</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d5_Omega_Speedmaster_yellow</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/Wvt9w8Pp/d5-Omega-Speedmaster-yellow-0.jpg | https://i.ibb.co/VpxmkCf6/d5-Omega-Speedmaster-yellow-1.jpg | https://i.ibb.co/fGCW1Tt6/d5-Omega-Speedmaster-yellow-2.jpg | https://i.ibb.co/TDhBWcrk/d5-Omega-Speedmaster-yellow-3.jpg | https://i.ibb.co/gZWQc4nk/d5-Omega-Speedmaster-yellow-4.jpg | https://i.ibb.co/vvxdwvn2/d5-Omega-Speedmaster-yellow-5.jpg | https://i.ibb.co/DfmgvpXR/d5-Omega-Speedmaster-yellow-6.jpg | https://i.ibb.co/jvRTJgmG/d5-Omega-Speedmaster-yellow-7.jpg</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Omega Speedmaster чёрный жёлтый</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Omega Speedmaster Dark Side of the Moon — чёрный с жёлтым, мужские&lt;br&gt;&lt;br&gt;Чёрная керамика по всему корпусу, циферблат с лунной фактурой и одна яркая деталь — жёлтая секундная стрелка и жёлтая строчка на перфорированном кожаном ремешке.&lt;br&gt;&lt;br&gt;• Механизм: механический с автоподзаводом&lt;br&gt;• Корпус: чёрная керамика, 44 мм&lt;br&gt;• Циферблат: чёрный, лунная фактура, три счётчика хронографа, жёлтая стрелка&lt;br&gt;• Ремешок: перфорированная кожа с жёлтой строчкой&lt;br&gt;• Функции: хронограф, тахиметр, водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы omega мужские, omega speedmaster, хронограф керамика, наручные часы механика&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83000</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Omega</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/eq0ONBd3abwiaQ</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод | Хронограф | Секундомер</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кожаный</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d5_Omega_Speedmaster_grey</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/k2T8TCG6/d5-Omega-Speedmaster-grey-0.jpg | https://i.ibb.co/nNX2wZc6/d5-Omega-Speedmaster-grey-1.jpg | https://i.ibb.co/wFfXw2QR/d5-Omega-Speedmaster-grey-2.jpg | https://i.ibb.co/Ps1LpQM5/d5-Omega-Speedmaster-grey-3.jpg | https://i.ibb.co/RkVz9wPw/d5-Omega-Speedmaster-grey-4.jpg | https://i.ibb.co/Cs8nWTrj/d5-Omega-Speedmaster-grey-5.jpg | https://i.ibb.co/sp7Y8yNn/d5-Omega-Speedmaster-grey-6.jpg | https://i.ibb.co/5WzWwj8c/d5-Omega-Speedmaster-grey-7.jpg</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Omega Speedmaster чёрный серый</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Omega Speedmaster Dark Side of the Moon — серый циферблат, мужские&lt;br&gt;&lt;br&gt;Чёрная керамика и серый циферблат с фактурой лунной поверхности — самый сдержанный вариант линейки: без цветных акцентов, на тёмном текстильном ремешке.&lt;br&gt;&lt;br&gt;• Механизм: механический с автоподзаводом&lt;br&gt;• Корпус: чёрная керамика, 44 мм&lt;br&gt;• Циферблат: серый, лунная фактура, три счётчика хронографа&lt;br&gt;• Ремешок: чёрный текстиль&lt;br&gt;• Функции: хронограф, тахиметр, водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы omega мужские, omega speedmaster серый, хронограф керамика, наручные часы механика&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83000</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Omega</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Серый</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/WeCuimbaIwz_7A</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод | Хронограф | Секундомер</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Текстиль</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d5_Cartier_oval_gold</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/HpMjnkLH/d5-Cartier-oval-gold-0.jpg | https://i.ibb.co/FLHDjJxc/d5-Cartier-oval-gold-1.jpg | https://i.ibb.co/bjVLcx3R/d5-Cartier-oval-gold-2.jpg | https://i.ibb.co/rKZqfzRw/d5-Cartier-oval-gold-3.jpg | https://i.ibb.co/h12wF96N/d5-Cartier-oval-gold-4.jpg | https://i.ibb.co/Y7JT6MPH/d5-Cartier-oval-gold-5.jpg | https://i.ibb.co/rKTxrQWq/d5-Cartier-oval-gold-6.jpg</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Cartier овальные золото женские</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier — овальный золотой корпус, женские&lt;br&gt;&lt;br&gt;Небольшой овальный корпус цвета золота с искрящимся циферблатом и тонкий чёрный кожаный ремешок — часы-украшение, которое носят как браслет.&lt;br&gt;&lt;br&gt;• Механизм: кварцевый&lt;br&gt;• Корпус: цвет золота, овальный&lt;br&gt;• Циферблат: искрящийся, серебристый&lt;br&gt;• Ремешок: тонкая чёрная кожа&lt;br&gt;• Функции: водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы cartier женские, cartier овальные, золотые часы женские, наручные часы кварц&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67500</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золотой</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/-FY3Qsr2mee8OQ</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Женские</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кожаный</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d5_Tissot_Classic_34_blue_steel</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://iili.io/nT3UVF1.jpg | https://iili.io/nT3Uml9.jpg | https://iili.io/nT3gwg9.jpg | https://iili.io/nT3rGYF.jpg | https://iili.io/nT34nwJ.jpg | https://iili.io/nT3P3kF.jpg</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Tissot Ballade 34 мм голубой сталь</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tissot Ballade 34 мм — голубой циферблат, сталь, женские&lt;br&gt;&lt;br&gt;Циферблат с лучистым узором в холодном голубом тоне, рифлёный безель и стальной браслет — спокойная классика, которая не выходит из моды.&lt;br&gt;&lt;br&gt;• Механизм: кварцевый&lt;br&gt;• Корпус: сталь, 34 мм, рифлёный безель&lt;br&gt;• Циферблат: голубой, лучистый узор, окно даты&lt;br&gt;• Браслет: сталь&lt;br&gt;• Функции: дата, водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы tissot женские, tissot ballade 34, часы сталь женские, наручные часы кварц&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28000</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tissot</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Голубой</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Серебряный</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/_p_sH3YU6lh-lA</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Женские</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Календарь</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d5_Tissot_Classic_34_blue_gold</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://iili.io/nT3QAF4.jpg | https://iili.io/nT3ZKib.jpg | https://iili.io/nT3ZEbt.jpg | https://iili.io/nT3tI24.jpg | https://iili.io/nT3tcCu.jpg | https://iili.io/nT3DKcx.jpg</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Tissot Ballade 34 мм синий сталь золото</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tissot Ballade 34 мм — синий циферблат, сталь и золото, женские&lt;br&gt;&lt;br&gt;Глубокий синий циферблат с лучистым узором, золотистый рифлёный безель и двухцветный браслет: сочетание металлов подходит и к серебряным, и к золотым украшениям.&lt;br&gt;&lt;br&gt;• Механизм: кварцевый&lt;br&gt;• Корпус: сталь с золотистым безелем, 34 мм&lt;br&gt;• Циферблат: синий, лучистый узор, окно даты&lt;br&gt;• Браслет: сталь с золотистыми звеньями&lt;br&gt;• Функции: дата, водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы tissot женские, tissot ballade синий, часы сталь золото, наручные часы кварц&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28000</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tissot</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Синий</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золотой</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/cp9JkBrLie8W0g</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Женские</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Календарь</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d5_Tissot_Classic_40_silver</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://iili.io/nTFJvpf.jpg | https://iili.io/nTF2aRa.jpg | https://iili.io/nTF3s2t.jpg | https://iili.io/nTFFiox.jpg | https://iili.io/nTFf9d7.jpg | https://iili.io/nTFBaRt.jpg</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Tissot Ballade 40 мм серебристый золото</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tissot Ballade 40 мм — серебристый циферблат, сталь и золото, мужские&lt;br&gt;&lt;br&gt;Классические 40 мм: серебристый циферблат с лучистым узором, золотистый рифлёный безель и двухцветный браслет — строгие часы под рубашку и костюм.&lt;br&gt;&lt;br&gt;• Механизм: кварцевый&lt;br&gt;• Корпус: сталь с золотистым безелем, 40 мм&lt;br&gt;• Циферблат: серебристый, лучистый узор, окно даты&lt;br&gt;• Браслет: сталь с золотистыми звеньями&lt;br&gt;• Функции: дата, водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы tissot мужские, tissot ballade 40, часы сталь золото, наручные часы кварц&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28000</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tissot</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Серебряный</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золотой</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/mwMs0sOmz-TXUg</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Календарь</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d5_Tissot_rect_green</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://iili.io/nTFIjdx.jpg | https://iili.io/nTFT92f.jpg | https://iili.io/nTFunnt.jpg | https://iili.io/nTFAceR.jpg | https://iili.io/nTFRgZN.jpg</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Tissot прямоугольные зелёный женские</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tissot — прямоугольный корпус, зелёный циферблат, женские&lt;br&gt;&lt;br&gt;Небольшой прямоугольный корпус со скошенными углами, насыщенный зелёный циферблат и ремешок из мятной кожи — акцент, который работает и с офисным, и с летним образом.&lt;br&gt;&lt;br&gt;• Механизм: кварцевый&lt;br&gt;• Корпус: сталь, прямоугольный&lt;br&gt;• Циферблат: зелёный&lt;br&gt;• Ремешок: зелёная кожа&lt;br&gt;• Функции: водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы tissot женские, tissot прямоугольные, часы зелёные женские, наручные часы кожа&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30500</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tissot</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/iWkxVw8RDL_bmQ</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Женские</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кожаный</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d5_Tissot_rect_gold</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79105123170</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Манежная пл.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://iili.io/nTFcXr7.jpg | https://iili.io/nTF0BDJ.jpg | https://iili.io/nTF1K12.jpg | https://iili.io/nTF1gEl.jpg | https://iili.io/nTFEYG4.jpg</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В сообщениях</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Tissot прямоугольные золото женские</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tissot — прямоугольный золотой корпус, женские&lt;br&gt;&lt;br&gt;Тонкий прямоугольный корпус цвета золота, светлый перламутровый циферблат и чёрный ремешок с фактурой под крокодила — часы на выход и на каждый день.&lt;br&gt;&lt;br&gt;• Механизм: кварцевый&lt;br&gt;• Корпус: цвет золота, прямоугольный&lt;br&gt;• Циферблат: светлый, перламутровый&lt;br&gt;• Ремешок: чёрная кожа с тиснением&lt;br&gt;• Функции: водозащита&lt;br&gt;• Комплект: фирменная коробка и документы&lt;br&gt;&lt;br&gt;✔️ Уточните наличие перед заказом — напишите в чат, отвечу за 5 минут, какие цвета есть прямо сейчас.&lt;br&gt;✔️ Проверка при получении: вскрываете в пункте выдачи, смотрите, и только потом забираете.&lt;br&gt;✔️ Гарантия на механизм — 1 год.&lt;br&gt;✔️ Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;часы tissot женские, tissot прямоугольные золото, золотые часы женские, наручные часы кожа&lt;br&gt;&lt;br&gt;Качество vhs - лучшее на рынке</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По браку — 24 часа</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30500</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tissot</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золотой</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://yadi.sk/d/DZ6cXJn4vWY60A</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Женские</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кожаный</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ульяна</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ilyabalabay@mail.ru</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="M5:M1048576">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/ilya_feed.xlsx
+++ b/ilya_feed.xlsx
@@ -2024,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:Z5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="50" customHeight="1">
@@ -2160,6 +2160,11 @@
           <t>Декларация</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Документы не нужны</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -2263,6 +2268,11 @@
           <t>Необязательный</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -2360,6 +2370,11 @@
           <t>Номер декларации о соответствии, формат ТС RU Д-CN.РА01.В.48941/23</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Подтверждаю / Пропустить</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2485,6 +2500,11 @@
       <c r="Y5" t="inlineStr">
         <is>
           <t>ЕАЭС N RU Д-CN.РА08.В.56534/26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y21"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="50" customHeight="1">
@@ -2968,6 +2988,11 @@
           <t>Декларация</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Документы не нужны</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -3071,6 +3096,11 @@
           <t>Необязательный</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -3168,6 +3198,11 @@
           <t>Номер декларации о соответствии, формат ТС RU Д-CN.РА01.В.48941/23</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Подтверждаю / Пропустить</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3295,6 +3330,11 @@
           <t>ЕАЭС N RU Д-CN.РА09.В.14143/26</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3422,6 +3462,11 @@
           <t>ЕАЭС N RU Д-CN.РА09.В.14143/26</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3549,6 +3594,11 @@
           <t>ЕАЭС N RU Д-CN.РА09.В.14143/26</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3676,6 +3726,11 @@
           <t>ЕАЭС N RU Д-CN.РА09.В.14143/26</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3803,6 +3858,11 @@
           <t>ЕАЭС N RU Д-CN.РА09.В.14143/26</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3930,6 +3990,11 @@
           <t>ЕАЭС N RU Д-CN.РА09.В.14143/26</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4057,6 +4122,11 @@
           <t>ЕАЭС N RU Д-CN.РА09.В.14143/26</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4184,6 +4254,11 @@
           <t>ЕАЭС N RU Д-CN.РА09.В.14143/26</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4311,6 +4386,11 @@
           <t>ЕАЭС N RU Д-CN.РА09.В.14143/26</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4438,6 +4518,11 @@
           <t>ЕАЭС N RU Д-CN.РА09.В.14143/26</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4565,6 +4650,11 @@
           <t>ЕАЭС N RU Д-CN.РА09.В.14143/26</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4692,6 +4782,11 @@
           <t>ЕАЭС N RU Д-CN.РА08.В.56534/26</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4819,6 +4914,11 @@
           <t>ЕАЭС N RU Д-CN.РА08.В.56534/26</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4946,6 +5046,11 @@
           <t>ЕАЭС N RU Д-CN.РА08.В.56534/26</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5073,6 +5178,11 @@
           <t>ЕАЭС N RU Д-CN.РА08.В.56534/26</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5200,6 +5310,11 @@
           <t>ЕАЭС N RU Д-CN.РА09.В.14143/26</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5325,6 +5440,11 @@
       <c r="Y21" t="inlineStr">
         <is>
           <t>ЕАЭС N RU Д-CN.РА09.В.14143/26</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ54"/>
+  <dimension ref="A1:AK54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -5871,6 +5991,11 @@
           <t>Декларация</t>
         </is>
       </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Документы не нужны</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -6029,6 +6154,11 @@
           <t>Необязательный</t>
         </is>
       </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -6186,6 +6316,11 @@
           <t>Номер декларации о соответствии, формат ТС RU Д-CN.РА01.В.48941/23</t>
         </is>
       </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Подтверждаю / Пропустить</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6358,6 +6493,11 @@
           <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
         </is>
       </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6530,6 +6670,11 @@
           <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
         </is>
       </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6702,6 +6847,11 @@
           <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
         </is>
       </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6879,6 +7029,11 @@
           <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
         </is>
       </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7051,6 +7206,11 @@
           <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
         </is>
       </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7223,6 +7383,11 @@
           <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
         </is>
       </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7395,6 +7560,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7567,6 +7737,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7739,6 +7914,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7911,6 +8091,11 @@
           <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
         </is>
       </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8083,6 +8268,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8255,6 +8445,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8427,6 +8622,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8599,6 +8799,11 @@
           <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
         </is>
       </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8771,6 +8976,11 @@
           <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
         </is>
       </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8943,6 +9153,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9115,6 +9330,11 @@
           <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
         </is>
       </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9287,6 +9507,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9459,6 +9684,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9631,6 +9861,11 @@
           <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
         </is>
       </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9783,6 +10018,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9935,6 +10175,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -10087,6 +10332,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -10239,6 +10489,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -10391,6 +10646,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -10543,6 +10803,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -10695,6 +10960,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -10847,6 +11117,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -10999,6 +11274,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -11151,6 +11431,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -11303,6 +11588,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -11455,6 +11745,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -11607,6 +11902,11 @@
           <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
         </is>
       </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -11759,6 +12059,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -11911,6 +12216,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -12063,6 +12373,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -12215,6 +12530,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -12367,6 +12687,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -12519,6 +12844,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12671,6 +13001,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -12823,6 +13158,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -12975,6 +13315,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -13127,6 +13472,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -13279,6 +13629,11 @@
           <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
         </is>
       </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -13431,6 +13786,11 @@
           <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
         </is>
       </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -13583,6 +13943,11 @@
           <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
         </is>
       </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -13735,6 +14100,11 @@
           <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
         </is>
       </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -13887,6 +14257,11 @@
           <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
         </is>
       </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -14039,6 +14414,11 @@
           <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
         </is>
       </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -14189,6 +14569,11 @@
       <c r="AI54" t="inlineStr">
         <is>
           <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
         </is>
       </c>
     </row>
@@ -69283,7 +69668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB5"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="50" customHeight="1">
@@ -69434,6 +69819,11 @@
           <t>Декларация</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Документы не нужны</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -69546,6 +69936,11 @@
           <t>Необязательный</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -69653,6 +70048,11 @@
           <t>Номер декларации о соответствии, формат ТС RU Д-CN.РА01.В.48941/23</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Подтверждаю / Пропустить</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -69783,6 +70183,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>28.24.11.000 — Инструменты ручные электрические</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
         </is>
       </c>
     </row>
@@ -70127,7 +70532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:Z5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="50" customHeight="1">
@@ -70263,6 +70668,11 @@
           <t>Декларация</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Документы не нужны</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -70366,6 +70776,11 @@
           <t>Необязательный</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -70463,6 +70878,11 @@
           <t>Номер декларации о соответствии, формат ТС RU Д-CN.РА01.В.48941/23</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Подтверждаю / Пропустить</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -70588,6 +71008,11 @@
       <c r="Y5" t="inlineStr">
         <is>
           <t>ЕАЭС N RU Д-CN.РА08.В.56534/26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
         </is>
       </c>
     </row>
@@ -70816,7 +71241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="50" customHeight="1">
@@ -70952,6 +71377,11 @@
           <t>Декларация</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Документы не нужны</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -71054,6 +71484,11 @@
           <t>Необязательный</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -71151,6 +71586,11 @@
           <t>Номер декларации о соответствии, формат ТС RU Д-CN.РА01.В.48941/23</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Подтверждаю / Пропустить</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -71268,6 +71708,11 @@
           <t>26.70.22.110 — Бинокли</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -71385,6 +71830,11 @@
           <t>26.70.22.110 — Бинокли</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -71502,6 +71952,11 @@
           <t>26.70.22.110 — Бинокли</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -71617,6 +72072,11 @@
       <c r="X8" t="inlineStr">
         <is>
           <t>26.70.22.110 — Бинокли</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Подтверждаю</t>
         </is>
       </c>
     </row>

--- a/ilya_feed.xlsx
+++ b/ilya_feed.xlsx
@@ -6490,7 +6490,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -12370,7 +12370,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -12527,7 +12527,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -13155,7 +13155,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -13312,7 +13312,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -13469,7 +13469,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>26.52.12.110 — Часы наручные и карманные механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -14097,7 +14097,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -14411,7 +14411,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -14568,7 +14568,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>26.52.12.120 — Часы наручные и карманные электронно-механические прочие</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -71705,7 +71705,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26.70.22.110 — Бинокли</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -71827,7 +71827,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26.70.22.110 — Бинокли</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -71949,7 +71949,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26.70.22.110 — Бинокли</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -72071,7 +72071,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26.70.22.110 — Бинокли</t>
+          <t>Не требуется</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">

--- a/ilya_feed.xlsx
+++ b/ilya_feed.xlsx
@@ -2409,7 +2409,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>🎁 К каждому заказу — налобный фонарик в ПОДАРОК!&lt;br&gt;🔥ЦЕНА ДО КОНЦА НЕДЕЛИ (2350 вместо 2990)!!!🔥&lt;br&gt;&lt;br&gt;🔥 Фонарь РМ60-TG — тот самый СТРАХ ДРОНОВ. 5000 метров белого лазера в твоих руках&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Аналогов по мощности на Авито — единицы.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — это НЕЧТО!&lt;br&gt;&lt;br&gt;❓ Почему «Страх Дронов»? Всё просто: луч бьёт на 5 000 метров — выше, чем летает любой коптер. Направьте «Колосса» в ночное небо — и всё, что там висит, окажется как на ладони. 8 000 люмен белого лазера не оставляют дрону шансов остаться незамеченным, а его камере — что-то разглядеть против луча.&lt;br&gt;Когда включаешь первый раз в темноте — понимаешь, что всё остальное было игрушками. Луч уходит за горизонт. Вас будут спрашивать только одно: где купил? 😅&lt;br&gt;&lt;br&gt;🔦 Диод PM60-TG «Белый лазер» — до 8 000 люмен&lt;br&gt;📏 Дальность луча — 5 000 метров&lt;br&gt;🔋 4 аккумулятора 18650 в комплекте — до 8 часов работы&lt;br&gt;🔌 Зарядка USB Type-C (кабель в комплекте)&lt;br&gt;🔍 Zoom-фокусировка — от широкого пятна до узкого «лазерного» луча&lt;br&gt;💧 Защита IPX6 — ливень и грязь не страшны&lt;br&gt;🦾 Корпус из авиационного алюминия — выдержит падение&lt;br&gt;🧲 Светящиеся ручки — легко найти в полной темноте&lt;br&gt;📊 Индикатор заряда — всегда знаешь, сколько осталось&lt;br&gt;&lt;br&gt;⚡ 5 режимов: Турбо / Яркий / Умеренный / Экономичный / Стробоскоп&lt;br&gt;✔️ Идеально для: наблюдения за небом, охраны объектов, рыбалки, охоты, туризма, кемпинга, ремонта, дачи&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь «Колосс» + 4 аккумулятора 18650 + кабель Type-C + налобный фонарик в подарок 🎁&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.</t>
+          <t>🎁 К каждому заказу — налобный фонарик в ПОДАРОК!&lt;br&gt;🔥ЦЕНА ДО КОНЦА НЕДЕЛИ (2350 вместо 2990)!!!🔥&lt;br&gt;&lt;br&gt;🔥 Фонарь РМ60-TG — тот самый СТРАХ ДРОНОВ. 5000 метров белого лазера в твоих руках&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Аналогов по мощности на Авито — единицы.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — это НЕЧТО!&lt;br&gt;&lt;br&gt;❓ Почему «Страх Дронов»? Всё просто: луч бьёт на 5 000 метров — выше, чем летает любой коптер. Направьте «Колосса» в ночное небо — и всё, что там висит, окажется как на ладони. 8 000 люмен белого лазера не оставляют дрону шансов остаться незамеченным, а его камере — что-то разглядеть против луча.&lt;br&gt;Когда включаешь первый раз в темноте — понимаешь, что всё остальное было игрушками. Луч уходит за горизонт. Вас будут спрашивать только одно: где купил? 😅&lt;br&gt;&lt;br&gt;🔦 Диод PM60-TG «Белый лазер» — до 8 000 люмен&lt;br&gt;📏 Дальность луча — 5 000 метров&lt;br&gt;🔋 4 аккумулятора 18650 в комплекте — до 8 часов работы&lt;br&gt;🔌 Зарядка USB Type-C (кабель в комплекте)&lt;br&gt;🔍 Zoom-фокусировка — от широкого пятна до узкого «лазерного» луча&lt;br&gt;💧 Защита IPX6 — ливень и грязь не страшны&lt;br&gt;🦾 Корпус из авиационного алюминия — выдержит падение&lt;br&gt;🧲 Светящиеся ручки — легко найти в полной темноте&lt;br&gt;📊 Индикатор заряда — всегда знаешь, сколько осталось&lt;br&gt;&lt;br&gt;⚡ 5 режимов: Турбо / Яркий / Умеренный / Экономичный / Стробоскоп&lt;br&gt;✔️ Идеально для: наблюдения за небом, охраны объектов, рыбалки, охоты, туризма, кемпинга, ремонта, дачи&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь «Колосс» + 4 аккумулятора 18650 + кабель Type-C + налобный фонарик в подарок 🎁&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>🚗 Yemao A200 — фонарь с дальним и ближним светом, как у автомобиля. 5200 люмен двойной системы Dual-Core&lt;br&gt;✅ Новинка Yemao Japan. Аналог SK-05 Pro — в 7 раз дешевле.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — на турбо-режиме он прожигает картон, снято вживую!&lt;br&gt;&lt;br&gt;У машины не зря два света: дальний пробивает дорогу вперёд, ближний заливает всё вокруг. Этот фонарь устроен так же — прожектор SST36 бьёт вдаль, панель SLWAV4×3 даёт широкую заливку, и работать они могут ОДНОВРЕМЕННО. Для каждого света — своя кнопка (на кнопке прожектора — фирменный котик 🐱, покупатели в восторге). По цена/качеству спокойно спорит с Fenix, Olight и Nitecore. 😎&lt;br&gt;&lt;br&gt;🔦 Dual-Light — до 5200 люмен: дальний + ближний, по отдельности или вместе&lt;br&gt;🎛 29 режимов: стробоскоп, SOS, комбинированный свет, RGB-подсветка с эффектами&lt;br&gt;🎮 Две отдельные кнопки — мгновенный доступ без перелистывания меню&lt;br&gt;🔋 Аккумулятор 5600 мАч — от 4 до 100 часов работы в зависимости от режима&lt;br&gt;🔌 Быстрая зарядка USB Type-C (~3 часа) + дисплей уровня заряда&lt;br&gt;🧲 Магнит в хвосте — крепится к капоту и любому металлу&lt;br&gt;🦾 Авиационный алюминий, падение до 1 м, влагозащита IPX4&lt;br&gt;📏 Формат EDC — 113×49×26 мм, помещается в карман куртки&lt;br&gt;&lt;br&gt;✔️ Идеально для: авто (лучший фонарь в бардачок), рыбалки, охоты, гаража, кемпинга, охраны, EDC&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь Yemao A200 + кабель USB-C&lt;br&gt;&lt;br&gt;🎁 Эффектный подарок мужчине — вау-эффект с первого включения&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ Объявление активно = товар в наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.</t>
+          <t>🚗 Yemao A200 — фонарь с дальним и ближним светом, как у автомобиля. 5200 люмен двойной системы Dual-Core&lt;br&gt;✅ Новинка Yemao Japan. Аналог SK-05 Pro — в 7 раз дешевле.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — на турбо-режиме он прожигает картон, снято вживую!&lt;br&gt;&lt;br&gt;У машины не зря два света: дальний пробивает дорогу вперёд, ближний заливает всё вокруг. Этот фонарь устроен так же — прожектор SST36 бьёт вдаль, панель SLWAV4×3 даёт широкую заливку, и работать они могут ОДНОВРЕМЕННО. Для каждого света — своя кнопка (на кнопке прожектора — фирменный котик 🐱, покупатели в восторге). По цена/качеству спокойно спорит с Fenix, Olight и Nitecore. 😎&lt;br&gt;&lt;br&gt;🔦 Dual-Light — до 5200 люмен: дальний + ближний, по отдельности или вместе&lt;br&gt;🎛 29 режимов: стробоскоп, SOS, комбинированный свет, RGB-подсветка с эффектами&lt;br&gt;🎮 Две отдельные кнопки — мгновенный доступ без перелистывания меню&lt;br&gt;🔋 Аккумулятор 5600 мАч — от 4 до 100 часов работы в зависимости от режима&lt;br&gt;🔌 Быстрая зарядка USB Type-C (~3 часа) + дисплей уровня заряда&lt;br&gt;🧲 Магнит в хвосте — крепится к капоту и любому металлу&lt;br&gt;🦾 Авиационный алюминий, падение до 1 м, влагозащита IPX4&lt;br&gt;📏 Формат EDC — 113×49×26 мм, помещается в карман куртки&lt;br&gt;&lt;br&gt;✔️ Идеально для: авто (лучший фонарь в бардачок), рыбалки, охоты, гаража, кемпинга, охраны, EDC&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь Yemao A200 + кабель USB-C&lt;br&gt;&lt;br&gt;🎁 Эффектный подарок мужчине — вау-эффект с первого включения&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ Объявление активно = товар в наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>🧰 Yemao M31 — швейцарский нож в мире фонарей. 16 режимов, 3 кнопки, магнит, крюк и даже линейка&lt;br&gt;✅ Новинка 2026 года. Только оригинал Yemao — остерегайтесь дешёвых копий.&lt;br&gt;&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — за минуту он делает больше, чем обычный фонарь за всю жизнь!&lt;br&gt;&lt;br&gt;🎨 Цвет корпуса — сюрприз: оранжевый, зелёный, серый или чёрный. Напишите в отзыве, какой достался вам 😉&lt;br&gt;Обычный фонарь умеет светить. Этот — светит на 95 метров, примагничивается к капоту, подвешивается за крюк к палатке, цепляется на кепку вместо налобника, встаёт на руль велосипеда, меняет цвет как световой меч и измеряет детали встроенной линейкой. И всё это — 75 грамм в кармане. &lt;br&gt;&lt;br&gt;Один раз попользуетесь — и уже не поймёте, как жили без него. 😅&lt;br&gt;💡 Диод P50 — до 680 люмен, сфокусированный луч до 95 метров&lt;br&gt;🎛 16 режимов, 3 отдельные кнопки — мгновенный доступ без перелистывания&lt;br&gt;🌈 RGB-панель: красный (ночное зрение) / синий (аварийный сигнал) / зелёный (охота) / тёплый белый (уютный свет в лагере)&lt;br&gt;⚠️ Стробоскоп — привлечь внимание или обозначить себя на дороге&lt;br&gt;🧲 Мощный магнит в хвосте — к капоту, гаражной балке, любому металлу&lt;br&gt;🪝 Складной крюк — подвесить в палатке или на ветку&lt;br&gt;📎 Зажим-трансформер — на карман, кепку или рюкзак&lt;br&gt;🚴 Велокрепление В КОМПЛЕКТЕ — готовый велофонарь&lt;br&gt;📏 Встроенная линейка 10 см — замер без поисков рулетки&lt;br&gt;🔋 Аккумулятор 1000 мАч — до 12 часов работы, индикатор заряда&lt;br&gt;🔌 Зарядка USB Type-C&lt;br&gt;&lt;br&gt;🦾 Алюминиевый сплав, вес 75 г, падение с 1 м, влагозащита IPX4&lt;br&gt;✔️ Идеально для: EDC (каждый день с собой), велосипеда, гаража и ремонта, кемпинга, рыбалки, авто (аварийный свет), прогулок с собакой&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь M31 + кабель Type-C + велокрепление + инструкция + подарочная коробка 🎁 — готовый подарок мужчине&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически. Себе и в подарок!&lt;br&gt;🏆 Настоящая гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, каждый проверяю лично перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.</t>
+          <t>🧰 Yemao M31 — швейцарский нож в мире фонарей. 16 режимов, 3 кнопки, магнит, крюк и даже линейка&lt;br&gt;✅ Новинка 2026 года. Только оригинал Yemao — остерегайтесь дешёвых копий.&lt;br&gt;&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — за минуту он делает больше, чем обычный фонарь за всю жизнь!&lt;br&gt;&lt;br&gt;🎨 Цвет корпуса — сюрприз: оранжевый, зелёный, серый или чёрный. Напишите в отзыве, какой достался вам 😉&lt;br&gt;Обычный фонарь умеет светить. Этот — светит на 95 метров, примагничивается к капоту, подвешивается за крюк к палатке, цепляется на кепку вместо налобника, встаёт на руль велосипеда, меняет цвет как световой меч и измеряет детали встроенной линейкой. И всё это — 75 грамм в кармане. &lt;br&gt;&lt;br&gt;Один раз попользуетесь — и уже не поймёте, как жили без него. 😅&lt;br&gt;💡 Диод P50 — до 680 люмен, сфокусированный луч до 95 метров&lt;br&gt;🎛 16 режимов, 3 отдельные кнопки — мгновенный доступ без перелистывания&lt;br&gt;🌈 RGB-панель: красный (ночное зрение) / синий (аварийный сигнал) / зелёный (охота) / тёплый белый (уютный свет в лагере)&lt;br&gt;⚠️ Стробоскоп — привлечь внимание или обозначить себя на дороге&lt;br&gt;🧲 Мощный магнит в хвосте — к капоту, гаражной балке, любому металлу&lt;br&gt;🪝 Складной крюк — подвесить в палатке или на ветку&lt;br&gt;📎 Зажим-трансформер — на карман, кепку или рюкзак&lt;br&gt;🚴 Велокрепление В КОМПЛЕКТЕ — готовый велофонарь&lt;br&gt;📏 Встроенная линейка 10 см — замер без поисков рулетки&lt;br&gt;🔋 Аккумулятор 1000 мАч — до 12 часов работы, индикатор заряда&lt;br&gt;🔌 Зарядка USB Type-C&lt;br&gt;&lt;br&gt;🦾 Алюминиевый сплав, вес 75 г, падение с 1 м, влагозащита IPX4&lt;br&gt;✔️ Идеально для: EDC (каждый день с собой), велосипеда, гаража и ремонта, кемпинга, рыбалки, авто (аварийный свет), прогулок с собакой&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь M31 + кабель Type-C + велокрепление + инструкция + подарочная коробка 🎁 — готовый подарок мужчине&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически. Себе и в подарок!&lt;br&gt;🏆 Настоящая гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, каждый проверяю лично перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>🥉 Yemao F40CU — фонарь из ЦЕЛЬНОЙ МЕДИ. 1200 люмен в корпусе, который с годами становится только красивее&lt;br&gt;✅ Оригинал Yemao. Таких фонарей на Авито — единицы.&lt;br&gt;🔥 Напишите — пришлю видео реальной яркости!&lt;br&gt;&lt;br&gt;Медь — металл с характером. Она тяжело и приятно лежит в руке, быстро отводит тепло от диода (фонарь может дольше работать в турбо), а со временем покрывается благородной патиной — через год у вас будет фонарь, какого нет больше ни у кого. Это вещь уровня медных Zippo и кастомных ножей — только ещё и светит как карманный прожектор. 😎&lt;br&gt;&lt;br&gt;🥉 Корпус — цельная медь: премиальный вид + лучшее охлаждение диода&lt;br&gt;⚡ Яркость до 1200 люмен, дальность до 200 метров&lt;br&gt;🎛 8 режимов: от «лунного» ночника до турбо + SOS, стробоскоп, красная вспышка&lt;br&gt;🧲 Магнит в хвосте — крепится к любому металлу, работайте двумя руками&lt;br&gt;🔋 Аккумулятор 16340 в комплекте — до 6 часов работы&lt;br&gt;🔌 Зарядка USB Type-C за 3,5 часа&lt;br&gt;🛡 Защита от перегрева и переполюсовки — умная электроника бережёт фонарь&lt;br&gt;💧 Влагозащита IP66 — ливень не страшен&lt;br&gt;🦾 Ударопрочность до 1,5 метра&lt;br&gt;🏮 Абажур-рассеиватель в комплекте — превращает фонарь в лампу для палатки&lt;br&gt;&lt;br&gt;✔️ Идеально для: EDC-коллекции, рыбалки, походов, работы, дома — и как статусная вещь в кармане&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь F40CU + аккумулятор 16340 + кабель Type-C + абажур-рассеиватель + инструкция + подарочная коробка&lt;br&gt;&lt;br&gt;🎁 Тот самый подарок мужчине, у которого «всё есть» — медь решает&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.</t>
+          <t>🥉 Yemao F40CU — фонарь из ЦЕЛЬНОЙ МЕДИ. 1200 люмен в корпусе, который с годами становится только красивее&lt;br&gt;✅ Оригинал Yemao. Таких фонарей на Авито — единицы.&lt;br&gt;🔥 Напишите — пришлю видео реальной яркости!&lt;br&gt;&lt;br&gt;Медь — металл с характером. Она тяжело и приятно лежит в руке, быстро отводит тепло от диода (фонарь может дольше работать в турбо), а со временем покрывается благородной патиной — через год у вас будет фонарь, какого нет больше ни у кого. Это вещь уровня медных Zippo и кастомных ножей — только ещё и светит как карманный прожектор. 😎&lt;br&gt;&lt;br&gt;🥉 Корпус — цельная медь: премиальный вид + лучшее охлаждение диода&lt;br&gt;⚡ Яркость до 1200 люмен, дальность до 200 метров&lt;br&gt;🎛 8 режимов: от «лунного» ночника до турбо + SOS, стробоскоп, красная вспышка&lt;br&gt;🧲 Магнит в хвосте — крепится к любому металлу, работайте двумя руками&lt;br&gt;🔋 Аккумулятор 16340 в комплекте — до 6 часов работы&lt;br&gt;🔌 Зарядка USB Type-C за 3,5 часа&lt;br&gt;🛡 Защита от перегрева и переполюсовки — умная электроника бережёт фонарь&lt;br&gt;💧 Влагозащита IP66 — ливень не страшен&lt;br&gt;🦾 Ударопрочность до 1,5 метра&lt;br&gt;🏮 Абажур-рассеиватель в комплекте — превращает фонарь в лампу для палатки&lt;br&gt;&lt;br&gt;✔️ Идеально для: EDC-коллекции, рыбалки, походов, работы, дома — и как статусная вещь в кармане&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь F40CU + аккумулятор 16340 + кабель Type-C + абажур-рассеиватель + инструкция + подарочная коробка&lt;br&gt;&lt;br&gt;🎁 Тот самый подарок мужчине, у которого «всё есть» — медь решает&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>🔑 Yemao M02X — фонарик-брелок, после которого большой фонарь остаётся дома. 280 люмен + УФ на связке ключей&lt;br&gt;✅ Новинка 2026 года. Покупатели берут сразу по 2–3 штуки — себе и в подарок.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — не поверите, что ТАК светит брелок!&lt;br&gt;&lt;br&gt;Правило фонарей простое: лучший фонарь — тот, который с собой. Большой остаётся в ящике, а этот малыш живёт на ключах и оказывается в руке за секунду: тёмный подъезд, замочная скважина, упавшие под сиденье ключи, щиток в гараже. Двойной клик — и 280 люмен турбо-режима бьют на 30 метров. Для брелока это просто неприлично много. 😅&lt;br&gt;&lt;br&gt;⚡ До 280 люмен — турбо двойным нажатием&lt;br&gt;📏 Дальность — до 30 метров&lt;br&gt;🟣 УФ-режим — проверка купюр и документов прямо на кассе&lt;br&gt;🎛 Режимы: яркий / эконом / стробоскоп / SOS&lt;br&gt;🔋 До 22 часов работы в экономе&lt;br&gt;🔌 Зарядка USB Type-C за ~2 часа — никаких батареек, зарядил и забыл&lt;br&gt;🦾 Авиационный алюминий — падения до 1,5 м переживёт&lt;br&gt;💧 Влагозащита IP44 — дождь не помеха&lt;br&gt;🔑 Крепится на ключи, молнию рюкзака, шлёвку джинсов&lt;br&gt;&lt;br&gt;✔️ Идеально: на ключи, в машину, на рыбалку и в поход, на вело-прогулки, дома в ящик у двери&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарик Yemao M02X + кабель Type-C + упаковка&lt;br&gt;&lt;br&gt;🎁 Лучший недорогой подарок мужчине — автомобилисту, туристу и «тому, у кого всё есть». Дарите — и вам будут пользоваться каждый день.&lt;br&gt;&lt;br&gt;💸 От 2 штук — скидка 10% автоматически. Возьмите на все связки ключей в семье!&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.</t>
+          <t>🔑 Yemao M02X — фонарик-брелок, после которого большой фонарь остаётся дома. 280 люмен + УФ на связке ключей&lt;br&gt;✅ Новинка 2026 года. Покупатели берут сразу по 2–3 штуки — себе и в подарок.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — не поверите, что ТАК светит брелок!&lt;br&gt;&lt;br&gt;Правило фонарей простое: лучший фонарь — тот, который с собой. Большой остаётся в ящике, а этот малыш живёт на ключах и оказывается в руке за секунду: тёмный подъезд, замочная скважина, упавшие под сиденье ключи, щиток в гараже. Двойной клик — и 280 люмен турбо-режима бьют на 30 метров. Для брелока это просто неприлично много. 😅&lt;br&gt;&lt;br&gt;⚡ До 280 люмен — турбо двойным нажатием&lt;br&gt;📏 Дальность — до 30 метров&lt;br&gt;🟣 УФ-режим — проверка купюр и документов прямо на кассе&lt;br&gt;🎛 Режимы: яркий / эконом / стробоскоп / SOS&lt;br&gt;🔋 До 22 часов работы в экономе&lt;br&gt;🔌 Зарядка USB Type-C за ~2 часа — никаких батареек, зарядил и забыл&lt;br&gt;🦾 Авиационный алюминий — падения до 1,5 м переживёт&lt;br&gt;💧 Влагозащита IP44 — дождь не помеха&lt;br&gt;🔑 Крепится на ключи, молнию рюкзака, шлёвку джинсов&lt;br&gt;&lt;br&gt;✔️ Идеально: на ключи, в машину, на рыбалку и в поход, на вело-прогулки, дома в ящик у двери&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарик Yemao M02X + кабель Type-C + упаковка&lt;br&gt;&lt;br&gt;🎁 Лучший недорогой подарок мужчине — автомобилисту, туристу и «тому, у кого всё есть». Дарите — и вам будут пользоваться каждый день.&lt;br&gt;&lt;br&gt;💸 От 2 штук — скидка 10% автоматически. Возьмите на все связки ключей в семье!&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>🔋 YM-F303X — фонарь, который светит СУТКИ без розетки. Флагманский диод Luminus SST40 и два аккумулятора 21700 в комплекте&lt;br&gt;✅ Новинка 2026 года. По параметрам спорит с Fenix E30R и Nitecore HC65 V2 — по цене почти вдвое ниже.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — честные люксы, а не цифры с потолка!&lt;br&gt;&lt;br&gt;За что вы платите, покупая «бренд»? За логотип. Здесь тот же эталонный диод Luminus SST40, тот же авиационный алюминий 6065 и та же годовая гарантия — но без наценки за имя. А в комплекте сразу ДВА аккумулятора 21700 по 5000 мАч: один в фонаре, второй в кармане — вот и сутки автономии в лесу, на смене или при отключении света. 💪&lt;br&gt;&lt;br&gt;☀️ Luminus SST40 — до 1600 люмен, луч больше 200 метров&lt;br&gt;💡 COB-панель до 1000 лм — широкий заливной свет для работы в упор, 4 режима&lt;br&gt;🔄 Голова поворачивается на 90° — свет туда, куда нужно, а не куда получилось&lt;br&gt;🧲 Магнит в хвосте — на капот, трубу, холодильник&lt;br&gt;🔋 2 × 21700 на 5000 мАч В КОМПЛЕКТЕ — до суток работы&lt;br&gt;🔌 Быстрая зарядка USB Type-C&lt;br&gt;🦾 Авиационный алюминий 6065 — падения, дождь и «армейские будни»&lt;br&gt;&lt;br&gt;📊 ЧЕСТНЫЕ РЕЖИМЫ (замеры, а не маркетинг):&lt;br&gt;🚀 Турбо — 1600 лм / 203 м / 1,5 ч&lt;br&gt;🌙 Средний — 350 лм / 93 м / ~18 ч&lt;br&gt;🐢 Эконом — 150 лм / 62 м / 37+ ч&lt;br&gt;⚠️ Строб — 1600 лм, сигнальный&lt;br&gt;💡 COB-заливка — от 5 до 120 часов в зависимости от яркости&lt;br&gt;&lt;br&gt;✔️ Идеально для: охоты и рыбалки, походов, стройки и гаража, работы под капотом, EDC, аварийного света дома&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь YM-F303X + 2 аккумулятора 21700 (5000 мАч) + кабель USB-C + брендированная коробка — готовый подарок 🎁&lt;br&gt;&lt;br&gt;🏆 Нам доверяют: более 600 покупателей, 1000+ фонарей уже в руках владельцев&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, каждый проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — всё расскажу и покажу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.</t>
+          <t>🔋 YM-F303X — фонарь, который светит СУТКИ без розетки. Флагманский диод Luminus SST40 и два аккумулятора 21700 в комплекте&lt;br&gt;✅ Новинка 2026 года. По параметрам спорит с Fenix E30R и Nitecore HC65 V2 — по цене почти вдвое ниже.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — честные люксы, а не цифры с потолка!&lt;br&gt;&lt;br&gt;За что вы платите, покупая «бренд»? За логотип. Здесь тот же эталонный диод Luminus SST40, тот же авиационный алюминий 6065 и та же годовая гарантия — но без наценки за имя. А в комплекте сразу ДВА аккумулятора 21700 по 5000 мАч: один в фонаре, второй в кармане — вот и сутки автономии в лесу, на смене или при отключении света. 💪&lt;br&gt;&lt;br&gt;☀️ Luminus SST40 — до 1600 люмен, луч больше 200 метров&lt;br&gt;💡 COB-панель до 1000 лм — широкий заливной свет для работы в упор, 4 режима&lt;br&gt;🔄 Голова поворачивается на 90° — свет туда, куда нужно, а не куда получилось&lt;br&gt;🧲 Магнит в хвосте — на капот, трубу, холодильник&lt;br&gt;🔋 2 × 21700 на 5000 мАч В КОМПЛЕКТЕ — до суток работы&lt;br&gt;🔌 Быстрая зарядка USB Type-C&lt;br&gt;🦾 Авиационный алюминий 6065 — падения, дождь и «армейские будни»&lt;br&gt;&lt;br&gt;📊 ЧЕСТНЫЕ РЕЖИМЫ (замеры, а не маркетинг):&lt;br&gt;🚀 Турбо — 1600 лм / 203 м / 1,5 ч&lt;br&gt;🌙 Средний — 350 лм / 93 м / ~18 ч&lt;br&gt;🐢 Эконом — 150 лм / 62 м / 37+ ч&lt;br&gt;⚠️ Строб — 1600 лм, сигнальный&lt;br&gt;💡 COB-заливка — от 5 до 120 часов в зависимости от яркости&lt;br&gt;&lt;br&gt;✔️ Идеально для: охоты и рыбалки, походов, стройки и гаража, работы под капотом, EDC, аварийного света дома&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь YM-F303X + 2 аккумулятора 21700 (5000 мАч) + кабель USB-C + брендированная коробка — готовый подарок 🎁&lt;br&gt;&lt;br&gt;🏆 Нам доверяют: более 600 покупателей, 1000+ фонарей уже в руках владельцев&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, каждый проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — всё расскажу и покажу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>🔦 Yemao PM60 — днём прожектор на 3 километра, ночью уютный ночник. Два характера в одном фонаре&lt;br&gt;✅ Хит продаж второй год подряд! Только оригинал Yemao — берегитесь дешёвых копий.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — и луч на 3 км, и светящаяся ручка вживую!&lt;br&gt;&lt;br&gt;Жмёте кнопку — и диод PM60 выдаёт 10 000 люмен: луч видно за 3 километра, поле и лес освещены как прожектором. А вечером в палатке включаете ЭКСКЛЮЗИВ этой модели — мягкую подсветку ручки под стеклом: режим ночника и живой «свечи», уютный свет для лагеря, ребёнка, чтения. Такого нет больше ни у кого. 🕯&lt;br&gt;&lt;br&gt;⚡ Диод PM60 — до 10 000 люмен, луч до 3000 метров&lt;br&gt;🕯 Светящаяся ручка — ночник и режим свечи, фирменная фишка Yemao&lt;br&gt;🎛 11 режимов: от боевого луча до SOS и стробоскопа&lt;br&gt;🔋 Аккумулятор 26650 на 5000 мАч + переходники под другие форматы АКБ&lt;br&gt;⚡️ Функция Power Bank — зарядит телефон в дороге&lt;br&gt;🔌 Быстрая зарядка USB Type-C&lt;br&gt;📷 Крепление под штатив — свет для фото и работы без рук&lt;br&gt;🇯🇵 Разработка — Япония, сборка — под строгим японским контролем качества&lt;br&gt;&lt;br&gt;✔️ Идеально для: охоты, рыбалки, кемпинга, дачи, гаража, экстренных ситуаций и отключений света&lt;br&gt;&lt;br&gt;📦 Богатый комплект: фонарь Yemao + АКБ 26650 + переходники под другие аккумуляторы + кабель Type-C + темляк + крепление для штатива + ПРЕМИУМ подарочный кейс&lt;br&gt;&lt;br&gt;🎁 Готовый подарок мужчине — вручать можно прямо в кейсе: 23 февраля, день рождения, Новый год&lt;br&gt;&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически&lt;br&gt;&lt;br&gt;🏆 НАСТОЯЩАЯ гарантия 1 год (кроме механических повреждений) · Сертифицировано&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, проверяю каждый перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;🔦 Загляните в профиль — там ещё много мощных фонарей по лучшим ценам!&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.</t>
+          <t>🔦 Yemao PM60 — днём прожектор на 3 километра, ночью уютный ночник. Два характера в одном фонаре&lt;br&gt;✅ Хит продаж второй год подряд! Только оригинал Yemao — берегитесь дешёвых копий.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — и луч на 3 км, и светящаяся ручка вживую!&lt;br&gt;&lt;br&gt;Жмёте кнопку — и диод PM60 выдаёт 10 000 люмен: луч видно за 3 километра, поле и лес освещены как прожектором. А вечером в палатке включаете ЭКСКЛЮЗИВ этой модели — мягкую подсветку ручки под стеклом: режим ночника и живой «свечи», уютный свет для лагеря, ребёнка, чтения. Такого нет больше ни у кого. 🕯&lt;br&gt;&lt;br&gt;⚡ Диод PM60 — до 10 000 люмен, луч до 3000 метров&lt;br&gt;🕯 Светящаяся ручка — ночник и режим свечи, фирменная фишка Yemao&lt;br&gt;🎛 11 режимов: от боевого луча до SOS и стробоскопа&lt;br&gt;🔋 Аккумулятор 26650 на 5000 мАч + переходники под другие форматы АКБ&lt;br&gt;⚡️ Функция Power Bank — зарядит телефон в дороге&lt;br&gt;🔌 Быстрая зарядка USB Type-C&lt;br&gt;📷 Крепление под штатив — свет для фото и работы без рук&lt;br&gt;🇯🇵 Разработка — Япония, сборка — под строгим японским контролем качества&lt;br&gt;&lt;br&gt;✔️ Идеально для: охоты, рыбалки, кемпинга, дачи, гаража, экстренных ситуаций и отключений света&lt;br&gt;&lt;br&gt;📦 Богатый комплект: фонарь Yemao + АКБ 26650 + переходники под другие аккумуляторы + кабель Type-C + темляк + крепление для штатива + ПРЕМИУМ подарочный кейс&lt;br&gt;&lt;br&gt;🎁 Готовый подарок мужчине — вручать можно прямо в кейсе: 23 февраля, день рождения, Новый год&lt;br&gt;&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически&lt;br&gt;&lt;br&gt;🏆 НАСТОЯЩАЯ гарантия 1 год (кроме механических повреждений) · Сертифицировано&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, проверяю каждый перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;🔦 Загляните в профиль — там ещё много мощных фонарей по лучшим ценам!&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>💡 Налобник Yemao, который светит ярче автомобильных фар. 3000 люмен на лбу — руки свободны&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Сборка уровня Fenix и Armytek — в разы дешевле.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру!&lt;br&gt;❗ ВНИМАНИЕ: в комплекте 1 мощный аккумулятор (не 2, как на видео) — цена указана честно за этот комплект.&lt;br&gt;&lt;br&gt;Надеваете — и перед вами 200 метров дневного света, а обе руки заняты делом: снастями, инструментом, рулём мотоцикла. Никаких меню и перелистываний режимов: одна кнопка — включил и работаешь. Именно за эту простоту его любят те, кто пользуется фонарём каждый день, а не раз в год. 💪&lt;br&gt;&lt;br&gt;📌 Реальные 3000 люмен — без китайских «маркетинговых» цифр&lt;br&gt;📏 Видимость до 200 метров&lt;br&gt;🔋 Аккумулятор 21700 на 5000 мАч в комплекте — до 20 часов работы&lt;br&gt;🎛 Управление одной кнопкой — вкл/выкл, ничего лишнего&lt;br&gt;🔌 Зарядка USB Type-C&lt;br&gt;🦾 Корпус из авиационного алюминия — переживёт падения и удары&lt;br&gt;💧 Влагозащита IPX4 — дождь и снег не страшны&lt;br&gt;🎽 Удобное регулируемое крепление на голову&lt;br&gt;✔️ Идеально для: охоты, рыбалки, туризма, стройки, гаража, авто и мото, дачи, спасателей, охраны, тактических задач&lt;br&gt;📦 В комплекте: налобный фонарь + аккумулятор 21700 (5000 мАч) + кабель Type-C + крепление на голову&lt;br&gt;&lt;br&gt;🎁 Готовый подарок мужчине — на день рождения или 23 февраля&lt;br&gt;💸 Скидка 10% на второй товар — возьмите второй для напарника&lt;br&gt;🏆 Гарантия 1 год · Официальная сертификация&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;🤝 Возможна встреча / самовывоз — уточняйте&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.</t>
+          <t>💡 Налобник Yemao, который светит ярче автомобильных фар. 3000 люмен на лбу — руки свободны&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Сборка уровня Fenix и Armytek — в разы дешевле.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру!&lt;br&gt;❗ ВНИМАНИЕ: в комплекте 1 мощный аккумулятор (не 2, как на видео) — цена указана честно за этот комплект.&lt;br&gt;&lt;br&gt;Надеваете — и перед вами 200 метров дневного света, а обе руки заняты делом: снастями, инструментом, рулём мотоцикла. Никаких меню и перелистываний режимов: одна кнопка — включил и работаешь. Именно за эту простоту его любят те, кто пользуется фонарём каждый день, а не раз в год. 💪&lt;br&gt;&lt;br&gt;📌 Реальные 3000 люмен — без китайских «маркетинговых» цифр&lt;br&gt;📏 Видимость до 200 метров&lt;br&gt;🔋 Аккумулятор 21700 на 5000 мАч в комплекте — до 20 часов работы&lt;br&gt;🎛 Управление одной кнопкой — вкл/выкл, ничего лишнего&lt;br&gt;🔌 Зарядка USB Type-C&lt;br&gt;🦾 Корпус из авиационного алюминия — переживёт падения и удары&lt;br&gt;💧 Влагозащита IPX4 — дождь и снег не страшны&lt;br&gt;🎽 Удобное регулируемое крепление на голову&lt;br&gt;✔️ Идеально для: охоты, рыбалки, туризма, стройки, гаража, авто и мото, дачи, спасателей, охраны, тактических задач&lt;br&gt;📦 В комплекте: налобный фонарь + аккумулятор 21700 (5000 мАч) + кабель Type-C + крепление на голову&lt;br&gt;&lt;br&gt;🎁 Готовый подарок мужчине — на день рождения или 23 февраля&lt;br&gt;💸 Скидка 10% на второй товар — возьмите второй для напарника&lt;br&gt;🏆 Гарантия 1 год · Официальная сертификация&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;🤝 Возможна встреча / самовывоз — уточняйте&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>💡 YM-M18 — 5,5 сантиметра, в которых спрятано ШЕСТЬ источников света. Сенсор, магнит, УФ и 14 режимов&lt;br&gt;Цвет фонарика кладется случайно: оранжевый, синий, зеленый&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Мультитул в мире фонарей.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — все 6 источников света показаны вживую!&lt;br&gt;&lt;br&gt;Посчитаем: дальний луч, широкая COB-заливка, ультрафиолет для купюр, цветная RGB-панель, красно-синяя аварийка и световые эффекты. Это ШЕСТЬ фонарей, купленных по цене одного — и все они помещаются в корпус размером с большой палец. А включается он взмахом руки: сенсор срабатывает, даже когда руки в масле, в перчатках или заняты. 🤯&lt;br&gt;&lt;br&gt;⚡ Основной луч — до 270 люмен, дальность до 80 метров&lt;br&gt;💡 COB-панель — мощная широкая заливка для работы вблизи&lt;br&gt;🟣 УФ-свет — проверка купюр и документов&lt;br&gt;🌈 RGB — красный / синий / зелёный / жёлтый&lt;br&gt;🚨 Красно-синий аварийный сигнал — обозначить себя на дороге&lt;br&gt;✨ Эффекты «мигание» и «дыхание»&lt;br&gt;🙌 Сенсор — взмах рукой = вкл/выкл, плюс обычные быстрые кнопки&lt;br&gt;🎛 Всего 14 режимов: 3 уровня яркости, строб, SOS и все панели&lt;br&gt;🧲 Магнит — прилепили к капоту и работаете двумя руками&lt;br&gt;📎 Клипса — на карман или кепку (мгновенный налобник)&lt;br&gt;📏 Размер — всего 55 мм, не почувствуете в кармане&lt;br&gt;🔋 До 8 часов работы, зарядка USB Type-C&lt;br&gt;🦾 Прочный алюминий, ударопрочный, влагозащита IPX4&lt;br&gt;&lt;br&gt;✔️ Идеально для: машины (аварийка + магнит = маст-хэв), гаража и ремонта, походов, рыбалки, дома, EDC на каждый день&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь YM-M18 + кабель Type-C + упаковка (готовый подарок 🎁)&lt;br&gt;&lt;br&gt;💸 От 2 штук — скидка 10% автоматически. Один в карман, один в бардачок!&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю каждый перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.</t>
+          <t>💡 YM-M18 — 5,5 сантиметра, в которых спрятано ШЕСТЬ источников света. Сенсор, магнит, УФ и 14 режимов&lt;br&gt;Цвет фонарика кладется случайно: оранжевый, синий, зеленый&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Мультитул в мире фонарей.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — все 6 источников света показаны вживую!&lt;br&gt;&lt;br&gt;Посчитаем: дальний луч, широкая COB-заливка, ультрафиолет для купюр, цветная RGB-панель, красно-синяя аварийка и световые эффекты. Это ШЕСТЬ фонарей, купленных по цене одного — и все они помещаются в корпус размером с большой палец. А включается он взмахом руки: сенсор срабатывает, даже когда руки в масле, в перчатках или заняты. 🤯&lt;br&gt;&lt;br&gt;⚡ Основной луч — до 270 люмен, дальность до 80 метров&lt;br&gt;💡 COB-панель — мощная широкая заливка для работы вблизи&lt;br&gt;🟣 УФ-свет — проверка купюр и документов&lt;br&gt;🌈 RGB — красный / синий / зелёный / жёлтый&lt;br&gt;🚨 Красно-синий аварийный сигнал — обозначить себя на дороге&lt;br&gt;✨ Эффекты «мигание» и «дыхание»&lt;br&gt;🙌 Сенсор — взмах рукой = вкл/выкл, плюс обычные быстрые кнопки&lt;br&gt;🎛 Всего 14 режимов: 3 уровня яркости, строб, SOS и все панели&lt;br&gt;🧲 Магнит — прилепили к капоту и работаете двумя руками&lt;br&gt;📎 Клипса — на карман или кепку (мгновенный налобник)&lt;br&gt;📏 Размер — всего 55 мм, не почувствуете в кармане&lt;br&gt;🔋 До 8 часов работы, зарядка USB Type-C&lt;br&gt;🦾 Прочный алюминий, ударопрочный, влагозащита IPX4&lt;br&gt;&lt;br&gt;✔️ Идеально для: машины (аварийка + магнит = маст-хэв), гаража и ремонта, походов, рыбалки, дома, EDC на каждый день&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь YM-M18 + кабель Type-C + упаковка (готовый подарок 🎁)&lt;br&gt;&lt;br&gt;💸 От 2 штук — скидка 10% автоматически. Один в карман, один в бардачок!&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю каждый перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>🏟 Фонарь-зверь Yemao — ярче стадионного прожектора. До 15 000 люмен, луч до 5 км и ВОСЕМЬ аккумуляторов в комплекте&lt;br&gt;✅ Только оригинал Yemao — остерегайтесь дешёвых копий с нашими видео.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — луч до горизонта снят вживую!&lt;br&gt;&lt;br&gt;Включаете турбо — и поле до самого леса залито светом, как футбольный газон в финале. Зум собирает свет в тонкий «лазерный» луч на 5 километров или разливает на сотни квадратных метров. А главное — 8 аккумуляторов 18650 в комплекте: пока четыре работают, четыре ждут в кейсе. Энергии хватит на всю смену, и телефон ещё зарядите. 💪&lt;br&gt;&lt;br&gt;⚡ Яркость — до 15 000 люмен&lt;br&gt;📏 Дальность луча — до 5 000 метров, реально «достреливает» до горизонта&lt;br&gt;🔍 Zoom — от игольного луча до широченной заливки&lt;br&gt;🔋 8 (!) аккумуляторов 18650 в комплекте — до 7 часов от одного заряда + полный запасной комплект&lt;br&gt;⚡️ Функция Power Bank — фонарь зарядит ваш телефон в лесу&lt;br&gt;🎛 7 режимов: от «лунного» ночника до турбо, SOS и стробоскопа&lt;br&gt;🦾 Авиационный алюминий — переживёт падения; ударная кромка разобьёт стекло авто в экстренной ситуации&lt;br&gt;💧 Защита IP65 — дождь, снег, грязь&lt;br&gt;🔌 Быстрая зарядка Type-C + индикатор заряда&lt;br&gt;&lt;br&gt;✔️ Проверен теми, кто работает ночью: охотники, рыбаки, охрана, спасатели, туристы&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь + 8 АКБ 18650 + ремень + кабель Type-C + ПОДАРОЧНЫЙ кейс-чехол — вручать можно прямо в нём 🎁&lt;br&gt;&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, каждый тестирую перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.</t>
+          <t>🏟 Фонарь-зверь Yemao — ярче стадионного прожектора. До 15 000 люмен, луч до 5 км и ВОСЕМЬ аккумуляторов в комплекте&lt;br&gt;✅ Только оригинал Yemao — остерегайтесь дешёвых копий с нашими видео.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — луч до горизонта снят вживую!&lt;br&gt;&lt;br&gt;Включаете турбо — и поле до самого леса залито светом, как футбольный газон в финале. Зум собирает свет в тонкий «лазерный» луч на 5 километров или разливает на сотни квадратных метров. А главное — 8 аккумуляторов 18650 в комплекте: пока четыре работают, четыре ждут в кейсе. Энергии хватит на всю смену, и телефон ещё зарядите. 💪&lt;br&gt;&lt;br&gt;⚡ Яркость — до 15 000 люмен&lt;br&gt;📏 Дальность луча — до 5 000 метров, реально «достреливает» до горизонта&lt;br&gt;🔍 Zoom — от игольного луча до широченной заливки&lt;br&gt;🔋 8 (!) аккумуляторов 18650 в комплекте — до 7 часов от одного заряда + полный запасной комплект&lt;br&gt;⚡️ Функция Power Bank — фонарь зарядит ваш телефон в лесу&lt;br&gt;🎛 7 режимов: от «лунного» ночника до турбо, SOS и стробоскопа&lt;br&gt;🦾 Авиационный алюминий — переживёт падения; ударная кромка разобьёт стекло авто в экстренной ситуации&lt;br&gt;💧 Защита IP65 — дождь, снег, грязь&lt;br&gt;🔌 Быстрая зарядка Type-C + индикатор заряда&lt;br&gt;&lt;br&gt;✔️ Проверен теми, кто работает ночью: охотники, рыбаки, охрана, спасатели, туристы&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь + 8 АКБ 18650 + ремень + кабель Type-C + ПОДАРОЧНЫЙ кейс-чехол — вручать можно прямо в нём 🎁&lt;br&gt;&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, каждый тестирую перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>🔥Hастоящая гарантия 1 год!&lt;br&gt;Бeзупрeчный рейтинг ⭐️⭐️⭐️⭐️⭐️&lt;br&gt;❗️Нет аналогов на Авито! Другие продавцы копируют фото и видео и выдают свой товар за этот&lt;br&gt;&lt;br&gt;🌌 Прожектор, который превращает ночь в день. 336 LED + повербанк + солнечная батарея — 3 в 1&lt;br&gt;&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — реальная яркость снята на камеру!&lt;br&gt;Выключился свет? Стемнело в походе? Сел телефон посреди рыбалки? Этот прожектор закрывает все три проблемы одной кнопкой. Панель из 336 диодов заливает светом до 150 м² — во дворе становится светло, как днём. А когда розетки нет неделями — он заряжает сам себя от солнца. 😎&lt;br&gt;&lt;br&gt;💡 336 LED-диодов — заливает светом площадь до 150 м²&lt;br&gt;🎛 5 режимов: холодный / тёплый / комбинированный / приглушённый / аварийный стробоскоп&lt;br&gt;🔋 Аккумулятор 12 000 мАч — до 15 часов света без подзарядки&lt;br&gt;☀️ Солнечная панель — заряжается сам, пока вы на природе&lt;br&gt;⚡️ Функция PowerBank — подзарядит телефон там, где нет розеток&lt;br&gt;🔌 Быстрая зарядка от сети через USB Type-C&lt;br&gt;🧲 Магнит + крючок + ножка-подставка — поставьте, подвесьте или примагнитьте к капоту&lt;br&gt;🌧 Защита IP66 — ливень, мороз и жара ему безразличны&lt;br&gt;Размер: 20х15х5см, вес 500гр&lt;br&gt;✔️ Идеально для: кемпинга и палатки, дачи и гаража, рыбалки и охоты, вечерних посиделок, работ во дворе, аварийного света при отключениях&lt;br&gt;&lt;br&gt;🎁 Готовый подарок мужчине: на дачника&lt;br&gt;💸 От 2 штук — скидка 10% автоматически&lt;br&gt;📦 В комплекте: прожектор + кабель Type-C&lt;br&gt;&lt;br&gt;🏆 Настоящая гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, всё проверено и протестировано перед отправкой&lt;br&gt;&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.</t>
+          <t>🔥Hастоящая гарантия 1 год!&lt;br&gt;Бeзупрeчный рейтинг ⭐️⭐️⭐️⭐️⭐️&lt;br&gt;❗️Нет аналогов на Авито! Другие продавцы копируют фото и видео и выдают свой товар за этот&lt;br&gt;&lt;br&gt;🌌 Прожектор, который превращает ночь в день. 336 LED + повербанк + солнечная батарея — 3 в 1&lt;br&gt;&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — реальная яркость снята на камеру!&lt;br&gt;Выключился свет? Стемнело в походе? Сел телефон посреди рыбалки? Этот прожектор закрывает все три проблемы одной кнопкой. Панель из 336 диодов заливает светом до 150 м² — во дворе становится светло, как днём. А когда розетки нет неделями — он заряжает сам себя от солнца. 😎&lt;br&gt;&lt;br&gt;💡 336 LED-диодов — заливает светом площадь до 150 м²&lt;br&gt;🎛 5 режимов: холодный / тёплый / комбинированный / приглушённый / аварийный стробоскоп&lt;br&gt;🔋 Аккумулятор 12 000 мАч — до 15 часов света без подзарядки&lt;br&gt;☀️ Солнечная панель — заряжается сам, пока вы на природе&lt;br&gt;⚡️ Функция PowerBank — подзарядит телефон там, где нет розеток&lt;br&gt;🔌 Быстрая зарядка от сети через USB Type-C&lt;br&gt;🧲 Магнит + крючок + ножка-подставка — поставьте, подвесьте или примагнитьте к капоту&lt;br&gt;🌧 Защита IP66 — ливень, мороз и жара ему безразличны&lt;br&gt;Размер: 20х15х5см, вес 500гр&lt;br&gt;✔️ Идеально для: кемпинга и палатки, дачи и гаража, рыбалки и охоты, вечерних посиделок, работ во дворе, аварийного света при отключениях&lt;br&gt;&lt;br&gt;🎁 Готовый подарок мужчине: на дачника&lt;br&gt;💸 От 2 штук — скидка 10% автоматически&lt;br&gt;📦 В комплекте: прожектор + кабель Type-C&lt;br&gt;&lt;br&gt;🏆 Настоящая гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, всё проверено и протестировано перед отправкой&lt;br&gt;&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>🙌 Yemao — налобник весом 48 грамм с сенсорным управлением. Провёл рукой — включился. Забыл, что он на голове&lt;br&gt;✅ Новинка 2026 года. Цвет — чёрный или синий, кладётся случайно (напишите в отзыве, какой достался 😉)&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — жестовое управление показано вживую!&lt;br&gt;&lt;br&gt;48 грамм — это меньше половины смартфона: надели и перестали замечать. А кнопку искать не нужно вовсе: взмах рукой перед фонарём — включился, ещё взмах — выключился. Руки в грязи, в перчатках, заняты снастями — неважно, работает всегда. И это не один фонарь, а три: на голову, на кепку и на велосипед — крепления все в комплекте. 💪&lt;br&gt;&lt;br&gt;🙌 Сенсор — вкл/выкл взмахом руки, даже в перчатках и на ходу&lt;br&gt;⚡ Яркость до 500 люмен, дальность до 150 метров&lt;br&gt;💡 Два света: широкая заливка + дальний луч&lt;br&gt;🎛 7 режимов, включая красный (ночное зрение) и SOS&lt;br&gt;🔄 Поворот на 180° — направьте свет куда нужно&lt;br&gt;🪶 Вес — всего 48 грамм, на голове не ощущается&lt;br&gt;🔋 До 5 часов работы, зарядка по USB&lt;br&gt;💧 Влагозащита IPX4 — дождь не помеха&lt;br&gt;🦾 Прочный корпус&lt;br&gt;&lt;br&gt;⚙️ 3 В 1 — крепления в комплекте:&lt;br&gt;✔ На голову — классический налобник&lt;br&gt;✔ Клипса — на кепку или одежду&lt;br&gt;✔ Велокрепление — готовый велофонарь&lt;br&gt;&lt;br&gt;✔️ Идеально для: рыбалки, походов, велосипеда, ремонта, работы под капотом, прогулок с собакой&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь + крепление на голову + клипса + велокрепление + кабель USB&lt;br&gt;&lt;br&gt;🎁 Недорогой подарок, которым реально пользуются каждый день&lt;br&gt;&lt;br&gt;💸 От 2 штук — скидка 10% автоматически. Себе и на второй велосипед!&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.</t>
+          <t>🙌 Yemao — налобник весом 48 грамм с сенсорным управлением. Провёл рукой — включился. Забыл, что он на голове&lt;br&gt;✅ Новинка 2026 года. Цвет — чёрный или синий, кладётся случайно (напишите в отзыве, какой достался 😉)&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — жестовое управление показано вживую!&lt;br&gt;&lt;br&gt;48 грамм — это меньше половины смартфона: надели и перестали замечать. А кнопку искать не нужно вовсе: взмах рукой перед фонарём — включился, ещё взмах — выключился. Руки в грязи, в перчатках, заняты снастями — неважно, работает всегда. И это не один фонарь, а три: на голову, на кепку и на велосипед — крепления все в комплекте. 💪&lt;br&gt;&lt;br&gt;🙌 Сенсор — вкл/выкл взмахом руки, даже в перчатках и на ходу&lt;br&gt;⚡ Яркость до 500 люмен, дальность до 150 метров&lt;br&gt;💡 Два света: широкая заливка + дальний луч&lt;br&gt;🎛 7 режимов, включая красный (ночное зрение) и SOS&lt;br&gt;🔄 Поворот на 180° — направьте свет куда нужно&lt;br&gt;🪶 Вес — всего 48 грамм, на голове не ощущается&lt;br&gt;🔋 До 5 часов работы, зарядка по USB&lt;br&gt;💧 Влагозащита IPX4 — дождь не помеха&lt;br&gt;🦾 Прочный корпус&lt;br&gt;&lt;br&gt;⚙️ 3 В 1 — крепления в комплекте:&lt;br&gt;✔ На голову — классический налобник&lt;br&gt;✔ Клипса — на кепку или одежду&lt;br&gt;✔ Велокрепление — готовый велофонарь&lt;br&gt;&lt;br&gt;✔️ Идеально для: рыбалки, походов, велосипеда, ремонта, работы под капотом, прогулок с собакой&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь + крепление на голову + клипса + велокрепление + кабель USB&lt;br&gt;&lt;br&gt;🎁 Недорогой подарок, которым реально пользуются каждый день&lt;br&gt;&lt;br&gt;💸 От 2 штук — скидка 10% автоматически. Себе и на второй велосипед!&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>🔥 СПЕЦИАЛЬНАЯ ЦЕНА ДО КОНЦА НЕДЕЛИ — всего 1095 ₽ вместо 1440 ₽! 🔥&lt;br&gt;&lt;br&gt;🔦 PM30 PRO — сверхмощный аккумуляторный фонарь с дальностью луча до 3000 метров!&lt;br&gt;&lt;br&gt;✅ Гарантия 12 месяцев&lt;br&gt;✅ Рейтинг покупателей — 5.0&lt;br&gt;✅ Аккумулятор 3000 мАч в комплекте (честная ёмкость)&lt;br&gt;✅ Редкая модель, которую сложно найти на Авито&lt;br&gt;✅ Не путайте с дешёвыми копиями и подделками&lt;br&gt;&lt;br&gt;❤️ Добавьте объявление в избранное, чтобы не потерять выгодное предложение.&lt;br&gt;&lt;br&gt;💡 PM30 PRO — компактный, но очень мощный светодиодный фонарь для любых задач: от ремонта автомобиля до рыбалки и путешествий.&lt;br&gt;&lt;br&gt;⚡️ Основные характеристики:&lt;br&gt;&lt;br&gt;🔹 Дальность свечения до 3 км&lt;br&gt;🔹 Яркость до 13 000 люмен&lt;br&gt;🔹 Современный светодиод с мощным сфокусированным лучом&lt;br&gt;🔹 Освещает территорию значительно лучше многих крупногабаритных прожекторов&lt;br&gt;&lt;br&gt;📦 Возможности фонаря:&lt;br&gt;&lt;br&gt;✔️ 9 режимов работы&lt;br&gt;✔️ Максимальный, средний и экономичный режимы&lt;br&gt;✔️ Стробоскоп и сигнал SOS&lt;br&gt;✔️ Красная подсветка&lt;br&gt;✔️ Регулируемый фокус луча (зум)&lt;br&gt;✔️ Работа от аккумулятора и батареек&lt;br&gt;✔️ Зарядка через Type-C&lt;br&gt;✔️ Магнит для крепления к металлическим поверхностям&lt;br&gt;✔️ Индикация уровня заряда на дисплее&lt;br&gt;✔️ Возможность использовать как Power Bank&lt;br&gt;&lt;br&gt;💪 Преимущества:&lt;br&gt;&lt;br&gt;✔️ Влагозащита IP65&lt;br&gt;✔️ Надёжный ударопрочный корпус&lt;br&gt;✔️ Компактные размеры — всего 16,8 см&lt;br&gt;✔️ Поставляется в подарочной упаковке&lt;br&gt;✔️ Удобно хранить в машине, рюкзаке или дома&lt;br&gt;&lt;br&gt;🎯 Отлично подойдёт для:&lt;br&gt;&lt;br&gt;🎣 Рыбалки&lt;br&gt;🏕 Туризма и кемпинга&lt;br&gt;🚗 Автомобиля&lt;br&gt;🔧 Строительных и ремонтных работ&lt;br&gt;🚴 Велопрогулок&lt;br&gt;🏹 Активного отдыха и выездов на природу&lt;br&gt;&lt;br&gt;🎁 Практичный подарок для мужчины, мужа, отца, брата, друга или коллеги.&lt;br&gt;&lt;br&gt;💸 При покупке двух и более товаров действует дополнительная скидка 10%.&lt;br&gt;&lt;br&gt;🚚 Быстрая отправка Авито Доставкой по всей России.&lt;br&gt;&lt;br&gt;⚠️ Внимание! Не направляйте луч в глаза людям и животным. Рекомендуется хранить в недоступном для детей месте.&lt;br&gt;&lt;br&gt;❗️ Оформляйте заказ или пишите в сообщения прямо сейчас — количество фонарей по акционной цене ограничено!</t>
+          <t>🔥 СПЕЦИАЛЬНАЯ ЦЕНА ДО КОНЦА НЕДЕЛИ — всего 1095 ₽ вместо 1440 ₽! 🔥&lt;br&gt;&lt;br&gt;🔦 PM30 PRO — сверхмощный аккумуляторный фонарь с дальностью луча до 3000 метров!&lt;br&gt;&lt;br&gt;✅ Гарантия 12 месяцев&lt;br&gt;✅ Рейтинг покупателей — 5.0&lt;br&gt;✅ Аккумулятор 3000 мАч в комплекте (честная ёмкость)&lt;br&gt;✅ Редкая модель, которую сложно найти на Авито&lt;br&gt;✅ Не путайте с дешёвыми копиями и подделками&lt;br&gt;&lt;br&gt;❤️ Добавьте объявление в избранное, чтобы не потерять выгодное предложение.&lt;br&gt;&lt;br&gt;💡 PM30 PRO — компактный, но очень мощный светодиодный фонарь для любых задач: от ремонта автомобиля до рыбалки и путешествий.&lt;br&gt;&lt;br&gt;⚡️ Основные характеристики:&lt;br&gt;&lt;br&gt;🔹 Дальность свечения до 3 км&lt;br&gt;🔹 Яркость до 13 000 люмен&lt;br&gt;🔹 Современный светодиод с мощным сфокусированным лучом&lt;br&gt;🔹 Освещает территорию значительно лучше многих крупногабаритных прожекторов&lt;br&gt;&lt;br&gt;📦 Возможности фонаря:&lt;br&gt;&lt;br&gt;✔️ 9 режимов работы&lt;br&gt;✔️ Максимальный, средний и экономичный режимы&lt;br&gt;✔️ Стробоскоп и сигнал SOS&lt;br&gt;✔️ Красная подсветка&lt;br&gt;✔️ Регулируемый фокус луча (зум)&lt;br&gt;✔️ Работа от аккумулятора и батареек&lt;br&gt;✔️ Зарядка через Type-C&lt;br&gt;✔️ Магнит для крепления к металлическим поверхностям&lt;br&gt;✔️ Индикация уровня заряда на дисплее&lt;br&gt;✔️ Возможность использовать как Power Bank&lt;br&gt;&lt;br&gt;💪 Преимущества:&lt;br&gt;&lt;br&gt;✔️ Влагозащита IP65&lt;br&gt;✔️ Надёжный ударопрочный корпус&lt;br&gt;✔️ Компактные размеры — всего 16,8 см&lt;br&gt;✔️ Поставляется в подарочной упаковке&lt;br&gt;✔️ Удобно хранить в машине, рюкзаке или дома&lt;br&gt;&lt;br&gt;🎯 Отлично подойдёт для:&lt;br&gt;&lt;br&gt;🎣 Рыбалки&lt;br&gt;🏕 Туризма и кемпинга&lt;br&gt;🚗 Автомобиля&lt;br&gt;🔧 Строительных и ремонтных работ&lt;br&gt;🚴 Велопрогулок&lt;br&gt;🏹 Активного отдыха и выездов на природу&lt;br&gt;&lt;br&gt;🎁 Практичный подарок для мужчины, мужа, отца, брата, друга или коллеги.&lt;br&gt;&lt;br&gt;💸 При покупке двух и более товаров действует дополнительная скидка 10%.&lt;br&gt;&lt;br&gt;🚚 Быстрая отправка Авито Доставкой по всей России.&lt;br&gt;&lt;br&gt;⚠️ Внимание! Не направляйте луч в глаза людям и животным. Рекомендуется хранить в недоступном для детей месте.&lt;br&gt;&lt;br&gt;❗️ Оформляйте заказ или пишите в сообщения прямо сейчас — количество фонарей по акционной цене ограничено!&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>🔦 УФ фонарь 365 nm — покажет то, что от вас скрывают. Профессиональный фонарь Вуда в металле&lt;br&gt;✅ Настоящие 365 нанометров — не дешёвый «фиолетовый диод» 395 nm, а профессиональный UV.&lt;br&gt;&lt;br&gt;🔥 Видео ОБЯЗАТЕЛЬНО к просмотру — эффект видно с первой секунды!&lt;br&gt;Посветите на купюру — проявятся защитные метки. На кровать в отеле — и вы узнаете, как там убирают. На пляж с янтарём — камни вспыхнут в темноте сами. Этот фонарь показывает слой реальности, который обычным глазом не увидеть. Первое включение — всегда «вау». 😳&lt;br&gt;💡 ЧТО ОН НАХОДИТ:&lt;br&gt;✔ Янтарь и минералы — светятся в темноте, поиск на пляже превращается в охоту за сокровищами&lt;br&gt;✔ Купюры, документы, паспорта — мгновенная проверка подлинности&lt;br&gt;✔ Скрытые пятна и следы — проверка отелей, квартир, мебели, авто перед покупкой&lt;br&gt;✔ Утечки фреона и техжидкостей — незаменим в автосервисе&lt;br&gt;✔ Сушка гель-лака — работает для маникюра&lt;br&gt;✔ Светонакопительные приманки — заряжает за секунды, рыбаки оценят&lt;br&gt;&lt;br&gt;⚡ ХАРАКТЕРИСТИКИ:&lt;br&gt;🌑 Длина волны 365 nm — профессиональный стандарт (фонарь Вуда)&lt;br&gt;📏 Компактный — всего 12,5 см, лежит в кармане&lt;br&gt;🔋 Аккумулятор 18650 в комплекте — до 3 часов работы&lt;br&gt;🦾 Цельнометаллический ударопрочный корпус&lt;br&gt;💧 Защита IP65 — влага и пыль не страшны&lt;br&gt;✔️ Кому: коллекционерам и янтарщикам, мастерам маникюра, автосервисам, рыбакам, туристам, всем кто работает с деньгами и документами&lt;br&gt;&lt;br&gt;📦 В комплекте: УФ фонарь 365 nm + аккумулятор 18650 + зарядка + кейс&lt;br&gt;🎁 Самый необычный подарок — удивляет с первого включения, проверено&lt;br&gt;💸 От 2 товаров — скидка 10% автоматически&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.</t>
+          <t>🔦 УФ фонарь 365 nm — покажет то, что от вас скрывают. Профессиональный фонарь Вуда в металле&lt;br&gt;✅ Настоящие 365 нанометров — не дешёвый «фиолетовый диод» 395 nm, а профессиональный UV.&lt;br&gt;&lt;br&gt;🔥 Видео ОБЯЗАТЕЛЬНО к просмотру — эффект видно с первой секунды!&lt;br&gt;Посветите на купюру — проявятся защитные метки. На кровать в отеле — и вы узнаете, как там убирают. На пляж с янтарём — камни вспыхнут в темноте сами. Этот фонарь показывает слой реальности, который обычным глазом не увидеть. Первое включение — всегда «вау». 😳&lt;br&gt;💡 ЧТО ОН НАХОДИТ:&lt;br&gt;✔ Янтарь и минералы — светятся в темноте, поиск на пляже превращается в охоту за сокровищами&lt;br&gt;✔ Купюры, документы, паспорта — мгновенная проверка подлинности&lt;br&gt;✔ Скрытые пятна и следы — проверка отелей, квартир, мебели, авто перед покупкой&lt;br&gt;✔ Утечки фреона и техжидкостей — незаменим в автосервисе&lt;br&gt;✔ Сушка гель-лака — работает для маникюра&lt;br&gt;✔ Светонакопительные приманки — заряжает за секунды, рыбаки оценят&lt;br&gt;&lt;br&gt;⚡ ХАРАКТЕРИСТИКИ:&lt;br&gt;🌑 Длина волны 365 nm — профессиональный стандарт (фонарь Вуда)&lt;br&gt;📏 Компактный — всего 12,5 см, лежит в кармане&lt;br&gt;🔋 Аккумулятор 18650 в комплекте — до 3 часов работы&lt;br&gt;🦾 Цельнометаллический ударопрочный корпус&lt;br&gt;💧 Защита IP65 — влага и пыль не страшны&lt;br&gt;✔️ Кому: коллекционерам и янтарщикам, мастерам маникюра, автосервисам, рыбакам, туристам, всем кто работает с деньгами и документами&lt;br&gt;&lt;br&gt;📦 В комплекте: УФ фонарь 365 nm + аккумулятор 18650 + зарядка + кейс&lt;br&gt;🎁 Самый необычный подарок — удивляет с первого включения, проверено&lt;br&gt;💸 От 2 товаров — скидка 10% автоматически&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>🔦 Малыш весом 60 грамм, который светит на 300 метров. Белый лазер PM20-TG в корпусе размером с палец&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Остерегайтесь копий — наши видео используют другие продавцы, а высылают обычный диод.&lt;br&gt;&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — досмотрите до конца, там вся мощность!&lt;br&gt;&lt;br&gt;Помещается в кулак целиком: 8,4 × 2,4 см. А луч — как у фонарей в пять раз крупнее. Секрет — кристалл нового поколения PM20-TG «белый лазер»: плотный чёткий луч до 300 метров, который отлично читается даже в городской засветке. Достаёте его из кармана при друзьях — дальше начинаются вопросы. 😅&lt;br&gt;&lt;br&gt;⚡ Вес — всего 60 г, размер 8,4 × 2,4 см&lt;br&gt;📏 Дальность луча — до 300 метров&lt;br&gt;💎 Кристалл PM20-TG «белый лазер» — мощнее классических диодов&lt;br&gt;🔍 Zoom-фокусировка — от широкого пятна до игольного луча&lt;br&gt;🎛 2 уровня яркости + стробоскоп + SOS&lt;br&gt;🧢 Клипса в комплекте — цепляете на кепку и получаете налобник&lt;br&gt;🔋 Аккумулятор 16340 в комплекте&lt;br&gt;🔌 Зарядка USB Type-C (кабель в комплекте)&lt;br&gt;❗ Важно: аккумулятор вставляется ПЛЮСОМ к пружине — наоборот от привычного. Это не брак, так задумано производителем. Памятка будет в посылке.&lt;br&gt;&lt;br&gt;✔️ Идеально для: EDC (каждый день в кармане), рыбалки, охоты, авто, прогулок с собакой, подарка мужчине&lt;br&gt;📦 В комплекте: фонарь + аккумулятор 16340 + кабель Type-C + клипса&lt;br&gt;⚠️ Не светите в глаза людям и животным и не давайте детям — это серьёзный прибор, а не игрушка.&lt;br&gt;&lt;br&gt;💸 От 2 штук — скидка 10% автоматически. Возьмите второй в бардачок!&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, каждый фонарь тестирую лично перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.</t>
+          <t>🔦 Малыш весом 60 грамм, который светит на 300 метров. Белый лазер PM20-TG в корпусе размером с палец&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Остерегайтесь копий — наши видео используют другие продавцы, а высылают обычный диод.&lt;br&gt;&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — досмотрите до конца, там вся мощность!&lt;br&gt;&lt;br&gt;Помещается в кулак целиком: 8,4 × 2,4 см. А луч — как у фонарей в пять раз крупнее. Секрет — кристалл нового поколения PM20-TG «белый лазер»: плотный чёткий луч до 300 метров, который отлично читается даже в городской засветке. Достаёте его из кармана при друзьях — дальше начинаются вопросы. 😅&lt;br&gt;&lt;br&gt;⚡ Вес — всего 60 г, размер 8,4 × 2,4 см&lt;br&gt;📏 Дальность луча — до 300 метров&lt;br&gt;💎 Кристалл PM20-TG «белый лазер» — мощнее классических диодов&lt;br&gt;🔍 Zoom-фокусировка — от широкого пятна до игольного луча&lt;br&gt;🎛 2 уровня яркости + стробоскоп + SOS&lt;br&gt;🧢 Клипса в комплекте — цепляете на кепку и получаете налобник&lt;br&gt;🔋 Аккумулятор 16340 в комплекте&lt;br&gt;🔌 Зарядка USB Type-C (кабель в комплекте)&lt;br&gt;❗ Важно: аккумулятор вставляется ПЛЮСОМ к пружине — наоборот от привычного. Это не брак, так задумано производителем. Памятка будет в посылке.&lt;br&gt;&lt;br&gt;✔️ Идеально для: EDC (каждый день в кармане), рыбалки, охоты, авто, прогулок с собакой, подарка мужчине&lt;br&gt;📦 В комплекте: фонарь + аккумулятор 16340 + кабель Type-C + клипса&lt;br&gt;⚠️ Не светите в глаза людям и животным и не давайте детям — это серьёзный прибор, а не игрушка.&lt;br&gt;&lt;br&gt;💸 От 2 штук — скидка 10% автоматически. Возьмите второй в бардачок!&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, каждый фонарь тестирую лично перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>🙌 Налобник, который включается взмахом руки. Датчик движения + 10 000 люмен + свет до 1000 метров&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Оригинал с диодом PM30 — остерегайтесь слабых копий с нашими фото (коробка может отличаться).&lt;br&gt;&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — жест рукой и мощность луча надо видеть!&lt;br&gt;&lt;br&gt;Руки в перчатках? В грязи? Заняты снастями или инструментом? Просто проведите ладонью перед фонарём — включился. Ещё взмах — выключился. Никаких кнопок на морозе, никакой возни. Один раз попробуете — обычные налобники покажутся прошлым веком. А по мощности это не налобник, а прожектор на лбу: луч достаёт туда, где обычные фонари уже «сдулись». 💪&lt;br&gt;&lt;br&gt;🙌 Датчик движения — управление взмахом руки, идеально в перчатках и на морозе&lt;br&gt;⚡ Яркость до 10 000 люмен — диод PM30 нового поколения&lt;br&gt;📏 Дальность луча — до 1000 метров&lt;br&gt;🔋 3 аккумулятора в комплекте — 6900 мАч суммарно, до 20 часов в эконом-режиме&lt;br&gt;⚡️ Функция Power Bank — подзарядит телефон на природе&lt;br&gt;📊 Дисплей-индикатор заряда — точно знаете остаток&lt;br&gt;🎛 Режимы: максимальный / средний / эконом / стробоскоп / SOS&lt;br&gt;💧 Защита IPX6 — дождь, грязь и пыль не страшны&lt;br&gt;🦾 Ударопрочный корпус, надёжное регулируемое крепление на голову&lt;br&gt;✔️ Идеально для: рыбалки и охоты, походов, стройки и работы, гаража, авто (аварийные ситуации), ежедневного использования&lt;br&gt;&lt;br&gt;📦 В комплекте: налобный фонарь + 3 аккумулятора + кабель USB + крепление + упаковка&lt;br&gt;🎁 Тот редкий подарок мужчине, которым реально пользуются каждый день&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, проверяю каждый перед отправкой&lt;br&gt;&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.</t>
+          <t>🙌 Налобник, который включается взмахом руки. Датчик движения + 10 000 люмен + свет до 1000 метров&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Оригинал с диодом PM30 — остерегайтесь слабых копий с нашими фото (коробка может отличаться).&lt;br&gt;&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — жест рукой и мощность луча надо видеть!&lt;br&gt;&lt;br&gt;Руки в перчатках? В грязи? Заняты снастями или инструментом? Просто проведите ладонью перед фонарём — включился. Ещё взмах — выключился. Никаких кнопок на морозе, никакой возни. Один раз попробуете — обычные налобники покажутся прошлым веком. А по мощности это не налобник, а прожектор на лбу: луч достаёт туда, где обычные фонари уже «сдулись». 💪&lt;br&gt;&lt;br&gt;🙌 Датчик движения — управление взмахом руки, идеально в перчатках и на морозе&lt;br&gt;⚡ Яркость до 10 000 люмен — диод PM30 нового поколения&lt;br&gt;📏 Дальность луча — до 1000 метров&lt;br&gt;🔋 3 аккумулятора в комплекте — 6900 мАч суммарно, до 20 часов в эконом-режиме&lt;br&gt;⚡️ Функция Power Bank — подзарядит телефон на природе&lt;br&gt;📊 Дисплей-индикатор заряда — точно знаете остаток&lt;br&gt;🎛 Режимы: максимальный / средний / эконом / стробоскоп / SOS&lt;br&gt;💧 Защита IPX6 — дождь, грязь и пыль не страшны&lt;br&gt;🦾 Ударопрочный корпус, надёжное регулируемое крепление на голову&lt;br&gt;✔️ Идеально для: рыбалки и охоты, походов, стройки и работы, гаража, авто (аварийные ситуации), ежедневного использования&lt;br&gt;&lt;br&gt;📦 В комплекте: налобный фонарь + 3 аккумулятора + кабель USB + крепление + упаковка&lt;br&gt;🎁 Тот редкий подарок мужчине, которым реально пользуются каждый день&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, проверяю каждый перед отправкой&lt;br&gt;&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>🔦 Yemao — фонарь меньше ладони, который светит за большой. 1500 люмен из кармана джинсов&lt;br&gt;✅ Только оригинал Yemao — копии светят тускло и умирают через месяц.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — сравнение размера и яркости впечатляет!&lt;br&gt;&lt;br&gt;Знакомая история: мощный фонарь есть, но он дома — потому что таскать его тяжело. Этот исчезает в кармане джинсов и достаётся не раздумывая. А когда нажимаете кнопку — 1500 люмен, каких ждёшь от фонаря втрое крупнее. Плюс магнит: прилепили под капотом или к батарее — и обе руки в деле. 💪&lt;br&gt;&lt;br&gt;⚡ Яркость до 1500 люмен — уровень «взрослых» фонарей&lt;br&gt;📏 Дальность луча — до 80 метров&lt;br&gt;🎛 6 режимов: максимальный / средний / эконом / стробоскоп / аварийный / красно-синяя вспышка&lt;br&gt;🚨 Красно-синяя вспышка — обозначить себя на трассе при поломке&lt;br&gt;🧲 Магнит + клипса — работа без рук, крепление на карман и кепку&lt;br&gt;🔋 Аккумулятор 14500 в комплекте — до 10 часов работы&lt;br&gt;🔌 Зарядка USB Type-C&lt;br&gt;🦾 Прочный алюминиевый корпус&lt;br&gt;💧 Влагозащита IPX4 — дождь не страшен&lt;br&gt;&lt;br&gt;✔️ Идеально для: EDC (каждый день в кармане), машины, рыбалки, походов, охоты, работы и дома&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь + аккумулятор 14500 + кабель Type-C + инструкция + коробка (готовый подарок 🎁)&lt;br&gt;&lt;br&gt;🎁 Подарок мужчине, которым пользуются каждый день, а не раз в год&lt;br&gt;&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ Новый, каждый проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 Авито Доставка по всей России + СДЭК / Почта / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.</t>
+          <t>🔦 Yemao — фонарь меньше ладони, который светит за большой. 1500 люмен из кармана джинсов&lt;br&gt;✅ Только оригинал Yemao — копии светят тускло и умирают через месяц.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — сравнение размера и яркости впечатляет!&lt;br&gt;&lt;br&gt;Знакомая история: мощный фонарь есть, но он дома — потому что таскать его тяжело. Этот исчезает в кармане джинсов и достаётся не раздумывая. А когда нажимаете кнопку — 1500 люмен, каких ждёшь от фонаря втрое крупнее. Плюс магнит: прилепили под капотом или к батарее — и обе руки в деле. 💪&lt;br&gt;&lt;br&gt;⚡ Яркость до 1500 люмен — уровень «взрослых» фонарей&lt;br&gt;📏 Дальность луча — до 80 метров&lt;br&gt;🎛 6 режимов: максимальный / средний / эконом / стробоскоп / аварийный / красно-синяя вспышка&lt;br&gt;🚨 Красно-синяя вспышка — обозначить себя на трассе при поломке&lt;br&gt;🧲 Магнит + клипса — работа без рук, крепление на карман и кепку&lt;br&gt;🔋 Аккумулятор 14500 в комплекте — до 10 часов работы&lt;br&gt;🔌 Зарядка USB Type-C&lt;br&gt;🦾 Прочный алюминиевый корпус&lt;br&gt;💧 Влагозащита IPX4 — дождь не страшен&lt;br&gt;&lt;br&gt;✔️ Идеально для: EDC (каждый день в кармане), машины, рыбалки, походов, охоты, работы и дома&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь + аккумулятор 14500 + кабель Type-C + инструкция + коробка (готовый подарок 🎁)&lt;br&gt;&lt;br&gt;🎁 Подарок мужчине, которым пользуются каждый день, а не раз в год&lt;br&gt;&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ Новый, каждый проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 Авито Доставка по всей России + СДЭК / Почта / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>🔦 Фонарик аккумуляторный с зажигалкой YEMAO M21 — свет и огонь в одном корпусе. Цвет корпуса может отличаться! Есть разные цвета!&lt;br&gt;&lt;br&gt;EDC-фонарь размером с зажигалку, весит 36 грамм. Сверху светодиод XTE-55, снизу спиральная электроимпульсная зажигалка. Ни газа, ни бензина — заряжается через USB Type-C.&lt;br&gt;&lt;br&gt;🎥 Видео-обзор обязательно к просмотру — поджиг спиралью и все режимы света видно вживую.&lt;br&gt;💸 Скидка 10% при заказе от 2 любых товаров — применяется автоматически.&lt;br&gt;&lt;br&gt;🔥 Почему обычная зажигалка подводит именно тогда, когда нужна&lt;br&gt;&lt;br&gt;На ветру пламя сдувает, на морозе газ густеет и не даёт огня, а бензиновая выветривается за неделю в кармане. Всё это происходит ровно в тот момент, когда надо развести костёр или прикурить на берегу.&lt;br&gt;&lt;br&gt;Спираль M21 раскаляется докрасна — ей всё равно, дует ветер или нет. Пламени, которое можно задуть, здесь просто нет: это ветрозащитная USB-зажигалка без топлива. Заряда хватает примерно на 50 поджигов, а зарядить можно от повербанка.&lt;br&gt;&lt;br&gt;⚡ Характеристики&lt;br&gt;&lt;br&gt;✔️ Светодиод XTE-55 — до 300 люмен, два уровня яркости и стробоскоп&lt;br&gt;✔️ Боковая RGB-панель: белый свет, красный, мигание красный/синий, разноцветная подсветка&lt;br&gt;✔️ Электроимпульсная зажигалка — около 50 поджигов на одном заряде&lt;br&gt;✔️ Работа от 120 до 390 минут в зависимости от режима&lt;br&gt;✔️ Магнит — крепится к металлу, руки свободны&lt;br&gt;✔️ Стальная клипса — карман, кепка, рюкзак, ремень, ключи&lt;br&gt;✔️ Размер 8 × 2,2 см, вес 36 г — не чувствуется в кармане&lt;br&gt;✔️ Корпус ABS + нержавеющая сталь, защита IP54, падение с 1 метра&lt;br&gt;✔️ Встроенный аккумулятор, зарядка USB Type-C&lt;br&gt;&lt;br&gt;🎛 Три источника в одном&lt;br&gt;&lt;br&gt;Переключатель сбоку выбирает, чем пользуетесь: основной луч, боковая RGB-панель или зажигалка. Одна вещь вместо фонарика, зажигалки и сигнальной подсветки.&lt;br&gt;&lt;br&gt;🎯 Где пригодится&lt;br&gt;&lt;br&gt;🏕 Поход и костёр — поджиг на ветру, свет в палатке&lt;br&gt;🎣 Рыбалка — красный свет не сбивает ночное зрение&lt;br&gt;🚗 Автомобиль — примагнитил к капоту, обе руки свободны&lt;br&gt;🔧 Гараж и ремонт — подсветка там, куда не дотянуть лампой&lt;br&gt;🎒 EDC на каждый день — висит на рюкзаке или на ключах как брелок-фонарик&lt;br&gt;🏠 Дом и дача — газовая плита, свечи, мангал&lt;br&gt;&lt;br&gt;🎁 Подарок мужчине, который не ляжет в ящик&lt;br&gt;&lt;br&gt;Курящему, туристу, рыбаку, автомобилисту — вещь, которой пользуются каждый день, а не хранят в коробке.&lt;br&gt;&lt;br&gt;📦 В комплекте&lt;br&gt;&lt;br&gt;Фонарик YEMAO M21&lt;br&gt;Кабель USB Type-C&lt;br&gt;Инструкция на русском&lt;br&gt;Подарочная коробка&lt;br&gt;&lt;br&gt;🔥 Фонарь • зажигалка • RGB • магнит • клипса • Type-C • 36 г&lt;br&gt;&lt;br&gt;⚠️ Спираль во время работы нагревается — это нормально. Детям не давать.&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ Каждый фонарик проверяю перед отправкой&lt;br&gt;📦 В наличии&lt;br&gt;🚚 Отправка в день заказа, доставка по всей России&lt;br&gt;&lt;br&gt;⚡ Нажимайте «Купить с доставкой» — отправлю в день заказа, количество по такой цене ограничено!</t>
+          <t>🔦 Фонарик аккумуляторный с зажигалкой YEMAO M21 — свет и огонь в одном корпусе. Цвет корпуса может отличаться! Есть разные цвета!&lt;br&gt;&lt;br&gt;EDC-фонарь размером с зажигалку, весит 36 грамм. Сверху светодиод XTE-55, снизу спиральная электроимпульсная зажигалка. Ни газа, ни бензина — заряжается через USB Type-C.&lt;br&gt;&lt;br&gt;🎥 Видео-обзор обязательно к просмотру — поджиг спиралью и все режимы света видно вживую.&lt;br&gt;💸 Скидка 10% при заказе от 2 любых товаров — применяется автоматически.&lt;br&gt;&lt;br&gt;🔥 Почему обычная зажигалка подводит именно тогда, когда нужна&lt;br&gt;&lt;br&gt;На ветру пламя сдувает, на морозе газ густеет и не даёт огня, а бензиновая выветривается за неделю в кармане. Всё это происходит ровно в тот момент, когда надо развести костёр или прикурить на берегу.&lt;br&gt;&lt;br&gt;Спираль M21 раскаляется докрасна — ей всё равно, дует ветер или нет. Пламени, которое можно задуть, здесь просто нет: это ветрозащитная USB-зажигалка без топлива. Заряда хватает примерно на 50 поджигов, а зарядить можно от повербанка.&lt;br&gt;&lt;br&gt;⚡ Характеристики&lt;br&gt;&lt;br&gt;✔️ Светодиод XTE-55 — до 300 люмен, два уровня яркости и стробоскоп&lt;br&gt;✔️ Боковая RGB-панель: белый свет, красный, мигание красный/синий, разноцветная подсветка&lt;br&gt;✔️ Электроимпульсная зажигалка — около 50 поджигов на одном заряде&lt;br&gt;✔️ Работа от 120 до 390 минут в зависимости от режима&lt;br&gt;✔️ Магнит — крепится к металлу, руки свободны&lt;br&gt;✔️ Стальная клипса — карман, кепка, рюкзак, ремень, ключи&lt;br&gt;✔️ Размер 8 × 2,2 см, вес 36 г — не чувствуется в кармане&lt;br&gt;✔️ Корпус ABS + нержавеющая сталь, защита IP54, падение с 1 метра&lt;br&gt;✔️ Встроенный аккумулятор, зарядка USB Type-C&lt;br&gt;&lt;br&gt;🎛 Три источника в одном&lt;br&gt;&lt;br&gt;Переключатель сбоку выбирает, чем пользуетесь: основной луч, боковая RGB-панель или зажигалка. Одна вещь вместо фонарика, зажигалки и сигнальной подсветки.&lt;br&gt;&lt;br&gt;🎯 Где пригодится&lt;br&gt;&lt;br&gt;🏕 Поход и костёр — поджиг на ветру, свет в палатке&lt;br&gt;🎣 Рыбалка — красный свет не сбивает ночное зрение&lt;br&gt;🚗 Автомобиль — примагнитил к капоту, обе руки свободны&lt;br&gt;🔧 Гараж и ремонт — подсветка там, куда не дотянуть лампой&lt;br&gt;🎒 EDC на каждый день — висит на рюкзаке или на ключах как брелок-фонарик&lt;br&gt;🏠 Дом и дача — газовая плита, свечи, мангал&lt;br&gt;&lt;br&gt;🎁 Подарок мужчине, который не ляжет в ящик&lt;br&gt;&lt;br&gt;Курящему, туристу, рыбаку, автомобилисту — вещь, которой пользуются каждый день, а не хранят в коробке.&lt;br&gt;&lt;br&gt;📦 В комплекте&lt;br&gt;&lt;br&gt;Фонарик YEMAO M21&lt;br&gt;Кабель USB Type-C&lt;br&gt;Инструкция на русском&lt;br&gt;Подарочная коробка&lt;br&gt;&lt;br&gt;🔥 Фонарь • зажигалка • RGB • магнит • клипса • Type-C • 36 г&lt;br&gt;&lt;br&gt;⚠️ Спираль во время работы нагревается — это нормально. Детям не давать.&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ Каждый фонарик проверяю перед отправкой&lt;br&gt;📦 В наличии&lt;br&gt;🚚 Отправка в день заказа, доставка по всей России&lt;br&gt;&lt;br&gt;⚡ Нажимайте «Купить с доставкой» — отправлю в день заказа, количество по такой цене ограничено!&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -70092,7 +70092,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>💨 Воздуходувка мощнее урагана. Поток 53 м/с — ураган по шкале Бофорта начинается с 33&lt;br&gt;✅ Новинка для России, 2026 год. Аналогов на Авито нет.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — смотрите, что творит этот малыш!&lt;br&gt;&lt;br&gt;Пыль в клавиатуре, песок в багажнике, шерсть под сиденьями, листья на крыльце, снег на машине — всему этому осталось жить до первого нажатия кнопки. Бесщёточный турбо-мотор разгоняет воздух до 53 метров в секунду: это официально сильнее урагана. А режим пылесоса добирает то, что нельзя просто сдуть. 🌪&lt;br&gt;❗️(Бывает версия без фонарика! К ней кладем налобный фонарик в подарок! Воздуходувка та же!)&lt;br&gt;&lt;br&gt;⚡ Бесщёточный турбо-мотор — мощь и долгий ресурс&lt;br&gt;💨 Поток до 53 м/с — сдувает пыль, песок, шерсть, листья, снег&lt;br&gt;🧹 2 в 1: воздуходувка + вакуумный режим — для салона авто, ПК и труднодоступных мест&lt;br&gt;🎚 Плавная регулировка — от лёгкого бриза до полного урагана&lt;br&gt;🔋 Аккумулятор 4000 мАч — до 2,5 часов работы без розетки&lt;br&gt;💡 LED-подсветка + сигнальная лампа — работайте даже в темноте&lt;br&gt;📏 Компактная — лежит в бардачке, заменяет компрессор, пылесос и щётку&lt;br&gt;&lt;br&gt;✔️ Идеально для: продувки ПК и электроники, уборки салона авто, гаража, дачи, сдувания листьев и снега, шерсти домашних животных&lt;br&gt;&lt;br&gt;🆚 Мощнее большинства моделей Stihl, Bosch, Makita, Greenworks, DeWALT, Ryobi, Champion, Worx, Bort — за заметно меньшие деньги&lt;br&gt;&lt;br&gt;🎁 Подарок мужчине, который «сдует» все остальные: автомобилисту, дачнику, айтишнику, любителю техники&lt;br&gt;&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически&lt;br&gt;&lt;br&gt;🏆 РЕАЛЬНАЯ гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс (нужна только Почта — напишите, договоримся!)&lt;br&gt;&lt;br&gt;🔦 Загляните в профиль — там ещё много мощных гаджетов по лучшим ценам!&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.</t>
+          <t>💨 Воздуходувка мощнее урагана. Поток 53 м/с — ураган по шкале Бофорта начинается с 33&lt;br&gt;✅ Новинка для России, 2026 год. Аналогов на Авито нет.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — смотрите, что творит этот малыш!&lt;br&gt;&lt;br&gt;Пыль в клавиатуре, песок в багажнике, шерсть под сиденьями, листья на крыльце, снег на машине — всему этому осталось жить до первого нажатия кнопки. Бесщёточный турбо-мотор разгоняет воздух до 53 метров в секунду: это официально сильнее урагана. А режим пылесоса добирает то, что нельзя просто сдуть. 🌪&lt;br&gt;❗️(Бывает версия без фонарика! К ней кладем налобный фонарик в подарок! Воздуходувка та же!)&lt;br&gt;&lt;br&gt;⚡ Бесщёточный турбо-мотор — мощь и долгий ресурс&lt;br&gt;💨 Поток до 53 м/с — сдувает пыль, песок, шерсть, листья, снег&lt;br&gt;🧹 2 в 1: воздуходувка + вакуумный режим — для салона авто, ПК и труднодоступных мест&lt;br&gt;🎚 Плавная регулировка — от лёгкого бриза до полного урагана&lt;br&gt;🔋 Аккумулятор 4000 мАч — до 2,5 часов работы без розетки&lt;br&gt;💡 LED-подсветка + сигнальная лампа — работайте даже в темноте&lt;br&gt;📏 Компактная — лежит в бардачке, заменяет компрессор, пылесос и щётку&lt;br&gt;&lt;br&gt;✔️ Идеально для: продувки ПК и электроники, уборки салона авто, гаража, дачи, сдувания листьев и снега, шерсти домашних животных&lt;br&gt;&lt;br&gt;🆚 Мощнее большинства моделей Stihl, Bosch, Makita, Greenworks, DeWALT, Ryobi, Champion, Worx, Bort — за заметно меньшие деньги&lt;br&gt;&lt;br&gt;🎁 Подарок мужчине, который «сдует» все остальные: автомобилисту, дачнику, айтишнику, любителю техники&lt;br&gt;&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически&lt;br&gt;&lt;br&gt;🏆 РЕАЛЬНАЯ гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс (нужна только Почта — напишите, договоримся!)&lt;br&gt;&lt;br&gt;🔦 Загляните в профиль — там ещё много мощных гаджетов по лучшим ценам!&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -70917,7 +70917,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>💡 «Маяк» PM60-TG — налобный прожектор, светящий на 3 километра. 10 000 люмен на лбу, руки свободны&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Самый мощный налобник, который вы найдёте на Авито.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — реальная яркость, без фильтров и монтажа!&lt;br&gt;&lt;br&gt;Название «Маяк» — не для красоты. Включаете максимум — и лес, поле или стройплощадка освещены до горизонта, а соседи по берегу думают, что приехала машина с прожектором. При этом обе руки свободны: снасти, инструмент, руль. Один заряд — до 15 часов работы. 💪&lt;br&gt;&lt;br&gt;⚡ Диод PM60-TG «белый лазер» + LED — до 10 000 люмен&lt;br&gt;📏 Луч — до 3000 метров&lt;br&gt;🎛 3 режима: максимальный / экономичный / SOS&lt;br&gt;🔴 Задний красный фонарь — вас видно на трассе и в колонне, безопасность в темноте&lt;br&gt;🔋 3 аккумулятора 18650 в комплекте — до 15 часов от заряда&lt;br&gt;⚡️ Функция Power Bank — подзарядит телефон в походе&lt;br&gt;📊 Индикатор заряда — без сюрпризов&lt;br&gt;💧 Влагозащита IPX6 — дождь, снег, грязь&lt;br&gt;🦾 Ударопрочный корпус, надёжное крепление на голову&lt;br&gt;✔️ Идеально для: рыбалки и охоты, стройки и ремонта, походов, гаража, авто и дачи, работы в темноте&lt;br&gt;📦 В комплекте: фонарь «Маяк» PM60-TG + крепление на голову + 3 аккумулятора 18650 + кабель USB + упаковка&lt;br&gt;🎁 Подарок, которым реально пользуются, а не ставят на полку&lt;br&gt;💸 От 2 штук — скидка 10% автоматически&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю каждый перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.</t>
+          <t>💡 «Маяк» PM60-TG — налобный прожектор, светящий на 3 километра. 10 000 люмен на лбу, руки свободны&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Самый мощный налобник, который вы найдёте на Авито.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — реальная яркость, без фильтров и монтажа!&lt;br&gt;&lt;br&gt;Название «Маяк» — не для красоты. Включаете максимум — и лес, поле или стройплощадка освещены до горизонта, а соседи по берегу думают, что приехала машина с прожектором. При этом обе руки свободны: снасти, инструмент, руль. Один заряд — до 15 часов работы. 💪&lt;br&gt;&lt;br&gt;⚡ Диод PM60-TG «белый лазер» + LED — до 10 000 люмен&lt;br&gt;📏 Луч — до 3000 метров&lt;br&gt;🎛 3 режима: максимальный / экономичный / SOS&lt;br&gt;🔴 Задний красный фонарь — вас видно на трассе и в колонне, безопасность в темноте&lt;br&gt;🔋 3 аккумулятора 18650 в комплекте — до 15 часов от заряда&lt;br&gt;⚡️ Функция Power Bank — подзарядит телефон в походе&lt;br&gt;📊 Индикатор заряда — без сюрпризов&lt;br&gt;💧 Влагозащита IPX6 — дождь, снег, грязь&lt;br&gt;🦾 Ударопрочный корпус, надёжное крепление на голову&lt;br&gt;✔️ Идеально для: рыбалки и охоты, стройки и ремонта, походов, гаража, авто и дачи, работы в темноте&lt;br&gt;📦 В комплекте: фонарь «Маяк» PM60-TG + крепление на голову + 3 аккумулятора 18650 + кабель USB + упаковка&lt;br&gt;🎁 Подарок, которым реально пользуются, а не ставят на полку&lt;br&gt;💸 От 2 штук — скидка 10% автоматически&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю каждый перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -71625,7 +71625,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>🔭 «Титан» — бинокль, в который видно кратеры Луны. Честный рабочий зум 20х и объективы 60 мм&lt;br&gt;✅ Новый, в заводской упаковке. В наличии — отправка сегодня.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — показываю РЕАЛЬНОЕ приближение, без накрученных кратностей!&lt;br&gt;&lt;br&gt;Наведите его вечером на Луну — и увидите кратеры. Днём — лодку на другом берегу, зверя на опушке за километры, детали зданий через весь город. Огромные 60-мм объективы собирают столько света, что картинка остаётся яркой даже в сумерках и на рассвете — в самое ценное время для охотника и рыбака. 🌙&lt;br&gt;&lt;br&gt;❗ ЧЕСТНО О ГЛАВНОМ&lt;br&gt;Рынок завален биноклями «1000x zoom» с чужими фото: мутная дрожащая картинка и бесполезное увеличение. Внешне — похожи. Внутри — пропасть. «Титан» — это настоящая оптическая схема Porro с призмами BaK4: честные рабочие 20 крат, при которых ДЕЙСТВИТЕЛЬНО видно, а не «мыло».&lt;br&gt;&lt;br&gt;⚙️ ХАРАКТЕРИСТИКИ:&lt;br&gt;🔍 Увеличение — до 20х (реальное рабочее), регулируемый зум&lt;br&gt;🔭 Диаметр объективов — 60 мм: максимум света и деталей&lt;br&gt;💎 Призмы BaK4 + просветлённые линзы — чёткость без искажений по краям&lt;br&gt;📏 Дальность наблюдения — до 5 км&lt;br&gt;🌅 Высокая светосила — работает в сумерках и на рассвете&lt;br&gt;🌐 Широкий угол обзора — легко вести движущийся объект&lt;br&gt;🦾 Надёжная конструкция, цвет чёрный, размер 235х205мм, вес 970гр.&lt;br&gt;&lt;br&gt;Модель: 20–180x100, система Porro&lt;br&gt;&lt;br&gt;✔️ Идеально для: охоты и рыбалки, туризма, наблюдения за природой и Луной, стадионов и концертов, города и архитектуры&lt;br&gt;&lt;br&gt;📦 В комплекте: бинокль «Титан» + заводская упаковка&lt;br&gt;&lt;br&gt;🎁 Солидный подарок мужчине или подростку — от такого не отказываются&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;⭐ Довольные покупатели уже в отзывах&lt;br&gt;✅ В наличии, проверяю оптику перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 Авито Доставка по РФ · Москва и МО — возможна встреча 🤝&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.</t>
+          <t>🔭 «Титан» — бинокль, в который видно кратеры Луны. Честный рабочий зум 20х и объективы 60 мм&lt;br&gt;✅ Новый, в заводской упаковке. В наличии — отправка сегодня.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — показываю РЕАЛЬНОЕ приближение, без накрученных кратностей!&lt;br&gt;&lt;br&gt;Наведите его вечером на Луну — и увидите кратеры. Днём — лодку на другом берегу, зверя на опушке за километры, детали зданий через весь город. Огромные 60-мм объективы собирают столько света, что картинка остаётся яркой даже в сумерках и на рассвете — в самое ценное время для охотника и рыбака. 🌙&lt;br&gt;&lt;br&gt;❗ ЧЕСТНО О ГЛАВНОМ&lt;br&gt;Рынок завален биноклями «1000x zoom» с чужими фото: мутная дрожащая картинка и бесполезное увеличение. Внешне — похожи. Внутри — пропасть. «Титан» — это настоящая оптическая схема Porro с призмами BaK4: честные рабочие 20 крат, при которых ДЕЙСТВИТЕЛЬНО видно, а не «мыло».&lt;br&gt;&lt;br&gt;⚙️ ХАРАКТЕРИСТИКИ:&lt;br&gt;🔍 Увеличение — до 20х (реальное рабочее), регулируемый зум&lt;br&gt;🔭 Диаметр объективов — 60 мм: максимум света и деталей&lt;br&gt;💎 Призмы BaK4 + просветлённые линзы — чёткость без искажений по краям&lt;br&gt;📏 Дальность наблюдения — до 5 км&lt;br&gt;🌅 Высокая светосила — работает в сумерках и на рассвете&lt;br&gt;🌐 Широкий угол обзора — легко вести движущийся объект&lt;br&gt;🦾 Надёжная конструкция, цвет чёрный, размер 235х205мм, вес 970гр.&lt;br&gt;&lt;br&gt;Модель: 20–180x100, система Porro&lt;br&gt;&lt;br&gt;✔️ Идеально для: охоты и рыбалки, туризма, наблюдения за природой и Луной, стадионов и концертов, города и архитектуры&lt;br&gt;&lt;br&gt;📦 В комплекте: бинокль «Титан» + заводская упаковка&lt;br&gt;&lt;br&gt;🎁 Солидный подарок мужчине или подростку — от такого не отказываются&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;⭐ Довольные покупатели уже в отзывах&lt;br&gt;✅ В наличии, проверяю оптику перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 Авито Доставка по РФ · Москва и МО — возможна встреча 🤝&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -71747,7 +71747,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>🔭 Бинокль Comet AW-26 20х50 с автофокусом — резкость крутить не нужно&lt;br&gt;&lt;br&gt;Мощный 20-кратный бинокль с объективами 50 мм для охоты, рыбалки и туризма. Поднёс к глазам — и сразу видишь картинку, без возни с колёсиками.&lt;br&gt;&lt;br&gt;🎥 Видео-обзор стоит посмотреть: снято, как он приближает реальные объекты.&lt;br&gt;💸 Скидка 10% при заказе от 2 любых товаров — применяется автоматически.&lt;br&gt;&lt;br&gt;😤 Знакомая история с обычным биноклем&lt;br&gt;&lt;br&gt;Заметили что-то вдалеке, схватили бинокль — а там мутное пятно. Крутите одно колесо, второе, подстраиваете под каждый глаз. Пока навелись — птица улетела, зверь ушёл, момент на поле пропущен.&lt;br&gt;&lt;br&gt;🔍 У Comet AW-26 система автофокуса: наводите на объект и сразу видите его резко. Не нужно настраивать ничего каждый раз — это и отличает его от обычных охотничьих биноклей в той же цене.&lt;br&gt;&lt;br&gt;⚡ Характеристики&lt;br&gt;&lt;br&gt;✔️ Кратность 20х — бинокль дальнего видения, далёкие объекты видно в деталях&lt;br&gt;✔️ Объективы 50 мм — светосильные, работают и днём, и в сумерках&lt;br&gt;✔️ Автофокус — резкость подстраивать не нужно&lt;br&gt;✔️ Поле зрения 168 футов на 1000 ярдов — широкий обзор, удобно вести объект&lt;br&gt;✔️ Просветлённая оптика (coated optics) — меньше бликов, честные цвета&lt;br&gt;✔️ Регулировка расстояния между окулярами — под ваши глаза&lt;br&gt;✔️ Обрезиненный ударопрочный корпус — не скользит в руке&lt;br&gt;✔️ Пылевлагозащита — не боится сырости на природе&lt;br&gt;✔️ Складная конструкция, чехол в комплекте&lt;br&gt;&lt;br&gt;🎯 Где пригодится&lt;br&gt;&lt;br&gt;🌲 Охотничий бинокль — рассмотреть зверя раньше, чем он заметит вас&lt;br&gt;🎣 Рыбалка — читать воду и следить за противоположным берегом&lt;br&gt;🏔 Туризм, походы и альпинизм — панорамы, вершины, дальний берег&lt;br&gt;🏟 Стадион и концерт — видно лица, а не силуэты&lt;br&gt;🦅 Наблюдение за птицами и природой&lt;br&gt;🏡 Дача — посмотреть, что происходит за участком&lt;br&gt;🌌 Луна и звёзды — на 20 кратах видно кратеры&lt;br&gt;&lt;br&gt;🎁 Подарок мужчине, который точно пригодится&lt;br&gt;&lt;br&gt;Охотнику, рыбаку, туристу, отцу или деду — бинокль достают из чехла, а не убирают в шкаф.&lt;br&gt;&lt;br&gt;📦 В комплекте&lt;br&gt;&lt;br&gt;Бинокль Comet AW-26 20х50&lt;br&gt;Чехол&lt;br&gt;Ремешок на шею&lt;br&gt;Крышка окуляров и 2 крышки объективов&lt;br&gt;Салфетка для чистки линз&lt;br&gt;Инструкция и упаковка&lt;br&gt;&lt;br&gt;🔥 20 крат • объектив 50 мм • автофокус • просветлённая оптика • обрезиненный корпус • чехол&lt;br&gt;&lt;br&gt;Мощность профессионального бинокля без сложной настройки — поднял и смотришь.&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ Каждый бинокль проверяю перед отправкой&lt;br&gt;📦 В наличии&lt;br&gt;🚚 Отправка в день заказа, доставка по всей России&lt;br&gt;&lt;br&gt;⚠️ Не смотреть через бинокль на солнце — можно повредить зрение.&lt;br&gt;&lt;br&gt;⚡ Нажимайте «Купить с доставкой» — отправлю в день заказа, количество по этой цене ограничено!</t>
+          <t>🔭 Бинокль Comet AW-26 20х50 с автофокусом — резкость крутить не нужно&lt;br&gt;&lt;br&gt;Мощный 20-кратный бинокль с объективами 50 мм для охоты, рыбалки и туризма. Поднёс к глазам — и сразу видишь картинку, без возни с колёсиками.&lt;br&gt;&lt;br&gt;🎥 Видео-обзор стоит посмотреть: снято, как он приближает реальные объекты.&lt;br&gt;💸 Скидка 10% при заказе от 2 любых товаров — применяется автоматически.&lt;br&gt;&lt;br&gt;😤 Знакомая история с обычным биноклем&lt;br&gt;&lt;br&gt;Заметили что-то вдалеке, схватили бинокль — а там мутное пятно. Крутите одно колесо, второе, подстраиваете под каждый глаз. Пока навелись — птица улетела, зверь ушёл, момент на поле пропущен.&lt;br&gt;&lt;br&gt;🔍 У Comet AW-26 система автофокуса: наводите на объект и сразу видите его резко. Не нужно настраивать ничего каждый раз — это и отличает его от обычных охотничьих биноклей в той же цене.&lt;br&gt;&lt;br&gt;⚡ Характеристики&lt;br&gt;&lt;br&gt;✔️ Кратность 20х — бинокль дальнего видения, далёкие объекты видно в деталях&lt;br&gt;✔️ Объективы 50 мм — светосильные, работают и днём, и в сумерках&lt;br&gt;✔️ Автофокус — резкость подстраивать не нужно&lt;br&gt;✔️ Поле зрения 168 футов на 1000 ярдов — широкий обзор, удобно вести объект&lt;br&gt;✔️ Просветлённая оптика (coated optics) — меньше бликов, честные цвета&lt;br&gt;✔️ Регулировка расстояния между окулярами — под ваши глаза&lt;br&gt;✔️ Обрезиненный ударопрочный корпус — не скользит в руке&lt;br&gt;✔️ Пылевлагозащита — не боится сырости на природе&lt;br&gt;✔️ Складная конструкция, чехол в комплекте&lt;br&gt;&lt;br&gt;🎯 Где пригодится&lt;br&gt;&lt;br&gt;🌲 Охотничий бинокль — рассмотреть зверя раньше, чем он заметит вас&lt;br&gt;🎣 Рыбалка — читать воду и следить за противоположным берегом&lt;br&gt;🏔 Туризм, походы и альпинизм — панорамы, вершины, дальний берег&lt;br&gt;🏟 Стадион и концерт — видно лица, а не силуэты&lt;br&gt;🦅 Наблюдение за птицами и природой&lt;br&gt;🏡 Дача — посмотреть, что происходит за участком&lt;br&gt;🌌 Луна и звёзды — на 20 кратах видно кратеры&lt;br&gt;&lt;br&gt;🎁 Подарок мужчине, который точно пригодится&lt;br&gt;&lt;br&gt;Охотнику, рыбаку, туристу, отцу или деду — бинокль достают из чехла, а не убирают в шкаф.&lt;br&gt;&lt;br&gt;📦 В комплекте&lt;br&gt;&lt;br&gt;Бинокль Comet AW-26 20х50&lt;br&gt;Чехол&lt;br&gt;Ремешок на шею&lt;br&gt;Крышка окуляров и 2 крышки объективов&lt;br&gt;Салфетка для чистки линз&lt;br&gt;Инструкция и упаковка&lt;br&gt;&lt;br&gt;🔥 20 крат • объектив 50 мм • автофокус • просветлённая оптика • обрезиненный корпус • чехол&lt;br&gt;&lt;br&gt;Мощность профессионального бинокля без сложной настройки — поднял и смотришь.&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ Каждый бинокль проверяю перед отправкой&lt;br&gt;📦 В наличии&lt;br&gt;🚚 Отправка в день заказа, доставка по всей России&lt;br&gt;&lt;br&gt;⚠️ Не смотреть через бинокль на солнце — можно повредить зрение.&lt;br&gt;&lt;br&gt;⚡ Нажимайте «Купить с доставкой» — отправлю в день заказа, количество по этой цене ограничено!&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -71869,7 +71869,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>🦅 «Орёл» 80×80 — бинокль с дальномерной сеткой и честным увеличением 30х. Крупные объекты видны за 15 км&lt;br&gt;✅ Прямые поставки — без наценок и посредников.&lt;br&gt;🔥 Напишите — пришлю видео реальной картинки через окуляры!&lt;br&gt;&lt;br&gt;Огромные 80-мм линзы — главный козырь «Орла»: они собирают максимум света, поэтому картинка остаётся яркой в сумерках и на рассвете, когда зверь выходит кормиться, а обычные бинокли уже «слепнут». Детально рассматривайте объекты до 1,5 км, крупные — корабли, вышки, склоны — за 15 км. А дальномерная сетка на правом окуляре позволяет прикинуть дистанцию до цели — фишка, за которую этот бинокль любят охотники. 🎯&lt;br&gt;&lt;br&gt;🔍 Увеличение 30х — честное рабочее, без «накрученных» цифр&lt;br&gt;🔭 Объективы 80 мм — максимум света, уверенная работа в сумерках&lt;br&gt;📐 Дальномерная сетка на правом окуляре — оценка расстояния до объекта&lt;br&gt;💎 Призмы Porro + стекло BaK-4 — чистое светлое изображение&lt;br&gt;🌈 Многослойное просветление FMC — яркие натуральные цвета&lt;br&gt;👓 Регулировка фокуса и диоптрий ±3 — настройка под ваше зрение, работает и в очках&lt;br&gt;💧 Влагозащищённый ударопрочный корпус, защита от запотевания — дождь, снег, бездорожье&lt;br&gt;🇩🇪 Оптика немецкого уровня качества&lt;br&gt;&lt;br&gt;✔️ Идеально для: охоты и рыбалки, туризма, наблюдения за природой, стадионов, работы на местности&lt;br&gt;&lt;br&gt;📦 В комплекте: бинокль «Орёл» 80×80 + чехол + ремешок&lt;br&gt;&lt;br&gt;🎁 Солидный подарок мужчине — на 23 февраля, юбилей, день рождения, профессиональный праздник&lt;br&gt;&lt;br&gt;💸 От 2 штук — скидка 10% автоматически в корзине&lt;br&gt;&lt;br&gt;🏆 Гарантия качества · Официальная сертификация&lt;br&gt;✅ В наличии, проверяю оптику перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 Авито Доставка по РФ / самовывоз&lt;br&gt;&lt;br&gt;🔦 Загляните в профиль — там ещё много оптики и мощных фонарей по лучшим ценам!&lt;br&gt;☎️ Есть вопросы? Пишите — проконсультирую.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.</t>
+          <t>🦅 «Орёл» 80×80 — бинокль с дальномерной сеткой и честным увеличением 30х. Крупные объекты видны за 15 км&lt;br&gt;✅ Прямые поставки — без наценок и посредников.&lt;br&gt;🔥 Напишите — пришлю видео реальной картинки через окуляры!&lt;br&gt;&lt;br&gt;Огромные 80-мм линзы — главный козырь «Орла»: они собирают максимум света, поэтому картинка остаётся яркой в сумерках и на рассвете, когда зверь выходит кормиться, а обычные бинокли уже «слепнут». Детально рассматривайте объекты до 1,5 км, крупные — корабли, вышки, склоны — за 15 км. А дальномерная сетка на правом окуляре позволяет прикинуть дистанцию до цели — фишка, за которую этот бинокль любят охотники. 🎯&lt;br&gt;&lt;br&gt;🔍 Увеличение 30х — честное рабочее, без «накрученных» цифр&lt;br&gt;🔭 Объективы 80 мм — максимум света, уверенная работа в сумерках&lt;br&gt;📐 Дальномерная сетка на правом окуляре — оценка расстояния до объекта&lt;br&gt;💎 Призмы Porro + стекло BaK-4 — чистое светлое изображение&lt;br&gt;🌈 Многослойное просветление FMC — яркие натуральные цвета&lt;br&gt;👓 Регулировка фокуса и диоптрий ±3 — настройка под ваше зрение, работает и в очках&lt;br&gt;💧 Влагозащищённый ударопрочный корпус, защита от запотевания — дождь, снег, бездорожье&lt;br&gt;🇩🇪 Оптика немецкого уровня качества&lt;br&gt;&lt;br&gt;✔️ Идеально для: охоты и рыбалки, туризма, наблюдения за природой, стадионов, работы на местности&lt;br&gt;&lt;br&gt;📦 В комплекте: бинокль «Орёл» 80×80 + чехол + ремешок&lt;br&gt;&lt;br&gt;🎁 Солидный подарок мужчине — на 23 февраля, юбилей, день рождения, профессиональный праздник&lt;br&gt;&lt;br&gt;💸 От 2 штук — скидка 10% автоматически в корзине&lt;br&gt;&lt;br&gt;🏆 Гарантия качества · Официальная сертификация&lt;br&gt;✅ В наличии, проверяю оптику перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 Авито Доставка по РФ / самовывоз&lt;br&gt;&lt;br&gt;🔦 Загляните в профиль — там ещё много оптики и мощных фонарей по лучшим ценам!&lt;br&gt;☎️ Есть вопросы? Пишите — проконсультирую.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -71991,7 +71991,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>🔭 «Агент» — бинокль-малыш, который видит за километр. Зум х15 в корпусе размером с ладонь&lt;br&gt;&lt;br&gt;✅ Аналогов на Авито нет. Осторожно: наши видео копируют и высылают дешёвые подделки.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — приближение показано вживую! (Цвет линз может отличаться)&lt;br&gt;&lt;br&gt;Большой бинокль вечно остаётся дома — тяжёлый, громоздкий, жалко таскать. «Агент» живёт в кармане куртки и достаётся за секунду: номер машины, птица на дереве, поплавок на том берегу — всё как на ладони. Приближает как серьёзная оптика, а весит как смартфон. 😎&lt;br&gt;&lt;br&gt;🔍 Увеличение х15 — детали видны на расстоянии до 1 км&lt;br&gt;📏 Размер с ладонь — карман куртки, бардачок, боковой карман рюкзака&lt;br&gt;🌇 Работает в сумерках — многослойное просветление линз даёт яркую картинку при слабом свете&lt;br&gt;💧 Линзы не запотевают&lt;br&gt;🦾 Корпус ABS + резина — переживёт падения, дождь и рюкзачную жизнь&lt;br&gt;&lt;br&gt;👀 КОМУ ЗАЙДЁТ:&lt;br&gt;🎣 Рыбакам и охотникам — заметите поклёвку и дичь раньше других&lt;br&gt;⚽ Болельщикам — билет на галёрку, обзор как с VIP-трибуны&lt;br&gt;🌍 Туристам — вся оптика в кармане вместо килограммового БПЦ на шее&lt;br&gt;🚢 На природе и в путешествиях — корабли, горы, архитектура в деталях&lt;br&gt;👦 Подросткам — безопасный и по-настоящему увлекательный, лучше очередной игрушки&lt;br&gt;📦 В комплекте: бинокль «Агент» + чехол + шнурок на руку/шею + салфетка для линз + инструкция&lt;br&gt;🎯 Это реальная оптика, а не сувенир: доступная альтернатива Veber, Levenhuk, Nikon, Bushnell и советских БПЦ.&lt;br&gt;&lt;br&gt;🎁 Готовый подарок мужчине или подростку — на 23 февраля, день рождения или просто так&lt;br&gt;&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю оптику перед отправкой&lt;br&gt;&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.</t>
+          <t>🔭 «Агент» — бинокль-малыш, который видит за километр. Зум х15 в корпусе размером с ладонь&lt;br&gt;&lt;br&gt;✅ Аналогов на Авито нет. Осторожно: наши видео копируют и высылают дешёвые подделки.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — приближение показано вживую! (Цвет линз может отличаться)&lt;br&gt;&lt;br&gt;Большой бинокль вечно остаётся дома — тяжёлый, громоздкий, жалко таскать. «Агент» живёт в кармане куртки и достаётся за секунду: номер машины, птица на дереве, поплавок на том берегу — всё как на ладони. Приближает как серьёзная оптика, а весит как смартфон. 😎&lt;br&gt;&lt;br&gt;🔍 Увеличение х15 — детали видны на расстоянии до 1 км&lt;br&gt;📏 Размер с ладонь — карман куртки, бардачок, боковой карман рюкзака&lt;br&gt;🌇 Работает в сумерках — многослойное просветление линз даёт яркую картинку при слабом свете&lt;br&gt;💧 Линзы не запотевают&lt;br&gt;🦾 Корпус ABS + резина — переживёт падения, дождь и рюкзачную жизнь&lt;br&gt;&lt;br&gt;👀 КОМУ ЗАЙДЁТ:&lt;br&gt;🎣 Рыбакам и охотникам — заметите поклёвку и дичь раньше других&lt;br&gt;⚽ Болельщикам — билет на галёрку, обзор как с VIP-трибуны&lt;br&gt;🌍 Туристам — вся оптика в кармане вместо килограммового БПЦ на шее&lt;br&gt;🚢 На природе и в путешествиях — корабли, горы, архитектура в деталях&lt;br&gt;👦 Подросткам — безопасный и по-настоящему увлекательный, лучше очередной игрушки&lt;br&gt;📦 В комплекте: бинокль «Агент» + чехол + шнурок на руку/шею + салфетка для линз + инструкция&lt;br&gt;🎯 Это реальная оптика, а не сувенир: доступная альтернатива Veber, Levenhuk, Nikon, Bushnell и советских БПЦ.&lt;br&gt;&lt;br&gt;🎁 Готовый подарок мужчине или подростку — на 23 февраля, день рождения или просто так&lt;br&gt;&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю оптику перед отправкой&lt;br&gt;&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">

--- a/ilya_feed.xlsx
+++ b/ilya_feed.xlsx
@@ -2409,7 +2409,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>🎁 К каждому заказу — налобный фонарик в ПОДАРОК!&lt;br&gt;🔥ЦЕНА ДО КОНЦА НЕДЕЛИ (2350 вместо 2990)!!!🔥&lt;br&gt;&lt;br&gt;🔥 Фонарь РМ60-TG — тот самый СТРАХ ДРОНОВ. 5000 метров белого лазера в твоих руках&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Аналогов по мощности на Авито — единицы.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — это НЕЧТО!&lt;br&gt;&lt;br&gt;❓ Почему «Страх Дронов»? Всё просто: луч бьёт на 5 000 метров — выше, чем летает любой коптер. Направьте «Колосса» в ночное небо — и всё, что там висит, окажется как на ладони. 8 000 люмен белого лазера не оставляют дрону шансов остаться незамеченным, а его камере — что-то разглядеть против луча.&lt;br&gt;Когда включаешь первый раз в темноте — понимаешь, что всё остальное было игрушками. Луч уходит за горизонт. Вас будут спрашивать только одно: где купил? 😅&lt;br&gt;&lt;br&gt;🔦 Диод PM60-TG «Белый лазер» — до 8 000 люмен&lt;br&gt;📏 Дальность луча — 5 000 метров&lt;br&gt;🔋 4 аккумулятора 18650 в комплекте — до 8 часов работы&lt;br&gt;🔌 Зарядка USB Type-C (кабель в комплекте)&lt;br&gt;🔍 Zoom-фокусировка — от широкого пятна до узкого «лазерного» луча&lt;br&gt;💧 Защита IPX6 — ливень и грязь не страшны&lt;br&gt;🦾 Корпус из авиационного алюминия — выдержит падение&lt;br&gt;🧲 Светящиеся ручки — легко найти в полной темноте&lt;br&gt;📊 Индикатор заряда — всегда знаешь, сколько осталось&lt;br&gt;&lt;br&gt;⚡ 5 режимов: Турбо / Яркий / Умеренный / Экономичный / Стробоскоп&lt;br&gt;✔️ Идеально для: наблюдения за небом, охраны объектов, рыбалки, охоты, туризма, кемпинга, ремонта, дачи&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь «Колосс» + 4 аккумулятора 18650 + кабель Type-C + налобный фонарик в подарок 🎁&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">🎁 К каждому заказу — налобный фонарик в ПОДАРОК!&lt;br&gt;🔥ЦЕНА ДО КОНЦА НЕДЕЛИ (2350 вместо 2990)!!!🔥&lt;br&gt;&lt;br&gt;🔥 Фонарь РМ60-TG — тот самый СТРАХ ДРОНОВ. 5000 метров белого лазера в твоих руках&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Аналогов по мощности на Авито — единицы.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — это НЕЧТО!&lt;br&gt;&lt;br&gt;❓ Почему «Страх Дронов»? Всё просто: луч бьёт на 5 000 метров — выше, чем летает любой коптер. Направьте «Колосса» в ночное небо — и всё, что там висит, окажется как на ладони. 8 000 люмен белого лазера не оставляют дрону шансов остаться незамеченным, а его камере — что-то разглядеть против луча.&lt;br&gt;Когда включаешь первый раз в темноте — понимаешь, что всё остальное было игрушками. Луч уходит за горизонт. Вас будут спрашивать только одно: где купил? 😅&lt;br&gt;&lt;br&gt;🔦 Диод PM60-TG «Белый лазер» — до 8 000 люмен&lt;br&gt;📏 Дальность луча — 5 000 метров&lt;br&gt;🔋 4 аккумулятора 18650 в комплекте — до 8 часов работы&lt;br&gt;🔌 Зарядка USB Type-C (кабель в комплекте)&lt;br&gt;🔍 Zoom-фокусировка — от широкого пятна до узкого «лазерного» луча&lt;br&gt;💧 Защита IPX6 — ливень и грязь не страшны&lt;br&gt;🦾 Корпус из авиационного алюминия — выдержит падение&lt;br&gt;🧲 Светящиеся ручки — легко найти в полной темноте&lt;br&gt;📊 Индикатор заряда — всегда знаешь, сколько осталось&lt;br&gt;&lt;br&gt;⚡ 5 режимов: Турбо / Яркий / Умеренный / Экономичный / Стробоскоп&lt;br&gt;✔️ Идеально для: наблюдения за небом, охраны объектов, рыбалки, охоты, туризма, кемпинга, ремонта, дачи&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь «Колосс» + 4 аккумулятора 18650 + кабель Type-C + налобный фонарик в подарок 🎁&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>🚗 Yemao A200 — фонарь с дальним и ближним светом, как у автомобиля. 5200 люмен двойной системы Dual-Core&lt;br&gt;✅ Новинка Yemao Japan. Аналог SK-05 Pro — в 7 раз дешевле.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — на турбо-режиме он прожигает картон, снято вживую!&lt;br&gt;&lt;br&gt;У машины не зря два света: дальний пробивает дорогу вперёд, ближний заливает всё вокруг. Этот фонарь устроен так же — прожектор SST36 бьёт вдаль, панель SLWAV4×3 даёт широкую заливку, и работать они могут ОДНОВРЕМЕННО. Для каждого света — своя кнопка (на кнопке прожектора — фирменный котик 🐱, покупатели в восторге). По цена/качеству спокойно спорит с Fenix, Olight и Nitecore. 😎&lt;br&gt;&lt;br&gt;🔦 Dual-Light — до 5200 люмен: дальний + ближний, по отдельности или вместе&lt;br&gt;🎛 29 режимов: стробоскоп, SOS, комбинированный свет, RGB-подсветка с эффектами&lt;br&gt;🎮 Две отдельные кнопки — мгновенный доступ без перелистывания меню&lt;br&gt;🔋 Аккумулятор 5600 мАч — от 4 до 100 часов работы в зависимости от режима&lt;br&gt;🔌 Быстрая зарядка USB Type-C (~3 часа) + дисплей уровня заряда&lt;br&gt;🧲 Магнит в хвосте — крепится к капоту и любому металлу&lt;br&gt;🦾 Авиационный алюминий, падение до 1 м, влагозащита IPX4&lt;br&gt;📏 Формат EDC — 113×49×26 мм, помещается в карман куртки&lt;br&gt;&lt;br&gt;✔️ Идеально для: авто (лучший фонарь в бардачок), рыбалки, охоты, гаража, кемпинга, охраны, EDC&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь Yemao A200 + кабель USB-C&lt;br&gt;&lt;br&gt;🎁 Эффектный подарок мужчине — вау-эффект с первого включения&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ Объявление активно = товар в наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">🚗 Yemao A200 — фонарь с дальним и ближним светом, как у автомобиля. 5200 люмен двойной системы Dual-Core&lt;br&gt;✅ Новинка Yemao Japan. Аналог SK-05 Pro — в 7 раз дешевле.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — на турбо-режиме он прожигает картон, снято вживую!&lt;br&gt;&lt;br&gt;У машины не зря два света: дальний пробивает дорогу вперёд, ближний заливает всё вокруг. Этот фонарь устроен так же — прожектор SST36 бьёт вдаль, панель SLWAV4×3 даёт широкую заливку, и работать они могут ОДНОВРЕМЕННО. Для каждого света — своя кнопка (на кнопке прожектора — фирменный котик 🐱, покупатели в восторге). По цена/качеству спокойно спорит с Fenix, Olight и Nitecore. 😎&lt;br&gt;&lt;br&gt;🔦 Dual-Light — до 5200 люмен: дальний + ближний, по отдельности или вместе&lt;br&gt;🎛 29 режимов: стробоскоп, SOS, комбинированный свет, RGB-подсветка с эффектами&lt;br&gt;🎮 Две отдельные кнопки — мгновенный доступ без перелистывания меню&lt;br&gt;🔋 Аккумулятор 5600 мАч — от 4 до 100 часов работы в зависимости от режима&lt;br&gt;🔌 Быстрая зарядка USB Type-C (~3 часа) + дисплей уровня заряда&lt;br&gt;🧲 Магнит в хвосте — крепится к капоту и любому металлу&lt;br&gt;🦾 Авиационный алюминий, падение до 1 м, влагозащита IPX4&lt;br&gt;📏 Формат EDC — 113×49×26 мм, помещается в карман куртки&lt;br&gt;&lt;br&gt;✔️ Идеально для: авто (лучший фонарь в бардачок), рыбалки, охоты, гаража, кемпинга, охраны, EDC&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь Yemao A200 + кабель USB-C&lt;br&gt;&lt;br&gt;🎁 Эффектный подарок мужчине — вау-эффект с первого включения&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ Объявление активно = товар в наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>🧰 Yemao M31 — швейцарский нож в мире фонарей. 16 режимов, 3 кнопки, магнит, крюк и даже линейка&lt;br&gt;✅ Новинка 2026 года. Только оригинал Yemao — остерегайтесь дешёвых копий.&lt;br&gt;&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — за минуту он делает больше, чем обычный фонарь за всю жизнь!&lt;br&gt;&lt;br&gt;🎨 Цвет корпуса — сюрприз: оранжевый, зелёный, серый или чёрный. Напишите в отзыве, какой достался вам 😉&lt;br&gt;Обычный фонарь умеет светить. Этот — светит на 95 метров, примагничивается к капоту, подвешивается за крюк к палатке, цепляется на кепку вместо налобника, встаёт на руль велосипеда, меняет цвет как световой меч и измеряет детали встроенной линейкой. И всё это — 75 грамм в кармане. &lt;br&gt;&lt;br&gt;Один раз попользуетесь — и уже не поймёте, как жили без него. 😅&lt;br&gt;💡 Диод P50 — до 680 люмен, сфокусированный луч до 95 метров&lt;br&gt;🎛 16 режимов, 3 отдельные кнопки — мгновенный доступ без перелистывания&lt;br&gt;🌈 RGB-панель: красный (ночное зрение) / синий (аварийный сигнал) / зелёный (охота) / тёплый белый (уютный свет в лагере)&lt;br&gt;⚠️ Стробоскоп — привлечь внимание или обозначить себя на дороге&lt;br&gt;🧲 Мощный магнит в хвосте — к капоту, гаражной балке, любому металлу&lt;br&gt;🪝 Складной крюк — подвесить в палатке или на ветку&lt;br&gt;📎 Зажим-трансформер — на карман, кепку или рюкзак&lt;br&gt;🚴 Велокрепление В КОМПЛЕКТЕ — готовый велофонарь&lt;br&gt;📏 Встроенная линейка 10 см — замер без поисков рулетки&lt;br&gt;🔋 Аккумулятор 1000 мАч — до 12 часов работы, индикатор заряда&lt;br&gt;🔌 Зарядка USB Type-C&lt;br&gt;&lt;br&gt;🦾 Алюминиевый сплав, вес 75 г, падение с 1 м, влагозащита IPX4&lt;br&gt;✔️ Идеально для: EDC (каждый день с собой), велосипеда, гаража и ремонта, кемпинга, рыбалки, авто (аварийный свет), прогулок с собакой&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь M31 + кабель Type-C + велокрепление + инструкция + подарочная коробка 🎁 — готовый подарок мужчине&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически. Себе и в подарок!&lt;br&gt;🏆 Настоящая гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, каждый проверяю лично перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">🧰 Yemao M31 — швейцарский нож в мире фонарей. 16 режимов, 3 кнопки, магнит, крюк и даже линейка&lt;br&gt;✅ Новинка 2026 года. Только оригинал Yemao — остерегайтесь дешёвых копий.&lt;br&gt;&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — за минуту он делает больше, чем обычный фонарь за всю жизнь!&lt;br&gt;&lt;br&gt;🎨 Цвет корпуса — сюрприз: оранжевый, зелёный, серый или чёрный. Напишите в отзыве, какой достался вам 😉&lt;br&gt;Обычный фонарь умеет светить. Этот — светит на 95 метров, примагничивается к капоту, подвешивается за крюк к палатке, цепляется на кепку вместо налобника, встаёт на руль велосипеда, меняет цвет как световой меч и измеряет детали встроенной линейкой. И всё это — 75 грамм в кармане. &lt;br&gt;&lt;br&gt;Один раз попользуетесь — и уже не поймёте, как жили без него. 😅&lt;br&gt;💡 Диод P50 — до 680 люмен, сфокусированный луч до 95 метров&lt;br&gt;🎛 16 режимов, 3 отдельные кнопки — мгновенный доступ без перелистывания&lt;br&gt;🌈 RGB-панель: красный (ночное зрение) / синий (аварийный сигнал) / зелёный (охота) / тёплый белый (уютный свет в лагере)&lt;br&gt;⚠️ Стробоскоп — привлечь внимание или обозначить себя на дороге&lt;br&gt;🧲 Мощный магнит в хвосте — к капоту, гаражной балке, любому металлу&lt;br&gt;🪝 Складной крюк — подвесить в палатке или на ветку&lt;br&gt;📎 Зажим-трансформер — на карман, кепку или рюкзак&lt;br&gt;🚴 Велокрепление В КОМПЛЕКТЕ — готовый велофонарь&lt;br&gt;📏 Встроенная линейка 10 см — замер без поисков рулетки&lt;br&gt;🔋 Аккумулятор 1000 мАч — до 12 часов работы, индикатор заряда&lt;br&gt;🔌 Зарядка USB Type-C&lt;br&gt;&lt;br&gt;🦾 Алюминиевый сплав, вес 75 г, падение с 1 м, влагозащита IPX4&lt;br&gt;✔️ Идеально для: EDC (каждый день с собой), велосипеда, гаража и ремонта, кемпинга, рыбалки, авто (аварийный свет), прогулок с собакой&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь M31 + кабель Type-C + велокрепление + инструкция + подарочная коробка 🎁 — готовый подарок мужчине&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически. Себе и в подарок!&lt;br&gt;🏆 Настоящая гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, каждый проверяю лично перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>🥉 Yemao F40CU — фонарь из ЦЕЛЬНОЙ МЕДИ. 1200 люмен в корпусе, который с годами становится только красивее&lt;br&gt;✅ Оригинал Yemao. Таких фонарей на Авито — единицы.&lt;br&gt;🔥 Напишите — пришлю видео реальной яркости!&lt;br&gt;&lt;br&gt;Медь — металл с характером. Она тяжело и приятно лежит в руке, быстро отводит тепло от диода (фонарь может дольше работать в турбо), а со временем покрывается благородной патиной — через год у вас будет фонарь, какого нет больше ни у кого. Это вещь уровня медных Zippo и кастомных ножей — только ещё и светит как карманный прожектор. 😎&lt;br&gt;&lt;br&gt;🥉 Корпус — цельная медь: премиальный вид + лучшее охлаждение диода&lt;br&gt;⚡ Яркость до 1200 люмен, дальность до 200 метров&lt;br&gt;🎛 8 режимов: от «лунного» ночника до турбо + SOS, стробоскоп, красная вспышка&lt;br&gt;🧲 Магнит в хвосте — крепится к любому металлу, работайте двумя руками&lt;br&gt;🔋 Аккумулятор 16340 в комплекте — до 6 часов работы&lt;br&gt;🔌 Зарядка USB Type-C за 3,5 часа&lt;br&gt;🛡 Защита от перегрева и переполюсовки — умная электроника бережёт фонарь&lt;br&gt;💧 Влагозащита IP66 — ливень не страшен&lt;br&gt;🦾 Ударопрочность до 1,5 метра&lt;br&gt;🏮 Абажур-рассеиватель в комплекте — превращает фонарь в лампу для палатки&lt;br&gt;&lt;br&gt;✔️ Идеально для: EDC-коллекции, рыбалки, походов, работы, дома — и как статусная вещь в кармане&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь F40CU + аккумулятор 16340 + кабель Type-C + абажур-рассеиватель + инструкция + подарочная коробка&lt;br&gt;&lt;br&gt;🎁 Тот самый подарок мужчине, у которого «всё есть» — медь решает&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">🥉 Yemao F40CU — фонарь из ЦЕЛЬНОЙ МЕДИ. 1200 люмен в корпусе, который с годами становится только красивее&lt;br&gt;✅ Оригинал Yemao. Таких фонарей на Авито — единицы.&lt;br&gt;🔥 Напишите — пришлю видео реальной яркости!&lt;br&gt;&lt;br&gt;Медь — металл с характером. Она тяжело и приятно лежит в руке, быстро отводит тепло от диода (фонарь может дольше работать в турбо), а со временем покрывается благородной патиной — через год у вас будет фонарь, какого нет больше ни у кого. Это вещь уровня медных Zippo и кастомных ножей — только ещё и светит как карманный прожектор. 😎&lt;br&gt;&lt;br&gt;🥉 Корпус — цельная медь: премиальный вид + лучшее охлаждение диода&lt;br&gt;⚡ Яркость до 1200 люмен, дальность до 200 метров&lt;br&gt;🎛 8 режимов: от «лунного» ночника до турбо + SOS, стробоскоп, красная вспышка&lt;br&gt;🧲 Магнит в хвосте — крепится к любому металлу, работайте двумя руками&lt;br&gt;🔋 Аккумулятор 16340 в комплекте — до 6 часов работы&lt;br&gt;🔌 Зарядка USB Type-C за 3,5 часа&lt;br&gt;🛡 Защита от перегрева и переполюсовки — умная электроника бережёт фонарь&lt;br&gt;💧 Влагозащита IP66 — ливень не страшен&lt;br&gt;🦾 Ударопрочность до 1,5 метра&lt;br&gt;🏮 Абажур-рассеиватель в комплекте — превращает фонарь в лампу для палатки&lt;br&gt;&lt;br&gt;✔️ Идеально для: EDC-коллекции, рыбалки, походов, работы, дома — и как статусная вещь в кармане&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь F40CU + аккумулятор 16340 + кабель Type-C + абажур-рассеиватель + инструкция + подарочная коробка&lt;br&gt;&lt;br&gt;🎁 Тот самый подарок мужчине, у которого «всё есть» — медь решает&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>🔑 Yemao M02X — фонарик-брелок, после которого большой фонарь остаётся дома. 280 люмен + УФ на связке ключей&lt;br&gt;✅ Новинка 2026 года. Покупатели берут сразу по 2–3 штуки — себе и в подарок.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — не поверите, что ТАК светит брелок!&lt;br&gt;&lt;br&gt;Правило фонарей простое: лучший фонарь — тот, который с собой. Большой остаётся в ящике, а этот малыш живёт на ключах и оказывается в руке за секунду: тёмный подъезд, замочная скважина, упавшие под сиденье ключи, щиток в гараже. Двойной клик — и 280 люмен турбо-режима бьют на 30 метров. Для брелока это просто неприлично много. 😅&lt;br&gt;&lt;br&gt;⚡ До 280 люмен — турбо двойным нажатием&lt;br&gt;📏 Дальность — до 30 метров&lt;br&gt;🟣 УФ-режим — проверка купюр и документов прямо на кассе&lt;br&gt;🎛 Режимы: яркий / эконом / стробоскоп / SOS&lt;br&gt;🔋 До 22 часов работы в экономе&lt;br&gt;🔌 Зарядка USB Type-C за ~2 часа — никаких батареек, зарядил и забыл&lt;br&gt;🦾 Авиационный алюминий — падения до 1,5 м переживёт&lt;br&gt;💧 Влагозащита IP44 — дождь не помеха&lt;br&gt;🔑 Крепится на ключи, молнию рюкзака, шлёвку джинсов&lt;br&gt;&lt;br&gt;✔️ Идеально: на ключи, в машину, на рыбалку и в поход, на вело-прогулки, дома в ящик у двери&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарик Yemao M02X + кабель Type-C + упаковка&lt;br&gt;&lt;br&gt;🎁 Лучший недорогой подарок мужчине — автомобилисту, туристу и «тому, у кого всё есть». Дарите — и вам будут пользоваться каждый день.&lt;br&gt;&lt;br&gt;💸 От 2 штук — скидка 10% автоматически. Возьмите на все связки ключей в семье!&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">🔑 Yemao M02X — фонарик-брелок, после которого большой фонарь остаётся дома. 280 люмен + УФ на связке ключей&lt;br&gt;✅ Новинка 2026 года. Покупатели берут сразу по 2–3 штуки — себе и в подарок.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — не поверите, что ТАК светит брелок!&lt;br&gt;&lt;br&gt;Правило фонарей простое: лучший фонарь — тот, который с собой. Большой остаётся в ящике, а этот малыш живёт на ключах и оказывается в руке за секунду: тёмный подъезд, замочная скважина, упавшие под сиденье ключи, щиток в гараже. Двойной клик — и 280 люмен турбо-режима бьют на 30 метров. Для брелока это просто неприлично много. 😅&lt;br&gt;&lt;br&gt;⚡ До 280 люмен — турбо двойным нажатием&lt;br&gt;📏 Дальность — до 30 метров&lt;br&gt;🟣 УФ-режим — проверка купюр и документов прямо на кассе&lt;br&gt;🎛 Режимы: яркий / эконом / стробоскоп / SOS&lt;br&gt;🔋 До 22 часов работы в экономе&lt;br&gt;🔌 Зарядка USB Type-C за ~2 часа — никаких батареек, зарядил и забыл&lt;br&gt;🦾 Авиационный алюминий — падения до 1,5 м переживёт&lt;br&gt;💧 Влагозащита IP44 — дождь не помеха&lt;br&gt;🔑 Крепится на ключи, молнию рюкзака, шлёвку джинсов&lt;br&gt;&lt;br&gt;✔️ Идеально: на ключи, в машину, на рыбалку и в поход, на вело-прогулки, дома в ящик у двери&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарик Yemao M02X + кабель Type-C + упаковка&lt;br&gt;&lt;br&gt;🎁 Лучший недорогой подарок мужчине — автомобилисту, туристу и «тому, у кого всё есть». Дарите — и вам будут пользоваться каждый день.&lt;br&gt;&lt;br&gt;💸 От 2 штук — скидка 10% автоматически. Возьмите на все связки ключей в семье!&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>🔋 YM-F303X — фонарь, который светит СУТКИ без розетки. Флагманский диод Luminus SST40 и два аккумулятора 21700 в комплекте&lt;br&gt;✅ Новинка 2026 года. По параметрам спорит с Fenix E30R и Nitecore HC65 V2 — по цене почти вдвое ниже.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — честные люксы, а не цифры с потолка!&lt;br&gt;&lt;br&gt;За что вы платите, покупая «бренд»? За логотип. Здесь тот же эталонный диод Luminus SST40, тот же авиационный алюминий 6065 и та же годовая гарантия — но без наценки за имя. А в комплекте сразу ДВА аккумулятора 21700 по 5000 мАч: один в фонаре, второй в кармане — вот и сутки автономии в лесу, на смене или при отключении света. 💪&lt;br&gt;&lt;br&gt;☀️ Luminus SST40 — до 1600 люмен, луч больше 200 метров&lt;br&gt;💡 COB-панель до 1000 лм — широкий заливной свет для работы в упор, 4 режима&lt;br&gt;🔄 Голова поворачивается на 90° — свет туда, куда нужно, а не куда получилось&lt;br&gt;🧲 Магнит в хвосте — на капот, трубу, холодильник&lt;br&gt;🔋 2 × 21700 на 5000 мАч В КОМПЛЕКТЕ — до суток работы&lt;br&gt;🔌 Быстрая зарядка USB Type-C&lt;br&gt;🦾 Авиационный алюминий 6065 — падения, дождь и «армейские будни»&lt;br&gt;&lt;br&gt;📊 ЧЕСТНЫЕ РЕЖИМЫ (замеры, а не маркетинг):&lt;br&gt;🚀 Турбо — 1600 лм / 203 м / 1,5 ч&lt;br&gt;🌙 Средний — 350 лм / 93 м / ~18 ч&lt;br&gt;🐢 Эконом — 150 лм / 62 м / 37+ ч&lt;br&gt;⚠️ Строб — 1600 лм, сигнальный&lt;br&gt;💡 COB-заливка — от 5 до 120 часов в зависимости от яркости&lt;br&gt;&lt;br&gt;✔️ Идеально для: охоты и рыбалки, походов, стройки и гаража, работы под капотом, EDC, аварийного света дома&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь YM-F303X + 2 аккумулятора 21700 (5000 мАч) + кабель USB-C + брендированная коробка — готовый подарок 🎁&lt;br&gt;&lt;br&gt;🏆 Нам доверяют: более 600 покупателей, 1000+ фонарей уже в руках владельцев&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, каждый проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — всё расскажу и покажу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">🔋 YM-F303X — фонарь, который светит СУТКИ без розетки. Флагманский диод Luminus SST40 и два аккумулятора 21700 в комплекте&lt;br&gt;✅ Новинка 2026 года. По параметрам спорит с Fenix E30R и Nitecore HC65 V2 — по цене почти вдвое ниже.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — честные люксы, а не цифры с потолка!&lt;br&gt;&lt;br&gt;За что вы платите, покупая «бренд»? За логотип. Здесь тот же эталонный диод Luminus SST40, тот же авиационный алюминий 6065 и та же годовая гарантия — но без наценки за имя. А в комплекте сразу ДВА аккумулятора 21700 по 5000 мАч: один в фонаре, второй в кармане — вот и сутки автономии в лесу, на смене или при отключении света. 💪&lt;br&gt;&lt;br&gt;☀️ Luminus SST40 — до 1600 люмен, луч больше 200 метров&lt;br&gt;💡 COB-панель до 1000 лм — широкий заливной свет для работы в упор, 4 режима&lt;br&gt;🔄 Голова поворачивается на 90° — свет туда, куда нужно, а не куда получилось&lt;br&gt;🧲 Магнит в хвосте — на капот, трубу, холодильник&lt;br&gt;🔋 2 × 21700 на 5000 мАч В КОМПЛЕКТЕ — до суток работы&lt;br&gt;🔌 Быстрая зарядка USB Type-C&lt;br&gt;🦾 Авиационный алюминий 6065 — падения, дождь и «армейские будни»&lt;br&gt;&lt;br&gt;📊 ЧЕСТНЫЕ РЕЖИМЫ (замеры, а не маркетинг):&lt;br&gt;🚀 Турбо — 1600 лм / 203 м / 1,5 ч&lt;br&gt;🌙 Средний — 350 лм / 93 м / ~18 ч&lt;br&gt;🐢 Эконом — 150 лм / 62 м / 37+ ч&lt;br&gt;⚠️ Строб — 1600 лм, сигнальный&lt;br&gt;💡 COB-заливка — от 5 до 120 часов в зависимости от яркости&lt;br&gt;&lt;br&gt;✔️ Идеально для: охоты и рыбалки, походов, стройки и гаража, работы под капотом, EDC, аварийного света дома&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь YM-F303X + 2 аккумулятора 21700 (5000 мАч) + кабель USB-C + брендированная коробка — готовый подарок 🎁&lt;br&gt;&lt;br&gt;🏆 Нам доверяют: более 600 покупателей, 1000+ фонарей уже в руках владельцев&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, каждый проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — всё расскажу и покажу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>🔦 Yemao PM60 — днём прожектор на 3 километра, ночью уютный ночник. Два характера в одном фонаре&lt;br&gt;✅ Хит продаж второй год подряд! Только оригинал Yemao — берегитесь дешёвых копий.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — и луч на 3 км, и светящаяся ручка вживую!&lt;br&gt;&lt;br&gt;Жмёте кнопку — и диод PM60 выдаёт 10 000 люмен: луч видно за 3 километра, поле и лес освещены как прожектором. А вечером в палатке включаете ЭКСКЛЮЗИВ этой модели — мягкую подсветку ручки под стеклом: режим ночника и живой «свечи», уютный свет для лагеря, ребёнка, чтения. Такого нет больше ни у кого. 🕯&lt;br&gt;&lt;br&gt;⚡ Диод PM60 — до 10 000 люмен, луч до 3000 метров&lt;br&gt;🕯 Светящаяся ручка — ночник и режим свечи, фирменная фишка Yemao&lt;br&gt;🎛 11 режимов: от боевого луча до SOS и стробоскопа&lt;br&gt;🔋 Аккумулятор 26650 на 5000 мАч + переходники под другие форматы АКБ&lt;br&gt;⚡️ Функция Power Bank — зарядит телефон в дороге&lt;br&gt;🔌 Быстрая зарядка USB Type-C&lt;br&gt;📷 Крепление под штатив — свет для фото и работы без рук&lt;br&gt;🇯🇵 Разработка — Япония, сборка — под строгим японским контролем качества&lt;br&gt;&lt;br&gt;✔️ Идеально для: охоты, рыбалки, кемпинга, дачи, гаража, экстренных ситуаций и отключений света&lt;br&gt;&lt;br&gt;📦 Богатый комплект: фонарь Yemao + АКБ 26650 + переходники под другие аккумуляторы + кабель Type-C + темляк + крепление для штатива + ПРЕМИУМ подарочный кейс&lt;br&gt;&lt;br&gt;🎁 Готовый подарок мужчине — вручать можно прямо в кейсе: 23 февраля, день рождения, Новый год&lt;br&gt;&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически&lt;br&gt;&lt;br&gt;🏆 НАСТОЯЩАЯ гарантия 1 год (кроме механических повреждений) · Сертифицировано&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, проверяю каждый перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;🔦 Загляните в профиль — там ещё много мощных фонарей по лучшим ценам!&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">🔦 Yemao PM60 — днём прожектор на 3 километра, ночью уютный ночник. Два характера в одном фонаре&lt;br&gt;✅ Хит продаж второй год подряд! Только оригинал Yemao — берегитесь дешёвых копий.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — и луч на 3 км, и светящаяся ручка вживую!&lt;br&gt;&lt;br&gt;Жмёте кнопку — и диод PM60 выдаёт 10 000 люмен: луч видно за 3 километра, поле и лес освещены как прожектором. А вечером в палатке включаете ЭКСКЛЮЗИВ этой модели — мягкую подсветку ручки под стеклом: режим ночника и живой «свечи», уютный свет для лагеря, ребёнка, чтения. Такого нет больше ни у кого. 🕯&lt;br&gt;&lt;br&gt;⚡ Диод PM60 — до 10 000 люмен, луч до 3000 метров&lt;br&gt;🕯 Светящаяся ручка — ночник и режим свечи, фирменная фишка Yemao&lt;br&gt;🎛 11 режимов: от боевого луча до SOS и стробоскопа&lt;br&gt;🔋 Аккумулятор 26650 на 5000 мАч + переходники под другие форматы АКБ&lt;br&gt;⚡️ Функция Power Bank — зарядит телефон в дороге&lt;br&gt;🔌 Быстрая зарядка USB Type-C&lt;br&gt;📷 Крепление под штатив — свет для фото и работы без рук&lt;br&gt;🇯🇵 Разработка — Япония, сборка — под строгим японским контролем качества&lt;br&gt;&lt;br&gt;✔️ Идеально для: охоты, рыбалки, кемпинга, дачи, гаража, экстренных ситуаций и отключений света&lt;br&gt;&lt;br&gt;📦 Богатый комплект: фонарь Yemao + АКБ 26650 + переходники под другие аккумуляторы + кабель Type-C + темляк + крепление для штатива + ПРЕМИУМ подарочный кейс&lt;br&gt;&lt;br&gt;🎁 Готовый подарок мужчине — вручать можно прямо в кейсе: 23 февраля, день рождения, Новый год&lt;br&gt;&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически&lt;br&gt;&lt;br&gt;🏆 НАСТОЯЩАЯ гарантия 1 год (кроме механических повреждений) · Сертифицировано&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, проверяю каждый перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;🔦 Загляните в профиль — там ещё много мощных фонарей по лучшим ценам!&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>💡 Налобник Yemao, который светит ярче автомобильных фар. 3000 люмен на лбу — руки свободны&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Сборка уровня Fenix и Armytek — в разы дешевле.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру!&lt;br&gt;❗ ВНИМАНИЕ: в комплекте 1 мощный аккумулятор (не 2, как на видео) — цена указана честно за этот комплект.&lt;br&gt;&lt;br&gt;Надеваете — и перед вами 200 метров дневного света, а обе руки заняты делом: снастями, инструментом, рулём мотоцикла. Никаких меню и перелистываний режимов: одна кнопка — включил и работаешь. Именно за эту простоту его любят те, кто пользуется фонарём каждый день, а не раз в год. 💪&lt;br&gt;&lt;br&gt;📌 Реальные 3000 люмен — без китайских «маркетинговых» цифр&lt;br&gt;📏 Видимость до 200 метров&lt;br&gt;🔋 Аккумулятор 21700 на 5000 мАч в комплекте — до 20 часов работы&lt;br&gt;🎛 Управление одной кнопкой — вкл/выкл, ничего лишнего&lt;br&gt;🔌 Зарядка USB Type-C&lt;br&gt;🦾 Корпус из авиационного алюминия — переживёт падения и удары&lt;br&gt;💧 Влагозащита IPX4 — дождь и снег не страшны&lt;br&gt;🎽 Удобное регулируемое крепление на голову&lt;br&gt;✔️ Идеально для: охоты, рыбалки, туризма, стройки, гаража, авто и мото, дачи, спасателей, охраны, тактических задач&lt;br&gt;📦 В комплекте: налобный фонарь + аккумулятор 21700 (5000 мАч) + кабель Type-C + крепление на голову&lt;br&gt;&lt;br&gt;🎁 Готовый подарок мужчине — на день рождения или 23 февраля&lt;br&gt;💸 Скидка 10% на второй товар — возьмите второй для напарника&lt;br&gt;🏆 Гарантия 1 год · Официальная сертификация&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;🤝 Возможна встреча / самовывоз — уточняйте&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">💡 Налобник Yemao, который светит ярче автомобильных фар. 3000 люмен на лбу — руки свободны&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Сборка уровня Fenix и Armytek — в разы дешевле.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру!&lt;br&gt;❗ ВНИМАНИЕ: в комплекте 1 мощный аккумулятор (не 2, как на видео) — цена указана честно за этот комплект.&lt;br&gt;&lt;br&gt;Надеваете — и перед вами 200 метров дневного света, а обе руки заняты делом: снастями, инструментом, рулём мотоцикла. Никаких меню и перелистываний режимов: одна кнопка — включил и работаешь. Именно за эту простоту его любят те, кто пользуется фонарём каждый день, а не раз в год. 💪&lt;br&gt;&lt;br&gt;📌 Реальные 3000 люмен — без китайских «маркетинговых» цифр&lt;br&gt;📏 Видимость до 200 метров&lt;br&gt;🔋 Аккумулятор 21700 на 5000 мАч в комплекте — до 20 часов работы&lt;br&gt;🎛 Управление одной кнопкой — вкл/выкл, ничего лишнего&lt;br&gt;🔌 Зарядка USB Type-C&lt;br&gt;🦾 Корпус из авиационного алюминия — переживёт падения и удары&lt;br&gt;💧 Влагозащита IPX4 — дождь и снег не страшны&lt;br&gt;🎽 Удобное регулируемое крепление на голову&lt;br&gt;✔️ Идеально для: охоты, рыбалки, туризма, стройки, гаража, авто и мото, дачи, спасателей, охраны, тактических задач&lt;br&gt;📦 В комплекте: налобный фонарь + аккумулятор 21700 (5000 мАч) + кабель Type-C + крепление на голову&lt;br&gt;&lt;br&gt;🎁 Готовый подарок мужчине — на день рождения или 23 февраля&lt;br&gt;💸 Скидка 10% на второй товар — возьмите второй для напарника&lt;br&gt;🏆 Гарантия 1 год · Официальная сертификация&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;🤝 Возможна встреча / самовывоз — уточняйте&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>💡 YM-M18 — 5,5 сантиметра, в которых спрятано ШЕСТЬ источников света. Сенсор, магнит, УФ и 14 режимов&lt;br&gt;Цвет фонарика кладется случайно: оранжевый, синий, зеленый&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Мультитул в мире фонарей.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — все 6 источников света показаны вживую!&lt;br&gt;&lt;br&gt;Посчитаем: дальний луч, широкая COB-заливка, ультрафиолет для купюр, цветная RGB-панель, красно-синяя аварийка и световые эффекты. Это ШЕСТЬ фонарей, купленных по цене одного — и все они помещаются в корпус размером с большой палец. А включается он взмахом руки: сенсор срабатывает, даже когда руки в масле, в перчатках или заняты. 🤯&lt;br&gt;&lt;br&gt;⚡ Основной луч — до 270 люмен, дальность до 80 метров&lt;br&gt;💡 COB-панель — мощная широкая заливка для работы вблизи&lt;br&gt;🟣 УФ-свет — проверка купюр и документов&lt;br&gt;🌈 RGB — красный / синий / зелёный / жёлтый&lt;br&gt;🚨 Красно-синий аварийный сигнал — обозначить себя на дороге&lt;br&gt;✨ Эффекты «мигание» и «дыхание»&lt;br&gt;🙌 Сенсор — взмах рукой = вкл/выкл, плюс обычные быстрые кнопки&lt;br&gt;🎛 Всего 14 режимов: 3 уровня яркости, строб, SOS и все панели&lt;br&gt;🧲 Магнит — прилепили к капоту и работаете двумя руками&lt;br&gt;📎 Клипса — на карман или кепку (мгновенный налобник)&lt;br&gt;📏 Размер — всего 55 мм, не почувствуете в кармане&lt;br&gt;🔋 До 8 часов работы, зарядка USB Type-C&lt;br&gt;🦾 Прочный алюминий, ударопрочный, влагозащита IPX4&lt;br&gt;&lt;br&gt;✔️ Идеально для: машины (аварийка + магнит = маст-хэв), гаража и ремонта, походов, рыбалки, дома, EDC на каждый день&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь YM-M18 + кабель Type-C + упаковка (готовый подарок 🎁)&lt;br&gt;&lt;br&gt;💸 От 2 штук — скидка 10% автоматически. Один в карман, один в бардачок!&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю каждый перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">💡 YM-M18 — 5,5 сантиметра, в которых спрятано ШЕСТЬ источников света. Сенсор, магнит, УФ и 14 режимов&lt;br&gt;Цвет фонарика кладется случайно: оранжевый, синий, зеленый&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Мультитул в мире фонарей.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — все 6 источников света показаны вживую!&lt;br&gt;&lt;br&gt;Посчитаем: дальний луч, широкая COB-заливка, ультрафиолет для купюр, цветная RGB-панель, красно-синяя аварийка и световые эффекты. Это ШЕСТЬ фонарей, купленных по цене одного — и все они помещаются в корпус размером с большой палец. А включается он взмахом руки: сенсор срабатывает, даже когда руки в масле, в перчатках или заняты. 🤯&lt;br&gt;&lt;br&gt;⚡ Основной луч — до 270 люмен, дальность до 80 метров&lt;br&gt;💡 COB-панель — мощная широкая заливка для работы вблизи&lt;br&gt;🟣 УФ-свет — проверка купюр и документов&lt;br&gt;🌈 RGB — красный / синий / зелёный / жёлтый&lt;br&gt;🚨 Красно-синий аварийный сигнал — обозначить себя на дороге&lt;br&gt;✨ Эффекты «мигание» и «дыхание»&lt;br&gt;🙌 Сенсор — взмах рукой = вкл/выкл, плюс обычные быстрые кнопки&lt;br&gt;🎛 Всего 14 режимов: 3 уровня яркости, строб, SOS и все панели&lt;br&gt;🧲 Магнит — прилепили к капоту и работаете двумя руками&lt;br&gt;📎 Клипса — на карман или кепку (мгновенный налобник)&lt;br&gt;📏 Размер — всего 55 мм, не почувствуете в кармане&lt;br&gt;🔋 До 8 часов работы, зарядка USB Type-C&lt;br&gt;🦾 Прочный алюминий, ударопрочный, влагозащита IPX4&lt;br&gt;&lt;br&gt;✔️ Идеально для: машины (аварийка + магнит = маст-хэв), гаража и ремонта, походов, рыбалки, дома, EDC на каждый день&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь YM-M18 + кабель Type-C + упаковка (готовый подарок 🎁)&lt;br&gt;&lt;br&gt;💸 От 2 штук — скидка 10% автоматически. Один в карман, один в бардачок!&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю каждый перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>🏟 Фонарь-зверь Yemao — ярче стадионного прожектора. До 15 000 люмен, луч до 5 км и ВОСЕМЬ аккумуляторов в комплекте&lt;br&gt;✅ Только оригинал Yemao — остерегайтесь дешёвых копий с нашими видео.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — луч до горизонта снят вживую!&lt;br&gt;&lt;br&gt;Включаете турбо — и поле до самого леса залито светом, как футбольный газон в финале. Зум собирает свет в тонкий «лазерный» луч на 5 километров или разливает на сотни квадратных метров. А главное — 8 аккумуляторов 18650 в комплекте: пока четыре работают, четыре ждут в кейсе. Энергии хватит на всю смену, и телефон ещё зарядите. 💪&lt;br&gt;&lt;br&gt;⚡ Яркость — до 15 000 люмен&lt;br&gt;📏 Дальность луча — до 5 000 метров, реально «достреливает» до горизонта&lt;br&gt;🔍 Zoom — от игольного луча до широченной заливки&lt;br&gt;🔋 8 (!) аккумуляторов 18650 в комплекте — до 7 часов от одного заряда + полный запасной комплект&lt;br&gt;⚡️ Функция Power Bank — фонарь зарядит ваш телефон в лесу&lt;br&gt;🎛 7 режимов: от «лунного» ночника до турбо, SOS и стробоскопа&lt;br&gt;🦾 Авиационный алюминий — переживёт падения; ударная кромка разобьёт стекло авто в экстренной ситуации&lt;br&gt;💧 Защита IP65 — дождь, снег, грязь&lt;br&gt;🔌 Быстрая зарядка Type-C + индикатор заряда&lt;br&gt;&lt;br&gt;✔️ Проверен теми, кто работает ночью: охотники, рыбаки, охрана, спасатели, туристы&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь + 8 АКБ 18650 + ремень + кабель Type-C + ПОДАРОЧНЫЙ кейс-чехол — вручать можно прямо в нём 🎁&lt;br&gt;&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, каждый тестирую перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">🏟 Фонарь-зверь Yemao — ярче стадионного прожектора. До 15 000 люмен, луч до 5 км и ВОСЕМЬ аккумуляторов в комплекте&lt;br&gt;✅ Только оригинал Yemao — остерегайтесь дешёвых копий с нашими видео.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — луч до горизонта снят вживую!&lt;br&gt;&lt;br&gt;Включаете турбо — и поле до самого леса залито светом, как футбольный газон в финале. Зум собирает свет в тонкий «лазерный» луч на 5 километров или разливает на сотни квадратных метров. А главное — 8 аккумуляторов 18650 в комплекте: пока четыре работают, четыре ждут в кейсе. Энергии хватит на всю смену, и телефон ещё зарядите. 💪&lt;br&gt;&lt;br&gt;⚡ Яркость — до 15 000 люмен&lt;br&gt;📏 Дальность луча — до 5 000 метров, реально «достреливает» до горизонта&lt;br&gt;🔍 Zoom — от игольного луча до широченной заливки&lt;br&gt;🔋 8 (!) аккумуляторов 18650 в комплекте — до 7 часов от одного заряда + полный запасной комплект&lt;br&gt;⚡️ Функция Power Bank — фонарь зарядит ваш телефон в лесу&lt;br&gt;🎛 7 режимов: от «лунного» ночника до турбо, SOS и стробоскопа&lt;br&gt;🦾 Авиационный алюминий — переживёт падения; ударная кромка разобьёт стекло авто в экстренной ситуации&lt;br&gt;💧 Защита IP65 — дождь, снег, грязь&lt;br&gt;🔌 Быстрая зарядка Type-C + индикатор заряда&lt;br&gt;&lt;br&gt;✔️ Проверен теми, кто работает ночью: охотники, рыбаки, охрана, спасатели, туристы&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь + 8 АКБ 18650 + ремень + кабель Type-C + ПОДАРОЧНЫЙ кейс-чехол — вручать можно прямо в нём 🎁&lt;br&gt;&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, каждый тестирую перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>🔥Hастоящая гарантия 1 год!&lt;br&gt;Бeзупрeчный рейтинг ⭐️⭐️⭐️⭐️⭐️&lt;br&gt;❗️Нет аналогов на Авито! Другие продавцы копируют фото и видео и выдают свой товар за этот&lt;br&gt;&lt;br&gt;🌌 Прожектор, который превращает ночь в день. 336 LED + повербанк + солнечная батарея — 3 в 1&lt;br&gt;&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — реальная яркость снята на камеру!&lt;br&gt;Выключился свет? Стемнело в походе? Сел телефон посреди рыбалки? Этот прожектор закрывает все три проблемы одной кнопкой. Панель из 336 диодов заливает светом до 150 м² — во дворе становится светло, как днём. А когда розетки нет неделями — он заряжает сам себя от солнца. 😎&lt;br&gt;&lt;br&gt;💡 336 LED-диодов — заливает светом площадь до 150 м²&lt;br&gt;🎛 5 режимов: холодный / тёплый / комбинированный / приглушённый / аварийный стробоскоп&lt;br&gt;🔋 Аккумулятор 12 000 мАч — до 15 часов света без подзарядки&lt;br&gt;☀️ Солнечная панель — заряжается сам, пока вы на природе&lt;br&gt;⚡️ Функция PowerBank — подзарядит телефон там, где нет розеток&lt;br&gt;🔌 Быстрая зарядка от сети через USB Type-C&lt;br&gt;🧲 Магнит + крючок + ножка-подставка — поставьте, подвесьте или примагнитьте к капоту&lt;br&gt;🌧 Защита IP66 — ливень, мороз и жара ему безразличны&lt;br&gt;Размер: 20х15х5см, вес 500гр&lt;br&gt;✔️ Идеально для: кемпинга и палатки, дачи и гаража, рыбалки и охоты, вечерних посиделок, работ во дворе, аварийного света при отключениях&lt;br&gt;&lt;br&gt;🎁 Готовый подарок мужчине: на дачника&lt;br&gt;💸 От 2 штук — скидка 10% автоматически&lt;br&gt;📦 В комплекте: прожектор + кабель Type-C&lt;br&gt;&lt;br&gt;🏆 Настоящая гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, всё проверено и протестировано перед отправкой&lt;br&gt;&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">🔥Hастоящая гарантия 1 год!&lt;br&gt;Бeзупрeчный рейтинг ⭐️⭐️⭐️⭐️⭐️&lt;br&gt;❗️Нет аналогов на Авито! Другие продавцы копируют фото и видео и выдают свой товар за этот&lt;br&gt;&lt;br&gt;🌌 Прожектор, который превращает ночь в день. 336 LED + повербанк + солнечная батарея — 3 в 1&lt;br&gt;&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — реальная яркость снята на камеру!&lt;br&gt;Выключился свет? Стемнело в походе? Сел телефон посреди рыбалки? Этот прожектор закрывает все три проблемы одной кнопкой. Панель из 336 диодов заливает светом до 150 м² — во дворе становится светло, как днём. А когда розетки нет неделями — он заряжает сам себя от солнца. 😎&lt;br&gt;&lt;br&gt;💡 336 LED-диодов — заливает светом площадь до 150 м²&lt;br&gt;🎛 5 режимов: холодный / тёплый / комбинированный / приглушённый / аварийный стробоскоп&lt;br&gt;🔋 Аккумулятор 12 000 мАч — до 15 часов света без подзарядки&lt;br&gt;☀️ Солнечная панель — заряжается сам, пока вы на природе&lt;br&gt;⚡️ Функция PowerBank — подзарядит телефон там, где нет розеток&lt;br&gt;🔌 Быстрая зарядка от сети через USB Type-C&lt;br&gt;🧲 Магнит + крючок + ножка-подставка — поставьте, подвесьте или примагнитьте к капоту&lt;br&gt;🌧 Защита IP66 — ливень, мороз и жара ему безразличны&lt;br&gt;Размер: 20х15х5см, вес 500гр&lt;br&gt;✔️ Идеально для: кемпинга и палатки, дачи и гаража, рыбалки и охоты, вечерних посиделок, работ во дворе, аварийного света при отключениях&lt;br&gt;&lt;br&gt;🎁 Готовый подарок мужчине: на дачника&lt;br&gt;💸 От 2 штук — скидка 10% автоматически&lt;br&gt;📦 В комплекте: прожектор + кабель Type-C&lt;br&gt;&lt;br&gt;🏆 Настоящая гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, всё проверено и протестировано перед отправкой&lt;br&gt;&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>🙌 Yemao — налобник весом 48 грамм с сенсорным управлением. Провёл рукой — включился. Забыл, что он на голове&lt;br&gt;✅ Новинка 2026 года. Цвет — чёрный или синий, кладётся случайно (напишите в отзыве, какой достался 😉)&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — жестовое управление показано вживую!&lt;br&gt;&lt;br&gt;48 грамм — это меньше половины смартфона: надели и перестали замечать. А кнопку искать не нужно вовсе: взмах рукой перед фонарём — включился, ещё взмах — выключился. Руки в грязи, в перчатках, заняты снастями — неважно, работает всегда. И это не один фонарь, а три: на голову, на кепку и на велосипед — крепления все в комплекте. 💪&lt;br&gt;&lt;br&gt;🙌 Сенсор — вкл/выкл взмахом руки, даже в перчатках и на ходу&lt;br&gt;⚡ Яркость до 500 люмен, дальность до 150 метров&lt;br&gt;💡 Два света: широкая заливка + дальний луч&lt;br&gt;🎛 7 режимов, включая красный (ночное зрение) и SOS&lt;br&gt;🔄 Поворот на 180° — направьте свет куда нужно&lt;br&gt;🪶 Вес — всего 48 грамм, на голове не ощущается&lt;br&gt;🔋 До 5 часов работы, зарядка по USB&lt;br&gt;💧 Влагозащита IPX4 — дождь не помеха&lt;br&gt;🦾 Прочный корпус&lt;br&gt;&lt;br&gt;⚙️ 3 В 1 — крепления в комплекте:&lt;br&gt;✔ На голову — классический налобник&lt;br&gt;✔ Клипса — на кепку или одежду&lt;br&gt;✔ Велокрепление — готовый велофонарь&lt;br&gt;&lt;br&gt;✔️ Идеально для: рыбалки, походов, велосипеда, ремонта, работы под капотом, прогулок с собакой&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь + крепление на голову + клипса + велокрепление + кабель USB&lt;br&gt;&lt;br&gt;🎁 Недорогой подарок, которым реально пользуются каждый день&lt;br&gt;&lt;br&gt;💸 От 2 штук — скидка 10% автоматически. Себе и на второй велосипед!&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">🙌 Yemao — налобник весом 48 грамм с сенсорным управлением. Провёл рукой — включился. Забыл, что он на голове&lt;br&gt;✅ Новинка 2026 года. Цвет — чёрный или синий, кладётся случайно (напишите в отзыве, какой достался 😉)&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — жестовое управление показано вживую!&lt;br&gt;&lt;br&gt;48 грамм — это меньше половины смартфона: надели и перестали замечать. А кнопку искать не нужно вовсе: взмах рукой перед фонарём — включился, ещё взмах — выключился. Руки в грязи, в перчатках, заняты снастями — неважно, работает всегда. И это не один фонарь, а три: на голову, на кепку и на велосипед — крепления все в комплекте. 💪&lt;br&gt;&lt;br&gt;🙌 Сенсор — вкл/выкл взмахом руки, даже в перчатках и на ходу&lt;br&gt;⚡ Яркость до 500 люмен, дальность до 150 метров&lt;br&gt;💡 Два света: широкая заливка + дальний луч&lt;br&gt;🎛 7 режимов, включая красный (ночное зрение) и SOS&lt;br&gt;🔄 Поворот на 180° — направьте свет куда нужно&lt;br&gt;🪶 Вес — всего 48 грамм, на голове не ощущается&lt;br&gt;🔋 До 5 часов работы, зарядка по USB&lt;br&gt;💧 Влагозащита IPX4 — дождь не помеха&lt;br&gt;🦾 Прочный корпус&lt;br&gt;&lt;br&gt;⚙️ 3 В 1 — крепления в комплекте:&lt;br&gt;✔ На голову — классический налобник&lt;br&gt;✔ Клипса — на кепку или одежду&lt;br&gt;✔ Велокрепление — готовый велофонарь&lt;br&gt;&lt;br&gt;✔️ Идеально для: рыбалки, походов, велосипеда, ремонта, работы под капотом, прогулок с собакой&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь + крепление на голову + клипса + велокрепление + кабель USB&lt;br&gt;&lt;br&gt;🎁 Недорогой подарок, которым реально пользуются каждый день&lt;br&gt;&lt;br&gt;💸 От 2 штук — скидка 10% автоматически. Себе и на второй велосипед!&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>🔥 СПЕЦИАЛЬНАЯ ЦЕНА ДО КОНЦА НЕДЕЛИ — всего 1095 ₽ вместо 1440 ₽! 🔥&lt;br&gt;&lt;br&gt;🔦 PM30 PRO — сверхмощный аккумуляторный фонарь с дальностью луча до 3000 метров!&lt;br&gt;&lt;br&gt;✅ Гарантия 12 месяцев&lt;br&gt;✅ Рейтинг покупателей — 5.0&lt;br&gt;✅ Аккумулятор 3000 мАч в комплекте (честная ёмкость)&lt;br&gt;✅ Редкая модель, которую сложно найти на Авито&lt;br&gt;✅ Не путайте с дешёвыми копиями и подделками&lt;br&gt;&lt;br&gt;❤️ Добавьте объявление в избранное, чтобы не потерять выгодное предложение.&lt;br&gt;&lt;br&gt;💡 PM30 PRO — компактный, но очень мощный светодиодный фонарь для любых задач: от ремонта автомобиля до рыбалки и путешествий.&lt;br&gt;&lt;br&gt;⚡️ Основные характеристики:&lt;br&gt;&lt;br&gt;🔹 Дальность свечения до 3 км&lt;br&gt;🔹 Яркость до 13 000 люмен&lt;br&gt;🔹 Современный светодиод с мощным сфокусированным лучом&lt;br&gt;🔹 Освещает территорию значительно лучше многих крупногабаритных прожекторов&lt;br&gt;&lt;br&gt;📦 Возможности фонаря:&lt;br&gt;&lt;br&gt;✔️ 9 режимов работы&lt;br&gt;✔️ Максимальный, средний и экономичный режимы&lt;br&gt;✔️ Стробоскоп и сигнал SOS&lt;br&gt;✔️ Красная подсветка&lt;br&gt;✔️ Регулируемый фокус луча (зум)&lt;br&gt;✔️ Работа от аккумулятора и батареек&lt;br&gt;✔️ Зарядка через Type-C&lt;br&gt;✔️ Магнит для крепления к металлическим поверхностям&lt;br&gt;✔️ Индикация уровня заряда на дисплее&lt;br&gt;✔️ Возможность использовать как Power Bank&lt;br&gt;&lt;br&gt;💪 Преимущества:&lt;br&gt;&lt;br&gt;✔️ Влагозащита IP65&lt;br&gt;✔️ Надёжный ударопрочный корпус&lt;br&gt;✔️ Компактные размеры — всего 16,8 см&lt;br&gt;✔️ Поставляется в подарочной упаковке&lt;br&gt;✔️ Удобно хранить в машине, рюкзаке или дома&lt;br&gt;&lt;br&gt;🎯 Отлично подойдёт для:&lt;br&gt;&lt;br&gt;🎣 Рыбалки&lt;br&gt;🏕 Туризма и кемпинга&lt;br&gt;🚗 Автомобиля&lt;br&gt;🔧 Строительных и ремонтных работ&lt;br&gt;🚴 Велопрогулок&lt;br&gt;🏹 Активного отдыха и выездов на природу&lt;br&gt;&lt;br&gt;🎁 Практичный подарок для мужчины, мужа, отца, брата, друга или коллеги.&lt;br&gt;&lt;br&gt;💸 При покупке двух и более товаров действует дополнительная скидка 10%.&lt;br&gt;&lt;br&gt;🚚 Быстрая отправка Авито Доставкой по всей России.&lt;br&gt;&lt;br&gt;⚠️ Внимание! Не направляйте луч в глаза людям и животным. Рекомендуется хранить в недоступном для детей месте.&lt;br&gt;&lt;br&gt;❗️ Оформляйте заказ или пишите в сообщения прямо сейчас — количество фонарей по акционной цене ограничено!&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">🔥 СПЕЦИАЛЬНАЯ ЦЕНА ДО КОНЦА НЕДЕЛИ — всего 1095 ₽ вместо 1440 ₽! 🔥&lt;br&gt;&lt;br&gt;🔦 PM30 PRO — сверхмощный аккумуляторный фонарь с дальностью луча до 3000 метров!&lt;br&gt;&lt;br&gt;✅ Гарантия 12 месяцев&lt;br&gt;✅ Рейтинг покупателей — 5.0&lt;br&gt;✅ Аккумулятор 3000 мАч в комплекте (честная ёмкость)&lt;br&gt;✅ Редкая модель, которую сложно найти на Авито&lt;br&gt;✅ Не путайте с дешёвыми копиями и подделками&lt;br&gt;&lt;br&gt;❤️ Добавьте объявление в избранное, чтобы не потерять выгодное предложение.&lt;br&gt;&lt;br&gt;💡 PM30 PRO — компактный, но очень мощный светодиодный фонарь для любых задач: от ремонта автомобиля до рыбалки и путешествий.&lt;br&gt;&lt;br&gt;⚡️ Основные характеристики:&lt;br&gt;&lt;br&gt;🔹 Дальность свечения до 3 км&lt;br&gt;🔹 Яркость до 13 000 люмен&lt;br&gt;🔹 Современный светодиод с мощным сфокусированным лучом&lt;br&gt;🔹 Освещает территорию значительно лучше многих крупногабаритных прожекторов&lt;br&gt;&lt;br&gt;📦 Возможности фонаря:&lt;br&gt;&lt;br&gt;✔️ 9 режимов работы&lt;br&gt;✔️ Максимальный, средний и экономичный режимы&lt;br&gt;✔️ Стробоскоп и сигнал SOS&lt;br&gt;✔️ Красная подсветка&lt;br&gt;✔️ Регулируемый фокус луча (зум)&lt;br&gt;✔️ Работа от аккумулятора и батареек&lt;br&gt;✔️ Зарядка через Type-C&lt;br&gt;✔️ Магнит для крепления к металлическим поверхностям&lt;br&gt;✔️ Индикация уровня заряда на дисплее&lt;br&gt;✔️ Возможность использовать как Power Bank&lt;br&gt;&lt;br&gt;💪 Преимущества:&lt;br&gt;&lt;br&gt;✔️ Влагозащита IP65&lt;br&gt;✔️ Надёжный ударопрочный корпус&lt;br&gt;✔️ Компактные размеры — всего 16,8 см&lt;br&gt;✔️ Поставляется в подарочной упаковке&lt;br&gt;✔️ Удобно хранить в машине, рюкзаке или дома&lt;br&gt;&lt;br&gt;🎯 Отлично подойдёт для:&lt;br&gt;&lt;br&gt;🎣 Рыбалки&lt;br&gt;🏕 Туризма и кемпинга&lt;br&gt;🚗 Автомобиля&lt;br&gt;🔧 Строительных и ремонтных работ&lt;br&gt;🚴 Велопрогулок&lt;br&gt;🏹 Активного отдыха и выездов на природу&lt;br&gt;&lt;br&gt;🎁 Практичный подарок для мужчины, мужа, отца, брата, друга или коллеги.&lt;br&gt;&lt;br&gt;💸 При покупке двух и более товаров действует дополнительная скидка 10%.&lt;br&gt;&lt;br&gt;🚚 Быстрая отправка Авито Доставкой по всей России.&lt;br&gt;&lt;br&gt;⚠️ Внимание! Не направляйте луч в глаза людям и животным. Рекомендуется хранить в недоступном для детей месте.&lt;br&gt;&lt;br&gt;❗️ Оформляйте заказ или пишите в сообщения прямо сейчас — количество фонарей по акционной цене ограничено!&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>🔦 УФ фонарь 365 nm — покажет то, что от вас скрывают. Профессиональный фонарь Вуда в металле&lt;br&gt;✅ Настоящие 365 нанометров — не дешёвый «фиолетовый диод» 395 nm, а профессиональный UV.&lt;br&gt;&lt;br&gt;🔥 Видео ОБЯЗАТЕЛЬНО к просмотру — эффект видно с первой секунды!&lt;br&gt;Посветите на купюру — проявятся защитные метки. На кровать в отеле — и вы узнаете, как там убирают. На пляж с янтарём — камни вспыхнут в темноте сами. Этот фонарь показывает слой реальности, который обычным глазом не увидеть. Первое включение — всегда «вау». 😳&lt;br&gt;💡 ЧТО ОН НАХОДИТ:&lt;br&gt;✔ Янтарь и минералы — светятся в темноте, поиск на пляже превращается в охоту за сокровищами&lt;br&gt;✔ Купюры, документы, паспорта — мгновенная проверка подлинности&lt;br&gt;✔ Скрытые пятна и следы — проверка отелей, квартир, мебели, авто перед покупкой&lt;br&gt;✔ Утечки фреона и техжидкостей — незаменим в автосервисе&lt;br&gt;✔ Сушка гель-лака — работает для маникюра&lt;br&gt;✔ Светонакопительные приманки — заряжает за секунды, рыбаки оценят&lt;br&gt;&lt;br&gt;⚡ ХАРАКТЕРИСТИКИ:&lt;br&gt;🌑 Длина волны 365 nm — профессиональный стандарт (фонарь Вуда)&lt;br&gt;📏 Компактный — всего 12,5 см, лежит в кармане&lt;br&gt;🔋 Аккумулятор 18650 в комплекте — до 3 часов работы&lt;br&gt;🦾 Цельнометаллический ударопрочный корпус&lt;br&gt;💧 Защита IP65 — влага и пыль не страшны&lt;br&gt;✔️ Кому: коллекционерам и янтарщикам, мастерам маникюра, автосервисам, рыбакам, туристам, всем кто работает с деньгами и документами&lt;br&gt;&lt;br&gt;📦 В комплекте: УФ фонарь 365 nm + аккумулятор 18650 + зарядка + кейс&lt;br&gt;🎁 Самый необычный подарок — удивляет с первого включения, проверено&lt;br&gt;💸 От 2 товаров — скидка 10% автоматически&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">🔦 УФ фонарь 365 nm — покажет то, что от вас скрывают. Профессиональный фонарь Вуда в металле&lt;br&gt;✅ Настоящие 365 нанометров — не дешёвый «фиолетовый диод» 395 nm, а профессиональный UV.&lt;br&gt;&lt;br&gt;🔥 Видео ОБЯЗАТЕЛЬНО к просмотру — эффект видно с первой секунды!&lt;br&gt;Посветите на купюру — проявятся защитные метки. На кровать в отеле — и вы узнаете, как там убирают. На пляж с янтарём — камни вспыхнут в темноте сами. Этот фонарь показывает слой реальности, который обычным глазом не увидеть. Первое включение — всегда «вау». 😳&lt;br&gt;💡 ЧТО ОН НАХОДИТ:&lt;br&gt;✔ Янтарь и минералы — светятся в темноте, поиск на пляже превращается в охоту за сокровищами&lt;br&gt;✔ Купюры, документы, паспорта — мгновенная проверка подлинности&lt;br&gt;✔ Скрытые пятна и следы — проверка отелей, квартир, мебели, авто перед покупкой&lt;br&gt;✔ Утечки фреона и техжидкостей — незаменим в автосервисе&lt;br&gt;✔ Сушка гель-лака — работает для маникюра&lt;br&gt;✔ Светонакопительные приманки — заряжает за секунды, рыбаки оценят&lt;br&gt;&lt;br&gt;⚡ ХАРАКТЕРИСТИКИ:&lt;br&gt;🌑 Длина волны 365 nm — профессиональный стандарт (фонарь Вуда)&lt;br&gt;📏 Компактный — всего 12,5 см, лежит в кармане&lt;br&gt;🔋 Аккумулятор 18650 в комплекте — до 3 часов работы&lt;br&gt;🦾 Цельнометаллический ударопрочный корпус&lt;br&gt;💧 Защита IP65 — влага и пыль не страшны&lt;br&gt;✔️ Кому: коллекционерам и янтарщикам, мастерам маникюра, автосервисам, рыбакам, туристам, всем кто работает с деньгами и документами&lt;br&gt;&lt;br&gt;📦 В комплекте: УФ фонарь 365 nm + аккумулятор 18650 + зарядка + кейс&lt;br&gt;🎁 Самый необычный подарок — удивляет с первого включения, проверено&lt;br&gt;💸 От 2 товаров — скидка 10% автоматически&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>🔦 Малыш весом 60 грамм, который светит на 300 метров. Белый лазер PM20-TG в корпусе размером с палец&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Остерегайтесь копий — наши видео используют другие продавцы, а высылают обычный диод.&lt;br&gt;&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — досмотрите до конца, там вся мощность!&lt;br&gt;&lt;br&gt;Помещается в кулак целиком: 8,4 × 2,4 см. А луч — как у фонарей в пять раз крупнее. Секрет — кристалл нового поколения PM20-TG «белый лазер»: плотный чёткий луч до 300 метров, который отлично читается даже в городской засветке. Достаёте его из кармана при друзьях — дальше начинаются вопросы. 😅&lt;br&gt;&lt;br&gt;⚡ Вес — всего 60 г, размер 8,4 × 2,4 см&lt;br&gt;📏 Дальность луча — до 300 метров&lt;br&gt;💎 Кристалл PM20-TG «белый лазер» — мощнее классических диодов&lt;br&gt;🔍 Zoom-фокусировка — от широкого пятна до игольного луча&lt;br&gt;🎛 2 уровня яркости + стробоскоп + SOS&lt;br&gt;🧢 Клипса в комплекте — цепляете на кепку и получаете налобник&lt;br&gt;🔋 Аккумулятор 16340 в комплекте&lt;br&gt;🔌 Зарядка USB Type-C (кабель в комплекте)&lt;br&gt;❗ Важно: аккумулятор вставляется ПЛЮСОМ к пружине — наоборот от привычного. Это не брак, так задумано производителем. Памятка будет в посылке.&lt;br&gt;&lt;br&gt;✔️ Идеально для: EDC (каждый день в кармане), рыбалки, охоты, авто, прогулок с собакой, подарка мужчине&lt;br&gt;📦 В комплекте: фонарь + аккумулятор 16340 + кабель Type-C + клипса&lt;br&gt;⚠️ Не светите в глаза людям и животным и не давайте детям — это серьёзный прибор, а не игрушка.&lt;br&gt;&lt;br&gt;💸 От 2 штук — скидка 10% автоматически. Возьмите второй в бардачок!&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, каждый фонарь тестирую лично перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">🔦 Малыш весом 60 грамм, который светит на 300 метров. Белый лазер PM20-TG в корпусе размером с палец&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Остерегайтесь копий — наши видео используют другие продавцы, а высылают обычный диод.&lt;br&gt;&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — досмотрите до конца, там вся мощность!&lt;br&gt;&lt;br&gt;Помещается в кулак целиком: 8,4 × 2,4 см. А луч — как у фонарей в пять раз крупнее. Секрет — кристалл нового поколения PM20-TG «белый лазер»: плотный чёткий луч до 300 метров, который отлично читается даже в городской засветке. Достаёте его из кармана при друзьях — дальше начинаются вопросы. 😅&lt;br&gt;&lt;br&gt;⚡ Вес — всего 60 г, размер 8,4 × 2,4 см&lt;br&gt;📏 Дальность луча — до 300 метров&lt;br&gt;💎 Кристалл PM20-TG «белый лазер» — мощнее классических диодов&lt;br&gt;🔍 Zoom-фокусировка — от широкого пятна до игольного луча&lt;br&gt;🎛 2 уровня яркости + стробоскоп + SOS&lt;br&gt;🧢 Клипса в комплекте — цепляете на кепку и получаете налобник&lt;br&gt;🔋 Аккумулятор 16340 в комплекте&lt;br&gt;🔌 Зарядка USB Type-C (кабель в комплекте)&lt;br&gt;❗ Важно: аккумулятор вставляется ПЛЮСОМ к пружине — наоборот от привычного. Это не брак, так задумано производителем. Памятка будет в посылке.&lt;br&gt;&lt;br&gt;✔️ Идеально для: EDC (каждый день в кармане), рыбалки, охоты, авто, прогулок с собакой, подарка мужчине&lt;br&gt;📦 В комплекте: фонарь + аккумулятор 16340 + кабель Type-C + клипса&lt;br&gt;⚠️ Не светите в глаза людям и животным и не давайте детям — это серьёзный прибор, а не игрушка.&lt;br&gt;&lt;br&gt;💸 От 2 штук — скидка 10% автоматически. Возьмите второй в бардачок!&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, каждый фонарь тестирую лично перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>🙌 Налобник, который включается взмахом руки. Датчик движения + 10 000 люмен + свет до 1000 метров&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Оригинал с диодом PM30 — остерегайтесь слабых копий с нашими фото (коробка может отличаться).&lt;br&gt;&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — жест рукой и мощность луча надо видеть!&lt;br&gt;&lt;br&gt;Руки в перчатках? В грязи? Заняты снастями или инструментом? Просто проведите ладонью перед фонарём — включился. Ещё взмах — выключился. Никаких кнопок на морозе, никакой возни. Один раз попробуете — обычные налобники покажутся прошлым веком. А по мощности это не налобник, а прожектор на лбу: луч достаёт туда, где обычные фонари уже «сдулись». 💪&lt;br&gt;&lt;br&gt;🙌 Датчик движения — управление взмахом руки, идеально в перчатках и на морозе&lt;br&gt;⚡ Яркость до 10 000 люмен — диод PM30 нового поколения&lt;br&gt;📏 Дальность луча — до 1000 метров&lt;br&gt;🔋 3 аккумулятора в комплекте — 6900 мАч суммарно, до 20 часов в эконом-режиме&lt;br&gt;⚡️ Функция Power Bank — подзарядит телефон на природе&lt;br&gt;📊 Дисплей-индикатор заряда — точно знаете остаток&lt;br&gt;🎛 Режимы: максимальный / средний / эконом / стробоскоп / SOS&lt;br&gt;💧 Защита IPX6 — дождь, грязь и пыль не страшны&lt;br&gt;🦾 Ударопрочный корпус, надёжное регулируемое крепление на голову&lt;br&gt;✔️ Идеально для: рыбалки и охоты, походов, стройки и работы, гаража, авто (аварийные ситуации), ежедневного использования&lt;br&gt;&lt;br&gt;📦 В комплекте: налобный фонарь + 3 аккумулятора + кабель USB + крепление + упаковка&lt;br&gt;🎁 Тот редкий подарок мужчине, которым реально пользуются каждый день&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, проверяю каждый перед отправкой&lt;br&gt;&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">🙌 Налобник, который включается взмахом руки. Датчик движения + 10 000 люмен + свет до 1000 метров&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Оригинал с диодом PM30 — остерегайтесь слабых копий с нашими фото (коробка может отличаться).&lt;br&gt;&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — жест рукой и мощность луча надо видеть!&lt;br&gt;&lt;br&gt;Руки в перчатках? В грязи? Заняты снастями или инструментом? Просто проведите ладонью перед фонарём — включился. Ещё взмах — выключился. Никаких кнопок на морозе, никакой возни. Один раз попробуете — обычные налобники покажутся прошлым веком. А по мощности это не налобник, а прожектор на лбу: луч достаёт туда, где обычные фонари уже «сдулись». 💪&lt;br&gt;&lt;br&gt;🙌 Датчик движения — управление взмахом руки, идеально в перчатках и на морозе&lt;br&gt;⚡ Яркость до 10 000 люмен — диод PM30 нового поколения&lt;br&gt;📏 Дальность луча — до 1000 метров&lt;br&gt;🔋 3 аккумулятора в комплекте — 6900 мАч суммарно, до 20 часов в эконом-режиме&lt;br&gt;⚡️ Функция Power Bank — подзарядит телефон на природе&lt;br&gt;📊 Дисплей-индикатор заряда — точно знаете остаток&lt;br&gt;🎛 Режимы: максимальный / средний / эконом / стробоскоп / SOS&lt;br&gt;💧 Защита IPX6 — дождь, грязь и пыль не страшны&lt;br&gt;🦾 Ударопрочный корпус, надёжное регулируемое крепление на голову&lt;br&gt;✔️ Идеально для: рыбалки и охоты, походов, стройки и работы, гаража, авто (аварийные ситуации), ежедневного использования&lt;br&gt;&lt;br&gt;📦 В комплекте: налобный фонарь + 3 аккумулятора + кабель USB + крепление + упаковка&lt;br&gt;🎁 Тот редкий подарок мужчине, которым реально пользуются каждый день&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, проверяю каждый перед отправкой&lt;br&gt;&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>🔦 Yemao — фонарь меньше ладони, который светит за большой. 1500 люмен из кармана джинсов&lt;br&gt;✅ Только оригинал Yemao — копии светят тускло и умирают через месяц.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — сравнение размера и яркости впечатляет!&lt;br&gt;&lt;br&gt;Знакомая история: мощный фонарь есть, но он дома — потому что таскать его тяжело. Этот исчезает в кармане джинсов и достаётся не раздумывая. А когда нажимаете кнопку — 1500 люмен, каких ждёшь от фонаря втрое крупнее. Плюс магнит: прилепили под капотом или к батарее — и обе руки в деле. 💪&lt;br&gt;&lt;br&gt;⚡ Яркость до 1500 люмен — уровень «взрослых» фонарей&lt;br&gt;📏 Дальность луча — до 80 метров&lt;br&gt;🎛 6 режимов: максимальный / средний / эконом / стробоскоп / аварийный / красно-синяя вспышка&lt;br&gt;🚨 Красно-синяя вспышка — обозначить себя на трассе при поломке&lt;br&gt;🧲 Магнит + клипса — работа без рук, крепление на карман и кепку&lt;br&gt;🔋 Аккумулятор 14500 в комплекте — до 10 часов работы&lt;br&gt;🔌 Зарядка USB Type-C&lt;br&gt;🦾 Прочный алюминиевый корпус&lt;br&gt;💧 Влагозащита IPX4 — дождь не страшен&lt;br&gt;&lt;br&gt;✔️ Идеально для: EDC (каждый день в кармане), машины, рыбалки, походов, охоты, работы и дома&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь + аккумулятор 14500 + кабель Type-C + инструкция + коробка (готовый подарок 🎁)&lt;br&gt;&lt;br&gt;🎁 Подарок мужчине, которым пользуются каждый день, а не раз в год&lt;br&gt;&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ Новый, каждый проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 Авито Доставка по всей России + СДЭК / Почта / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">🔦 Yemao — фонарь меньше ладони, который светит за большой. 1500 люмен из кармана джинсов&lt;br&gt;✅ Только оригинал Yemao — копии светят тускло и умирают через месяц.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — сравнение размера и яркости впечатляет!&lt;br&gt;&lt;br&gt;Знакомая история: мощный фонарь есть, но он дома — потому что таскать его тяжело. Этот исчезает в кармане джинсов и достаётся не раздумывая. А когда нажимаете кнопку — 1500 люмен, каких ждёшь от фонаря втрое крупнее. Плюс магнит: прилепили под капотом или к батарее — и обе руки в деле. 💪&lt;br&gt;&lt;br&gt;⚡ Яркость до 1500 люмен — уровень «взрослых» фонарей&lt;br&gt;📏 Дальность луча — до 80 метров&lt;br&gt;🎛 6 режимов: максимальный / средний / эконом / стробоскоп / аварийный / красно-синяя вспышка&lt;br&gt;🚨 Красно-синяя вспышка — обозначить себя на трассе при поломке&lt;br&gt;🧲 Магнит + клипса — работа без рук, крепление на карман и кепку&lt;br&gt;🔋 Аккумулятор 14500 в комплекте — до 10 часов работы&lt;br&gt;🔌 Зарядка USB Type-C&lt;br&gt;🦾 Прочный алюминиевый корпус&lt;br&gt;💧 Влагозащита IPX4 — дождь не страшен&lt;br&gt;&lt;br&gt;✔️ Идеально для: EDC (каждый день в кармане), машины, рыбалки, походов, охоты, работы и дома&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь + аккумулятор 14500 + кабель Type-C + инструкция + коробка (готовый подарок 🎁)&lt;br&gt;&lt;br&gt;🎁 Подарок мужчине, которым пользуются каждый день, а не раз в год&lt;br&gt;&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ Новый, каждый проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 Авито Доставка по всей России + СДЭК / Почта / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>🔦 Фонарик аккумуляторный с зажигалкой YEMAO M21 — свет и огонь в одном корпусе. Цвет корпуса может отличаться! Есть разные цвета!&lt;br&gt;&lt;br&gt;EDC-фонарь размером с зажигалку, весит 36 грамм. Сверху светодиод XTE-55, снизу спиральная электроимпульсная зажигалка. Ни газа, ни бензина — заряжается через USB Type-C.&lt;br&gt;&lt;br&gt;🎥 Видео-обзор обязательно к просмотру — поджиг спиралью и все режимы света видно вживую.&lt;br&gt;💸 Скидка 10% при заказе от 2 любых товаров — применяется автоматически.&lt;br&gt;&lt;br&gt;🔥 Почему обычная зажигалка подводит именно тогда, когда нужна&lt;br&gt;&lt;br&gt;На ветру пламя сдувает, на морозе газ густеет и не даёт огня, а бензиновая выветривается за неделю в кармане. Всё это происходит ровно в тот момент, когда надо развести костёр или прикурить на берегу.&lt;br&gt;&lt;br&gt;Спираль M21 раскаляется докрасна — ей всё равно, дует ветер или нет. Пламени, которое можно задуть, здесь просто нет: это ветрозащитная USB-зажигалка без топлива. Заряда хватает примерно на 50 поджигов, а зарядить можно от повербанка.&lt;br&gt;&lt;br&gt;⚡ Характеристики&lt;br&gt;&lt;br&gt;✔️ Светодиод XTE-55 — до 300 люмен, два уровня яркости и стробоскоп&lt;br&gt;✔️ Боковая RGB-панель: белый свет, красный, мигание красный/синий, разноцветная подсветка&lt;br&gt;✔️ Электроимпульсная зажигалка — около 50 поджигов на одном заряде&lt;br&gt;✔️ Работа от 120 до 390 минут в зависимости от режима&lt;br&gt;✔️ Магнит — крепится к металлу, руки свободны&lt;br&gt;✔️ Стальная клипса — карман, кепка, рюкзак, ремень, ключи&lt;br&gt;✔️ Размер 8 × 2,2 см, вес 36 г — не чувствуется в кармане&lt;br&gt;✔️ Корпус ABS + нержавеющая сталь, защита IP54, падение с 1 метра&lt;br&gt;✔️ Встроенный аккумулятор, зарядка USB Type-C&lt;br&gt;&lt;br&gt;🎛 Три источника в одном&lt;br&gt;&lt;br&gt;Переключатель сбоку выбирает, чем пользуетесь: основной луч, боковая RGB-панель или зажигалка. Одна вещь вместо фонарика, зажигалки и сигнальной подсветки.&lt;br&gt;&lt;br&gt;🎯 Где пригодится&lt;br&gt;&lt;br&gt;🏕 Поход и костёр — поджиг на ветру, свет в палатке&lt;br&gt;🎣 Рыбалка — красный свет не сбивает ночное зрение&lt;br&gt;🚗 Автомобиль — примагнитил к капоту, обе руки свободны&lt;br&gt;🔧 Гараж и ремонт — подсветка там, куда не дотянуть лампой&lt;br&gt;🎒 EDC на каждый день — висит на рюкзаке или на ключах как брелок-фонарик&lt;br&gt;🏠 Дом и дача — газовая плита, свечи, мангал&lt;br&gt;&lt;br&gt;🎁 Подарок мужчине, который не ляжет в ящик&lt;br&gt;&lt;br&gt;Курящему, туристу, рыбаку, автомобилисту — вещь, которой пользуются каждый день, а не хранят в коробке.&lt;br&gt;&lt;br&gt;📦 В комплекте&lt;br&gt;&lt;br&gt;Фонарик YEMAO M21&lt;br&gt;Кабель USB Type-C&lt;br&gt;Инструкция на русском&lt;br&gt;Подарочная коробка&lt;br&gt;&lt;br&gt;🔥 Фонарь • зажигалка • RGB • магнит • клипса • Type-C • 36 г&lt;br&gt;&lt;br&gt;⚠️ Спираль во время работы нагревается — это нормально. Детям не давать.&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ Каждый фонарик проверяю перед отправкой&lt;br&gt;📦 В наличии&lt;br&gt;🚚 Отправка в день заказа, доставка по всей России&lt;br&gt;&lt;br&gt;⚡ Нажимайте «Купить с доставкой» — отправлю в день заказа, количество по такой цене ограничено!&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">🔦 Фонарик аккумуляторный с зажигалкой YEMAO M21 — свет и огонь в одном корпусе. Цвет корпуса может отличаться! Есть разные цвета!&lt;br&gt;&lt;br&gt;EDC-фонарь размером с зажигалку, весит 36 грамм. Сверху светодиод XTE-55, снизу спиральная электроимпульсная зажигалка. Ни газа, ни бензина — заряжается через USB Type-C.&lt;br&gt;&lt;br&gt;🎥 Видео-обзор обязательно к просмотру — поджиг спиралью и все режимы света видно вживую.&lt;br&gt;💸 Скидка 10% при заказе от 2 любых товаров — применяется автоматически.&lt;br&gt;&lt;br&gt;🔥 Почему обычная зажигалка подводит именно тогда, когда нужна&lt;br&gt;&lt;br&gt;На ветру пламя сдувает, на морозе газ густеет и не даёт огня, а бензиновая выветривается за неделю в кармане. Всё это происходит ровно в тот момент, когда надо развести костёр или прикурить на берегу.&lt;br&gt;&lt;br&gt;Спираль M21 раскаляется докрасна — ей всё равно, дует ветер или нет. Пламени, которое можно задуть, здесь просто нет: это ветрозащитная USB-зажигалка без топлива. Заряда хватает примерно на 50 поджигов, а зарядить можно от повербанка.&lt;br&gt;&lt;br&gt;⚡ Характеристики&lt;br&gt;&lt;br&gt;✔️ Светодиод XTE-55 — до 300 люмен, два уровня яркости и стробоскоп&lt;br&gt;✔️ Боковая RGB-панель: белый свет, красный, мигание красный/синий, разноцветная подсветка&lt;br&gt;✔️ Электроимпульсная зажигалка — около 50 поджигов на одном заряде&lt;br&gt;✔️ Работа от 120 до 390 минут в зависимости от режима&lt;br&gt;✔️ Магнит — крепится к металлу, руки свободны&lt;br&gt;✔️ Стальная клипса — карман, кепка, рюкзак, ремень, ключи&lt;br&gt;✔️ Размер 8 × 2,2 см, вес 36 г — не чувствуется в кармане&lt;br&gt;✔️ Корпус ABS + нержавеющая сталь, защита IP54, падение с 1 метра&lt;br&gt;✔️ Встроенный аккумулятор, зарядка USB Type-C&lt;br&gt;&lt;br&gt;🎛 Три источника в одном&lt;br&gt;&lt;br&gt;Переключатель сбоку выбирает, чем пользуетесь: основной луч, боковая RGB-панель или зажигалка. Одна вещь вместо фонарика, зажигалки и сигнальной подсветки.&lt;br&gt;&lt;br&gt;🎯 Где пригодится&lt;br&gt;&lt;br&gt;🏕 Поход и костёр — поджиг на ветру, свет в палатке&lt;br&gt;🎣 Рыбалка — красный свет не сбивает ночное зрение&lt;br&gt;🚗 Автомобиль — примагнитил к капоту, обе руки свободны&lt;br&gt;🔧 Гараж и ремонт — подсветка там, куда не дотянуть лампой&lt;br&gt;🎒 EDC на каждый день — висит на рюкзаке или на ключах как брелок-фонарик&lt;br&gt;🏠 Дом и дача — газовая плита, свечи, мангал&lt;br&gt;&lt;br&gt;🎁 Подарок мужчине, который не ляжет в ящик&lt;br&gt;&lt;br&gt;Курящему, туристу, рыбаку, автомобилисту — вещь, которой пользуются каждый день, а не хранят в коробке.&lt;br&gt;&lt;br&gt;📦 В комплекте&lt;br&gt;&lt;br&gt;Фонарик YEMAO M21&lt;br&gt;Кабель USB Type-C&lt;br&gt;Инструкция на русском&lt;br&gt;Подарочная коробка&lt;br&gt;&lt;br&gt;🔥 Фонарь • зажигалка • RGB • магнит • клипса • Type-C • 36 г&lt;br&gt;&lt;br&gt;⚠️ Спираль во время работы нагревается — это нормально. Детям не давать.&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ Каждый фонарик проверяю перед отправкой&lt;br&gt;📦 В наличии&lt;br&gt;🚚 Отправка в день заказа, доставка по всей России&lt;br&gt;&lt;br&gt;⚡ Нажимайте «Купить с доставкой» — отправлю в день заказа, количество по такой цене ограничено!&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -70092,7 +70092,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>💨 Воздуходувка мощнее урагана. Поток 53 м/с — ураган по шкале Бофорта начинается с 33&lt;br&gt;✅ Новинка для России, 2026 год. Аналогов на Авито нет.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — смотрите, что творит этот малыш!&lt;br&gt;&lt;br&gt;Пыль в клавиатуре, песок в багажнике, шерсть под сиденьями, листья на крыльце, снег на машине — всему этому осталось жить до первого нажатия кнопки. Бесщёточный турбо-мотор разгоняет воздух до 53 метров в секунду: это официально сильнее урагана. А режим пылесоса добирает то, что нельзя просто сдуть. 🌪&lt;br&gt;❗️(Бывает версия без фонарика! К ней кладем налобный фонарик в подарок! Воздуходувка та же!)&lt;br&gt;&lt;br&gt;⚡ Бесщёточный турбо-мотор — мощь и долгий ресурс&lt;br&gt;💨 Поток до 53 м/с — сдувает пыль, песок, шерсть, листья, снег&lt;br&gt;🧹 2 в 1: воздуходувка + вакуумный режим — для салона авто, ПК и труднодоступных мест&lt;br&gt;🎚 Плавная регулировка — от лёгкого бриза до полного урагана&lt;br&gt;🔋 Аккумулятор 4000 мАч — до 2,5 часов работы без розетки&lt;br&gt;💡 LED-подсветка + сигнальная лампа — работайте даже в темноте&lt;br&gt;📏 Компактная — лежит в бардачке, заменяет компрессор, пылесос и щётку&lt;br&gt;&lt;br&gt;✔️ Идеально для: продувки ПК и электроники, уборки салона авто, гаража, дачи, сдувания листьев и снега, шерсти домашних животных&lt;br&gt;&lt;br&gt;🆚 Мощнее большинства моделей Stihl, Bosch, Makita, Greenworks, DeWALT, Ryobi, Champion, Worx, Bort — за заметно меньшие деньги&lt;br&gt;&lt;br&gt;🎁 Подарок мужчине, который «сдует» все остальные: автомобилисту, дачнику, айтишнику, любителю техники&lt;br&gt;&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически&lt;br&gt;&lt;br&gt;🏆 РЕАЛЬНАЯ гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс (нужна только Почта — напишите, договоримся!)&lt;br&gt;&lt;br&gt;🔦 Загляните в профиль — там ещё много мощных гаджетов по лучшим ценам!&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">💨 Воздуходувка мощнее урагана. Поток 53 м/с — ураган по шкале Бофорта начинается с 33&lt;br&gt;✅ Новинка для России, 2026 год. Аналогов на Авито нет.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — смотрите, что творит этот малыш!&lt;br&gt;&lt;br&gt;Пыль в клавиатуре, песок в багажнике, шерсть под сиденьями, листья на крыльце, снег на машине — всему этому осталось жить до первого нажатия кнопки. Бесщёточный турбо-мотор разгоняет воздух до 53 метров в секунду: это официально сильнее урагана. А режим пылесоса добирает то, что нельзя просто сдуть. 🌪&lt;br&gt;❗️(Бывает версия без фонарика! К ней кладем налобный фонарик в подарок! Воздуходувка та же!)&lt;br&gt;&lt;br&gt;⚡ Бесщёточный турбо-мотор — мощь и долгий ресурс&lt;br&gt;💨 Поток до 53 м/с — сдувает пыль, песок, шерсть, листья, снег&lt;br&gt;🧹 2 в 1: воздуходувка + вакуумный режим — для салона авто, ПК и труднодоступных мест&lt;br&gt;🎚 Плавная регулировка — от лёгкого бриза до полного урагана&lt;br&gt;🔋 Аккумулятор 4000 мАч — до 2,5 часов работы без розетки&lt;br&gt;💡 LED-подсветка + сигнальная лампа — работайте даже в темноте&lt;br&gt;📏 Компактная — лежит в бардачке, заменяет компрессор, пылесос и щётку&lt;br&gt;&lt;br&gt;✔️ Идеально для: продувки ПК и электроники, уборки салона авто, гаража, дачи, сдувания листьев и снега, шерсти домашних животных&lt;br&gt;&lt;br&gt;🆚 Мощнее большинства моделей Stihl, Bosch, Makita, Greenworks, DeWALT, Ryobi, Champion, Worx, Bort — за заметно меньшие деньги&lt;br&gt;&lt;br&gt;🎁 Подарок мужчине, который «сдует» все остальные: автомобилисту, дачнику, айтишнику, любителю техники&lt;br&gt;&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически&lt;br&gt;&lt;br&gt;🏆 РЕАЛЬНАЯ гарантия 1 год&lt;br&gt;⭐️ Безупречный рейтинг продавца&lt;br&gt;✅ В наличии, проверяю перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс (нужна только Почта — напишите, договоримся!)&lt;br&gt;&lt;br&gt;🔦 Загляните в профиль — там ещё много мощных гаджетов по лучшим ценам!&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -70917,7 +70917,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>💡 «Маяк» PM60-TG — налобный прожектор, светящий на 3 километра. 10 000 люмен на лбу, руки свободны&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Самый мощный налобник, который вы найдёте на Авито.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — реальная яркость, без фильтров и монтажа!&lt;br&gt;&lt;br&gt;Название «Маяк» — не для красоты. Включаете максимум — и лес, поле или стройплощадка освещены до горизонта, а соседи по берегу думают, что приехала машина с прожектором. При этом обе руки свободны: снасти, инструмент, руль. Один заряд — до 15 часов работы. 💪&lt;br&gt;&lt;br&gt;⚡ Диод PM60-TG «белый лазер» + LED — до 10 000 люмен&lt;br&gt;📏 Луч — до 3000 метров&lt;br&gt;🎛 3 режима: максимальный / экономичный / SOS&lt;br&gt;🔴 Задний красный фонарь — вас видно на трассе и в колонне, безопасность в темноте&lt;br&gt;🔋 3 аккумулятора 18650 в комплекте — до 15 часов от заряда&lt;br&gt;⚡️ Функция Power Bank — подзарядит телефон в походе&lt;br&gt;📊 Индикатор заряда — без сюрпризов&lt;br&gt;💧 Влагозащита IPX6 — дождь, снег, грязь&lt;br&gt;🦾 Ударопрочный корпус, надёжное крепление на голову&lt;br&gt;✔️ Идеально для: рыбалки и охоты, стройки и ремонта, походов, гаража, авто и дачи, работы в темноте&lt;br&gt;📦 В комплекте: фонарь «Маяк» PM60-TG + крепление на голову + 3 аккумулятора 18650 + кабель USB + упаковка&lt;br&gt;🎁 Подарок, которым реально пользуются, а не ставят на полку&lt;br&gt;💸 От 2 штук — скидка 10% автоматически&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю каждый перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">💡 «Маяк» PM60-TG — налобный прожектор, светящий на 3 километра. 10 000 люмен на лбу, руки свободны&lt;br&gt;&lt;br&gt;✅ Новинка 2026 года. Самый мощный налобник, который вы найдёте на Авито.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — реальная яркость, без фильтров и монтажа!&lt;br&gt;&lt;br&gt;Название «Маяк» — не для красоты. Включаете максимум — и лес, поле или стройплощадка освещены до горизонта, а соседи по берегу думают, что приехала машина с прожектором. При этом обе руки свободны: снасти, инструмент, руль. Один заряд — до 15 часов работы. 💪&lt;br&gt;&lt;br&gt;⚡ Диод PM60-TG «белый лазер» + LED — до 10 000 люмен&lt;br&gt;📏 Луч — до 3000 метров&lt;br&gt;🎛 3 режима: максимальный / экономичный / SOS&lt;br&gt;🔴 Задний красный фонарь — вас видно на трассе и в колонне, безопасность в темноте&lt;br&gt;🔋 3 аккумулятора 18650 в комплекте — до 15 часов от заряда&lt;br&gt;⚡️ Функция Power Bank — подзарядит телефон в походе&lt;br&gt;📊 Индикатор заряда — без сюрпризов&lt;br&gt;💧 Влагозащита IPX6 — дождь, снег, грязь&lt;br&gt;🦾 Ударопрочный корпус, надёжное крепление на голову&lt;br&gt;✔️ Идеально для: рыбалки и охоты, стройки и ремонта, походов, гаража, авто и дачи, работы в темноте&lt;br&gt;📦 В комплекте: фонарь «Маяк» PM60-TG + крепление на голову + 3 аккумулятора 18650 + кабель USB + упаковка&lt;br&gt;🎁 Подарок, которым реально пользуются, а не ставят на полку&lt;br&gt;💸 От 2 штук — скидка 10% автоматически&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю каждый перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс / 5Post&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -71625,7 +71625,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>🔭 «Титан» — бинокль, в который видно кратеры Луны. Честный рабочий зум 20х и объективы 60 мм&lt;br&gt;✅ Новый, в заводской упаковке. В наличии — отправка сегодня.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — показываю РЕАЛЬНОЕ приближение, без накрученных кратностей!&lt;br&gt;&lt;br&gt;Наведите его вечером на Луну — и увидите кратеры. Днём — лодку на другом берегу, зверя на опушке за километры, детали зданий через весь город. Огромные 60-мм объективы собирают столько света, что картинка остаётся яркой даже в сумерках и на рассвете — в самое ценное время для охотника и рыбака. 🌙&lt;br&gt;&lt;br&gt;❗ ЧЕСТНО О ГЛАВНОМ&lt;br&gt;Рынок завален биноклями «1000x zoom» с чужими фото: мутная дрожащая картинка и бесполезное увеличение. Внешне — похожи. Внутри — пропасть. «Титан» — это настоящая оптическая схема Porro с призмами BaK4: честные рабочие 20 крат, при которых ДЕЙСТВИТЕЛЬНО видно, а не «мыло».&lt;br&gt;&lt;br&gt;⚙️ ХАРАКТЕРИСТИКИ:&lt;br&gt;🔍 Увеличение — до 20х (реальное рабочее), регулируемый зум&lt;br&gt;🔭 Диаметр объективов — 60 мм: максимум света и деталей&lt;br&gt;💎 Призмы BaK4 + просветлённые линзы — чёткость без искажений по краям&lt;br&gt;📏 Дальность наблюдения — до 5 км&lt;br&gt;🌅 Высокая светосила — работает в сумерках и на рассвете&lt;br&gt;🌐 Широкий угол обзора — легко вести движущийся объект&lt;br&gt;🦾 Надёжная конструкция, цвет чёрный, размер 235х205мм, вес 970гр.&lt;br&gt;&lt;br&gt;Модель: 20–180x100, система Porro&lt;br&gt;&lt;br&gt;✔️ Идеально для: охоты и рыбалки, туризма, наблюдения за природой и Луной, стадионов и концертов, города и архитектуры&lt;br&gt;&lt;br&gt;📦 В комплекте: бинокль «Титан» + заводская упаковка&lt;br&gt;&lt;br&gt;🎁 Солидный подарок мужчине или подростку — от такого не отказываются&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;⭐ Довольные покупатели уже в отзывах&lt;br&gt;✅ В наличии, проверяю оптику перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 Авито Доставка по РФ · Москва и МО — возможна встреча 🤝&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">🔭 «Титан» — бинокль, в который видно кратеры Луны. Честный рабочий зум 20х и объективы 60 мм&lt;br&gt;✅ Новый, в заводской упаковке. В наличии — отправка сегодня.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — показываю РЕАЛЬНОЕ приближение, без накрученных кратностей!&lt;br&gt;&lt;br&gt;Наведите его вечером на Луну — и увидите кратеры. Днём — лодку на другом берегу, зверя на опушке за километры, детали зданий через весь город. Огромные 60-мм объективы собирают столько света, что картинка остаётся яркой даже в сумерках и на рассвете — в самое ценное время для охотника и рыбака. 🌙&lt;br&gt;&lt;br&gt;❗ ЧЕСТНО О ГЛАВНОМ&lt;br&gt;Рынок завален биноклями «1000x zoom» с чужими фото: мутная дрожащая картинка и бесполезное увеличение. Внешне — похожи. Внутри — пропасть. «Титан» — это настоящая оптическая схема Porro с призмами BaK4: честные рабочие 20 крат, при которых ДЕЙСТВИТЕЛЬНО видно, а не «мыло».&lt;br&gt;&lt;br&gt;⚙️ ХАРАКТЕРИСТИКИ:&lt;br&gt;🔍 Увеличение — до 20х (реальное рабочее), регулируемый зум&lt;br&gt;🔭 Диаметр объективов — 60 мм: максимум света и деталей&lt;br&gt;💎 Призмы BaK4 + просветлённые линзы — чёткость без искажений по краям&lt;br&gt;📏 Дальность наблюдения — до 5 км&lt;br&gt;🌅 Высокая светосила — работает в сумерках и на рассвете&lt;br&gt;🌐 Широкий угол обзора — легко вести движущийся объект&lt;br&gt;🦾 Надёжная конструкция, цвет чёрный, размер 235х205мм, вес 970гр.&lt;br&gt;&lt;br&gt;Модель: 20–180x100, система Porro&lt;br&gt;&lt;br&gt;✔️ Идеально для: охоты и рыбалки, туризма, наблюдения за природой и Луной, стадионов и концертов, города и архитектуры&lt;br&gt;&lt;br&gt;📦 В комплекте: бинокль «Титан» + заводская упаковка&lt;br&gt;&lt;br&gt;🎁 Солидный подарок мужчине или подростку — от такого не отказываются&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;⭐ Довольные покупатели уже в отзывах&lt;br&gt;✅ В наличии, проверяю оптику перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 Авито Доставка по РФ · Москва и МО — возможна встреча 🤝&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -71747,7 +71747,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>🔭 Бинокль Comet AW-26 20х50 с автофокусом — резкость крутить не нужно&lt;br&gt;&lt;br&gt;Мощный 20-кратный бинокль с объективами 50 мм для охоты, рыбалки и туризма. Поднёс к глазам — и сразу видишь картинку, без возни с колёсиками.&lt;br&gt;&lt;br&gt;🎥 Видео-обзор стоит посмотреть: снято, как он приближает реальные объекты.&lt;br&gt;💸 Скидка 10% при заказе от 2 любых товаров — применяется автоматически.&lt;br&gt;&lt;br&gt;😤 Знакомая история с обычным биноклем&lt;br&gt;&lt;br&gt;Заметили что-то вдалеке, схватили бинокль — а там мутное пятно. Крутите одно колесо, второе, подстраиваете под каждый глаз. Пока навелись — птица улетела, зверь ушёл, момент на поле пропущен.&lt;br&gt;&lt;br&gt;🔍 У Comet AW-26 система автофокуса: наводите на объект и сразу видите его резко. Не нужно настраивать ничего каждый раз — это и отличает его от обычных охотничьих биноклей в той же цене.&lt;br&gt;&lt;br&gt;⚡ Характеристики&lt;br&gt;&lt;br&gt;✔️ Кратность 20х — бинокль дальнего видения, далёкие объекты видно в деталях&lt;br&gt;✔️ Объективы 50 мм — светосильные, работают и днём, и в сумерках&lt;br&gt;✔️ Автофокус — резкость подстраивать не нужно&lt;br&gt;✔️ Поле зрения 168 футов на 1000 ярдов — широкий обзор, удобно вести объект&lt;br&gt;✔️ Просветлённая оптика (coated optics) — меньше бликов, честные цвета&lt;br&gt;✔️ Регулировка расстояния между окулярами — под ваши глаза&lt;br&gt;✔️ Обрезиненный ударопрочный корпус — не скользит в руке&lt;br&gt;✔️ Пылевлагозащита — не боится сырости на природе&lt;br&gt;✔️ Складная конструкция, чехол в комплекте&lt;br&gt;&lt;br&gt;🎯 Где пригодится&lt;br&gt;&lt;br&gt;🌲 Охотничий бинокль — рассмотреть зверя раньше, чем он заметит вас&lt;br&gt;🎣 Рыбалка — читать воду и следить за противоположным берегом&lt;br&gt;🏔 Туризм, походы и альпинизм — панорамы, вершины, дальний берег&lt;br&gt;🏟 Стадион и концерт — видно лица, а не силуэты&lt;br&gt;🦅 Наблюдение за птицами и природой&lt;br&gt;🏡 Дача — посмотреть, что происходит за участком&lt;br&gt;🌌 Луна и звёзды — на 20 кратах видно кратеры&lt;br&gt;&lt;br&gt;🎁 Подарок мужчине, который точно пригодится&lt;br&gt;&lt;br&gt;Охотнику, рыбаку, туристу, отцу или деду — бинокль достают из чехла, а не убирают в шкаф.&lt;br&gt;&lt;br&gt;📦 В комплекте&lt;br&gt;&lt;br&gt;Бинокль Comet AW-26 20х50&lt;br&gt;Чехол&lt;br&gt;Ремешок на шею&lt;br&gt;Крышка окуляров и 2 крышки объективов&lt;br&gt;Салфетка для чистки линз&lt;br&gt;Инструкция и упаковка&lt;br&gt;&lt;br&gt;🔥 20 крат • объектив 50 мм • автофокус • просветлённая оптика • обрезиненный корпус • чехол&lt;br&gt;&lt;br&gt;Мощность профессионального бинокля без сложной настройки — поднял и смотришь.&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ Каждый бинокль проверяю перед отправкой&lt;br&gt;📦 В наличии&lt;br&gt;🚚 Отправка в день заказа, доставка по всей России&lt;br&gt;&lt;br&gt;⚠️ Не смотреть через бинокль на солнце — можно повредить зрение.&lt;br&gt;&lt;br&gt;⚡ Нажимайте «Купить с доставкой» — отправлю в день заказа, количество по этой цене ограничено!&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">🔭 Бинокль Comet AW-26 20х50 с автофокусом — резкость крутить не нужно&lt;br&gt;&lt;br&gt;Мощный 20-кратный бинокль с объективами 50 мм для охоты, рыбалки и туризма. Поднёс к глазам — и сразу видишь картинку, без возни с колёсиками.&lt;br&gt;&lt;br&gt;🎥 Видео-обзор стоит посмотреть: снято, как он приближает реальные объекты.&lt;br&gt;💸 Скидка 10% при заказе от 2 любых товаров — применяется автоматически.&lt;br&gt;&lt;br&gt;😤 Знакомая история с обычным биноклем&lt;br&gt;&lt;br&gt;Заметили что-то вдалеке, схватили бинокль — а там мутное пятно. Крутите одно колесо, второе, подстраиваете под каждый глаз. Пока навелись — птица улетела, зверь ушёл, момент на поле пропущен.&lt;br&gt;&lt;br&gt;🔍 У Comet AW-26 система автофокуса: наводите на объект и сразу видите его резко. Не нужно настраивать ничего каждый раз — это и отличает его от обычных охотничьих биноклей в той же цене.&lt;br&gt;&lt;br&gt;⚡ Характеристики&lt;br&gt;&lt;br&gt;✔️ Кратность 20х — бинокль дальнего видения, далёкие объекты видно в деталях&lt;br&gt;✔️ Объективы 50 мм — светосильные, работают и днём, и в сумерках&lt;br&gt;✔️ Автофокус — резкость подстраивать не нужно&lt;br&gt;✔️ Поле зрения 168 футов на 1000 ярдов — широкий обзор, удобно вести объект&lt;br&gt;✔️ Просветлённая оптика (coated optics) — меньше бликов, честные цвета&lt;br&gt;✔️ Регулировка расстояния между окулярами — под ваши глаза&lt;br&gt;✔️ Обрезиненный ударопрочный корпус — не скользит в руке&lt;br&gt;✔️ Пылевлагозащита — не боится сырости на природе&lt;br&gt;✔️ Складная конструкция, чехол в комплекте&lt;br&gt;&lt;br&gt;🎯 Где пригодится&lt;br&gt;&lt;br&gt;🌲 Охотничий бинокль — рассмотреть зверя раньше, чем он заметит вас&lt;br&gt;🎣 Рыбалка — читать воду и следить за противоположным берегом&lt;br&gt;🏔 Туризм, походы и альпинизм — панорамы, вершины, дальний берег&lt;br&gt;🏟 Стадион и концерт — видно лица, а не силуэты&lt;br&gt;🦅 Наблюдение за птицами и природой&lt;br&gt;🏡 Дача — посмотреть, что происходит за участком&lt;br&gt;🌌 Луна и звёзды — на 20 кратах видно кратеры&lt;br&gt;&lt;br&gt;🎁 Подарок мужчине, который точно пригодится&lt;br&gt;&lt;br&gt;Охотнику, рыбаку, туристу, отцу или деду — бинокль достают из чехла, а не убирают в шкаф.&lt;br&gt;&lt;br&gt;📦 В комплекте&lt;br&gt;&lt;br&gt;Бинокль Comet AW-26 20х50&lt;br&gt;Чехол&lt;br&gt;Ремешок на шею&lt;br&gt;Крышка окуляров и 2 крышки объективов&lt;br&gt;Салфетка для чистки линз&lt;br&gt;Инструкция и упаковка&lt;br&gt;&lt;br&gt;🔥 20 крат • объектив 50 мм • автофокус • просветлённая оптика • обрезиненный корпус • чехол&lt;br&gt;&lt;br&gt;Мощность профессионального бинокля без сложной настройки — поднял и смотришь.&lt;br&gt;&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ Каждый бинокль проверяю перед отправкой&lt;br&gt;📦 В наличии&lt;br&gt;🚚 Отправка в день заказа, доставка по всей России&lt;br&gt;&lt;br&gt;⚠️ Не смотреть через бинокль на солнце — можно повредить зрение.&lt;br&gt;&lt;br&gt;⚡ Нажимайте «Купить с доставкой» — отправлю в день заказа, количество по этой цене ограничено!&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -71869,7 +71869,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>🦅 «Орёл» 80×80 — бинокль с дальномерной сеткой и честным увеличением 30х. Крупные объекты видны за 15 км&lt;br&gt;✅ Прямые поставки — без наценок и посредников.&lt;br&gt;🔥 Напишите — пришлю видео реальной картинки через окуляры!&lt;br&gt;&lt;br&gt;Огромные 80-мм линзы — главный козырь «Орла»: они собирают максимум света, поэтому картинка остаётся яркой в сумерках и на рассвете, когда зверь выходит кормиться, а обычные бинокли уже «слепнут». Детально рассматривайте объекты до 1,5 км, крупные — корабли, вышки, склоны — за 15 км. А дальномерная сетка на правом окуляре позволяет прикинуть дистанцию до цели — фишка, за которую этот бинокль любят охотники. 🎯&lt;br&gt;&lt;br&gt;🔍 Увеличение 30х — честное рабочее, без «накрученных» цифр&lt;br&gt;🔭 Объективы 80 мм — максимум света, уверенная работа в сумерках&lt;br&gt;📐 Дальномерная сетка на правом окуляре — оценка расстояния до объекта&lt;br&gt;💎 Призмы Porro + стекло BaK-4 — чистое светлое изображение&lt;br&gt;🌈 Многослойное просветление FMC — яркие натуральные цвета&lt;br&gt;👓 Регулировка фокуса и диоптрий ±3 — настройка под ваше зрение, работает и в очках&lt;br&gt;💧 Влагозащищённый ударопрочный корпус, защита от запотевания — дождь, снег, бездорожье&lt;br&gt;🇩🇪 Оптика немецкого уровня качества&lt;br&gt;&lt;br&gt;✔️ Идеально для: охоты и рыбалки, туризма, наблюдения за природой, стадионов, работы на местности&lt;br&gt;&lt;br&gt;📦 В комплекте: бинокль «Орёл» 80×80 + чехол + ремешок&lt;br&gt;&lt;br&gt;🎁 Солидный подарок мужчине — на 23 февраля, юбилей, день рождения, профессиональный праздник&lt;br&gt;&lt;br&gt;💸 От 2 штук — скидка 10% автоматически в корзине&lt;br&gt;&lt;br&gt;🏆 Гарантия качества · Официальная сертификация&lt;br&gt;✅ В наличии, проверяю оптику перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 Авито Доставка по РФ / самовывоз&lt;br&gt;&lt;br&gt;🔦 Загляните в профиль — там ещё много оптики и мощных фонарей по лучшим ценам!&lt;br&gt;☎️ Есть вопросы? Пишите — проконсультирую.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">🦅 «Орёл» 80×80 — бинокль с дальномерной сеткой и честным увеличением 30х. Крупные объекты видны за 15 км&lt;br&gt;✅ Прямые поставки — без наценок и посредников.&lt;br&gt;🔥 Напишите — пришлю видео реальной картинки через окуляры!&lt;br&gt;&lt;br&gt;Огромные 80-мм линзы — главный козырь «Орла»: они собирают максимум света, поэтому картинка остаётся яркой в сумерках и на рассвете, когда зверь выходит кормиться, а обычные бинокли уже «слепнут». Детально рассматривайте объекты до 1,5 км, крупные — корабли, вышки, склоны — за 15 км. А дальномерная сетка на правом окуляре позволяет прикинуть дистанцию до цели — фишка, за которую этот бинокль любят охотники. 🎯&lt;br&gt;&lt;br&gt;🔍 Увеличение 30х — честное рабочее, без «накрученных» цифр&lt;br&gt;🔭 Объективы 80 мм — максимум света, уверенная работа в сумерках&lt;br&gt;📐 Дальномерная сетка на правом окуляре — оценка расстояния до объекта&lt;br&gt;💎 Призмы Porro + стекло BaK-4 — чистое светлое изображение&lt;br&gt;🌈 Многослойное просветление FMC — яркие натуральные цвета&lt;br&gt;👓 Регулировка фокуса и диоптрий ±3 — настройка под ваше зрение, работает и в очках&lt;br&gt;💧 Влагозащищённый ударопрочный корпус, защита от запотевания — дождь, снег, бездорожье&lt;br&gt;🇩🇪 Оптика немецкого уровня качества&lt;br&gt;&lt;br&gt;✔️ Идеально для: охоты и рыбалки, туризма, наблюдения за природой, стадионов, работы на местности&lt;br&gt;&lt;br&gt;📦 В комплекте: бинокль «Орёл» 80×80 + чехол + ремешок&lt;br&gt;&lt;br&gt;🎁 Солидный подарок мужчине — на 23 февраля, юбилей, день рождения, профессиональный праздник&lt;br&gt;&lt;br&gt;💸 От 2 штук — скидка 10% автоматически в корзине&lt;br&gt;&lt;br&gt;🏆 Гарантия качества · Официальная сертификация&lt;br&gt;✅ В наличии, проверяю оптику перед отправкой&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 Авито Доставка по РФ / самовывоз&lt;br&gt;&lt;br&gt;🔦 Загляните в профиль — там ещё много оптики и мощных фонарей по лучшим ценам!&lt;br&gt;☎️ Есть вопросы? Пишите — проконсультирую.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -71991,7 +71991,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>🔭 «Агент» — бинокль-малыш, который видит за километр. Зум х15 в корпусе размером с ладонь&lt;br&gt;&lt;br&gt;✅ Аналогов на Авито нет. Осторожно: наши видео копируют и высылают дешёвые подделки.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — приближение показано вживую! (Цвет линз может отличаться)&lt;br&gt;&lt;br&gt;Большой бинокль вечно остаётся дома — тяжёлый, громоздкий, жалко таскать. «Агент» живёт в кармане куртки и достаётся за секунду: номер машины, птица на дереве, поплавок на том берегу — всё как на ладони. Приближает как серьёзная оптика, а весит как смартфон. 😎&lt;br&gt;&lt;br&gt;🔍 Увеличение х15 — детали видны на расстоянии до 1 км&lt;br&gt;📏 Размер с ладонь — карман куртки, бардачок, боковой карман рюкзака&lt;br&gt;🌇 Работает в сумерках — многослойное просветление линз даёт яркую картинку при слабом свете&lt;br&gt;💧 Линзы не запотевают&lt;br&gt;🦾 Корпус ABS + резина — переживёт падения, дождь и рюкзачную жизнь&lt;br&gt;&lt;br&gt;👀 КОМУ ЗАЙДЁТ:&lt;br&gt;🎣 Рыбакам и охотникам — заметите поклёвку и дичь раньше других&lt;br&gt;⚽ Болельщикам — билет на галёрку, обзор как с VIP-трибуны&lt;br&gt;🌍 Туристам — вся оптика в кармане вместо килограммового БПЦ на шее&lt;br&gt;🚢 На природе и в путешествиях — корабли, горы, архитектура в деталях&lt;br&gt;👦 Подросткам — безопасный и по-настоящему увлекательный, лучше очередной игрушки&lt;br&gt;📦 В комплекте: бинокль «Агент» + чехол + шнурок на руку/шею + салфетка для линз + инструкция&lt;br&gt;🎯 Это реальная оптика, а не сувенир: доступная альтернатива Veber, Levenhuk, Nikon, Bushnell и советских БПЦ.&lt;br&gt;&lt;br&gt;🎁 Готовый подарок мужчине или подростку — на 23 февраля, день рождения или просто так&lt;br&gt;&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю оптику перед отправкой&lt;br&gt;&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
+          <t xml:space="preserve">🔭 «Агент» — бинокль-малыш, который видит за километр. Зум х15 в корпусе размером с ладонь&lt;br&gt;&lt;br&gt;✅ Аналогов на Авито нет. Осторожно: наши видео копируют и высылают дешёвые подделки.&lt;br&gt;🔥 Видео-обзор ОБЯЗАТЕЛЕН к просмотру — приближение показано вживую! (Цвет линз может отличаться)&lt;br&gt;&lt;br&gt;Большой бинокль вечно остаётся дома — тяжёлый, громоздкий, жалко таскать. «Агент» живёт в кармане куртки и достаётся за секунду: номер машины, птица на дереве, поплавок на том берегу — всё как на ладони. Приближает как серьёзная оптика, а весит как смартфон. 😎&lt;br&gt;&lt;br&gt;🔍 Увеличение х15 — детали видны на расстоянии до 1 км&lt;br&gt;📏 Размер с ладонь — карман куртки, бардачок, боковой карман рюкзака&lt;br&gt;🌇 Работает в сумерках — многослойное просветление линз даёт яркую картинку при слабом свете&lt;br&gt;💧 Линзы не запотевают&lt;br&gt;🦾 Корпус ABS + резина — переживёт падения, дождь и рюкзачную жизнь&lt;br&gt;&lt;br&gt;👀 КОМУ ЗАЙДЁТ:&lt;br&gt;🎣 Рыбакам и охотникам — заметите поклёвку и дичь раньше других&lt;br&gt;⚽ Болельщикам — билет на галёрку, обзор как с VIP-трибуны&lt;br&gt;🌍 Туристам — вся оптика в кармане вместо килограммового БПЦ на шее&lt;br&gt;🚢 На природе и в путешествиях — корабли, горы, архитектура в деталях&lt;br&gt;👦 Подросткам — безопасный и по-настоящему увлекательный, лучше очередной игрушки&lt;br&gt;📦 В комплекте: бинокль «Агент» + чехол + шнурок на руку/шею + салфетка для линз + инструкция&lt;br&gt;🎯 Это реальная оптика, а не сувенир: доступная альтернатива Veber, Levenhuk, Nikon, Bushnell и советских БПЦ.&lt;br&gt;&lt;br&gt;🎁 Готовый подарок мужчине или подростку — на 23 февраля, день рождения или просто так&lt;br&gt;&lt;br&gt;💸 От 2 любых товаров — скидка 10% автоматически&lt;br&gt;🏆 Гарантия 1 год&lt;br&gt;✅ В наличии, проверяю оптику перед отправкой&lt;br&gt;&lt;br&gt;📦 Отправка в день заказа&lt;br&gt;🚚 СДЭК / Почта РФ / Авито Доставка / Яндекс&lt;br&gt;&lt;br&gt;☎️ Есть вопросы? Пишите — отвечаю сразу.&lt;br&gt;⭐️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Есть опт и дроп — пишите.&lt;br&gt;&lt;br&gt;🏢 Работаем с юрлицами и ИП, на опт — скидка. Отличный корпоративный подарок сотрудникам и партнёрам к Новому году, 23 Февраля и праздникам компании: полезная вещь, которой правда пользуются, а не убирают в ящик. Напишите, сколько штук нужно, — рассчитаем цену.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">

--- a/ilya_feed.xlsx
+++ b/ilya_feed.xlsx
@@ -4707,10 +4707,8 @@
           <t>Спорт и отдых</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>1150</t>
-        </is>
+      <c r="K16">
+        <v>1060</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>

--- a/ilya_feed.xlsx
+++ b/ilya_feed.xlsx
@@ -3255,10 +3255,8 @@
           <t>Спорт и отдых</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2678</t>
-        </is>
+      <c r="K5">
+        <v>2470</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -4969,10 +4967,8 @@
           <t>Спорт и отдых</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>1040</t>
-        </is>
+      <c r="K18">
+        <v>850</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -71885,10 +71881,8 @@
           <t>Фототехника</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2090</t>
-        </is>
+      <c r="L7">
+        <v>1740</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
